--- a/data/CS1/case33_1/case33_operational_data.xlsx
+++ b/data/CS1/case33_1/case33_operational_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/micaelsimoes/PycharmProjects/shared-resources-planning/data/CS1/case33_1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8508A09F-E4E8-6644-91DE-43AB79901C68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE8588B7-C3C6-3A43-AC51-8288806E596D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1000" yWindow="680" windowWidth="28400" windowHeight="18440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -454,12 +454,12 @@
         <v>1</v>
       </c>
       <c r="B2" s="1">
-        <f>E2*0.5</f>
-        <v>1.5</v>
+        <f>E2*0.3</f>
+        <v>0.89999999999999991</v>
       </c>
       <c r="C2" s="1">
-        <f>F2*0.5</f>
-        <v>0.89999999999999991</v>
+        <f>F2*0.3</f>
+        <v>0.53999999999999992</v>
       </c>
       <c r="D2" s="2">
         <v>2.6917900403768499E-2</v>
@@ -476,12 +476,12 @@
         <v>2</v>
       </c>
       <c r="B3" s="1">
-        <f t="shared" ref="B3:B33" si="0">E3*0.5</f>
-        <v>1.3499999999999999</v>
+        <f t="shared" ref="B3:B33" si="0">E3*0.3</f>
+        <v>0.80999999999999994</v>
       </c>
       <c r="C3" s="1">
-        <f t="shared" ref="C3:C33" si="1">F3*0.5</f>
-        <v>0.60000000000000009</v>
+        <f t="shared" ref="C3:C33" si="1">F3*0.3</f>
+        <v>0.36000000000000004</v>
       </c>
       <c r="D3" s="2">
         <v>2.4226110363391645E-2</v>
@@ -499,11 +499,11 @@
       </c>
       <c r="B4" s="1">
         <f t="shared" si="0"/>
-        <v>1.7999999999999998</v>
+        <v>1.0799999999999998</v>
       </c>
       <c r="C4" s="1">
         <f t="shared" si="1"/>
-        <v>1.2000000000000002</v>
+        <v>0.72000000000000008</v>
       </c>
       <c r="D4" s="2">
         <v>3.2301480484522194E-2</v>
@@ -521,11 +521,11 @@
       </c>
       <c r="B5" s="1">
         <f t="shared" si="0"/>
-        <v>0.89999999999999991</v>
+        <v>0.53999999999999992</v>
       </c>
       <c r="C5" s="1">
         <f t="shared" si="1"/>
-        <v>0.44999999999999996</v>
+        <v>0.26999999999999996</v>
       </c>
       <c r="D5" s="2">
         <v>1.6150740242261097E-2</v>
@@ -543,11 +543,11 @@
       </c>
       <c r="B6" s="1">
         <f t="shared" si="0"/>
-        <v>0.89999999999999991</v>
+        <v>0.53999999999999992</v>
       </c>
       <c r="C6" s="1">
         <f t="shared" si="1"/>
-        <v>0.30000000000000004</v>
+        <v>0.18000000000000002</v>
       </c>
       <c r="D6" s="2">
         <v>1.6150740242261097E-2</v>
@@ -565,11 +565,11 @@
       </c>
       <c r="B7" s="1">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>1.7999999999999998</v>
       </c>
       <c r="C7" s="1">
         <f t="shared" si="1"/>
-        <v>1.5</v>
+        <v>0.89999999999999991</v>
       </c>
       <c r="D7" s="2">
         <v>5.3835800807536999E-2</v>
@@ -587,11 +587,11 @@
       </c>
       <c r="B8" s="1">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>1.7999999999999998</v>
       </c>
       <c r="C8" s="1">
         <f t="shared" si="1"/>
-        <v>1.5</v>
+        <v>0.89999999999999991</v>
       </c>
       <c r="D8" s="2">
         <v>5.3835800807536999E-2</v>
@@ -609,11 +609,11 @@
       </c>
       <c r="B9" s="1">
         <f t="shared" si="0"/>
-        <v>0.89999999999999991</v>
+        <v>0.53999999999999992</v>
       </c>
       <c r="C9" s="1">
         <f t="shared" si="1"/>
-        <v>0.30000000000000004</v>
+        <v>0.18000000000000002</v>
       </c>
       <c r="D9" s="2">
         <v>1.6150740242261097E-2</v>
@@ -631,11 +631,11 @@
       </c>
       <c r="B10" s="1">
         <f t="shared" si="0"/>
-        <v>0.89999999999999991</v>
+        <v>0.53999999999999992</v>
       </c>
       <c r="C10" s="1">
         <f t="shared" si="1"/>
-        <v>0.30000000000000004</v>
+        <v>0.18000000000000002</v>
       </c>
       <c r="D10" s="2">
         <v>1.6150740242261097E-2</v>
@@ -653,11 +653,11 @@
       </c>
       <c r="B11" s="1">
         <f t="shared" si="0"/>
-        <v>0.67499999999999993</v>
+        <v>0.40499999999999997</v>
       </c>
       <c r="C11" s="1">
         <f t="shared" si="1"/>
-        <v>0.44999999999999996</v>
+        <v>0.26999999999999996</v>
       </c>
       <c r="D11" s="2">
         <v>1.2113055181695823E-2</v>
@@ -675,11 +675,11 @@
       </c>
       <c r="B12" s="1">
         <f t="shared" si="0"/>
-        <v>0.89999999999999991</v>
+        <v>0.53999999999999992</v>
       </c>
       <c r="C12" s="1">
         <f t="shared" si="1"/>
-        <v>0.52500000000000002</v>
+        <v>0.315</v>
       </c>
       <c r="D12" s="2">
         <v>1.6150740242261097E-2</v>
@@ -697,11 +697,11 @@
       </c>
       <c r="B13" s="1">
         <f t="shared" si="0"/>
-        <v>0.89999999999999991</v>
+        <v>0.53999999999999992</v>
       </c>
       <c r="C13" s="1">
         <f t="shared" si="1"/>
-        <v>0.52500000000000002</v>
+        <v>0.315</v>
       </c>
       <c r="D13" s="2">
         <v>1.6150740242261097E-2</v>
@@ -719,11 +719,11 @@
       </c>
       <c r="B14" s="1">
         <f t="shared" si="0"/>
-        <v>1.7999999999999998</v>
+        <v>1.0799999999999998</v>
       </c>
       <c r="C14" s="1">
         <f t="shared" si="1"/>
-        <v>1.2000000000000002</v>
+        <v>0.72000000000000008</v>
       </c>
       <c r="D14" s="2">
         <v>3.2301480484522194E-2</v>
@@ -741,11 +741,11 @@
       </c>
       <c r="B15" s="1">
         <f t="shared" si="0"/>
-        <v>0.89999999999999991</v>
+        <v>0.53999999999999992</v>
       </c>
       <c r="C15" s="1">
         <f t="shared" si="1"/>
-        <v>0.15000000000000002</v>
+        <v>9.0000000000000011E-2</v>
       </c>
       <c r="D15" s="2">
         <v>1.6150740242261097E-2</v>
@@ -763,11 +763,11 @@
       </c>
       <c r="B16" s="1">
         <f t="shared" si="0"/>
-        <v>0.89999999999999991</v>
+        <v>0.53999999999999992</v>
       </c>
       <c r="C16" s="1">
         <f t="shared" si="1"/>
-        <v>0.30000000000000004</v>
+        <v>0.18000000000000002</v>
       </c>
       <c r="D16" s="2">
         <v>1.6150740242261097E-2</v>
@@ -785,11 +785,11 @@
       </c>
       <c r="B17" s="1">
         <f t="shared" si="0"/>
-        <v>0.89999999999999991</v>
+        <v>0.53999999999999992</v>
       </c>
       <c r="C17" s="1">
         <f t="shared" si="1"/>
-        <v>0.30000000000000004</v>
+        <v>0.18000000000000002</v>
       </c>
       <c r="D17" s="2">
         <v>1.6150740242261097E-2</v>
@@ -807,11 +807,11 @@
       </c>
       <c r="B18" s="1">
         <f t="shared" si="0"/>
-        <v>1.3499999999999999</v>
+        <v>0.80999999999999994</v>
       </c>
       <c r="C18" s="1">
         <f t="shared" si="1"/>
-        <v>0.60000000000000009</v>
+        <v>0.36000000000000004</v>
       </c>
       <c r="D18" s="2">
         <v>2.4226110363391645E-2</v>
@@ -829,11 +829,11 @@
       </c>
       <c r="B19" s="1">
         <f t="shared" si="0"/>
-        <v>1.3499999999999999</v>
+        <v>0.80999999999999994</v>
       </c>
       <c r="C19" s="1">
         <f t="shared" si="1"/>
-        <v>0.60000000000000009</v>
+        <v>0.36000000000000004</v>
       </c>
       <c r="D19" s="2">
         <v>2.4226110363391645E-2</v>
@@ -851,11 +851,11 @@
       </c>
       <c r="B20" s="1">
         <f t="shared" si="0"/>
-        <v>1.3499999999999999</v>
+        <v>0.80999999999999994</v>
       </c>
       <c r="C20" s="1">
         <f t="shared" si="1"/>
-        <v>0.60000000000000009</v>
+        <v>0.36000000000000004</v>
       </c>
       <c r="D20" s="2">
         <v>2.4226110363391645E-2</v>
@@ -873,11 +873,11 @@
       </c>
       <c r="B21" s="1">
         <f t="shared" si="0"/>
-        <v>1.3499999999999999</v>
+        <v>0.80999999999999994</v>
       </c>
       <c r="C21" s="1">
         <f t="shared" si="1"/>
-        <v>0.60000000000000009</v>
+        <v>0.36000000000000004</v>
       </c>
       <c r="D21" s="2">
         <v>2.4226110363391645E-2</v>
@@ -895,11 +895,11 @@
       </c>
       <c r="B22" s="1">
         <f t="shared" si="0"/>
-        <v>1.3499999999999999</v>
+        <v>0.80999999999999994</v>
       </c>
       <c r="C22" s="1">
         <f t="shared" si="1"/>
-        <v>0.60000000000000009</v>
+        <v>0.36000000000000004</v>
       </c>
       <c r="D22" s="2">
         <v>2.4226110363391645E-2</v>
@@ -917,11 +917,11 @@
       </c>
       <c r="B23" s="1">
         <f t="shared" si="0"/>
-        <v>1.3499999999999999</v>
+        <v>0.80999999999999994</v>
       </c>
       <c r="C23" s="1">
         <f t="shared" si="1"/>
-        <v>0.75</v>
+        <v>0.44999999999999996</v>
       </c>
       <c r="D23" s="2">
         <v>2.4226110363391645E-2</v>
@@ -939,11 +939,11 @@
       </c>
       <c r="B24" s="1">
         <f t="shared" si="0"/>
-        <v>6.3000000000000007</v>
+        <v>3.7800000000000002</v>
       </c>
       <c r="C24" s="1">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>1.7999999999999998</v>
       </c>
       <c r="D24" s="2">
         <v>0.11305518169582769</v>
@@ -961,11 +961,11 @@
       </c>
       <c r="B25" s="1">
         <f t="shared" si="0"/>
-        <v>6.3000000000000007</v>
+        <v>3.7800000000000002</v>
       </c>
       <c r="C25" s="1">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>1.7999999999999998</v>
       </c>
       <c r="D25" s="2">
         <v>0.11305518169582769</v>
@@ -983,11 +983,11 @@
       </c>
       <c r="B26" s="1">
         <f t="shared" si="0"/>
-        <v>0.89999999999999991</v>
+        <v>0.53999999999999992</v>
       </c>
       <c r="C26" s="1">
         <f t="shared" si="1"/>
-        <v>0.375</v>
+        <v>0.22499999999999998</v>
       </c>
       <c r="D26" s="2">
         <v>1.6150740242261097E-2</v>
@@ -1005,11 +1005,11 @@
       </c>
       <c r="B27" s="1">
         <f t="shared" si="0"/>
-        <v>0.89999999999999991</v>
+        <v>0.53999999999999992</v>
       </c>
       <c r="C27" s="1">
         <f t="shared" si="1"/>
-        <v>0.375</v>
+        <v>0.22499999999999998</v>
       </c>
       <c r="D27" s="2">
         <v>1.6150740242261097E-2</v>
@@ -1027,11 +1027,11 @@
       </c>
       <c r="B28" s="1">
         <f t="shared" si="0"/>
-        <v>0.89999999999999991</v>
+        <v>0.53999999999999992</v>
       </c>
       <c r="C28" s="1">
         <f t="shared" si="1"/>
-        <v>0.30000000000000004</v>
+        <v>0.18000000000000002</v>
       </c>
       <c r="D28" s="2">
         <v>1.6150740242261097E-2</v>
@@ -1049,11 +1049,11 @@
       </c>
       <c r="B29" s="1">
         <f t="shared" si="0"/>
-        <v>1.7999999999999998</v>
+        <v>1.0799999999999998</v>
       </c>
       <c r="C29" s="1">
         <f t="shared" si="1"/>
-        <v>1.05</v>
+        <v>0.63</v>
       </c>
       <c r="D29" s="2">
         <v>3.2301480484522194E-2</v>
@@ -1071,11 +1071,11 @@
       </c>
       <c r="B30" s="1">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>1.7999999999999998</v>
       </c>
       <c r="C30" s="1">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>5.3999999999999995</v>
       </c>
       <c r="D30" s="2">
         <v>5.3835800807536999E-2</v>
@@ -1093,11 +1093,11 @@
       </c>
       <c r="B31" s="1">
         <f t="shared" si="0"/>
-        <v>2.25</v>
+        <v>1.3499999999999999</v>
       </c>
       <c r="C31" s="1">
         <f t="shared" si="1"/>
-        <v>1.05</v>
+        <v>0.63</v>
       </c>
       <c r="D31" s="2">
         <v>4.0376850605652742E-2</v>
@@ -1115,11 +1115,11 @@
       </c>
       <c r="B32" s="1">
         <f t="shared" si="0"/>
-        <v>3.1500000000000004</v>
+        <v>1.8900000000000001</v>
       </c>
       <c r="C32" s="1">
         <f t="shared" si="1"/>
-        <v>1.5</v>
+        <v>0.89999999999999991</v>
       </c>
       <c r="D32" s="2">
         <v>5.6527590847913846E-2</v>
@@ -1137,11 +1137,11 @@
       </c>
       <c r="B33" s="1">
         <f t="shared" si="0"/>
-        <v>0.89999999999999991</v>
+        <v>0.53999999999999992</v>
       </c>
       <c r="C33" s="1">
         <f t="shared" si="1"/>
-        <v>0.60000000000000009</v>
+        <v>0.36000000000000004</v>
       </c>
       <c r="D33" s="2">
         <v>1.6150740242261097E-2</v>

--- a/data/CS1/case33_1/case33_operational_data.xlsx
+++ b/data/CS1/case33_1/case33_operational_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/micaelsimoes/PycharmProjects/shared-resources-planning/data/CS1/case33_1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE8588B7-C3C6-3A43-AC51-8288806E596D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AA862B5-BD48-1D4F-B868-F1D87C2CC815}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1000" yWindow="680" windowWidth="28400" windowHeight="18440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1000" yWindow="680" windowWidth="28400" windowHeight="18440" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Characterization" sheetId="2" r:id="rId1"/>
@@ -73781,76 +73781,76 @@
         <v>1</v>
       </c>
       <c r="D2" s="1">
-        <v>11.307720000000002</v>
+        <v>1.8846200000000002</v>
       </c>
       <c r="E2" s="1">
-        <v>11.684920000000002</v>
+        <v>1.947486666666667</v>
       </c>
       <c r="F2" s="1">
-        <v>10.463159999999998</v>
+        <v>1.7438599999999997</v>
       </c>
       <c r="G2" s="1">
-        <v>9.9175999999999984</v>
+        <v>1.6529333333333331</v>
       </c>
       <c r="H2" s="1">
-        <v>8.1254400000000011</v>
+        <v>1.3542400000000001</v>
       </c>
       <c r="I2" s="1">
-        <v>6.8963200000000011</v>
+        <v>1.1493866666666668</v>
       </c>
       <c r="J2" s="1">
-        <v>8.4336400000000005</v>
+        <v>1.4056066666666667</v>
       </c>
       <c r="K2" s="1">
-        <v>1.4646399999999999</v>
+        <v>0.24410666666666667</v>
       </c>
       <c r="L2" s="1">
-        <v>1.288</v>
+        <v>0.21466666666666667</v>
       </c>
       <c r="M2" s="1">
-        <v>1.8777199999999996</v>
+        <v>0.31295333333333325</v>
       </c>
       <c r="N2" s="1">
-        <v>1.1058400000000002</v>
+        <v>0.1843066666666667</v>
       </c>
       <c r="O2" s="1">
-        <v>1.38184</v>
+        <v>0.23030666666666666</v>
       </c>
       <c r="P2" s="1">
-        <v>2.2015600000000006</v>
+        <v>0.36692666666666679</v>
       </c>
       <c r="Q2" s="1">
-        <v>4.0562800000000001</v>
+        <v>0.67604666666666668</v>
       </c>
       <c r="R2" s="1">
-        <v>4.3276799999999991</v>
+        <v>0.72127999999999981</v>
       </c>
       <c r="S2" s="1">
-        <v>4.2559199999999997</v>
+        <v>0.70931999999999995</v>
       </c>
       <c r="T2" s="1">
-        <v>2.3874</v>
+        <v>0.39789999999999998</v>
       </c>
       <c r="U2" s="1">
-        <v>4.8631199999999994</v>
+        <v>0.81051999999999991</v>
       </c>
       <c r="V2" s="1">
-        <v>2.8538399999999999</v>
+        <v>0.47564000000000001</v>
       </c>
       <c r="W2" s="1">
-        <v>2.0065199999999996</v>
+        <v>0.33441999999999994</v>
       </c>
       <c r="X2" s="1">
-        <v>3.0470400000000004</v>
+        <v>0.50784000000000007</v>
       </c>
       <c r="Y2" s="1">
-        <v>1.88324</v>
+        <v>0.31387333333333334</v>
       </c>
       <c r="Z2" s="1">
-        <v>8.5955600000000008</v>
+        <v>1.4325933333333334</v>
       </c>
       <c r="AA2" s="1">
-        <v>10.36196</v>
+        <v>1.7269933333333334</v>
       </c>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.2">
@@ -73864,76 +73864,76 @@
         <v>1</v>
       </c>
       <c r="D3" s="1">
-        <v>-25.53</v>
+        <v>-4.2549999999999999</v>
       </c>
       <c r="E3" s="1">
-        <v>-27.300079999999998</v>
+        <v>-4.5500133333333332</v>
       </c>
       <c r="F3" s="1">
-        <v>-30.704080000000005</v>
+        <v>-5.1173466666666672</v>
       </c>
       <c r="G3" s="1">
-        <v>-33.120919999999998</v>
+        <v>-5.520153333333333</v>
       </c>
       <c r="H3" s="1">
-        <v>-35.401600000000002</v>
+        <v>-5.900266666666667</v>
       </c>
       <c r="I3" s="1">
-        <v>-38.635400000000004</v>
+        <v>-6.439233333333334</v>
       </c>
       <c r="J3" s="1">
-        <v>-36.865319999999997</v>
+        <v>-6.1442199999999998</v>
       </c>
       <c r="K3" s="1">
-        <v>-41.353447999999993</v>
+        <v>-6.8922413333333319</v>
       </c>
       <c r="L3" s="1">
-        <v>-37.506927999999988</v>
+        <v>-6.2511546666666646</v>
       </c>
       <c r="M3" s="1">
-        <v>-55.091531999999994</v>
+        <v>-9.1819219999999984</v>
       </c>
       <c r="N3" s="1">
-        <v>-54.526928000000005</v>
+        <v>-9.0878213333333342</v>
       </c>
       <c r="O3" s="1">
-        <v>-49.845967999999999</v>
+        <v>-8.3076613333333338</v>
       </c>
       <c r="P3" s="1">
-        <v>-47.781487999999996</v>
+        <v>-7.963581333333333</v>
       </c>
       <c r="Q3" s="1">
-        <v>-46.132204000000002</v>
+        <v>-7.6887006666666666</v>
       </c>
       <c r="R3" s="1">
-        <v>-43.483064000000006</v>
+        <v>-7.247177333333334</v>
       </c>
       <c r="S3" s="1">
-        <v>-39.569751999999994</v>
+        <v>-6.594958666666666</v>
       </c>
       <c r="T3" s="1">
-        <v>-37.000008000000001</v>
+        <v>-6.1666680000000005</v>
       </c>
       <c r="U3" s="1">
-        <v>-33.111352000000004</v>
+        <v>-5.5185586666666673</v>
       </c>
       <c r="V3" s="1">
-        <v>-21.016755999999997</v>
+        <v>-3.5027926666666662</v>
       </c>
       <c r="W3" s="1">
-        <v>-23.520903999999994</v>
+        <v>-3.9201506666666659</v>
       </c>
       <c r="X3" s="1">
-        <v>-24.862631999999998</v>
+        <v>-4.1437719999999993</v>
       </c>
       <c r="Y3" s="1">
-        <v>-26.692419999999998</v>
+        <v>-4.4487366666666661</v>
       </c>
       <c r="Z3" s="1">
-        <v>-21.20692</v>
+        <v>-3.5344866666666666</v>
       </c>
       <c r="AA3" s="1">
-        <v>-22.534480000000002</v>
+        <v>-3.755746666666667</v>
       </c>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.2">
@@ -73947,76 +73947,76 @@
         <v>1</v>
       </c>
       <c r="D4" s="1">
-        <v>24.595187999999997</v>
+        <v>4.0991979999999995</v>
       </c>
       <c r="E4" s="1">
-        <v>26.31273599999999</v>
+        <v>4.3854559999999987</v>
       </c>
       <c r="F4" s="1">
-        <v>29.502651999999998</v>
+        <v>4.9171086666666666</v>
       </c>
       <c r="G4" s="1">
-        <v>31.745612000000005</v>
+        <v>5.2909353333333344</v>
       </c>
       <c r="H4" s="1">
-        <v>33.790219999999991</v>
+        <v>5.6317033333333315</v>
       </c>
       <c r="I4" s="1">
-        <v>36.896599999999999</v>
+        <v>6.1494333333333335</v>
       </c>
       <c r="J4" s="1">
-        <v>35.176199999999994</v>
+        <v>5.8626999999999994</v>
       </c>
       <c r="K4" s="1">
-        <v>39.696067999999997</v>
+        <v>6.6160113333333328</v>
       </c>
       <c r="L4" s="1">
-        <v>36.361068000000003</v>
+        <v>6.0601780000000005</v>
       </c>
       <c r="M4" s="1">
-        <v>41.490711999999995</v>
+        <v>6.9151186666666655</v>
       </c>
       <c r="N4" s="1">
-        <v>41.817403999999996</v>
+        <v>6.969567333333333</v>
       </c>
       <c r="O4" s="1">
-        <v>39.145171999999995</v>
+        <v>6.5241953333333322</v>
       </c>
       <c r="P4" s="1">
-        <v>37.825800000000001</v>
+        <v>6.3043000000000005</v>
       </c>
       <c r="Q4" s="1">
-        <v>36.853543999999999</v>
+        <v>6.1422573333333332</v>
       </c>
       <c r="R4" s="1">
-        <v>34.537536000000003</v>
+        <v>5.7562560000000005</v>
       </c>
       <c r="S4" s="1">
-        <v>31.444404000000002</v>
+        <v>5.2407340000000007</v>
       </c>
       <c r="T4" s="1">
-        <v>29.292891999999991</v>
+        <v>4.8821486666666649</v>
       </c>
       <c r="U4" s="1">
-        <v>26.180623999999998</v>
+        <v>4.3634373333333327</v>
       </c>
       <c r="V4" s="1">
-        <v>20.491527999999999</v>
+        <v>3.4152546666666663</v>
       </c>
       <c r="W4" s="1">
-        <v>22.935967999999999</v>
+        <v>3.822661333333333</v>
       </c>
       <c r="X4" s="1">
-        <v>24.372088000000002</v>
+        <v>4.0620146666666672</v>
       </c>
       <c r="Y4" s="1">
-        <v>26.253488000000001</v>
+        <v>4.3755813333333338</v>
       </c>
       <c r="Z4" s="1">
-        <v>20.428599999999999</v>
+        <v>3.4047666666666667</v>
       </c>
       <c r="AA4" s="1">
-        <v>21.723040000000005</v>
+        <v>3.6205066666666674</v>
       </c>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.2">
@@ -74030,76 +74030,76 @@
         <v>2</v>
       </c>
       <c r="D5" s="1">
-        <v>11.194642800000004</v>
+        <v>1.8657738000000006</v>
       </c>
       <c r="E5" s="1">
-        <v>11.684920000000002</v>
+        <v>1.947486666666667</v>
       </c>
       <c r="F5" s="1">
-        <v>10.8816864</v>
+        <v>1.8136143999999998</v>
       </c>
       <c r="G5" s="1">
-        <v>10.115951999999998</v>
+        <v>1.6859919999999997</v>
       </c>
       <c r="H5" s="1">
-        <v>7.9629311999999999</v>
+        <v>1.3271552</v>
       </c>
       <c r="I5" s="1">
-        <v>6.6204672000000011</v>
+        <v>1.1034112000000003</v>
       </c>
       <c r="J5" s="1">
-        <v>8.5179764000000002</v>
+        <v>1.4196627333333334</v>
       </c>
       <c r="K5" s="1">
-        <v>1.4353472</v>
+        <v>0.23922453333333335</v>
       </c>
       <c r="L5" s="1">
-        <v>1.3395200000000003</v>
+        <v>0.22325333333333339</v>
       </c>
       <c r="M5" s="1">
-        <v>1.9716059999999997</v>
+        <v>0.32860099999999998</v>
       </c>
       <c r="N5" s="1">
-        <v>1.0837232000000001</v>
+        <v>0.18062053333333336</v>
       </c>
       <c r="O5" s="1">
-        <v>1.3956583999999999</v>
+        <v>0.23260973333333332</v>
       </c>
       <c r="P5" s="1">
-        <v>2.2015600000000006</v>
+        <v>0.36692666666666679</v>
       </c>
       <c r="Q5" s="1">
-        <v>4.2590940000000002</v>
+        <v>0.70984900000000006</v>
       </c>
       <c r="R5" s="1">
-        <v>4.3276799999999991</v>
+        <v>0.72127999999999981</v>
       </c>
       <c r="S5" s="1">
-        <v>4.3410383999999995</v>
+        <v>0.72350639999999988</v>
       </c>
       <c r="T5" s="1">
-        <v>2.26803</v>
+        <v>0.37800499999999998</v>
       </c>
       <c r="U5" s="1">
-        <v>5.1062759999999985</v>
+        <v>0.85104599999999975</v>
       </c>
       <c r="V5" s="1">
-        <v>2.8823783999999999</v>
+        <v>0.4803964</v>
       </c>
       <c r="W5" s="1">
-        <v>2.0667155999999993</v>
+        <v>0.34445259999999989</v>
       </c>
       <c r="X5" s="1">
-        <v>3.0775104000000004</v>
+        <v>0.51291840000000011</v>
       </c>
       <c r="Y5" s="1">
-        <v>1.7890779999999999</v>
+        <v>0.29817966666666668</v>
       </c>
       <c r="Z5" s="1">
-        <v>8.767471200000001</v>
+        <v>1.4612452000000002</v>
       </c>
       <c r="AA5" s="1">
-        <v>10.36196</v>
+        <v>1.7269933333333334</v>
       </c>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.2">
@@ -74113,76 +74113,76 @@
         <v>2</v>
       </c>
       <c r="D6" s="1">
-        <v>-25.53</v>
+        <v>-4.2549999999999999</v>
       </c>
       <c r="E6" s="1">
-        <v>-27.027079199999999</v>
+        <v>-4.5045131999999999</v>
       </c>
       <c r="F6" s="1">
-        <v>-30.704080000000005</v>
+        <v>-5.1173466666666672</v>
       </c>
       <c r="G6" s="1">
-        <v>-31.464873999999998</v>
+        <v>-5.2441456666666664</v>
       </c>
       <c r="H6" s="1">
-        <v>-34.339551999999998</v>
+        <v>-5.7232586666666663</v>
       </c>
       <c r="I6" s="1">
-        <v>-37.089984000000001</v>
+        <v>-6.1816640000000005</v>
       </c>
       <c r="J6" s="1">
-        <v>-37.233973200000001</v>
+        <v>-6.2056621999999999</v>
       </c>
       <c r="K6" s="1">
-        <v>-41.353447999999993</v>
+        <v>-6.8922413333333319</v>
       </c>
       <c r="L6" s="1">
-        <v>-37.506927999999988</v>
+        <v>-6.2511546666666646</v>
       </c>
       <c r="M6" s="1">
-        <v>-54.540616679999992</v>
+        <v>-9.0901027799999987</v>
       </c>
       <c r="N6" s="1">
-        <v>-55.617466560000011</v>
+        <v>-9.2695777600000024</v>
       </c>
       <c r="O6" s="1">
-        <v>-48.849048639999999</v>
+        <v>-8.1415081066666666</v>
       </c>
       <c r="P6" s="1">
-        <v>-49.692747519999998</v>
+        <v>-8.2821245866666668</v>
       </c>
       <c r="Q6" s="1">
-        <v>-45.670881959999996</v>
+        <v>-7.6118136599999993</v>
       </c>
       <c r="R6" s="1">
-        <v>-45.222386560000011</v>
+        <v>-7.5370644266666682</v>
       </c>
       <c r="S6" s="1">
-        <v>-39.569751999999994</v>
+        <v>-6.594958666666666</v>
       </c>
       <c r="T6" s="1">
-        <v>-36.26000784</v>
+        <v>-6.0433346400000003</v>
       </c>
       <c r="U6" s="1">
-        <v>-31.786897920000001</v>
+        <v>-5.2978163199999999</v>
       </c>
       <c r="V6" s="1">
-        <v>-21.016755999999997</v>
+        <v>-3.5027926666666662</v>
       </c>
       <c r="W6" s="1">
-        <v>-23.285694959999994</v>
+        <v>-3.8809491599999988</v>
       </c>
       <c r="X6" s="1">
-        <v>-24.365379359999995</v>
+        <v>-4.0608965599999989</v>
       </c>
       <c r="Y6" s="1">
-        <v>-25.891647399999997</v>
+        <v>-4.3152745666666661</v>
       </c>
       <c r="Z6" s="1">
-        <v>-22.055196800000001</v>
+        <v>-3.6758661333333333</v>
       </c>
       <c r="AA6" s="1">
-        <v>-21.633100800000001</v>
+        <v>-3.6055168000000002</v>
       </c>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.2">
@@ -74196,76 +74196,76 @@
         <v>2</v>
       </c>
       <c r="D7" s="1">
-        <v>23.365428599999998</v>
+        <v>3.8942380999999995</v>
       </c>
       <c r="E7" s="1">
-        <v>27.102118079999993</v>
+        <v>4.5170196799999989</v>
       </c>
       <c r="F7" s="1">
-        <v>28.322545919999996</v>
+        <v>4.7204243199999993</v>
       </c>
       <c r="G7" s="1">
-        <v>30.158331400000002</v>
+        <v>5.0263885666666672</v>
       </c>
       <c r="H7" s="1">
-        <v>32.776513399999992</v>
+        <v>5.4627522333333323</v>
       </c>
       <c r="I7" s="1">
-        <v>38.003498000000008</v>
+        <v>6.3339163333333346</v>
       </c>
       <c r="J7" s="1">
-        <v>33.769151999999998</v>
+        <v>5.6281919999999994</v>
       </c>
       <c r="K7" s="1">
-        <v>38.108225280000006</v>
+        <v>6.3513708800000011</v>
       </c>
       <c r="L7" s="1">
-        <v>36.724678680000004</v>
+        <v>6.1207797800000003</v>
       </c>
       <c r="M7" s="1">
-        <v>40.245990639999995</v>
+        <v>6.7076651066666662</v>
       </c>
       <c r="N7" s="1">
-        <v>41.817403999999996</v>
+        <v>6.969567333333333</v>
       </c>
       <c r="O7" s="1">
-        <v>39.928075439999994</v>
+        <v>6.6546792399999992</v>
       </c>
       <c r="P7" s="1">
-        <v>36.312768000000005</v>
+        <v>6.0521280000000006</v>
       </c>
       <c r="Q7" s="1">
-        <v>37.59061487999999</v>
+        <v>6.2651024799999986</v>
       </c>
       <c r="R7" s="1">
-        <v>36.264412800000009</v>
+        <v>6.0440688000000016</v>
       </c>
       <c r="S7" s="1">
-        <v>32.387736120000007</v>
+        <v>5.3979560200000014</v>
       </c>
       <c r="T7" s="1">
-        <v>28.414105239999991</v>
+        <v>4.7356842066666651</v>
       </c>
       <c r="U7" s="1">
-        <v>27.227848959999996</v>
+        <v>4.537974826666666</v>
       </c>
       <c r="V7" s="1">
-        <v>21.516104399999996</v>
+        <v>3.5860173999999994</v>
       </c>
       <c r="W7" s="1">
-        <v>22.935967999999999</v>
+        <v>3.822661333333333</v>
       </c>
       <c r="X7" s="1">
-        <v>23.153483600000001</v>
+        <v>3.8589139333333335</v>
       </c>
       <c r="Y7" s="1">
-        <v>27.566162400000003</v>
+        <v>4.5943604000000002</v>
       </c>
       <c r="Z7" s="1">
-        <v>20.224313999999996</v>
+        <v>3.3707189999999994</v>
       </c>
       <c r="AA7" s="1">
-        <v>21.723040000000005</v>
+        <v>3.6205066666666674</v>
       </c>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.2">
@@ -74279,76 +74279,76 @@
         <v>3</v>
       </c>
       <c r="D8" s="1">
-        <v>10.970749944000001</v>
+        <v>1.8284583240000003</v>
       </c>
       <c r="E8" s="1">
-        <v>11.9186184</v>
+        <v>1.9864363999999999</v>
       </c>
       <c r="F8" s="1">
-        <v>10.990503263999999</v>
+        <v>1.8317505439999999</v>
       </c>
       <c r="G8" s="1">
-        <v>9.7113139199999985</v>
+        <v>1.6185523199999998</v>
       </c>
       <c r="H8" s="1">
-        <v>7.5647846399999992</v>
+        <v>1.2607974399999999</v>
       </c>
       <c r="I8" s="1">
-        <v>6.6866718720000007</v>
+        <v>1.1144453120000002</v>
       </c>
       <c r="J8" s="1">
-        <v>8.4327966360000008</v>
+        <v>1.4054661060000002</v>
       </c>
       <c r="K8" s="1">
-        <v>1.492761088</v>
+        <v>0.24879351466666666</v>
       </c>
       <c r="L8" s="1">
-        <v>1.3395200000000003</v>
+        <v>0.22325333333333339</v>
       </c>
       <c r="M8" s="1">
-        <v>1.8730256999999999</v>
+        <v>0.31217095</v>
       </c>
       <c r="N8" s="1">
-        <v>1.094560432</v>
+        <v>0.18242673866666667</v>
       </c>
       <c r="O8" s="1">
-        <v>1.3956583999999999</v>
+        <v>0.23260973333333332</v>
       </c>
       <c r="P8" s="1">
-        <v>2.1795444000000006</v>
+        <v>0.36325740000000012</v>
       </c>
       <c r="Q8" s="1">
-        <v>4.0461393000000001</v>
+        <v>0.67435655000000005</v>
       </c>
       <c r="R8" s="1">
-        <v>4.1978495999999996</v>
+        <v>0.69964159999999997</v>
       </c>
       <c r="S8" s="1">
-        <v>4.2108072479999992</v>
+        <v>0.7018012079999999</v>
       </c>
       <c r="T8" s="1">
-        <v>2.26803</v>
+        <v>0.37800499999999998</v>
       </c>
       <c r="U8" s="1">
-        <v>4.9530877199999983</v>
+        <v>0.82551461999999975</v>
       </c>
       <c r="V8" s="1">
-        <v>2.8247308319999997</v>
+        <v>0.47078847199999996</v>
       </c>
       <c r="W8" s="1">
-        <v>2.1700513799999994</v>
+        <v>0.3616752299999999</v>
       </c>
       <c r="X8" s="1">
-        <v>3.0775104000000004</v>
+        <v>0.51291840000000011</v>
       </c>
       <c r="Y8" s="1">
-        <v>1.8606411199999999</v>
+        <v>0.31010685333333332</v>
       </c>
       <c r="Z8" s="1">
-        <v>8.5921217760000008</v>
+        <v>1.4320202960000001</v>
       </c>
       <c r="AA8" s="1">
-        <v>9.9474815999999997</v>
+        <v>1.6579135999999999</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.2">
@@ -74362,76 +74362,76 @@
         <v>3</v>
       </c>
       <c r="D9" s="1">
-        <v>-24.253500000000003</v>
+        <v>-4.0422500000000001</v>
       </c>
       <c r="E9" s="1">
-        <v>-27.027079199999999</v>
+        <v>-4.5045131999999999</v>
       </c>
       <c r="F9" s="1">
-        <v>-29.168876000000004</v>
+        <v>-4.8614793333333344</v>
       </c>
       <c r="G9" s="1">
-        <v>-31.464873999999998</v>
+        <v>-5.2441456666666664</v>
       </c>
       <c r="H9" s="1">
-        <v>-35.713134080000003</v>
+        <v>-5.9521890133333342</v>
       </c>
       <c r="I9" s="1">
-        <v>-36.348184320000001</v>
+        <v>-6.0580307200000005</v>
       </c>
       <c r="J9" s="1">
-        <v>-38.350992396000002</v>
+        <v>-6.3918320660000001</v>
       </c>
       <c r="K9" s="1">
-        <v>-40.526379039999995</v>
+        <v>-6.7543965066666658</v>
       </c>
       <c r="L9" s="1">
-        <v>-39.382274399999986</v>
+        <v>-6.5637123999999973</v>
       </c>
       <c r="M9" s="1">
-        <v>-55.086022846799985</v>
+        <v>-9.181003807799998</v>
       </c>
       <c r="N9" s="1">
-        <v>-53.948942563200013</v>
+        <v>-8.9914904272000022</v>
       </c>
       <c r="O9" s="1">
-        <v>-50.314520099200003</v>
+        <v>-8.3857533498666665</v>
       </c>
       <c r="P9" s="1">
-        <v>-49.195820044800008</v>
+        <v>-8.199303340800002</v>
       </c>
       <c r="Q9" s="1">
-        <v>-47.954426057999996</v>
+        <v>-7.9924043429999996</v>
       </c>
       <c r="R9" s="1">
-        <v>-44.770162694400007</v>
+        <v>-7.4616937824000011</v>
       </c>
       <c r="S9" s="1">
-        <v>-39.569751999999994</v>
+        <v>-6.594958666666666</v>
       </c>
       <c r="T9" s="1">
-        <v>-35.8974077616</v>
+        <v>-5.9829012936000003</v>
       </c>
       <c r="U9" s="1">
-        <v>-33.058373836800001</v>
+        <v>-5.5097289728000005</v>
       </c>
       <c r="V9" s="1">
-        <v>-21.64725868</v>
+        <v>-3.6078764466666668</v>
       </c>
       <c r="W9" s="1">
-        <v>-23.052838010399991</v>
+        <v>-3.8421396683999984</v>
       </c>
       <c r="X9" s="1">
-        <v>-24.365379359999995</v>
+        <v>-4.0608965599999989</v>
       </c>
       <c r="Y9" s="1">
-        <v>-24.597065029999996</v>
+        <v>-4.099510838333333</v>
       </c>
       <c r="Z9" s="1">
-        <v>-21.834644831999999</v>
+        <v>-3.6391074719999996</v>
       </c>
       <c r="AA9" s="1">
-        <v>-22.714755839999999</v>
+        <v>-3.7857926399999999</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.2">
@@ -74445,76 +74445,76 @@
         <v>3</v>
       </c>
       <c r="D10" s="1">
-        <v>23.832737171999998</v>
+        <v>3.9721228619999995</v>
       </c>
       <c r="E10" s="1">
-        <v>25.747012175999995</v>
+        <v>4.2911686959999988</v>
       </c>
       <c r="F10" s="1">
-        <v>28.322545919999996</v>
+        <v>4.7204243199999993</v>
       </c>
       <c r="G10" s="1">
-        <v>29.253581458000003</v>
+        <v>4.8755969096666671</v>
       </c>
       <c r="H10" s="1">
-        <v>31.137687729999989</v>
+        <v>5.1896146216666645</v>
       </c>
       <c r="I10" s="1">
-        <v>36.103323100000004</v>
+        <v>6.0172205166666677</v>
       </c>
       <c r="J10" s="1">
-        <v>32.080694399999992</v>
+        <v>5.3467823999999986</v>
       </c>
       <c r="K10" s="1">
-        <v>36.202814016000005</v>
+        <v>6.0338023360000008</v>
       </c>
       <c r="L10" s="1">
-        <v>35.990185106400006</v>
+        <v>5.9983641844000006</v>
       </c>
       <c r="M10" s="1">
-        <v>41.050910452800004</v>
+        <v>6.8418184088000009</v>
       </c>
       <c r="N10" s="1">
-        <v>42.653752079999997</v>
+        <v>7.1089586799999998</v>
       </c>
       <c r="O10" s="1">
-        <v>37.931671668</v>
+        <v>6.3219452780000003</v>
       </c>
       <c r="P10" s="1">
-        <v>37.765278720000005</v>
+        <v>6.2942131200000011</v>
       </c>
       <c r="Q10" s="1">
-        <v>37.966521028799995</v>
+        <v>6.3277535047999995</v>
       </c>
       <c r="R10" s="1">
-        <v>36.989701056000008</v>
+        <v>6.1649501760000014</v>
       </c>
       <c r="S10" s="1">
-        <v>31.092226675200006</v>
+        <v>5.1820377792000007</v>
       </c>
       <c r="T10" s="1">
-        <v>29.55066944959999</v>
+        <v>4.9251115749333314</v>
       </c>
       <c r="U10" s="1">
-        <v>26.138735001599997</v>
+        <v>4.3564558335999992</v>
       </c>
       <c r="V10" s="1">
-        <v>22.591909619999996</v>
+        <v>3.7653182699999994</v>
       </c>
       <c r="W10" s="1">
-        <v>23.165327680000001</v>
+        <v>3.8608879466666668</v>
       </c>
       <c r="X10" s="1">
-        <v>24.079622944</v>
+        <v>4.0132704906666667</v>
       </c>
       <c r="Y10" s="1">
-        <v>28.393147272000007</v>
+        <v>4.7321912120000009</v>
       </c>
       <c r="Z10" s="1">
-        <v>20.426557139999996</v>
+        <v>3.4044261899999992</v>
       </c>
       <c r="AA10" s="1">
-        <v>22.809192000000007</v>
+        <v>3.8015320000000012</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.2">
@@ -74528,76 +74528,76 @@
         <v>1</v>
       </c>
       <c r="D11" s="1">
-        <v>10.742334000000001</v>
+        <v>1.7903890000000002</v>
       </c>
       <c r="E11" s="1">
-        <v>11.100674</v>
+        <v>1.8501123333333334</v>
       </c>
       <c r="F11" s="1">
-        <v>9.9400019999999998</v>
+        <v>1.6566669999999999</v>
       </c>
       <c r="G11" s="1">
-        <v>9.421719999999997</v>
+        <v>1.5702866666666662</v>
       </c>
       <c r="H11" s="1">
-        <v>7.7191679999999998</v>
+        <v>1.2865279999999999</v>
       </c>
       <c r="I11" s="1">
-        <v>6.5515040000000004</v>
+        <v>1.0919173333333334</v>
       </c>
       <c r="J11" s="1">
-        <v>8.0119579999999999</v>
+        <v>1.3353263333333334</v>
       </c>
       <c r="K11" s="1">
-        <v>1.391408</v>
+        <v>0.23190133333333332</v>
       </c>
       <c r="L11" s="1">
-        <v>1.2236</v>
+        <v>0.20393333333333333</v>
       </c>
       <c r="M11" s="1">
-        <v>1.7838339999999995</v>
+        <v>0.29730566666666658</v>
       </c>
       <c r="N11" s="1">
-        <v>1.050548</v>
+        <v>0.17509133333333335</v>
       </c>
       <c r="O11" s="1">
-        <v>1.3127479999999998</v>
+        <v>0.21879133333333331</v>
       </c>
       <c r="P11" s="1">
-        <v>2.0914820000000005</v>
+        <v>0.34858033333333344</v>
       </c>
       <c r="Q11" s="1">
-        <v>3.8534660000000001</v>
+        <v>0.64224433333333331</v>
       </c>
       <c r="R11" s="1">
-        <v>4.1112959999999994</v>
+        <v>0.68521599999999994</v>
       </c>
       <c r="S11" s="1">
-        <v>4.0431239999999988</v>
+        <v>0.67385399999999984</v>
       </c>
       <c r="T11" s="1">
-        <v>2.26803</v>
+        <v>0.37800499999999998</v>
       </c>
       <c r="U11" s="1">
-        <v>4.6199639999999986</v>
+        <v>0.76999399999999973</v>
       </c>
       <c r="V11" s="1">
-        <v>2.7111479999999997</v>
+        <v>0.45185799999999993</v>
       </c>
       <c r="W11" s="1">
-        <v>1.9061939999999995</v>
+        <v>0.3176989999999999</v>
       </c>
       <c r="X11" s="1">
-        <v>2.8946879999999999</v>
+        <v>0.48244799999999999</v>
       </c>
       <c r="Y11" s="1">
-        <v>1.7890779999999999</v>
+        <v>0.29817966666666668</v>
       </c>
       <c r="Z11" s="1">
-        <v>8.1657820000000001</v>
+        <v>1.3609636666666667</v>
       </c>
       <c r="AA11" s="1">
-        <v>9.8438619999999997</v>
+        <v>1.6406436666666666</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.2">
@@ -74611,76 +74611,76 @@
         <v>1</v>
       </c>
       <c r="D12" s="1">
-        <v>-25.223640000000003</v>
+        <v>-4.2039400000000002</v>
       </c>
       <c r="E12" s="1">
-        <v>-27.027079199999999</v>
+        <v>-4.5045131999999999</v>
       </c>
       <c r="F12" s="1">
-        <v>-27.710432200000003</v>
+        <v>-4.6184053666666669</v>
       </c>
       <c r="G12" s="1">
-        <v>-31.464873999999998</v>
+        <v>-5.2441456666666664</v>
       </c>
       <c r="H12" s="1">
-        <v>-35.356002739200001</v>
+        <v>-5.8926671231999999</v>
       </c>
       <c r="I12" s="1">
-        <v>-37.802111692799997</v>
+        <v>-6.3003519487999995</v>
       </c>
       <c r="J12" s="1">
-        <v>-37.200462624120007</v>
+        <v>-6.2000771040200009</v>
       </c>
       <c r="K12" s="1">
-        <v>-40.121115249599988</v>
+        <v>-6.6868525415999978</v>
       </c>
       <c r="L12" s="1">
-        <v>-40.169919887999988</v>
+        <v>-6.6949866479999978</v>
       </c>
       <c r="M12" s="1">
-        <v>-52.882581932927991</v>
+        <v>-8.8137636554879979</v>
       </c>
       <c r="N12" s="1">
-        <v>-54.488431988832026</v>
+        <v>-9.0814053314720038</v>
       </c>
       <c r="O12" s="1">
-        <v>-51.823955702176008</v>
+        <v>-8.6373259503626674</v>
       </c>
       <c r="P12" s="1">
-        <v>-47.719945443455998</v>
+        <v>-7.9533242405759994</v>
       </c>
       <c r="Q12" s="1">
-        <v>-45.556704755099993</v>
+        <v>-7.5927841258499988</v>
       </c>
       <c r="R12" s="1">
-        <v>-44.322461067456011</v>
+        <v>-7.3870768445760016</v>
       </c>
       <c r="S12" s="1">
-        <v>-39.569751999999994</v>
+        <v>-6.594958666666666</v>
       </c>
       <c r="T12" s="1">
-        <v>-37.333304072064003</v>
+        <v>-6.2222173453440002</v>
       </c>
       <c r="U12" s="1">
-        <v>-32.397206360063997</v>
+        <v>-5.3995343933439992</v>
       </c>
       <c r="V12" s="1">
-        <v>-20.7813683328</v>
+        <v>-3.4635613888000001</v>
       </c>
       <c r="W12" s="1">
-        <v>-23.283366390503993</v>
+        <v>-3.8805610650839988</v>
       </c>
       <c r="X12" s="1">
-        <v>-25.583648327999995</v>
+        <v>-4.2639413879999992</v>
       </c>
       <c r="Y12" s="1">
-        <v>-24.597065029999996</v>
+        <v>-4.099510838333333</v>
       </c>
       <c r="Z12" s="1">
-        <v>-21.17960548704</v>
+        <v>-3.52993424784</v>
       </c>
       <c r="AA12" s="1">
-        <v>-22.260460723199998</v>
+        <v>-3.7100767871999998</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.2">
@@ -74694,76 +74694,76 @@
         <v>1</v>
       </c>
       <c r="D13" s="1">
-        <v>22.641100313399999</v>
+        <v>3.7735167188999998</v>
       </c>
       <c r="E13" s="1">
-        <v>24.974601810719999</v>
+        <v>4.1624336351200002</v>
       </c>
       <c r="F13" s="1">
-        <v>28.605771379199993</v>
+        <v>4.7676285631999988</v>
       </c>
       <c r="G13" s="1">
-        <v>28.668509828840005</v>
+        <v>4.7780849714733344</v>
       </c>
       <c r="H13" s="1">
-        <v>30.82631085269999</v>
+        <v>5.137718475449998</v>
       </c>
       <c r="I13" s="1">
-        <v>36.464356331000005</v>
+        <v>6.0773927218333341</v>
       </c>
       <c r="J13" s="1">
-        <v>32.080694399999992</v>
+        <v>5.3467823999999986</v>
       </c>
       <c r="K13" s="1">
-        <v>36.564842156159997</v>
+        <v>6.0941403593599999</v>
       </c>
       <c r="L13" s="1">
-        <v>35.990185106400006</v>
+        <v>5.9983641844000006</v>
       </c>
       <c r="M13" s="1">
-        <v>42.282437766384007</v>
+        <v>7.0470729610640008</v>
       </c>
       <c r="N13" s="1">
-        <v>40.521064475999999</v>
+        <v>6.7535107459999999</v>
       </c>
       <c r="O13" s="1">
-        <v>36.035088084599998</v>
+        <v>6.0058480140999997</v>
       </c>
       <c r="P13" s="1">
-        <v>38.898237081600001</v>
+        <v>6.4830395136000005</v>
       </c>
       <c r="Q13" s="1">
-        <v>37.586855818511999</v>
+        <v>6.2644759697519996</v>
       </c>
       <c r="R13" s="1">
-        <v>36.24990703488001</v>
+        <v>6.0416511724800017</v>
       </c>
       <c r="S13" s="1">
-        <v>29.537615341440006</v>
+        <v>4.9229358902400007</v>
       </c>
       <c r="T13" s="1">
-        <v>31.028202922079991</v>
+        <v>5.1713671536799986</v>
       </c>
       <c r="U13" s="1">
-        <v>27.184284401663994</v>
+        <v>4.5307140669439994</v>
       </c>
       <c r="V13" s="1">
-        <v>22.817828716199998</v>
+        <v>3.8029714526999996</v>
       </c>
       <c r="W13" s="1">
-        <v>23.860287510400003</v>
+        <v>3.976714585066667</v>
       </c>
       <c r="X13" s="1">
-        <v>23.838826714560003</v>
+        <v>3.9731377857600005</v>
       </c>
       <c r="Y13" s="1">
-        <v>29.528873162880007</v>
+        <v>4.9214788604800015</v>
       </c>
       <c r="Z13" s="1">
-        <v>20.426557139999996</v>
+        <v>3.4044261899999992</v>
       </c>
       <c r="AA13" s="1">
-        <v>23.265375840000008</v>
+        <v>3.8775626400000012</v>
       </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.2">
@@ -74777,76 +74777,76 @@
         <v>2</v>
       </c>
       <c r="D14" s="1">
-        <v>11.172027360000001</v>
+        <v>1.8620045600000001</v>
       </c>
       <c r="E14" s="1">
-        <v>11.21168074</v>
+        <v>1.8686134566666668</v>
       </c>
       <c r="F14" s="1">
-        <v>9.9400019999999998</v>
+        <v>1.6566669999999999</v>
       </c>
       <c r="G14" s="1">
-        <v>9.6101543999999954</v>
+        <v>1.6016923999999992</v>
       </c>
       <c r="H14" s="1">
-        <v>7.7963596799999992</v>
+        <v>1.2993932799999999</v>
       </c>
       <c r="I14" s="1">
-        <v>6.3549588799999999</v>
+        <v>1.0591598133333333</v>
       </c>
       <c r="J14" s="1">
-        <v>8.3324363199999993</v>
+        <v>1.3887393866666666</v>
       </c>
       <c r="K14" s="1">
-        <v>1.37749392</v>
+        <v>0.22958232000000001</v>
       </c>
       <c r="L14" s="1">
-        <v>1.2603080000000002</v>
+        <v>0.21005133333333337</v>
       </c>
       <c r="M14" s="1">
-        <v>1.7659956599999995</v>
+        <v>0.29433260999999994</v>
       </c>
       <c r="N14" s="1">
-        <v>1.0820644399999999</v>
+        <v>0.18034407333333333</v>
       </c>
       <c r="O14" s="1">
-        <v>1.2471105999999998</v>
+        <v>0.20785176666666663</v>
       </c>
       <c r="P14" s="1">
-        <v>2.0914820000000005</v>
+        <v>0.34858033333333344</v>
       </c>
       <c r="Q14" s="1">
-        <v>3.96906998</v>
+        <v>0.66151166333333333</v>
       </c>
       <c r="R14" s="1">
-        <v>4.0290700799999994</v>
+        <v>0.67151167999999994</v>
       </c>
       <c r="S14" s="1">
-        <v>4.1239864799999983</v>
+        <v>0.68733107999999976</v>
       </c>
       <c r="T14" s="1">
-        <v>2.1773087999999996</v>
+        <v>0.36288479999999995</v>
       </c>
       <c r="U14" s="1">
-        <v>4.4351654399999987</v>
+        <v>0.73919423999999978</v>
       </c>
       <c r="V14" s="1">
-        <v>2.6027020799999998</v>
+        <v>0.43378367999999995</v>
       </c>
       <c r="W14" s="1">
-        <v>2.0015036999999993</v>
+        <v>0.33358394999999991</v>
       </c>
       <c r="X14" s="1">
-        <v>2.8078473600000002</v>
+        <v>0.46797456000000004</v>
       </c>
       <c r="Y14" s="1">
-        <v>1.8427503399999998</v>
+        <v>0.30712505666666662</v>
       </c>
       <c r="Z14" s="1">
-        <v>8.2474398200000003</v>
+        <v>1.3745733033333334</v>
       </c>
       <c r="AA14" s="1">
-        <v>9.6469847600000005</v>
+        <v>1.6078307933333333</v>
       </c>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.2">
@@ -74860,76 +74860,76 @@
         <v>2</v>
       </c>
       <c r="D15" s="1">
-        <v>-25.475876400000004</v>
+        <v>-4.2459794000000004</v>
       </c>
       <c r="E15" s="1">
-        <v>-26.486537616</v>
+        <v>-4.4144229360000002</v>
       </c>
       <c r="F15" s="1">
-        <v>-26.602014912000001</v>
+        <v>-4.4336691520000002</v>
       </c>
       <c r="G15" s="1">
-        <v>-30.206279039999995</v>
+        <v>-5.0343798399999988</v>
       </c>
       <c r="H15" s="1">
-        <v>-36.770242848768007</v>
+        <v>-6.1283738081280008</v>
       </c>
       <c r="I15" s="1">
-        <v>-37.046069458943997</v>
+        <v>-6.1743449098239997</v>
       </c>
       <c r="J15" s="1">
-        <v>-36.4564533716376</v>
+        <v>-6.0760755619396001</v>
       </c>
       <c r="K15" s="1">
-        <v>-38.516270639615982</v>
+        <v>-6.419378439935997</v>
       </c>
       <c r="L15" s="1">
-        <v>-40.571619086879991</v>
+        <v>-6.7619365144799986</v>
       </c>
       <c r="M15" s="1">
-        <v>-52.353756113598713</v>
+        <v>-8.7256260189331183</v>
       </c>
       <c r="N15" s="1">
-        <v>-56.667969268385299</v>
+        <v>-9.4446615447308826</v>
       </c>
       <c r="O15" s="1">
-        <v>-50.787476588132492</v>
+        <v>-8.4645794313554159</v>
       </c>
       <c r="P15" s="1">
-        <v>-47.242745989021444</v>
+        <v>-7.8737909981702403</v>
       </c>
       <c r="Q15" s="1">
-        <v>-43.734436564895987</v>
+        <v>-7.2890727608159978</v>
       </c>
       <c r="R15" s="1">
-        <v>-43.436011846106886</v>
+        <v>-7.2393353076844811</v>
       </c>
       <c r="S15" s="1">
-        <v>-37.591264399999993</v>
+        <v>-6.2652107333333324</v>
       </c>
       <c r="T15" s="1">
-        <v>-37.333304072064003</v>
+        <v>-6.2222173453440002</v>
       </c>
       <c r="U15" s="1">
-        <v>-32.073234296463355</v>
+        <v>-5.3455390494105588</v>
       </c>
       <c r="V15" s="1">
-        <v>-20.7813683328</v>
+        <v>-3.4635613888000001</v>
       </c>
       <c r="W15" s="1">
-        <v>-23.749033718314074</v>
+        <v>-3.958172286385679</v>
       </c>
       <c r="X15" s="1">
-        <v>-25.839484811279995</v>
+        <v>-4.3065808018799991</v>
       </c>
       <c r="Y15" s="1">
-        <v>-24.843035680299998</v>
+        <v>-4.1405059467166661</v>
       </c>
       <c r="Z15" s="1">
-        <v>-20.332421267558399</v>
+        <v>-3.3887368779263998</v>
       </c>
       <c r="AA15" s="1">
-        <v>-23.150879152127999</v>
+        <v>-3.8584798586879998</v>
       </c>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.2">
@@ -74943,76 +74943,76 @@
         <v>2</v>
       </c>
       <c r="D16" s="1">
-        <v>21.509045297729998</v>
+        <v>3.5848408829549996</v>
       </c>
       <c r="E16" s="1">
-        <v>23.975617738291199</v>
+        <v>3.9959362897151998</v>
       </c>
       <c r="F16" s="1">
-        <v>30.036059948159995</v>
+        <v>5.0060099913599991</v>
       </c>
       <c r="G16" s="1">
-        <v>27.521769435686402</v>
+        <v>4.5869615726144</v>
       </c>
       <c r="H16" s="1">
-        <v>32.367626395334987</v>
+        <v>5.3946043992224979</v>
       </c>
       <c r="I16" s="1">
-        <v>35.005782077760003</v>
+        <v>5.8342970129600005</v>
       </c>
       <c r="J16" s="1">
-        <v>32.401501343999996</v>
+        <v>5.4002502239999997</v>
       </c>
       <c r="K16" s="1">
-        <v>36.564842156159997</v>
+        <v>6.0941403593599999</v>
       </c>
       <c r="L16" s="1">
-        <v>34.190675851080009</v>
+        <v>5.6984459751800012</v>
       </c>
       <c r="M16" s="1">
-        <v>43.128086521711687</v>
+        <v>7.1880144202852811</v>
       </c>
       <c r="N16" s="1">
-        <v>39.710643186479999</v>
+        <v>6.6184405310800001</v>
       </c>
       <c r="O16" s="1">
-        <v>37.476491607983995</v>
+        <v>6.2460819346639989</v>
       </c>
       <c r="P16" s="1">
-        <v>37.342307598335999</v>
+        <v>6.2237179330560002</v>
       </c>
       <c r="Q16" s="1">
-        <v>38.714461493067354</v>
+        <v>6.4524102488445587</v>
       </c>
       <c r="R16" s="1">
-        <v>36.974905175577611</v>
+        <v>6.1624841959296015</v>
       </c>
       <c r="S16" s="1">
-        <v>29.832991494854404</v>
+        <v>4.9721652491424004</v>
       </c>
       <c r="T16" s="1">
-        <v>31.648766980521589</v>
+        <v>5.2747944967535982</v>
       </c>
       <c r="U16" s="1">
-        <v>26.640598713630716</v>
+        <v>4.4400997856051196</v>
       </c>
       <c r="V16" s="1">
-        <v>23.046007003361996</v>
+        <v>3.8410011672269992</v>
       </c>
       <c r="W16" s="1">
-        <v>23.860287510400003</v>
+        <v>3.976714585066667</v>
       </c>
       <c r="X16" s="1">
-        <v>24.792379783142401</v>
+        <v>4.1320632971903999</v>
       </c>
       <c r="Y16" s="1">
-        <v>30.11945062613761</v>
+        <v>5.0199084376896019</v>
       </c>
       <c r="Z16" s="1">
-        <v>20.630822711399997</v>
+        <v>3.4384704518999993</v>
       </c>
       <c r="AA16" s="1">
-        <v>22.334760806400009</v>
+        <v>3.7224601344000017</v>
       </c>
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.2">
@@ -75026,76 +75026,76 @@
         <v>3</v>
       </c>
       <c r="D17" s="1">
-        <v>10.613425992000002</v>
+        <v>1.7689043320000002</v>
       </c>
       <c r="E17" s="1">
-        <v>11.660147969600001</v>
+        <v>1.9433579949333335</v>
       </c>
       <c r="F17" s="1">
-        <v>9.8406019799999989</v>
+        <v>1.6401003299999999</v>
       </c>
       <c r="G17" s="1">
-        <v>10.090662119999996</v>
+        <v>1.6817770199999993</v>
       </c>
       <c r="H17" s="1">
-        <v>7.8743232767999993</v>
+        <v>1.3123872127999998</v>
       </c>
       <c r="I17" s="1">
-        <v>6.2914092912000008</v>
+        <v>1.0485682152000002</v>
       </c>
       <c r="J17" s="1">
-        <v>8.0824632303999984</v>
+        <v>1.3470772050666664</v>
       </c>
       <c r="K17" s="1">
-        <v>1.3912688592</v>
+        <v>0.2318781432</v>
       </c>
       <c r="L17" s="1">
-        <v>1.2603080000000002</v>
+        <v>0.21005133333333337</v>
       </c>
       <c r="M17" s="1">
-        <v>1.7130157901999996</v>
+        <v>0.28550263169999995</v>
       </c>
       <c r="N17" s="1">
-        <v>1.0712437956</v>
+        <v>0.1785406326</v>
       </c>
       <c r="O17" s="1">
-        <v>1.2346394939999998</v>
+        <v>0.20577324899999996</v>
       </c>
       <c r="P17" s="1">
-        <v>2.0914820000000005</v>
+        <v>0.34858033333333344</v>
       </c>
       <c r="Q17" s="1">
-        <v>4.0087606797999999</v>
+        <v>0.6681267799666667</v>
       </c>
       <c r="R17" s="1">
-        <v>4.2305235839999993</v>
+        <v>0.70508726399999988</v>
       </c>
       <c r="S17" s="1">
-        <v>3.9177871559999979</v>
+        <v>0.65296452599999966</v>
       </c>
       <c r="T17" s="1">
-        <v>2.1119895359999998</v>
+        <v>0.35199825599999995</v>
       </c>
       <c r="U17" s="1">
-        <v>4.3908137855999989</v>
+        <v>0.73180229759999982</v>
       </c>
       <c r="V17" s="1">
-        <v>2.6547561215999993</v>
+        <v>0.44245935359999988</v>
       </c>
       <c r="W17" s="1">
-        <v>2.0015036999999993</v>
+        <v>0.33358394999999991</v>
       </c>
       <c r="X17" s="1">
-        <v>2.7516904128000004</v>
+        <v>0.45861506880000008</v>
       </c>
       <c r="Y17" s="1">
-        <v>1.8427503399999998</v>
+        <v>0.30712505666666662</v>
       </c>
       <c r="Z17" s="1">
-        <v>7.9175422272000002</v>
+        <v>1.3195903712000001</v>
       </c>
       <c r="AA17" s="1">
-        <v>9.454045064799999</v>
+        <v>1.5756741774666665</v>
       </c>
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.2">
@@ -75109,76 +75109,76 @@
         <v>3</v>
       </c>
       <c r="D18" s="1">
-        <v>-25.221117636000006</v>
+        <v>-4.2035196060000013</v>
       </c>
       <c r="E18" s="1">
-        <v>-27.545999120640001</v>
+        <v>-4.5909998534400005</v>
       </c>
       <c r="F18" s="1">
-        <v>-25.271914166399998</v>
+        <v>-4.2119856944</v>
       </c>
       <c r="G18" s="1">
-        <v>-30.508341830399996</v>
+        <v>-5.084723638399999</v>
       </c>
       <c r="H18" s="1">
-        <v>-37.873350134231039</v>
+        <v>-6.3122250223718401</v>
       </c>
       <c r="I18" s="1">
-        <v>-37.416530153533429</v>
+        <v>-6.2360883589222382</v>
       </c>
       <c r="J18" s="1">
-        <v>-34.998195236772098</v>
+        <v>-5.8330325394620166</v>
       </c>
       <c r="K18" s="1">
-        <v>-39.286596052408299</v>
+        <v>-6.5477660087347163</v>
       </c>
       <c r="L18" s="1">
-        <v>-40.977335277748793</v>
+        <v>-6.8295558796247988</v>
       </c>
       <c r="M18" s="1">
-        <v>-50.259605869054766</v>
+        <v>-8.3766009781757944</v>
       </c>
       <c r="N18" s="1">
-        <v>-57.801328653753004</v>
+        <v>-9.6335547756255</v>
       </c>
       <c r="O18" s="1">
-        <v>-50.279601822251166</v>
+        <v>-8.3799336370418605</v>
       </c>
       <c r="P18" s="1">
-        <v>-48.660028368692089</v>
+        <v>-8.1100047281153476</v>
       </c>
       <c r="Q18" s="1">
-        <v>-45.046469661842863</v>
+        <v>-7.5077449436404775</v>
       </c>
       <c r="R18" s="1">
-        <v>-45.607812438412232</v>
+        <v>-7.6013020730687053</v>
       </c>
       <c r="S18" s="1">
-        <v>-39.094914975999991</v>
+        <v>-6.5158191626666655</v>
       </c>
       <c r="T18" s="1">
-        <v>-36.213304949902081</v>
+        <v>-6.0355508249836802</v>
       </c>
       <c r="U18" s="1">
-        <v>-33.035431325357258</v>
+        <v>-5.5059052208928767</v>
       </c>
       <c r="V18" s="1">
-        <v>-19.74229991616</v>
+        <v>-3.2903833193600001</v>
       </c>
       <c r="W18" s="1">
-        <v>-23.274053043947792</v>
+        <v>-3.8790088406579653</v>
       </c>
       <c r="X18" s="1">
-        <v>-25.581089963167198</v>
+        <v>-4.2635149938611994</v>
       </c>
       <c r="Y18" s="1">
-        <v>-24.097744609890999</v>
+        <v>-4.0162907683151667</v>
       </c>
       <c r="Z18" s="1">
-        <v>-19.92577284220723</v>
+        <v>-3.3209621403678717</v>
       </c>
       <c r="AA18" s="1">
-        <v>-23.150879152127999</v>
+        <v>-3.8584798586879998</v>
       </c>
     </row>
     <row r="19" spans="1:27" x14ac:dyDescent="0.2">
@@ -75192,76 +75192,76 @@
         <v>3</v>
       </c>
       <c r="D19" s="1">
-        <v>20.433593032843497</v>
+        <v>3.4055988388072493</v>
       </c>
       <c r="E19" s="1">
-        <v>24.455130093057022</v>
+        <v>4.0758550155095037</v>
       </c>
       <c r="F19" s="1">
-        <v>31.237502346086394</v>
+        <v>5.2062503910143993</v>
       </c>
       <c r="G19" s="1">
-        <v>28.897857907470723</v>
+        <v>4.8163096512451204</v>
       </c>
       <c r="H19" s="1">
-        <v>33.662331451148383</v>
+        <v>5.6103885751913971</v>
       </c>
       <c r="I19" s="1">
-        <v>33.955608615427202</v>
+        <v>5.6592681025712004</v>
       </c>
       <c r="J19" s="1">
-        <v>34.021576411199995</v>
+        <v>5.6702627351999988</v>
       </c>
       <c r="K19" s="1">
-        <v>38.393084263967999</v>
+        <v>6.3988473773279999</v>
       </c>
       <c r="L19" s="1">
-        <v>33.164955575547609</v>
+        <v>5.5274925959246017</v>
       </c>
       <c r="M19" s="1">
-        <v>43.128086521711687</v>
+        <v>7.1880144202852811</v>
       </c>
       <c r="N19" s="1">
-        <v>40.107749618344798</v>
+        <v>6.6846249363907999</v>
       </c>
       <c r="O19" s="1">
-        <v>36.726961775824321</v>
+        <v>6.1211602959707205</v>
       </c>
       <c r="P19" s="1">
-        <v>39.209422978252803</v>
+        <v>6.5349038297088002</v>
       </c>
       <c r="Q19" s="1">
-        <v>37.553027648275339</v>
+        <v>6.2588379413792232</v>
       </c>
       <c r="R19" s="1">
-        <v>35.126159916798734</v>
+        <v>5.8543599861331224</v>
       </c>
       <c r="S19" s="1">
-        <v>29.534661579905862</v>
+        <v>4.922443596650977</v>
       </c>
       <c r="T19" s="1">
-        <v>31.648766980521589</v>
+        <v>5.2747944967535982</v>
       </c>
       <c r="U19" s="1">
-        <v>27.173410687903328</v>
+        <v>4.528901781317221</v>
       </c>
       <c r="V19" s="1">
-        <v>23.967847283496475</v>
+        <v>3.9946412139160792</v>
       </c>
       <c r="W19" s="1">
-        <v>24.576096135712007</v>
+        <v>4.0960160226186675</v>
       </c>
       <c r="X19" s="1">
-        <v>24.792379783142401</v>
+        <v>4.1320632971903999</v>
       </c>
       <c r="Y19" s="1">
-        <v>29.517061613614857</v>
+        <v>4.9195102689358094</v>
       </c>
       <c r="Z19" s="1">
-        <v>19.805589802943995</v>
+        <v>3.3009316338239993</v>
       </c>
       <c r="AA19" s="1">
-        <v>21.664717982208007</v>
+        <v>3.610786330368001</v>
       </c>
     </row>
     <row r="20" spans="1:27" x14ac:dyDescent="0.2">
@@ -75275,76 +75275,76 @@
         <v>1</v>
       </c>
       <c r="D20" s="1">
-        <v>11.816567400000004</v>
+        <v>1.9694279000000006</v>
       </c>
       <c r="E20" s="1">
-        <v>12.210741400000002</v>
+        <v>2.0351235666666669</v>
       </c>
       <c r="F20" s="1">
-        <v>10.934002200000002</v>
+        <v>1.8223337000000004</v>
       </c>
       <c r="G20" s="1">
-        <v>10.363891999999998</v>
+        <v>1.7273153333333331</v>
       </c>
       <c r="H20" s="1">
-        <v>8.4910847999999994</v>
+        <v>1.4151807999999999</v>
       </c>
       <c r="I20" s="1">
-        <v>7.2066544000000006</v>
+        <v>1.2011090666666668</v>
       </c>
       <c r="J20" s="1">
-        <v>8.8131538000000003</v>
+        <v>1.4688589666666667</v>
       </c>
       <c r="K20" s="1">
-        <v>1.5305488000000003</v>
+        <v>0.25509146666666671</v>
       </c>
       <c r="L20" s="1">
-        <v>1.34596</v>
+        <v>0.22432666666666667</v>
       </c>
       <c r="M20" s="1">
-        <v>1.9622173999999994</v>
+        <v>0.32703623333333326</v>
       </c>
       <c r="N20" s="1">
-        <v>1.1556028</v>
+        <v>0.19260046666666666</v>
       </c>
       <c r="O20" s="1">
-        <v>1.4440227999999997</v>
+        <v>0.24067046666666661</v>
       </c>
       <c r="P20" s="1">
-        <v>2.3006302000000005</v>
+        <v>0.38343836666666675</v>
       </c>
       <c r="Q20" s="1">
-        <v>4.2388126000000002</v>
+        <v>0.70646876666666669</v>
       </c>
       <c r="R20" s="1">
-        <v>4.5224256</v>
+        <v>0.75373760000000001</v>
       </c>
       <c r="S20" s="1">
-        <v>4.4474363999999991</v>
+        <v>0.74123939999999988</v>
       </c>
       <c r="T20" s="1">
-        <v>2.4948329999999999</v>
+        <v>0.41580549999999999</v>
       </c>
       <c r="U20" s="1">
-        <v>5.0819603999999989</v>
+        <v>0.84699339999999979</v>
       </c>
       <c r="V20" s="1">
-        <v>2.9822628</v>
+        <v>0.49704379999999998</v>
       </c>
       <c r="W20" s="1">
-        <v>2.0968133999999994</v>
+        <v>0.34946889999999992</v>
       </c>
       <c r="X20" s="1">
-        <v>3.1841568000000007</v>
+        <v>0.53069280000000008</v>
       </c>
       <c r="Y20" s="1">
-        <v>1.9679857999999999</v>
+        <v>0.32799763333333332</v>
       </c>
       <c r="Z20" s="1">
-        <v>8.9823602000000005</v>
+        <v>1.4970600333333335</v>
       </c>
       <c r="AA20" s="1">
-        <v>10.828248199999999</v>
+        <v>1.8047080333333332</v>
       </c>
     </row>
     <row r="21" spans="1:27" x14ac:dyDescent="0.2">
@@ -75358,76 +75358,76 @@
         <v>1</v>
       </c>
       <c r="D21" s="1">
-        <v>-24.464484106920008</v>
+        <v>-4.0774140178200016</v>
       </c>
       <c r="E21" s="1">
-        <v>-28.923299076672002</v>
+        <v>-4.8205498461120007</v>
       </c>
       <c r="F21" s="1">
-        <v>-24.513756741407995</v>
+        <v>-4.0856261235679989</v>
       </c>
       <c r="G21" s="1">
-        <v>-31.118508667007994</v>
+        <v>-5.186418111167999</v>
       </c>
       <c r="H21" s="1">
-        <v>-39.388284139600287</v>
+        <v>-6.5647140232667143</v>
       </c>
       <c r="I21" s="1">
-        <v>-37.416530153533429</v>
+        <v>-6.2360883589222382</v>
       </c>
       <c r="J21" s="1">
-        <v>-35.348177189139825</v>
+        <v>-5.8913628648566378</v>
       </c>
       <c r="K21" s="1">
-        <v>-38.893730091884215</v>
+        <v>-6.4822883486473692</v>
       </c>
       <c r="L21" s="1">
-        <v>-41.387108630526271</v>
+        <v>-6.8978514384210454</v>
       </c>
       <c r="M21" s="1">
-        <v>-50.259605869054766</v>
+        <v>-8.3766009781757944</v>
       </c>
       <c r="N21" s="1">
-        <v>-57.22331536721547</v>
+        <v>-9.5372192278692456</v>
       </c>
       <c r="O21" s="1">
-        <v>-52.290785895141219</v>
+        <v>-8.7151309825235366</v>
       </c>
       <c r="P21" s="1">
-        <v>-48.660028368692089</v>
+        <v>-8.1100047281153476</v>
       </c>
       <c r="Q21" s="1">
-        <v>-46.397863751698146</v>
+        <v>-7.7329772919496911</v>
       </c>
       <c r="R21" s="1">
-        <v>-44.239578065259863</v>
+        <v>-7.3732630108766442</v>
       </c>
       <c r="S21" s="1">
-        <v>-38.31301667647999</v>
+        <v>-6.3855027794133319</v>
       </c>
       <c r="T21" s="1">
-        <v>-34.402639702406979</v>
+        <v>-5.7337732837344966</v>
       </c>
       <c r="U21" s="1">
-        <v>-33.035431325357258</v>
+        <v>-5.5059052208928767</v>
       </c>
       <c r="V21" s="1">
-        <v>-20.137145914483199</v>
+        <v>-3.3561909857471997</v>
       </c>
       <c r="W21" s="1">
-        <v>-23.972274635266224</v>
+        <v>-3.9953791058777042</v>
       </c>
       <c r="X21" s="1">
-        <v>-26.604333561693885</v>
+        <v>-4.4340555936156472</v>
       </c>
       <c r="Y21" s="1">
-        <v>-23.615789717693183</v>
+        <v>-3.9359649529488636</v>
       </c>
       <c r="Z21" s="1">
-        <v>-19.92577284220723</v>
+        <v>-3.3209621403678717</v>
       </c>
       <c r="AA21" s="1">
-        <v>-23.845405526691835</v>
+        <v>-3.9742342544486391</v>
       </c>
     </row>
     <row r="22" spans="1:27" x14ac:dyDescent="0.2">
@@ -75441,76 +75441,76 @@
         <v>1</v>
       </c>
       <c r="D22" s="1">
-        <v>19.411913381201323</v>
+        <v>3.2353188968668873</v>
       </c>
       <c r="E22" s="1">
-        <v>24.94423269491816</v>
+        <v>4.157372115819693</v>
       </c>
       <c r="F22" s="1">
-        <v>32.174627416468986</v>
+        <v>5.3624379027448308</v>
       </c>
       <c r="G22" s="1">
-        <v>28.319900749321302</v>
+        <v>4.7199834582202174</v>
       </c>
       <c r="H22" s="1">
-        <v>34.335578080171352</v>
+        <v>5.7225963466952257</v>
       </c>
       <c r="I22" s="1">
-        <v>33.616052529272928</v>
+        <v>5.6026754215454879</v>
       </c>
       <c r="J22" s="1">
-        <v>33.000929118863993</v>
+        <v>5.5001548531439992</v>
       </c>
       <c r="K22" s="1">
-        <v>39.544876791887035</v>
+        <v>6.5908127986478391</v>
       </c>
       <c r="L22" s="1">
-        <v>34.823203354324988</v>
+        <v>5.8038672257208317</v>
       </c>
       <c r="M22" s="1">
-        <v>44.421929117363042</v>
+        <v>7.4036548528938404</v>
       </c>
       <c r="N22" s="1">
-        <v>39.305594625977896</v>
+        <v>6.5509324376629827</v>
       </c>
       <c r="O22" s="1">
-        <v>37.461501011340808</v>
+        <v>6.2435835018901349</v>
       </c>
       <c r="P22" s="1">
-        <v>40.777799897382913</v>
+        <v>6.7962999828971524</v>
       </c>
       <c r="Q22" s="1">
-        <v>38.679618477723594</v>
+        <v>6.4466030796205986</v>
       </c>
       <c r="R22" s="1">
-        <v>34.072375119294769</v>
+        <v>5.6787291865491278</v>
       </c>
       <c r="S22" s="1">
-        <v>29.2393149641068</v>
+        <v>4.8732191606844664</v>
       </c>
       <c r="T22" s="1">
-        <v>32.281742320132018</v>
+        <v>5.38029038668867</v>
       </c>
       <c r="U22" s="1">
-        <v>26.358208367266233</v>
+        <v>4.3930347278777058</v>
       </c>
       <c r="V22" s="1">
-        <v>24.68688270200137</v>
+        <v>4.1144804503335619</v>
       </c>
       <c r="W22" s="1">
-        <v>25.559139981140483</v>
+        <v>4.2598566635234141</v>
       </c>
       <c r="X22" s="1">
-        <v>24.544455985310979</v>
+        <v>4.0907426642184967</v>
       </c>
       <c r="Y22" s="1">
-        <v>29.221890997478706</v>
+        <v>4.870315166246451</v>
       </c>
       <c r="Z22" s="1">
-        <v>20.201701599002874</v>
+        <v>3.3669502665004791</v>
       </c>
       <c r="AA22" s="1">
-        <v>21.881365162030086</v>
+        <v>3.646894193671681</v>
       </c>
     </row>
     <row r="23" spans="1:27" x14ac:dyDescent="0.2">
@@ -75524,76 +75524,76 @@
         <v>2</v>
       </c>
       <c r="D23" s="1">
-        <v>12.407395770000003</v>
+        <v>2.0678992950000006</v>
       </c>
       <c r="E23" s="1">
-        <v>12.821278469999999</v>
+        <v>2.1368797449999999</v>
       </c>
       <c r="F23" s="1">
-        <v>10.496642112</v>
+        <v>1.7494403519999999</v>
       </c>
       <c r="G23" s="1">
-        <v>10.052975239999999</v>
+        <v>1.6754958733333332</v>
       </c>
       <c r="H23" s="1">
-        <v>8.4061739519999996</v>
+        <v>1.4010289919999999</v>
       </c>
       <c r="I23" s="1">
-        <v>7.0625213120000012</v>
+        <v>1.1770868853333336</v>
       </c>
       <c r="J23" s="1">
-        <v>8.7250222619999995</v>
+        <v>1.4541703769999998</v>
       </c>
       <c r="K23" s="1">
-        <v>1.5458542880000001</v>
+        <v>0.25764238133333334</v>
       </c>
       <c r="L23" s="1">
-        <v>1.3190408</v>
+        <v>0.21984013333333333</v>
       </c>
       <c r="M23" s="1">
-        <v>1.9818395739999997</v>
+        <v>0.33030659566666659</v>
       </c>
       <c r="N23" s="1">
-        <v>1.2018269120000002</v>
+        <v>0.20030448533333337</v>
       </c>
       <c r="O23" s="1">
-        <v>1.5017837119999999</v>
+        <v>0.25029728533333334</v>
       </c>
       <c r="P23" s="1">
-        <v>2.2546175960000006</v>
+        <v>0.37576959933333343</v>
       </c>
       <c r="Q23" s="1">
-        <v>4.4083651040000005</v>
+        <v>0.73472751733333341</v>
       </c>
       <c r="R23" s="1">
-        <v>4.7485468799999992</v>
+        <v>0.79142447999999987</v>
       </c>
       <c r="S23" s="1">
-        <v>4.2250645799999997</v>
+        <v>0.70417742999999999</v>
       </c>
       <c r="T23" s="1">
-        <v>2.5696779900000002</v>
+        <v>0.42827966500000003</v>
       </c>
       <c r="U23" s="1">
-        <v>5.2852388159999988</v>
+        <v>0.88087313599999983</v>
       </c>
       <c r="V23" s="1">
-        <v>2.9226175440000004</v>
+        <v>0.48710292400000005</v>
       </c>
       <c r="W23" s="1">
-        <v>2.0758452659999995</v>
+        <v>0.34597421099999992</v>
       </c>
       <c r="X23" s="1">
-        <v>3.1841568000000007</v>
+        <v>0.53069280000000008</v>
       </c>
       <c r="Y23" s="1">
-        <v>2.0270253739999999</v>
+        <v>0.33783756233333334</v>
       </c>
       <c r="Z23" s="1">
-        <v>9.4314782100000016</v>
+        <v>1.5719130350000003</v>
       </c>
       <c r="AA23" s="1">
-        <v>11.044813164000001</v>
+        <v>1.8408021940000001</v>
       </c>
     </row>
     <row r="24" spans="1:27" x14ac:dyDescent="0.2">
@@ -75607,76 +75607,76 @@
         <v>2</v>
       </c>
       <c r="D24" s="1">
-        <v>-24.70912894798921</v>
+        <v>-4.118188157998202</v>
       </c>
       <c r="E24" s="1">
-        <v>-29.790998048972163</v>
+        <v>-4.9651663414953608</v>
       </c>
       <c r="F24" s="1">
-        <v>-24.023481606579836</v>
+        <v>-4.003913601096639</v>
       </c>
       <c r="G24" s="1">
-        <v>-30.496138493667832</v>
+        <v>-5.082689748944639</v>
       </c>
       <c r="H24" s="1">
-        <v>-39.782166980996294</v>
+        <v>-6.6303611634993826</v>
       </c>
       <c r="I24" s="1">
-        <v>-36.294034248927424</v>
+        <v>-6.0490057081545707</v>
       </c>
       <c r="J24" s="1">
-        <v>-34.641213645357034</v>
+        <v>-5.7735356075595057</v>
       </c>
       <c r="K24" s="1">
-        <v>-39.671604693721896</v>
+        <v>-6.6119341156203157</v>
       </c>
       <c r="L24" s="1">
-        <v>-43.042592975747326</v>
+        <v>-7.1737654959578876</v>
       </c>
       <c r="M24" s="1">
-        <v>-51.767394045126409</v>
+        <v>-8.6278990075210675</v>
       </c>
       <c r="N24" s="1">
-        <v>-54.934382752526858</v>
+        <v>-9.1557304587544763</v>
       </c>
       <c r="O24" s="1">
-        <v>-53.859509471995459</v>
+        <v>-8.9765849119992431</v>
       </c>
       <c r="P24" s="1">
-        <v>-47.200227517631333</v>
+        <v>-7.8667045862718892</v>
       </c>
       <c r="Q24" s="1">
-        <v>-45.469906476664185</v>
+        <v>-7.5783177461106979</v>
       </c>
       <c r="R24" s="1">
-        <v>-44.239578065259863</v>
+        <v>-7.3732630108766442</v>
       </c>
       <c r="S24" s="1">
-        <v>-36.780496009420787</v>
+        <v>-6.1300826682367981</v>
       </c>
       <c r="T24" s="1">
-        <v>-34.746666099431046</v>
+        <v>-5.7911110165718407</v>
       </c>
       <c r="U24" s="1">
-        <v>-31.383659759089397</v>
+        <v>-5.2306099598482332</v>
       </c>
       <c r="V24" s="1">
-        <v>-19.331660077903873</v>
+        <v>-3.2219433463173122</v>
       </c>
       <c r="W24" s="1">
-        <v>-23.972274635266224</v>
+        <v>-3.9953791058777042</v>
       </c>
       <c r="X24" s="1">
-        <v>-27.668506904161639</v>
+        <v>-4.6114178173602731</v>
       </c>
       <c r="Y24" s="1">
-        <v>-22.907316026162384</v>
+        <v>-3.8178860043603975</v>
       </c>
       <c r="Z24" s="1">
-        <v>-20.324288299051378</v>
+        <v>-3.3873813831752297</v>
       </c>
       <c r="AA24" s="1">
-        <v>-23.606951471424917</v>
+        <v>-3.934491911904153</v>
       </c>
     </row>
     <row r="25" spans="1:27" x14ac:dyDescent="0.2">
@@ -75690,76 +75690,76 @@
         <v>2</v>
       </c>
       <c r="D25" s="1">
-        <v>19.21779424738931</v>
+        <v>3.2029657078982186</v>
       </c>
       <c r="E25" s="1">
-        <v>24.94423269491816</v>
+        <v>4.157372115819693</v>
       </c>
       <c r="F25" s="1">
-        <v>30.565896045645538</v>
+        <v>5.0943160076075893</v>
       </c>
       <c r="G25" s="1">
-        <v>28.886298764307732</v>
+        <v>4.8143831273846223</v>
       </c>
       <c r="H25" s="1">
-        <v>35.022289641774783</v>
+        <v>5.8370482736291303</v>
       </c>
       <c r="I25" s="1">
-        <v>34.624534105151113</v>
+        <v>5.7707556841918519</v>
       </c>
       <c r="J25" s="1">
-        <v>33.330938410052632</v>
+        <v>5.5551564016754389</v>
       </c>
       <c r="K25" s="1">
-        <v>39.544876791887035</v>
+        <v>6.5908127986478391</v>
       </c>
       <c r="L25" s="1">
-        <v>33.082043186608736</v>
+        <v>5.5136738644347894</v>
       </c>
       <c r="M25" s="1">
-        <v>46.198806282057561</v>
+        <v>7.6998010470095934</v>
       </c>
       <c r="N25" s="1">
-        <v>40.484762464757239</v>
+        <v>6.7474604107928728</v>
       </c>
       <c r="O25" s="1">
-        <v>37.836116021454217</v>
+        <v>6.3060193369090358</v>
       </c>
       <c r="P25" s="1">
-        <v>40.777799897382913</v>
+        <v>6.7962999828971524</v>
       </c>
       <c r="Q25" s="1">
-        <v>38.292822292946362</v>
+        <v>6.3821370488243936</v>
       </c>
       <c r="R25" s="1">
-        <v>32.368756363330029</v>
+        <v>5.3947927272216711</v>
       </c>
       <c r="S25" s="1">
-        <v>27.777349215901456</v>
+        <v>4.6295582026502426</v>
       </c>
       <c r="T25" s="1">
-        <v>31.313290050528057</v>
+        <v>5.2188816750880092</v>
       </c>
       <c r="U25" s="1">
-        <v>25.83104419992091</v>
+        <v>4.305174033320152</v>
       </c>
       <c r="V25" s="1">
-        <v>24.68688270200137</v>
+        <v>4.1144804503335619</v>
       </c>
       <c r="W25" s="1">
-        <v>26.325914180574699</v>
+        <v>4.3876523634291162</v>
       </c>
       <c r="X25" s="1">
-        <v>23.317233186045428</v>
+        <v>3.8862055310075712</v>
       </c>
       <c r="Y25" s="1">
-        <v>30.68298554735264</v>
+        <v>5.1138309245587736</v>
       </c>
       <c r="Z25" s="1">
-        <v>19.797667567022817</v>
+        <v>3.2996112611704693</v>
       </c>
       <c r="AA25" s="1">
-        <v>22.537806116890987</v>
+        <v>3.7563010194818314</v>
       </c>
     </row>
     <row r="26" spans="1:27" x14ac:dyDescent="0.2">
@@ -75773,76 +75773,76 @@
         <v>3</v>
       </c>
       <c r="D26" s="1">
-        <v>12.779617643100003</v>
+        <v>2.1299362738500007</v>
       </c>
       <c r="E26" s="1">
-        <v>12.9494912547</v>
+        <v>2.15824854245</v>
       </c>
       <c r="F26" s="1">
-        <v>10.391675690880001</v>
+        <v>1.7319459484800002</v>
       </c>
       <c r="G26" s="1">
-        <v>10.555624001999998</v>
+        <v>1.7592706669999998</v>
       </c>
       <c r="H26" s="1">
-        <v>8.4902356915200006</v>
+        <v>1.4150392819200002</v>
       </c>
       <c r="I26" s="1">
-        <v>7.0625213120000012</v>
+        <v>1.1770868853333336</v>
       </c>
       <c r="J26" s="1">
-        <v>8.2887711488999987</v>
+        <v>1.3814618581499998</v>
       </c>
       <c r="K26" s="1">
-        <v>1.4685615736000002</v>
+        <v>0.24476026226666669</v>
       </c>
       <c r="L26" s="1">
-        <v>1.25308876</v>
+        <v>0.20884812666666666</v>
       </c>
       <c r="M26" s="1">
-        <v>1.9223843867799997</v>
+        <v>0.32039739779666659</v>
       </c>
       <c r="N26" s="1">
-        <v>1.1898086428800001</v>
+        <v>0.19830144048000001</v>
       </c>
       <c r="O26" s="1">
-        <v>1.5318193862399998</v>
+        <v>0.25530323103999997</v>
       </c>
       <c r="P26" s="1">
-        <v>2.2095252440800004</v>
+        <v>0.36825420734666675</v>
       </c>
       <c r="Q26" s="1">
-        <v>4.6287833592000007</v>
+        <v>0.77146389320000008</v>
       </c>
       <c r="R26" s="1">
-        <v>4.9859742239999996</v>
+        <v>0.83099570399999989</v>
       </c>
       <c r="S26" s="1">
-        <v>4.4363178089999993</v>
+        <v>0.73938630149999984</v>
       </c>
       <c r="T26" s="1">
-        <v>2.5953747699000003</v>
+        <v>0.43256246165000006</v>
       </c>
       <c r="U26" s="1">
-        <v>5.2852388159999988</v>
+        <v>0.88087313599999983</v>
       </c>
       <c r="V26" s="1">
-        <v>2.9226175440000004</v>
+        <v>0.48710292400000005</v>
       </c>
       <c r="W26" s="1">
-        <v>1.9928114553599996</v>
+        <v>0.33213524255999993</v>
       </c>
       <c r="X26" s="1">
-        <v>3.0886320960000004</v>
+        <v>0.51477201600000011</v>
       </c>
       <c r="Y26" s="1">
-        <v>2.0472956277400001</v>
+        <v>0.34121593795666666</v>
       </c>
       <c r="Z26" s="1">
-        <v>9.1485338637000009</v>
+        <v>1.5247556439500001</v>
       </c>
       <c r="AA26" s="1">
-        <v>11.376157558919999</v>
+        <v>1.8960262598199999</v>
       </c>
     </row>
     <row r="27" spans="1:27" x14ac:dyDescent="0.2">
@@ -75856,76 +75856,76 @@
         <v>3</v>
       </c>
       <c r="D27" s="1">
-        <v>-25.944585395388671</v>
+        <v>-4.3240975658981116</v>
       </c>
       <c r="E27" s="1">
-        <v>-29.493088068482443</v>
+        <v>-4.9155146780804069</v>
       </c>
       <c r="F27" s="1">
-        <v>-23.783246790514038</v>
+        <v>-3.9638744650856732</v>
       </c>
       <c r="G27" s="1">
-        <v>-29.581254338857796</v>
+        <v>-4.9302090564762997</v>
       </c>
       <c r="H27" s="1">
-        <v>-39.384345311186337</v>
+        <v>-6.5640575518643898</v>
       </c>
       <c r="I27" s="1">
-        <v>-37.382855276395254</v>
+        <v>-6.2304758793992088</v>
       </c>
       <c r="J27" s="1">
-        <v>-32.909152963089177</v>
+        <v>-5.4848588271815295</v>
       </c>
       <c r="K27" s="1">
-        <v>-39.274888646784682</v>
+        <v>-6.5458147744641133</v>
       </c>
       <c r="L27" s="1">
-        <v>-41.751315186474905</v>
+        <v>-6.9585525310791505</v>
       </c>
       <c r="M27" s="1">
-        <v>-53.320415866480204</v>
+        <v>-8.8867359777467012</v>
       </c>
       <c r="N27" s="1">
-        <v>-54.934382752526858</v>
+        <v>-9.1557304587544763</v>
       </c>
       <c r="O27" s="1">
-        <v>-53.859509471995459</v>
+        <v>-8.9765849119992431</v>
       </c>
       <c r="P27" s="1">
-        <v>-46.25622296727871</v>
+        <v>-7.7093704945464516</v>
       </c>
       <c r="Q27" s="1">
-        <v>-45.469906476664185</v>
+        <v>-7.5783177461106979</v>
       </c>
       <c r="R27" s="1">
-        <v>-45.124369626565063</v>
+        <v>-7.5207282710941774</v>
       </c>
       <c r="S27" s="1">
-        <v>-37.516105929609203</v>
+        <v>-6.2526843216015342</v>
       </c>
       <c r="T27" s="1">
-        <v>-35.789066082413981</v>
+        <v>-5.9648443470689969</v>
       </c>
       <c r="U27" s="1">
-        <v>-31.383659759089397</v>
+        <v>-5.2306099598482332</v>
       </c>
       <c r="V27" s="1">
-        <v>-19.718293279461953</v>
+        <v>-3.2863822132436589</v>
       </c>
       <c r="W27" s="1">
-        <v>-24.931165620676875</v>
+        <v>-4.1551942701128128</v>
       </c>
       <c r="X27" s="1">
-        <v>-26.838451697036792</v>
+        <v>-4.4730752828394653</v>
       </c>
       <c r="Y27" s="1">
-        <v>-23.136389186424005</v>
+        <v>-3.8560648644040008</v>
       </c>
       <c r="Z27" s="1">
-        <v>-19.30807388409881</v>
+        <v>-3.2180123140164683</v>
       </c>
       <c r="AA27" s="1">
-        <v>-24.079090500853418</v>
+        <v>-4.0131817501422367</v>
       </c>
     </row>
     <row r="28" spans="1:27" x14ac:dyDescent="0.2">
@@ -75939,76 +75939,76 @@
         <v>3</v>
       </c>
       <c r="D28" s="1">
-        <v>18.641260419967633</v>
+        <v>3.1068767366612722</v>
       </c>
       <c r="E28" s="1">
-        <v>24.195905714070619</v>
+        <v>4.0326509523451035</v>
       </c>
       <c r="F28" s="1">
-        <v>30.565896045645538</v>
+        <v>5.0943160076075893</v>
       </c>
       <c r="G28" s="1">
-        <v>29.75288772723696</v>
+        <v>4.9588146212061597</v>
       </c>
       <c r="H28" s="1">
-        <v>36.773404123863521</v>
+        <v>6.1289006873105869</v>
       </c>
       <c r="I28" s="1">
-        <v>34.278288764099599</v>
+        <v>5.7130481273499329</v>
       </c>
       <c r="J28" s="1">
-        <v>34.997485330555264</v>
+        <v>5.8329142217592107</v>
       </c>
       <c r="K28" s="1">
-        <v>38.753979256049298</v>
+        <v>6.4589965426748828</v>
       </c>
       <c r="L28" s="1">
-        <v>32.751222754742649</v>
+        <v>5.4585371257904418</v>
       </c>
       <c r="M28" s="1">
-        <v>48.508746596160449</v>
+        <v>8.0847910993600749</v>
       </c>
       <c r="N28" s="1">
-        <v>42.104152963347531</v>
+        <v>7.0173588272245881</v>
       </c>
       <c r="O28" s="1">
-        <v>36.701032540810594</v>
+        <v>6.1168387568017657</v>
       </c>
       <c r="P28" s="1">
-        <v>40.777799897382913</v>
+        <v>6.7962999828971524</v>
       </c>
       <c r="Q28" s="1">
-        <v>39.824535184664207</v>
+        <v>6.6374225307773678</v>
       </c>
       <c r="R28" s="1">
-        <v>32.368756363330029</v>
+        <v>5.3947927272216711</v>
       </c>
       <c r="S28" s="1">
-        <v>27.221802231583425</v>
+        <v>4.5369670385972372</v>
       </c>
       <c r="T28" s="1">
-        <v>30.373891349012215</v>
+        <v>5.0623152248353689</v>
       </c>
       <c r="U28" s="1">
-        <v>27.122596409916955</v>
+        <v>4.5204327349861595</v>
       </c>
       <c r="V28" s="1">
-        <v>24.68688270200137</v>
+        <v>4.1144804503335619</v>
       </c>
       <c r="W28" s="1">
-        <v>26.062655038768952</v>
+        <v>4.3437758397948256</v>
       </c>
       <c r="X28" s="1">
-        <v>24.249922513487242</v>
+        <v>4.0416537522478739</v>
       </c>
       <c r="Y28" s="1">
-        <v>29.762495980932062</v>
+        <v>4.9604159968220101</v>
       </c>
       <c r="Z28" s="1">
-        <v>20.391597594033499</v>
+        <v>3.3985995990055833</v>
       </c>
       <c r="AA28" s="1">
-        <v>21.861671933384258</v>
+        <v>3.6436119888973764</v>
       </c>
     </row>
     <row r="29" spans="1:27" x14ac:dyDescent="0.2">
@@ -76022,76 +76022,76 @@
         <v>1</v>
       </c>
       <c r="D29" s="1">
-        <v>11.225739030000002</v>
+        <v>1.8709565050000003</v>
       </c>
       <c r="E29" s="1">
-        <v>11.60020433</v>
+        <v>1.9333673883333333</v>
       </c>
       <c r="F29" s="1">
-        <v>10.38730209</v>
+        <v>1.7312170150000001</v>
       </c>
       <c r="G29" s="1">
-        <v>9.8456973999999988</v>
+        <v>1.6409495666666665</v>
       </c>
       <c r="H29" s="1">
-        <v>8.0665305600000003</v>
+        <v>1.3444217600000001</v>
       </c>
       <c r="I29" s="1">
-        <v>6.84632168</v>
+        <v>1.1410536133333333</v>
       </c>
       <c r="J29" s="1">
-        <v>8.3724961100000002</v>
+        <v>1.3954160183333333</v>
       </c>
       <c r="K29" s="1">
-        <v>1.4540213600000003</v>
+        <v>0.24233689333333339</v>
       </c>
       <c r="L29" s="1">
-        <v>1.278662</v>
+        <v>0.21311033333333332</v>
       </c>
       <c r="M29" s="1">
-        <v>1.8641065299999995</v>
+        <v>0.3106844216666666</v>
       </c>
       <c r="N29" s="1">
-        <v>1.0978226600000001</v>
+        <v>0.18297044333333334</v>
       </c>
       <c r="O29" s="1">
-        <v>1.3718216599999995</v>
+        <v>0.22863694333333326</v>
       </c>
       <c r="P29" s="1">
-        <v>2.1855986900000004</v>
+        <v>0.36426644833333338</v>
       </c>
       <c r="Q29" s="1">
-        <v>4.0268719700000002</v>
+        <v>0.6711453283333334</v>
       </c>
       <c r="R29" s="1">
-        <v>4.29630432</v>
+        <v>0.71605072000000003</v>
       </c>
       <c r="S29" s="1">
-        <v>4.2250645799999988</v>
+        <v>0.70417742999999977</v>
       </c>
       <c r="T29" s="1">
-        <v>2.3700913499999996</v>
+        <v>0.39501522499999991</v>
       </c>
       <c r="U29" s="1">
-        <v>4.8278623799999991</v>
+        <v>0.80464372999999989</v>
       </c>
       <c r="V29" s="1">
-        <v>2.8331496599999997</v>
+        <v>0.47219160999999993</v>
       </c>
       <c r="W29" s="1">
-        <v>1.9919727299999996</v>
+        <v>0.33199545499999994</v>
       </c>
       <c r="X29" s="1">
-        <v>3.0249489600000001</v>
+        <v>0.50415816000000002</v>
       </c>
       <c r="Y29" s="1">
-        <v>1.8695865099999998</v>
+        <v>0.31159775166666664</v>
       </c>
       <c r="Z29" s="1">
-        <v>8.5332421900000011</v>
+        <v>1.4222070316666668</v>
       </c>
       <c r="AA29" s="1">
-        <v>10.28683579</v>
+        <v>1.7144726316666665</v>
       </c>
     </row>
     <row r="30" spans="1:27" x14ac:dyDescent="0.2">
@@ -76105,76 +76105,76 @@
         <v>1</v>
       </c>
       <c r="D30" s="1">
-        <v>-25.685139541434783</v>
+        <v>-4.2808565902391305</v>
       </c>
       <c r="E30" s="1">
-        <v>-29.493088068482443</v>
+        <v>-4.9155146780804069</v>
       </c>
       <c r="F30" s="1">
-        <v>-23.06974938679862</v>
+        <v>-3.8449582311331034</v>
       </c>
       <c r="G30" s="1">
-        <v>-30.76450451241211</v>
+        <v>-5.1274174187353516</v>
       </c>
       <c r="H30" s="1">
-        <v>-40.959719123633796</v>
+        <v>-6.8266198539389658</v>
       </c>
       <c r="I30" s="1">
-        <v>-38.878169487451061</v>
+        <v>-6.4796949145751768</v>
       </c>
       <c r="J30" s="1">
-        <v>-34.554610611243632</v>
+        <v>-5.7591017685406056</v>
       </c>
       <c r="K30" s="1">
-        <v>-40.845884192656072</v>
+        <v>-6.807647365442679</v>
       </c>
       <c r="L30" s="1">
-        <v>-43.003854642069157</v>
+        <v>-7.1673091070115262</v>
       </c>
       <c r="M30" s="1">
-        <v>-54.386824183809807</v>
+        <v>-9.0644706973016351</v>
       </c>
       <c r="N30" s="1">
-        <v>-55.483726580052121</v>
+        <v>-9.2472877633420207</v>
       </c>
       <c r="O30" s="1">
-        <v>-54.398104566715411</v>
+        <v>-9.0663507611192351</v>
       </c>
       <c r="P30" s="1">
-        <v>-44.405974048587559</v>
+        <v>-7.4009956747645935</v>
       </c>
       <c r="Q30" s="1">
-        <v>-43.651110217597619</v>
+        <v>-7.2751850362662696</v>
       </c>
       <c r="R30" s="1">
-        <v>-46.026857019096362</v>
+        <v>-7.6711428365160605</v>
       </c>
       <c r="S30" s="1">
-        <v>-37.891266988905301</v>
+        <v>-6.3152111648175504</v>
       </c>
       <c r="T30" s="1">
-        <v>-36.146956743238121</v>
+        <v>-6.0244927905396866</v>
       </c>
       <c r="U30" s="1">
-        <v>-32.325169551862075</v>
+        <v>-5.3875282586436795</v>
       </c>
       <c r="V30" s="1">
-        <v>-18.732378615488852</v>
+        <v>-3.1220631025814751</v>
       </c>
       <c r="W30" s="1">
-        <v>-25.180477276883643</v>
+        <v>-4.1967462128139408</v>
       </c>
       <c r="X30" s="1">
-        <v>-25.76491362915532</v>
+        <v>-4.2941522715258866</v>
       </c>
       <c r="Y30" s="1">
-        <v>-23.830480862016724</v>
+        <v>-3.9717468103361209</v>
       </c>
       <c r="Z30" s="1">
-        <v>-19.694235361780787</v>
+        <v>-3.2823725602967979</v>
       </c>
       <c r="AA30" s="1">
-        <v>-25.28304502589609</v>
+        <v>-4.2138408376493484</v>
       </c>
     </row>
     <row r="31" spans="1:27" x14ac:dyDescent="0.2">
@@ -76188,76 +76188,76 @@
         <v>1</v>
       </c>
       <c r="D31" s="1">
-        <v>19.386910836766337</v>
+        <v>3.2311518061277229</v>
       </c>
       <c r="E31" s="1">
-        <v>24.437864771211324</v>
+        <v>4.0729774618685539</v>
       </c>
       <c r="F31" s="1">
-        <v>31.788531887471358</v>
+        <v>5.2980886479118929</v>
       </c>
       <c r="G31" s="1">
-        <v>30.347945481781696</v>
+        <v>5.0579909136302827</v>
       </c>
       <c r="H31" s="1">
-        <v>37.876606247579424</v>
+        <v>6.312767707929904</v>
       </c>
       <c r="I31" s="1">
-        <v>33.592722988817613</v>
+        <v>5.5987871648029355</v>
       </c>
       <c r="J31" s="1">
-        <v>33.247611064027495</v>
+        <v>5.5412685106712489</v>
       </c>
       <c r="K31" s="1">
-        <v>38.753979256049298</v>
+        <v>6.4589965426748828</v>
       </c>
       <c r="L31" s="1">
-        <v>33.40624720983751</v>
+        <v>5.5677078683062513</v>
       </c>
       <c r="M31" s="1">
-        <v>50.934183925968462</v>
+        <v>8.4890306543280776</v>
       </c>
       <c r="N31" s="1">
-        <v>41.262069904080583</v>
+        <v>6.8770116506800969</v>
       </c>
       <c r="O31" s="1">
-        <v>36.701032540810594</v>
+        <v>6.1168387568017657</v>
       </c>
       <c r="P31" s="1">
-        <v>42.408911893278223</v>
+        <v>7.0681519822130374</v>
       </c>
       <c r="Q31" s="1">
-        <v>37.833308425430992</v>
+        <v>6.305551404238499</v>
       </c>
       <c r="R31" s="1">
-        <v>32.368756363330029</v>
+        <v>5.3947927272216711</v>
       </c>
       <c r="S31" s="1">
-        <v>28.582892343162595</v>
+        <v>4.7638153905270988</v>
       </c>
       <c r="T31" s="1">
-        <v>30.070152435522093</v>
+        <v>5.0116920725870155</v>
       </c>
       <c r="U31" s="1">
-        <v>26.580144481718616</v>
+        <v>4.4300240802864357</v>
       </c>
       <c r="V31" s="1">
-        <v>25.180620356041402</v>
+        <v>4.1967700593402339</v>
       </c>
       <c r="W31" s="1">
-        <v>26.844534689932015</v>
+        <v>4.4740891149886695</v>
       </c>
       <c r="X31" s="1">
-        <v>24.734920963756991</v>
+        <v>4.1224868272928319</v>
       </c>
       <c r="Y31" s="1">
-        <v>28.869621101504098</v>
+        <v>4.8116035169173497</v>
       </c>
       <c r="Z31" s="1">
-        <v>20.595513569973836</v>
+        <v>3.4325855949956394</v>
       </c>
       <c r="AA31" s="1">
-        <v>22.080288652718099</v>
+        <v>3.6800481087863499</v>
       </c>
     </row>
     <row r="32" spans="1:27" x14ac:dyDescent="0.2">
@@ -76271,76 +76271,76 @@
         <v>2</v>
       </c>
       <c r="D32" s="1">
-        <v>11.113481639700002</v>
+        <v>1.8522469399500003</v>
       </c>
       <c r="E32" s="1">
-        <v>12.180214546500002</v>
+        <v>2.0300357577500003</v>
       </c>
       <c r="F32" s="1">
-        <v>10.38730209</v>
+        <v>1.7312170150000001</v>
       </c>
       <c r="G32" s="1">
-        <v>9.3534125299999982</v>
+        <v>1.5589020883333331</v>
       </c>
       <c r="H32" s="1">
-        <v>7.9858652544000011</v>
+        <v>1.3309775424000001</v>
       </c>
       <c r="I32" s="1">
-        <v>6.5040055960000007</v>
+        <v>1.0840009326666669</v>
       </c>
       <c r="J32" s="1">
-        <v>8.0375962655999995</v>
+        <v>1.3395993775999999</v>
       </c>
       <c r="K32" s="1">
-        <v>1.4976420008000004</v>
+        <v>0.2496070001333334</v>
       </c>
       <c r="L32" s="1">
-        <v>1.278662</v>
+        <v>0.21311033333333332</v>
       </c>
       <c r="M32" s="1">
-        <v>1.8268243993999995</v>
+        <v>0.30447073323333324</v>
       </c>
       <c r="N32" s="1">
-        <v>1.0868444334</v>
+        <v>0.18114073890000001</v>
       </c>
       <c r="O32" s="1">
-        <v>1.3855398765999996</v>
+        <v>0.23092331276666658</v>
       </c>
       <c r="P32" s="1">
-        <v>2.1637427031000005</v>
+        <v>0.3606237838500001</v>
       </c>
       <c r="Q32" s="1">
-        <v>3.9866032502999995</v>
+        <v>0.66443387504999996</v>
       </c>
       <c r="R32" s="1">
-        <v>4.3392673631999994</v>
+        <v>0.72321122719999986</v>
       </c>
       <c r="S32" s="1">
-        <v>4.0560619967999996</v>
+        <v>0.67601033279999989</v>
       </c>
       <c r="T32" s="1">
-        <v>2.3700913499999996</v>
+        <v>0.39501522499999991</v>
       </c>
       <c r="U32" s="1">
-        <v>5.0692554989999987</v>
+        <v>0.84487591649999982</v>
       </c>
       <c r="V32" s="1">
-        <v>2.7198236736000001</v>
+        <v>0.45330394560000004</v>
       </c>
       <c r="W32" s="1">
-        <v>2.0318121845999992</v>
+        <v>0.33863536409999989</v>
       </c>
       <c r="X32" s="1">
-        <v>2.9039510016000003</v>
+        <v>0.48399183360000003</v>
       </c>
       <c r="Y32" s="1">
-        <v>1.7948030495999998</v>
+        <v>0.29913384159999995</v>
       </c>
       <c r="Z32" s="1">
-        <v>8.4479097681000006</v>
+        <v>1.4079849613500002</v>
       </c>
       <c r="AA32" s="1">
-        <v>10.28683579</v>
+        <v>1.7144726316666665</v>
       </c>
     </row>
     <row r="33" spans="1:27" x14ac:dyDescent="0.2">
@@ -76354,76 +76354,76 @@
         <v>2</v>
       </c>
       <c r="D33" s="1">
-        <v>-25.171436750606084</v>
+        <v>-4.1952394584343473</v>
       </c>
       <c r="E33" s="1">
-        <v>-28.903226307112796</v>
+        <v>-4.8172043845187993</v>
       </c>
       <c r="F33" s="1">
-        <v>-22.608354399062645</v>
+        <v>-3.7680590665104408</v>
       </c>
       <c r="G33" s="1">
-        <v>-29.84156937703974</v>
+        <v>-4.9735948961732896</v>
       </c>
       <c r="H33" s="1">
-        <v>-43.00770507981548</v>
+        <v>-7.1679508466359136</v>
       </c>
       <c r="I33" s="1">
-        <v>-37.711824402827531</v>
+        <v>-6.2853040671379219</v>
       </c>
       <c r="J33" s="1">
-        <v>-35.245702823468505</v>
+        <v>-5.8742838039114176</v>
       </c>
       <c r="K33" s="1">
-        <v>-40.437425350729512</v>
+        <v>-6.7395708917882517</v>
       </c>
       <c r="L33" s="1">
-        <v>-41.713739002807081</v>
+        <v>-6.9522898338011805</v>
       </c>
       <c r="M33" s="1">
-        <v>-52.755219458295514</v>
+        <v>-8.7925365763825862</v>
       </c>
       <c r="N33" s="1">
-        <v>-52.709540251049511</v>
+        <v>-8.7849233751749178</v>
       </c>
       <c r="O33" s="1">
-        <v>-57.118009795051186</v>
+        <v>-9.5196682991751977</v>
       </c>
       <c r="P33" s="1">
-        <v>-45.738153270045188</v>
+        <v>-7.6230255450075317</v>
       </c>
       <c r="Q33" s="1">
-        <v>-44.524132421949567</v>
+        <v>-7.4206887369915941</v>
       </c>
       <c r="R33" s="1">
-        <v>-47.867931299860224</v>
+        <v>-7.977988549976704</v>
       </c>
       <c r="S33" s="1">
-        <v>-39.40691766846151</v>
+        <v>-6.5678196114102514</v>
       </c>
       <c r="T33" s="1">
-        <v>-35.785487175805741</v>
+        <v>-5.9642478626342905</v>
       </c>
       <c r="U33" s="1">
-        <v>-32.001917856343461</v>
+        <v>-5.3336529760572438</v>
       </c>
       <c r="V33" s="1">
-        <v>-18.91970240164374</v>
+        <v>-3.1532837336072901</v>
       </c>
       <c r="W33" s="1">
-        <v>-25.180477276883643</v>
+        <v>-4.1967462128139408</v>
       </c>
       <c r="X33" s="1">
-        <v>-26.280211901738426</v>
+        <v>-4.3800353169564046</v>
       </c>
       <c r="Y33" s="1">
-        <v>-25.022004905117562</v>
+        <v>-4.170334150852927</v>
       </c>
       <c r="Z33" s="1">
-        <v>-20.678947129869826</v>
+        <v>-3.4464911883116378</v>
       </c>
       <c r="AA33" s="1">
-        <v>-24.271723224860249</v>
+        <v>-4.0452872041433752</v>
       </c>
     </row>
     <row r="34" spans="1:27" x14ac:dyDescent="0.2">
@@ -76437,76 +76437,76 @@
         <v>2</v>
       </c>
       <c r="D34" s="1">
-        <v>18.417565294928021</v>
+        <v>3.0695942158213367</v>
       </c>
       <c r="E34" s="1">
-        <v>25.171000714347663</v>
+        <v>4.1951667857246102</v>
       </c>
       <c r="F34" s="1">
-        <v>30.199105293097791</v>
+        <v>5.0331842155162985</v>
       </c>
       <c r="G34" s="1">
-        <v>29.134027662510434</v>
+        <v>4.8556712770850723</v>
       </c>
       <c r="H34" s="1">
-        <v>35.982775935200458</v>
+        <v>5.9971293225334099</v>
       </c>
       <c r="I34" s="1">
-        <v>34.600504678482139</v>
+        <v>5.7667507797470234</v>
       </c>
       <c r="J34" s="1">
-        <v>31.917706621466394</v>
+        <v>5.319617770244399</v>
       </c>
       <c r="K34" s="1">
-        <v>36.816280293246834</v>
+        <v>6.1360467155411387</v>
       </c>
       <c r="L34" s="1">
-        <v>34.742497098231006</v>
+        <v>5.7904161830385013</v>
       </c>
       <c r="M34" s="1">
-        <v>48.387474729670039</v>
+        <v>8.0645791216116738</v>
       </c>
       <c r="N34" s="1">
-        <v>39.198966408876551</v>
+        <v>6.5331610681460921</v>
       </c>
       <c r="O34" s="1">
-        <v>38.536084167851122</v>
+        <v>6.422680694641854</v>
       </c>
       <c r="P34" s="1">
-        <v>43.257090131143784</v>
+        <v>7.209515021857297</v>
       </c>
       <c r="Q34" s="1">
-        <v>38.589974593939615</v>
+        <v>6.431662432323269</v>
       </c>
       <c r="R34" s="1">
-        <v>33.016131490596635</v>
+        <v>5.5026885817661055</v>
       </c>
       <c r="S34" s="1">
-        <v>28.582892343162595</v>
+        <v>4.7638153905270988</v>
       </c>
       <c r="T34" s="1">
-        <v>30.370853959877312</v>
+        <v>5.0618089933128854</v>
       </c>
       <c r="U34" s="1">
-        <v>25.782740147267059</v>
+        <v>4.2971233578778429</v>
       </c>
       <c r="V34" s="1">
-        <v>25.936038966722641</v>
+        <v>4.3226731611204405</v>
       </c>
       <c r="W34" s="1">
-        <v>27.381425383730658</v>
+        <v>4.563570897288443</v>
       </c>
       <c r="X34" s="1">
-        <v>23.498174915569141</v>
+        <v>3.91636248592819</v>
       </c>
       <c r="Y34" s="1">
-        <v>28.580924890489058</v>
+        <v>4.763487481748176</v>
       </c>
       <c r="Z34" s="1">
-        <v>19.565737891475145</v>
+        <v>3.2609563152458576</v>
       </c>
       <c r="AA34" s="1">
-        <v>22.74269731229964</v>
+        <v>3.7904495520499402</v>
       </c>
     </row>
     <row r="35" spans="1:27" x14ac:dyDescent="0.2">
@@ -76520,76 +76520,76 @@
         <v>3</v>
       </c>
       <c r="D35" s="1">
-        <v>11.113481639700002</v>
+        <v>1.8522469399500003</v>
       </c>
       <c r="E35" s="1">
-        <v>12.667423128360003</v>
+        <v>2.1112371880600005</v>
       </c>
       <c r="F35" s="1">
-        <v>10.38730209</v>
+        <v>1.7312170150000001</v>
       </c>
       <c r="G35" s="1">
-        <v>9.1663442793999987</v>
+        <v>1.5277240465666664</v>
       </c>
       <c r="H35" s="1">
-        <v>7.5865719916800014</v>
+        <v>1.2644286652800003</v>
       </c>
       <c r="I35" s="1">
-        <v>6.3739254840800008</v>
+        <v>1.0623209140133334</v>
       </c>
       <c r="J35" s="1">
-        <v>7.6357164523199996</v>
+        <v>1.27261940872</v>
       </c>
       <c r="K35" s="1">
-        <v>1.4676891607840006</v>
+        <v>0.24461486013066677</v>
       </c>
       <c r="L35" s="1">
-        <v>1.278662</v>
+        <v>0.21311033333333332</v>
       </c>
       <c r="M35" s="1">
-        <v>1.8450926433939996</v>
+        <v>0.3075154405656666</v>
       </c>
       <c r="N35" s="1">
-        <v>1.1411866550700001</v>
+        <v>0.190197775845</v>
       </c>
       <c r="O35" s="1">
-        <v>1.3716844778339996</v>
+        <v>0.22861407963899993</v>
       </c>
       <c r="P35" s="1">
-        <v>2.2719298382550006</v>
+        <v>0.37865497304250012</v>
       </c>
       <c r="Q35" s="1">
-        <v>4.0663353153059996</v>
+        <v>0.67772255255099989</v>
       </c>
       <c r="R35" s="1">
-        <v>4.4260527104639991</v>
+        <v>0.73767545174399984</v>
       </c>
       <c r="S35" s="1">
-        <v>3.9343801368959994</v>
+        <v>0.6557300228159999</v>
       </c>
       <c r="T35" s="1">
-        <v>2.4411940904999998</v>
+        <v>0.40686568174999999</v>
       </c>
       <c r="U35" s="1">
-        <v>4.9171778340299985</v>
+        <v>0.81952963900499975</v>
       </c>
       <c r="V35" s="1">
-        <v>2.828616620544</v>
+        <v>0.471436103424</v>
       </c>
       <c r="W35" s="1">
-        <v>1.9708578190619994</v>
+        <v>0.32847630317699988</v>
       </c>
       <c r="X35" s="1">
-        <v>2.7587534515200001</v>
+        <v>0.45979224192000001</v>
       </c>
       <c r="Y35" s="1">
-        <v>1.776855019104</v>
+        <v>0.29614250318399998</v>
       </c>
       <c r="Z35" s="1">
-        <v>8.6168679634620009</v>
+        <v>1.4361446605770001</v>
       </c>
       <c r="AA35" s="1">
-        <v>10.183967432100001</v>
+        <v>1.6973279053500001</v>
       </c>
     </row>
     <row r="36" spans="1:27" x14ac:dyDescent="0.2">
@@ -76603,76 +76603,76 @@
         <v>3</v>
       </c>
       <c r="D36" s="1">
-        <v>-26.430008588136388</v>
+        <v>-4.405001431356065</v>
       </c>
       <c r="E36" s="1">
-        <v>-30.348387622468437</v>
+        <v>-5.0580646037447394</v>
       </c>
       <c r="F36" s="1">
-        <v>-23.286605031034522</v>
+        <v>-3.8811008385057537</v>
       </c>
       <c r="G36" s="1">
-        <v>-30.438400764580539</v>
+        <v>-5.0730667940967562</v>
       </c>
       <c r="H36" s="1">
-        <v>-43.867859181411795</v>
+        <v>-7.3113098635686322</v>
       </c>
       <c r="I36" s="1">
-        <v>-39.59741562296891</v>
+        <v>-6.5995692704948183</v>
       </c>
       <c r="J36" s="1">
-        <v>-34.188331738764447</v>
+        <v>-5.6980552897940742</v>
       </c>
       <c r="K36" s="1">
-        <v>-41.246173857744104</v>
+        <v>-6.8743623096240176</v>
       </c>
       <c r="L36" s="1">
-        <v>-41.296601612779014</v>
+        <v>-6.8827669354631693</v>
       </c>
       <c r="M36" s="1">
-        <v>-51.172562874546657</v>
+        <v>-8.52876047909111</v>
       </c>
       <c r="N36" s="1">
-        <v>-50.074063238497047</v>
+        <v>-8.3456772064161751</v>
       </c>
       <c r="O36" s="1">
-        <v>-55.975649599150159</v>
+        <v>-9.3292749331916927</v>
       </c>
       <c r="P36" s="1">
-        <v>-43.451245606542926</v>
+        <v>-7.2418742677571544</v>
       </c>
       <c r="Q36" s="1">
-        <v>-44.078891097730072</v>
+        <v>-7.3464818496216786</v>
       </c>
       <c r="R36" s="1">
-        <v>-50.261327864853236</v>
+        <v>-8.3768879774755387</v>
       </c>
       <c r="S36" s="1">
-        <v>-40.589125198515362</v>
+        <v>-6.76485419975256</v>
       </c>
       <c r="T36" s="1">
-        <v>-33.996212817015447</v>
+        <v>-5.6660354695025745</v>
       </c>
       <c r="U36" s="1">
-        <v>-33.602013749160626</v>
+        <v>-5.6003356248601044</v>
       </c>
       <c r="V36" s="1">
-        <v>-19.108899425660177</v>
+        <v>-3.1848165709433629</v>
       </c>
       <c r="W36" s="1">
-        <v>-25.68408682242131</v>
+        <v>-4.2806811370702187</v>
       </c>
       <c r="X36" s="1">
-        <v>-25.491805544686269</v>
+        <v>-4.2486342574477112</v>
       </c>
       <c r="Y36" s="1">
-        <v>-24.021124708912858</v>
+        <v>-4.0035207848188099</v>
       </c>
       <c r="Z36" s="1">
-        <v>-21.50610501506462</v>
+        <v>-3.5843508358441034</v>
       </c>
       <c r="AA36" s="1">
-        <v>-23.786288760363043</v>
+        <v>-3.964381460060507</v>
       </c>
     </row>
     <row r="37" spans="1:27" x14ac:dyDescent="0.2">
@@ -76686,76 +76686,76 @@
         <v>3</v>
       </c>
       <c r="D37" s="1">
-        <v>18.417565294928021</v>
+        <v>3.0695942158213367</v>
       </c>
       <c r="E37" s="1">
-        <v>24.667580700060711</v>
+        <v>4.1112634500101182</v>
       </c>
       <c r="F37" s="1">
-        <v>30.199105293097791</v>
+        <v>5.0331842155162985</v>
       </c>
       <c r="G37" s="1">
-        <v>27.677326279384911</v>
+        <v>4.6128877132308181</v>
       </c>
       <c r="H37" s="1">
-        <v>37.062259213256475</v>
+        <v>6.1770432022094122</v>
       </c>
       <c r="I37" s="1">
-        <v>36.330529912406249</v>
+        <v>6.0550883187343745</v>
       </c>
       <c r="J37" s="1">
-        <v>33.194414886325049</v>
+        <v>5.5324024810541745</v>
       </c>
       <c r="K37" s="1">
-        <v>37.552605899111761</v>
+        <v>6.2587676498519604</v>
       </c>
       <c r="L37" s="1">
-        <v>34.742497098231006</v>
+        <v>5.7904161830385013</v>
       </c>
       <c r="M37" s="1">
-        <v>49.355224224263431</v>
+        <v>8.2258707040439045</v>
       </c>
       <c r="N37" s="1">
-        <v>40.766925065231618</v>
+        <v>6.794487510871936</v>
       </c>
       <c r="O37" s="1">
-        <v>39.692166692886651</v>
+        <v>6.6153611154811083</v>
       </c>
       <c r="P37" s="1">
-        <v>41.094235624586602</v>
+        <v>6.8490392707644334</v>
       </c>
       <c r="Q37" s="1">
-        <v>36.660475864242635</v>
+        <v>6.1100793107071061</v>
       </c>
       <c r="R37" s="1">
-        <v>33.676454120408565</v>
+        <v>5.6127423534014271</v>
       </c>
       <c r="S37" s="1">
-        <v>28.011234496299345</v>
+        <v>4.6685390827165572</v>
       </c>
       <c r="T37" s="1">
-        <v>30.978271039074858</v>
+        <v>5.1630451731791434</v>
       </c>
       <c r="U37" s="1">
-        <v>25.00925794284905</v>
+        <v>4.1682096571415084</v>
       </c>
       <c r="V37" s="1">
-        <v>26.973480525391544</v>
+        <v>4.4955800875652576</v>
       </c>
       <c r="W37" s="1">
-        <v>26.833796876056041</v>
+        <v>4.4722994793426736</v>
       </c>
       <c r="X37" s="1">
-        <v>23.263193166413448</v>
+        <v>3.8771988610689081</v>
       </c>
       <c r="Y37" s="1">
-        <v>28.580924890489058</v>
+        <v>4.763487481748176</v>
       </c>
       <c r="Z37" s="1">
-        <v>18.783108375816138</v>
+        <v>3.1305180626360229</v>
       </c>
       <c r="AA37" s="1">
-        <v>22.74269731229964</v>
+        <v>3.7904495520499402</v>
       </c>
     </row>
   </sheetData>

--- a/data/CS1/case33_1/case33_operational_data.xlsx
+++ b/data/CS1/case33_1/case33_operational_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/micaelsimoes/PycharmProjects/shared-resources-planning/data/CS1/case33_1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AA862B5-BD48-1D4F-B868-F1D87C2CC815}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A166F70-7DFC-0D40-80A0-A93C8AE5AD29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1000" yWindow="680" windowWidth="28400" windowHeight="18440" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -454,21 +454,20 @@
         <v>1</v>
       </c>
       <c r="B2" s="1">
-        <f>E2*0.3</f>
-        <v>0.89999999999999991</v>
+        <v>0.1</v>
       </c>
       <c r="C2" s="1">
-        <f>F2*0.3</f>
-        <v>0.53999999999999992</v>
+        <v>0.06</v>
       </c>
       <c r="D2" s="2">
+        <f>B2/SUM(B$2:B$33)</f>
         <v>2.6917900403768499E-2</v>
       </c>
-      <c r="E2" s="1">
-        <v>3</v>
-      </c>
-      <c r="F2" s="1">
-        <v>1.7999999999999998</v>
+      <c r="E2">
+        <v>0.1</v>
+      </c>
+      <c r="F2">
+        <v>0.06</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
@@ -476,21 +475,20 @@
         <v>2</v>
       </c>
       <c r="B3" s="1">
-        <f t="shared" ref="B3:B33" si="0">E3*0.3</f>
-        <v>0.80999999999999994</v>
+        <v>0.09</v>
       </c>
       <c r="C3" s="1">
-        <f t="shared" ref="C3:C33" si="1">F3*0.3</f>
-        <v>0.36000000000000004</v>
+        <v>0.04</v>
       </c>
       <c r="D3" s="2">
+        <f t="shared" ref="D3:D33" si="0">B3/SUM(B$2:B$33)</f>
         <v>2.4226110363391645E-2</v>
       </c>
-      <c r="E3" s="1">
-        <v>2.6999999999999997</v>
-      </c>
-      <c r="F3" s="1">
-        <v>1.2000000000000002</v>
+      <c r="E3">
+        <v>0.09</v>
+      </c>
+      <c r="F3">
+        <v>0.04</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
@@ -498,21 +496,20 @@
         <v>3</v>
       </c>
       <c r="B4" s="1">
+        <v>0.12</v>
+      </c>
+      <c r="C4" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="D4" s="2">
         <f t="shared" si="0"/>
-        <v>1.0799999999999998</v>
-      </c>
-      <c r="C4" s="1">
-        <f t="shared" si="1"/>
-        <v>0.72000000000000008</v>
-      </c>
-      <c r="D4" s="2">
         <v>3.2301480484522194E-2</v>
       </c>
-      <c r="E4" s="1">
-        <v>3.5999999999999996</v>
-      </c>
-      <c r="F4" s="1">
-        <v>2.4000000000000004</v>
+      <c r="E4">
+        <v>0.12</v>
+      </c>
+      <c r="F4">
+        <v>0.08</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
@@ -520,21 +517,20 @@
         <v>4</v>
       </c>
       <c r="B5" s="1">
+        <v>0.06</v>
+      </c>
+      <c r="C5" s="1">
+        <v>0.03</v>
+      </c>
+      <c r="D5" s="2">
         <f t="shared" si="0"/>
-        <v>0.53999999999999992</v>
-      </c>
-      <c r="C5" s="1">
-        <f t="shared" si="1"/>
-        <v>0.26999999999999996</v>
-      </c>
-      <c r="D5" s="2">
         <v>1.6150740242261097E-2</v>
       </c>
-      <c r="E5" s="1">
-        <v>1.7999999999999998</v>
-      </c>
-      <c r="F5" s="1">
-        <v>0.89999999999999991</v>
+      <c r="E5">
+        <v>0.06</v>
+      </c>
+      <c r="F5">
+        <v>0.03</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
@@ -542,21 +538,20 @@
         <v>5</v>
       </c>
       <c r="B6" s="1">
+        <v>0.06</v>
+      </c>
+      <c r="C6" s="1">
+        <v>0.02</v>
+      </c>
+      <c r="D6" s="2">
         <f t="shared" si="0"/>
-        <v>0.53999999999999992</v>
-      </c>
-      <c r="C6" s="1">
-        <f t="shared" si="1"/>
-        <v>0.18000000000000002</v>
-      </c>
-      <c r="D6" s="2">
         <v>1.6150740242261097E-2</v>
       </c>
-      <c r="E6" s="1">
-        <v>1.7999999999999998</v>
-      </c>
-      <c r="F6" s="1">
-        <v>0.60000000000000009</v>
+      <c r="E6">
+        <v>0.06</v>
+      </c>
+      <c r="F6">
+        <v>0.02</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
@@ -564,21 +559,20 @@
         <v>6</v>
       </c>
       <c r="B7" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="C7" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="D7" s="2">
         <f t="shared" si="0"/>
-        <v>1.7999999999999998</v>
-      </c>
-      <c r="C7" s="1">
-        <f t="shared" si="1"/>
-        <v>0.89999999999999991</v>
-      </c>
-      <c r="D7" s="2">
         <v>5.3835800807536999E-2</v>
       </c>
-      <c r="E7" s="1">
-        <v>6</v>
-      </c>
-      <c r="F7" s="1">
-        <v>3</v>
+      <c r="E7">
+        <v>0.2</v>
+      </c>
+      <c r="F7">
+        <v>0.1</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
@@ -586,21 +580,20 @@
         <v>7</v>
       </c>
       <c r="B8" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="C8" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="D8" s="2">
         <f t="shared" si="0"/>
-        <v>1.7999999999999998</v>
-      </c>
-      <c r="C8" s="1">
-        <f t="shared" si="1"/>
-        <v>0.89999999999999991</v>
-      </c>
-      <c r="D8" s="2">
         <v>5.3835800807536999E-2</v>
       </c>
-      <c r="E8" s="1">
-        <v>6</v>
-      </c>
-      <c r="F8" s="1">
-        <v>3</v>
+      <c r="E8">
+        <v>0.2</v>
+      </c>
+      <c r="F8">
+        <v>0.1</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
@@ -608,21 +601,20 @@
         <v>8</v>
       </c>
       <c r="B9" s="1">
+        <v>0.06</v>
+      </c>
+      <c r="C9" s="1">
+        <v>0.02</v>
+      </c>
+      <c r="D9" s="2">
         <f t="shared" si="0"/>
-        <v>0.53999999999999992</v>
-      </c>
-      <c r="C9" s="1">
-        <f t="shared" si="1"/>
-        <v>0.18000000000000002</v>
-      </c>
-      <c r="D9" s="2">
         <v>1.6150740242261097E-2</v>
       </c>
-      <c r="E9" s="1">
-        <v>1.7999999999999998</v>
-      </c>
-      <c r="F9" s="1">
-        <v>0.60000000000000009</v>
+      <c r="E9">
+        <v>0.06</v>
+      </c>
+      <c r="F9">
+        <v>0.02</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
@@ -630,21 +622,20 @@
         <v>9</v>
       </c>
       <c r="B10" s="1">
+        <v>0.06</v>
+      </c>
+      <c r="C10" s="1">
+        <v>0.02</v>
+      </c>
+      <c r="D10" s="2">
         <f t="shared" si="0"/>
-        <v>0.53999999999999992</v>
-      </c>
-      <c r="C10" s="1">
-        <f t="shared" si="1"/>
-        <v>0.18000000000000002</v>
-      </c>
-      <c r="D10" s="2">
         <v>1.6150740242261097E-2</v>
       </c>
-      <c r="E10" s="1">
-        <v>1.7999999999999998</v>
-      </c>
-      <c r="F10" s="1">
-        <v>0.60000000000000009</v>
+      <c r="E10">
+        <v>0.06</v>
+      </c>
+      <c r="F10">
+        <v>0.02</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
@@ -652,21 +643,20 @@
         <v>10</v>
       </c>
       <c r="B11" s="1">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="C11" s="1">
+        <v>0.03</v>
+      </c>
+      <c r="D11" s="2">
         <f t="shared" si="0"/>
-        <v>0.40499999999999997</v>
-      </c>
-      <c r="C11" s="1">
-        <f t="shared" si="1"/>
-        <v>0.26999999999999996</v>
-      </c>
-      <c r="D11" s="2">
         <v>1.2113055181695823E-2</v>
       </c>
-      <c r="E11" s="1">
-        <v>1.3499999999999999</v>
-      </c>
-      <c r="F11" s="1">
-        <v>0.89999999999999991</v>
+      <c r="E11">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="F11">
+        <v>0.03</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
@@ -674,21 +664,20 @@
         <v>11</v>
       </c>
       <c r="B12" s="1">
+        <v>0.06</v>
+      </c>
+      <c r="C12" s="1">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="D12" s="2">
         <f t="shared" si="0"/>
-        <v>0.53999999999999992</v>
-      </c>
-      <c r="C12" s="1">
-        <f t="shared" si="1"/>
-        <v>0.315</v>
-      </c>
-      <c r="D12" s="2">
         <v>1.6150740242261097E-2</v>
       </c>
-      <c r="E12" s="1">
-        <v>1.7999999999999998</v>
-      </c>
-      <c r="F12" s="1">
-        <v>1.05</v>
+      <c r="E12">
+        <v>0.06</v>
+      </c>
+      <c r="F12">
+        <v>3.5000000000000003E-2</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
@@ -696,21 +685,20 @@
         <v>12</v>
       </c>
       <c r="B13" s="1">
+        <v>0.06</v>
+      </c>
+      <c r="C13" s="1">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="D13" s="2">
         <f t="shared" si="0"/>
-        <v>0.53999999999999992</v>
-      </c>
-      <c r="C13" s="1">
-        <f t="shared" si="1"/>
-        <v>0.315</v>
-      </c>
-      <c r="D13" s="2">
         <v>1.6150740242261097E-2</v>
       </c>
-      <c r="E13" s="1">
-        <v>1.7999999999999998</v>
-      </c>
-      <c r="F13" s="1">
-        <v>1.05</v>
+      <c r="E13">
+        <v>0.06</v>
+      </c>
+      <c r="F13">
+        <v>3.5000000000000003E-2</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
@@ -718,21 +706,20 @@
         <v>13</v>
       </c>
       <c r="B14" s="1">
+        <v>0.12</v>
+      </c>
+      <c r="C14" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="D14" s="2">
         <f t="shared" si="0"/>
-        <v>1.0799999999999998</v>
-      </c>
-      <c r="C14" s="1">
-        <f t="shared" si="1"/>
-        <v>0.72000000000000008</v>
-      </c>
-      <c r="D14" s="2">
         <v>3.2301480484522194E-2</v>
       </c>
-      <c r="E14" s="1">
-        <v>3.5999999999999996</v>
-      </c>
-      <c r="F14" s="1">
-        <v>2.4000000000000004</v>
+      <c r="E14">
+        <v>0.12</v>
+      </c>
+      <c r="F14">
+        <v>0.08</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
@@ -740,21 +727,20 @@
         <v>14</v>
       </c>
       <c r="B15" s="1">
+        <v>0.06</v>
+      </c>
+      <c r="C15" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="D15" s="2">
         <f t="shared" si="0"/>
-        <v>0.53999999999999992</v>
-      </c>
-      <c r="C15" s="1">
-        <f t="shared" si="1"/>
-        <v>9.0000000000000011E-2</v>
-      </c>
-      <c r="D15" s="2">
         <v>1.6150740242261097E-2</v>
       </c>
-      <c r="E15" s="1">
-        <v>1.7999999999999998</v>
-      </c>
-      <c r="F15" s="1">
-        <v>0.30000000000000004</v>
+      <c r="E15">
+        <v>0.06</v>
+      </c>
+      <c r="F15">
+        <v>0.01</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
@@ -762,21 +748,20 @@
         <v>15</v>
       </c>
       <c r="B16" s="1">
+        <v>0.06</v>
+      </c>
+      <c r="C16" s="1">
+        <v>0.02</v>
+      </c>
+      <c r="D16" s="2">
         <f t="shared" si="0"/>
-        <v>0.53999999999999992</v>
-      </c>
-      <c r="C16" s="1">
-        <f t="shared" si="1"/>
-        <v>0.18000000000000002</v>
-      </c>
-      <c r="D16" s="2">
         <v>1.6150740242261097E-2</v>
       </c>
-      <c r="E16" s="1">
-        <v>1.7999999999999998</v>
-      </c>
-      <c r="F16" s="1">
-        <v>0.60000000000000009</v>
+      <c r="E16">
+        <v>0.06</v>
+      </c>
+      <c r="F16">
+        <v>0.02</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
@@ -784,21 +769,20 @@
         <v>16</v>
       </c>
       <c r="B17" s="1">
+        <v>0.06</v>
+      </c>
+      <c r="C17" s="1">
+        <v>0.02</v>
+      </c>
+      <c r="D17" s="2">
         <f t="shared" si="0"/>
-        <v>0.53999999999999992</v>
-      </c>
-      <c r="C17" s="1">
-        <f t="shared" si="1"/>
-        <v>0.18000000000000002</v>
-      </c>
-      <c r="D17" s="2">
         <v>1.6150740242261097E-2</v>
       </c>
-      <c r="E17" s="1">
-        <v>1.7999999999999998</v>
-      </c>
-      <c r="F17" s="1">
-        <v>0.60000000000000009</v>
+      <c r="E17">
+        <v>0.06</v>
+      </c>
+      <c r="F17">
+        <v>0.02</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
@@ -806,21 +790,20 @@
         <v>17</v>
       </c>
       <c r="B18" s="1">
+        <v>0.09</v>
+      </c>
+      <c r="C18" s="1">
+        <v>0.04</v>
+      </c>
+      <c r="D18" s="2">
         <f t="shared" si="0"/>
-        <v>0.80999999999999994</v>
-      </c>
-      <c r="C18" s="1">
-        <f t="shared" si="1"/>
-        <v>0.36000000000000004</v>
-      </c>
-      <c r="D18" s="2">
         <v>2.4226110363391645E-2</v>
       </c>
-      <c r="E18" s="1">
-        <v>2.6999999999999997</v>
-      </c>
-      <c r="F18" s="1">
-        <v>1.2000000000000002</v>
+      <c r="E18">
+        <v>0.09</v>
+      </c>
+      <c r="F18">
+        <v>0.04</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
@@ -828,21 +811,20 @@
         <v>18</v>
       </c>
       <c r="B19" s="1">
+        <v>0.09</v>
+      </c>
+      <c r="C19" s="1">
+        <v>0.04</v>
+      </c>
+      <c r="D19" s="2">
         <f t="shared" si="0"/>
-        <v>0.80999999999999994</v>
-      </c>
-      <c r="C19" s="1">
-        <f t="shared" si="1"/>
-        <v>0.36000000000000004</v>
-      </c>
-      <c r="D19" s="2">
         <v>2.4226110363391645E-2</v>
       </c>
-      <c r="E19" s="1">
-        <v>2.6999999999999997</v>
-      </c>
-      <c r="F19" s="1">
-        <v>1.2000000000000002</v>
+      <c r="E19">
+        <v>0.09</v>
+      </c>
+      <c r="F19">
+        <v>0.04</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
@@ -850,21 +832,20 @@
         <v>19</v>
       </c>
       <c r="B20" s="1">
+        <v>0.09</v>
+      </c>
+      <c r="C20" s="1">
+        <v>0.04</v>
+      </c>
+      <c r="D20" s="2">
         <f t="shared" si="0"/>
-        <v>0.80999999999999994</v>
-      </c>
-      <c r="C20" s="1">
-        <f t="shared" si="1"/>
-        <v>0.36000000000000004</v>
-      </c>
-      <c r="D20" s="2">
         <v>2.4226110363391645E-2</v>
       </c>
-      <c r="E20" s="1">
-        <v>2.6999999999999997</v>
-      </c>
-      <c r="F20" s="1">
-        <v>1.2000000000000002</v>
+      <c r="E20">
+        <v>0.09</v>
+      </c>
+      <c r="F20">
+        <v>0.04</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
@@ -872,21 +853,20 @@
         <v>20</v>
       </c>
       <c r="B21" s="1">
+        <v>0.09</v>
+      </c>
+      <c r="C21" s="1">
+        <v>0.04</v>
+      </c>
+      <c r="D21" s="2">
         <f t="shared" si="0"/>
-        <v>0.80999999999999994</v>
-      </c>
-      <c r="C21" s="1">
-        <f t="shared" si="1"/>
-        <v>0.36000000000000004</v>
-      </c>
-      <c r="D21" s="2">
         <v>2.4226110363391645E-2</v>
       </c>
-      <c r="E21" s="1">
-        <v>2.6999999999999997</v>
-      </c>
-      <c r="F21" s="1">
-        <v>1.2000000000000002</v>
+      <c r="E21">
+        <v>0.09</v>
+      </c>
+      <c r="F21">
+        <v>0.04</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
@@ -894,21 +874,20 @@
         <v>21</v>
       </c>
       <c r="B22" s="1">
+        <v>0.09</v>
+      </c>
+      <c r="C22" s="1">
+        <v>0.04</v>
+      </c>
+      <c r="D22" s="2">
         <f t="shared" si="0"/>
-        <v>0.80999999999999994</v>
-      </c>
-      <c r="C22" s="1">
-        <f t="shared" si="1"/>
-        <v>0.36000000000000004</v>
-      </c>
-      <c r="D22" s="2">
         <v>2.4226110363391645E-2</v>
       </c>
-      <c r="E22" s="1">
-        <v>2.6999999999999997</v>
-      </c>
-      <c r="F22" s="1">
-        <v>1.2000000000000002</v>
+      <c r="E22">
+        <v>0.09</v>
+      </c>
+      <c r="F22">
+        <v>0.04</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
@@ -916,21 +895,20 @@
         <v>22</v>
       </c>
       <c r="B23" s="1">
+        <v>0.09</v>
+      </c>
+      <c r="C23" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="D23" s="2">
         <f t="shared" si="0"/>
-        <v>0.80999999999999994</v>
-      </c>
-      <c r="C23" s="1">
-        <f t="shared" si="1"/>
-        <v>0.44999999999999996</v>
-      </c>
-      <c r="D23" s="2">
         <v>2.4226110363391645E-2</v>
       </c>
-      <c r="E23" s="1">
-        <v>2.6999999999999997</v>
-      </c>
-      <c r="F23" s="1">
-        <v>1.5</v>
+      <c r="E23">
+        <v>0.09</v>
+      </c>
+      <c r="F23">
+        <v>0.05</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
@@ -938,21 +916,20 @@
         <v>23</v>
       </c>
       <c r="B24" s="1">
+        <v>0.42</v>
+      </c>
+      <c r="C24" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="D24" s="2">
         <f t="shared" si="0"/>
-        <v>3.7800000000000002</v>
-      </c>
-      <c r="C24" s="1">
-        <f t="shared" si="1"/>
-        <v>1.7999999999999998</v>
-      </c>
-      <c r="D24" s="2">
         <v>0.11305518169582769</v>
       </c>
-      <c r="E24" s="1">
-        <v>12.600000000000001</v>
-      </c>
-      <c r="F24" s="1">
-        <v>6</v>
+      <c r="E24">
+        <v>0.42</v>
+      </c>
+      <c r="F24">
+        <v>0.2</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.2">
@@ -960,21 +937,20 @@
         <v>24</v>
       </c>
       <c r="B25" s="1">
+        <v>0.42</v>
+      </c>
+      <c r="C25" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="D25" s="2">
         <f t="shared" si="0"/>
-        <v>3.7800000000000002</v>
-      </c>
-      <c r="C25" s="1">
-        <f t="shared" si="1"/>
-        <v>1.7999999999999998</v>
-      </c>
-      <c r="D25" s="2">
         <v>0.11305518169582769</v>
       </c>
-      <c r="E25" s="1">
-        <v>12.600000000000001</v>
-      </c>
-      <c r="F25" s="1">
-        <v>6</v>
+      <c r="E25">
+        <v>0.42</v>
+      </c>
+      <c r="F25">
+        <v>0.2</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.2">
@@ -982,21 +958,20 @@
         <v>25</v>
       </c>
       <c r="B26" s="1">
+        <v>0.06</v>
+      </c>
+      <c r="C26" s="1">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="D26" s="2">
         <f t="shared" si="0"/>
-        <v>0.53999999999999992</v>
-      </c>
-      <c r="C26" s="1">
-        <f t="shared" si="1"/>
-        <v>0.22499999999999998</v>
-      </c>
-      <c r="D26" s="2">
         <v>1.6150740242261097E-2</v>
       </c>
-      <c r="E26" s="1">
-        <v>1.7999999999999998</v>
-      </c>
-      <c r="F26" s="1">
-        <v>0.75</v>
+      <c r="E26">
+        <v>0.06</v>
+      </c>
+      <c r="F26">
+        <v>2.5000000000000001E-2</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.2">
@@ -1004,21 +979,20 @@
         <v>26</v>
       </c>
       <c r="B27" s="1">
+        <v>0.06</v>
+      </c>
+      <c r="C27" s="1">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="D27" s="2">
         <f t="shared" si="0"/>
-        <v>0.53999999999999992</v>
-      </c>
-      <c r="C27" s="1">
-        <f t="shared" si="1"/>
-        <v>0.22499999999999998</v>
-      </c>
-      <c r="D27" s="2">
         <v>1.6150740242261097E-2</v>
       </c>
-      <c r="E27" s="1">
-        <v>1.7999999999999998</v>
-      </c>
-      <c r="F27" s="1">
-        <v>0.75</v>
+      <c r="E27">
+        <v>0.06</v>
+      </c>
+      <c r="F27">
+        <v>2.5000000000000001E-2</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.2">
@@ -1026,21 +1000,20 @@
         <v>27</v>
       </c>
       <c r="B28" s="1">
+        <v>0.06</v>
+      </c>
+      <c r="C28" s="1">
+        <v>0.02</v>
+      </c>
+      <c r="D28" s="2">
         <f t="shared" si="0"/>
-        <v>0.53999999999999992</v>
-      </c>
-      <c r="C28" s="1">
-        <f t="shared" si="1"/>
-        <v>0.18000000000000002</v>
-      </c>
-      <c r="D28" s="2">
         <v>1.6150740242261097E-2</v>
       </c>
-      <c r="E28" s="1">
-        <v>1.7999999999999998</v>
-      </c>
-      <c r="F28" s="1">
-        <v>0.60000000000000009</v>
+      <c r="E28">
+        <v>0.06</v>
+      </c>
+      <c r="F28">
+        <v>0.02</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.2">
@@ -1048,21 +1021,20 @@
         <v>28</v>
       </c>
       <c r="B29" s="1">
+        <v>0.12</v>
+      </c>
+      <c r="C29" s="1">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D29" s="2">
         <f t="shared" si="0"/>
-        <v>1.0799999999999998</v>
-      </c>
-      <c r="C29" s="1">
-        <f t="shared" si="1"/>
-        <v>0.63</v>
-      </c>
-      <c r="D29" s="2">
         <v>3.2301480484522194E-2</v>
       </c>
-      <c r="E29" s="1">
-        <v>3.5999999999999996</v>
-      </c>
-      <c r="F29" s="1">
-        <v>2.1</v>
+      <c r="E29">
+        <v>0.12</v>
+      </c>
+      <c r="F29">
+        <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.2">
@@ -1070,21 +1042,20 @@
         <v>29</v>
       </c>
       <c r="B30" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="C30" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="D30" s="2">
         <f t="shared" si="0"/>
-        <v>1.7999999999999998</v>
-      </c>
-      <c r="C30" s="1">
-        <f t="shared" si="1"/>
-        <v>5.3999999999999995</v>
-      </c>
-      <c r="D30" s="2">
         <v>5.3835800807536999E-2</v>
       </c>
-      <c r="E30" s="1">
-        <v>6</v>
-      </c>
-      <c r="F30" s="1">
-        <v>18</v>
+      <c r="E30">
+        <v>0.2</v>
+      </c>
+      <c r="F30">
+        <v>0.6</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
@@ -1092,21 +1063,20 @@
         <v>30</v>
       </c>
       <c r="B31" s="1">
+        <v>0.15</v>
+      </c>
+      <c r="C31" s="1">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D31" s="2">
         <f t="shared" si="0"/>
-        <v>1.3499999999999999</v>
-      </c>
-      <c r="C31" s="1">
-        <f t="shared" si="1"/>
-        <v>0.63</v>
-      </c>
-      <c r="D31" s="2">
         <v>4.0376850605652742E-2</v>
       </c>
-      <c r="E31" s="1">
-        <v>4.5</v>
-      </c>
-      <c r="F31" s="1">
-        <v>2.1</v>
+      <c r="E31">
+        <v>0.15</v>
+      </c>
+      <c r="F31">
+        <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
@@ -1114,21 +1084,20 @@
         <v>31</v>
       </c>
       <c r="B32" s="1">
+        <v>0.21</v>
+      </c>
+      <c r="C32" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="D32" s="2">
         <f t="shared" si="0"/>
-        <v>1.8900000000000001</v>
-      </c>
-      <c r="C32" s="1">
-        <f t="shared" si="1"/>
-        <v>0.89999999999999991</v>
-      </c>
-      <c r="D32" s="2">
         <v>5.6527590847913846E-2</v>
       </c>
-      <c r="E32" s="1">
-        <v>6.3000000000000007</v>
-      </c>
-      <c r="F32" s="1">
-        <v>3</v>
+      <c r="E32">
+        <v>0.21</v>
+      </c>
+      <c r="F32">
+        <v>0.1</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.2">
@@ -1136,21 +1105,20 @@
         <v>32</v>
       </c>
       <c r="B33" s="1">
+        <v>0.06</v>
+      </c>
+      <c r="C33" s="1">
+        <v>0.04</v>
+      </c>
+      <c r="D33" s="2">
         <f t="shared" si="0"/>
-        <v>0.53999999999999992</v>
-      </c>
-      <c r="C33" s="1">
-        <f t="shared" si="1"/>
-        <v>0.36000000000000004</v>
-      </c>
-      <c r="D33" s="2">
         <v>1.6150740242261097E-2</v>
       </c>
-      <c r="E33" s="1">
-        <v>1.7999999999999998</v>
-      </c>
-      <c r="F33" s="1">
-        <v>1.2000000000000002</v>
+      <c r="E33">
+        <v>0.06</v>
+      </c>
+      <c r="F33">
+        <v>0.04</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.2">
@@ -73680,7 +73648,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8D12B52-98C9-449E-BF4A-23F7CAD72921}">
-  <dimension ref="A1:AA37"/>
+  <dimension ref="A1:AA73"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="27.83203125" bestFit="1" customWidth="1"/>
@@ -73781,76 +73749,76 @@
         <v>1</v>
       </c>
       <c r="D2" s="1">
-        <v>1.8846200000000002</v>
+        <v>0.28269300000000003</v>
       </c>
       <c r="E2" s="1">
-        <v>1.947486666666667</v>
+        <v>0.29212300000000002</v>
       </c>
       <c r="F2" s="1">
-        <v>1.7438599999999997</v>
+        <v>0.26157899999999995</v>
       </c>
       <c r="G2" s="1">
-        <v>1.6529333333333331</v>
+        <v>0.24793999999999997</v>
       </c>
       <c r="H2" s="1">
-        <v>1.3542400000000001</v>
+        <v>0.20313600000000004</v>
       </c>
       <c r="I2" s="1">
-        <v>1.1493866666666668</v>
+        <v>0.17240800000000003</v>
       </c>
       <c r="J2" s="1">
-        <v>1.4056066666666667</v>
+        <v>0.210841</v>
       </c>
       <c r="K2" s="1">
-        <v>0.24410666666666667</v>
+        <v>3.6615999999999996E-2</v>
       </c>
       <c r="L2" s="1">
-        <v>0.21466666666666667</v>
+        <v>3.2199999999999999E-2</v>
       </c>
       <c r="M2" s="1">
-        <v>0.31295333333333325</v>
+        <v>4.6942999999999992E-2</v>
       </c>
       <c r="N2" s="1">
-        <v>0.1843066666666667</v>
+        <v>2.7646000000000004E-2</v>
       </c>
       <c r="O2" s="1">
-        <v>0.23030666666666666</v>
+        <v>3.4546E-2</v>
       </c>
       <c r="P2" s="1">
-        <v>0.36692666666666679</v>
+        <v>5.5039000000000018E-2</v>
       </c>
       <c r="Q2" s="1">
-        <v>0.67604666666666668</v>
+        <v>0.101407</v>
       </c>
       <c r="R2" s="1">
-        <v>0.72127999999999981</v>
+        <v>0.10819199999999998</v>
       </c>
       <c r="S2" s="1">
-        <v>0.70931999999999995</v>
+        <v>0.10639799999999999</v>
       </c>
       <c r="T2" s="1">
-        <v>0.39789999999999998</v>
+        <v>5.9685000000000002E-2</v>
       </c>
       <c r="U2" s="1">
-        <v>0.81051999999999991</v>
+        <v>0.12157799999999999</v>
       </c>
       <c r="V2" s="1">
-        <v>0.47564000000000001</v>
+        <v>7.1345999999999993E-2</v>
       </c>
       <c r="W2" s="1">
-        <v>0.33441999999999994</v>
+        <v>5.0162999999999992E-2</v>
       </c>
       <c r="X2" s="1">
-        <v>0.50784000000000007</v>
+        <v>7.6176000000000008E-2</v>
       </c>
       <c r="Y2" s="1">
-        <v>0.31387333333333334</v>
+        <v>4.7080999999999998E-2</v>
       </c>
       <c r="Z2" s="1">
-        <v>1.4325933333333334</v>
+        <v>0.21488900000000002</v>
       </c>
       <c r="AA2" s="1">
-        <v>1.7269933333333334</v>
+        <v>0.25904899999999997</v>
       </c>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.2">
@@ -73864,76 +73832,76 @@
         <v>1</v>
       </c>
       <c r="D3" s="1">
-        <v>-4.2549999999999999</v>
+        <v>-0.63824999999999998</v>
       </c>
       <c r="E3" s="1">
-        <v>-4.5500133333333332</v>
+        <v>-0.68250199999999994</v>
       </c>
       <c r="F3" s="1">
-        <v>-5.1173466666666672</v>
+        <v>-0.76760200000000012</v>
       </c>
       <c r="G3" s="1">
-        <v>-5.520153333333333</v>
+        <v>-0.82802299999999995</v>
       </c>
       <c r="H3" s="1">
-        <v>-5.900266666666667</v>
+        <v>-0.88504000000000005</v>
       </c>
       <c r="I3" s="1">
-        <v>-6.439233333333334</v>
+        <v>-0.9658850000000001</v>
       </c>
       <c r="J3" s="1">
-        <v>-6.1442199999999998</v>
+        <v>-0.92163299999999992</v>
       </c>
       <c r="K3" s="1">
-        <v>-6.8922413333333319</v>
+        <v>-1.0338361999999999</v>
       </c>
       <c r="L3" s="1">
-        <v>-6.2511546666666646</v>
+        <v>-0.93767319999999965</v>
       </c>
       <c r="M3" s="1">
-        <v>-9.1819219999999984</v>
+        <v>-1.3772882999999998</v>
       </c>
       <c r="N3" s="1">
-        <v>-9.0878213333333342</v>
+        <v>-1.3631732000000001</v>
       </c>
       <c r="O3" s="1">
-        <v>-8.3076613333333338</v>
+        <v>-1.2461492000000001</v>
       </c>
       <c r="P3" s="1">
-        <v>-7.963581333333333</v>
+        <v>-1.1945371999999999</v>
       </c>
       <c r="Q3" s="1">
-        <v>-7.6887006666666666</v>
+        <v>-1.1533051000000001</v>
       </c>
       <c r="R3" s="1">
-        <v>-7.247177333333334</v>
+        <v>-1.0870766000000001</v>
       </c>
       <c r="S3" s="1">
-        <v>-6.594958666666666</v>
+        <v>-0.9892437999999999</v>
       </c>
       <c r="T3" s="1">
-        <v>-6.1666680000000005</v>
+        <v>-0.92500020000000005</v>
       </c>
       <c r="U3" s="1">
-        <v>-5.5185586666666673</v>
+        <v>-0.82778380000000007</v>
       </c>
       <c r="V3" s="1">
-        <v>-3.5027926666666662</v>
+        <v>-0.52541889999999991</v>
       </c>
       <c r="W3" s="1">
-        <v>-3.9201506666666659</v>
+        <v>-0.58802259999999984</v>
       </c>
       <c r="X3" s="1">
-        <v>-4.1437719999999993</v>
+        <v>-0.62156579999999995</v>
       </c>
       <c r="Y3" s="1">
-        <v>-4.4487366666666661</v>
+        <v>-0.66731049999999992</v>
       </c>
       <c r="Z3" s="1">
-        <v>-3.5344866666666666</v>
+        <v>-0.53017300000000001</v>
       </c>
       <c r="AA3" s="1">
-        <v>-3.755746666666667</v>
+        <v>-0.56336200000000003</v>
       </c>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.2">
@@ -73947,76 +73915,76 @@
         <v>1</v>
       </c>
       <c r="D4" s="1">
-        <v>4.0991979999999995</v>
+        <v>0.61487969999999992</v>
       </c>
       <c r="E4" s="1">
-        <v>4.3854559999999987</v>
+        <v>0.6578183999999998</v>
       </c>
       <c r="F4" s="1">
-        <v>4.9171086666666666</v>
+        <v>0.7375662999999999</v>
       </c>
       <c r="G4" s="1">
-        <v>5.2909353333333344</v>
+        <v>0.79364030000000008</v>
       </c>
       <c r="H4" s="1">
-        <v>5.6317033333333315</v>
+        <v>0.84475549999999977</v>
       </c>
       <c r="I4" s="1">
-        <v>6.1494333333333335</v>
+        <v>0.92241499999999998</v>
       </c>
       <c r="J4" s="1">
-        <v>5.8626999999999994</v>
+        <v>0.87940499999999988</v>
       </c>
       <c r="K4" s="1">
-        <v>6.6160113333333328</v>
+        <v>0.99240169999999994</v>
       </c>
       <c r="L4" s="1">
-        <v>6.0601780000000005</v>
+        <v>0.90902670000000008</v>
       </c>
       <c r="M4" s="1">
-        <v>6.9151186666666655</v>
+        <v>1.0372678</v>
       </c>
       <c r="N4" s="1">
-        <v>6.969567333333333</v>
+        <v>1.0454351</v>
       </c>
       <c r="O4" s="1">
-        <v>6.5241953333333322</v>
+        <v>0.97862929999999992</v>
       </c>
       <c r="P4" s="1">
-        <v>6.3043000000000005</v>
+        <v>0.94564500000000007</v>
       </c>
       <c r="Q4" s="1">
-        <v>6.1422573333333332</v>
+        <v>0.92133860000000001</v>
       </c>
       <c r="R4" s="1">
-        <v>5.7562560000000005</v>
+        <v>0.86343840000000005</v>
       </c>
       <c r="S4" s="1">
-        <v>5.2407340000000007</v>
+        <v>0.78611010000000003</v>
       </c>
       <c r="T4" s="1">
-        <v>4.8821486666666649</v>
+        <v>0.73232229999999976</v>
       </c>
       <c r="U4" s="1">
-        <v>4.3634373333333327</v>
+        <v>0.65451559999999998</v>
       </c>
       <c r="V4" s="1">
-        <v>3.4152546666666663</v>
+        <v>0.51228819999999997</v>
       </c>
       <c r="W4" s="1">
-        <v>3.822661333333333</v>
+        <v>0.5733992</v>
       </c>
       <c r="X4" s="1">
-        <v>4.0620146666666672</v>
+        <v>0.60930220000000002</v>
       </c>
       <c r="Y4" s="1">
-        <v>4.3755813333333338</v>
+        <v>0.65633720000000007</v>
       </c>
       <c r="Z4" s="1">
-        <v>3.4047666666666667</v>
+        <v>0.51071500000000003</v>
       </c>
       <c r="AA4" s="1">
-        <v>3.6205066666666674</v>
+        <v>0.54307600000000011</v>
       </c>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.2">
@@ -74030,76 +73998,76 @@
         <v>2</v>
       </c>
       <c r="D5" s="1">
-        <v>1.8657738000000006</v>
+        <v>0.27986607000000008</v>
       </c>
       <c r="E5" s="1">
-        <v>1.947486666666667</v>
+        <v>0.29212300000000002</v>
       </c>
       <c r="F5" s="1">
-        <v>1.8136143999999998</v>
+        <v>0.27204215999999998</v>
       </c>
       <c r="G5" s="1">
-        <v>1.6859919999999997</v>
+        <v>0.25289879999999998</v>
       </c>
       <c r="H5" s="1">
-        <v>1.3271552</v>
+        <v>0.19907327999999999</v>
       </c>
       <c r="I5" s="1">
-        <v>1.1034112000000003</v>
+        <v>0.16551168000000002</v>
       </c>
       <c r="J5" s="1">
-        <v>1.4196627333333334</v>
+        <v>0.21294941000000001</v>
       </c>
       <c r="K5" s="1">
-        <v>0.23922453333333335</v>
+        <v>3.5883680000000001E-2</v>
       </c>
       <c r="L5" s="1">
-        <v>0.22325333333333339</v>
+        <v>3.3488000000000004E-2</v>
       </c>
       <c r="M5" s="1">
-        <v>0.32860099999999998</v>
+        <v>4.9290149999999991E-2</v>
       </c>
       <c r="N5" s="1">
-        <v>0.18062053333333336</v>
+        <v>2.7093080000000002E-2</v>
       </c>
       <c r="O5" s="1">
-        <v>0.23260973333333332</v>
+        <v>3.4891459999999999E-2</v>
       </c>
       <c r="P5" s="1">
-        <v>0.36692666666666679</v>
+        <v>5.5039000000000018E-2</v>
       </c>
       <c r="Q5" s="1">
-        <v>0.70984900000000006</v>
+        <v>0.10647735</v>
       </c>
       <c r="R5" s="1">
-        <v>0.72127999999999981</v>
+        <v>0.10819199999999998</v>
       </c>
       <c r="S5" s="1">
-        <v>0.72350639999999988</v>
+        <v>0.10852595999999999</v>
       </c>
       <c r="T5" s="1">
-        <v>0.37800499999999998</v>
+        <v>5.6700750000000001E-2</v>
       </c>
       <c r="U5" s="1">
-        <v>0.85104599999999975</v>
+        <v>0.12765689999999996</v>
       </c>
       <c r="V5" s="1">
-        <v>0.4803964</v>
+        <v>7.2059459999999992E-2</v>
       </c>
       <c r="W5" s="1">
-        <v>0.34445259999999989</v>
+        <v>5.166788999999998E-2</v>
       </c>
       <c r="X5" s="1">
-        <v>0.51291840000000011</v>
+        <v>7.6937760000000008E-2</v>
       </c>
       <c r="Y5" s="1">
-        <v>0.29817966666666668</v>
+        <v>4.4726950000000001E-2</v>
       </c>
       <c r="Z5" s="1">
-        <v>1.4612452000000002</v>
+        <v>0.21918678000000003</v>
       </c>
       <c r="AA5" s="1">
-        <v>1.7269933333333334</v>
+        <v>0.25904899999999997</v>
       </c>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.2">
@@ -74113,76 +74081,76 @@
         <v>2</v>
       </c>
       <c r="D6" s="1">
-        <v>-4.2549999999999999</v>
+        <v>-0.63824999999999998</v>
       </c>
       <c r="E6" s="1">
-        <v>-4.5045131999999999</v>
+        <v>-0.67567697999999998</v>
       </c>
       <c r="F6" s="1">
-        <v>-5.1173466666666672</v>
+        <v>-0.76760200000000012</v>
       </c>
       <c r="G6" s="1">
-        <v>-5.2441456666666664</v>
+        <v>-0.78662184999999996</v>
       </c>
       <c r="H6" s="1">
-        <v>-5.7232586666666663</v>
+        <v>-0.85848879999999994</v>
       </c>
       <c r="I6" s="1">
-        <v>-6.1816640000000005</v>
+        <v>-0.92724960000000001</v>
       </c>
       <c r="J6" s="1">
-        <v>-6.2056621999999999</v>
+        <v>-0.93084933000000003</v>
       </c>
       <c r="K6" s="1">
-        <v>-6.8922413333333319</v>
+        <v>-1.0338361999999999</v>
       </c>
       <c r="L6" s="1">
-        <v>-6.2511546666666646</v>
+        <v>-0.93767319999999965</v>
       </c>
       <c r="M6" s="1">
-        <v>-9.0901027799999987</v>
+        <v>-1.3635154169999999</v>
       </c>
       <c r="N6" s="1">
-        <v>-9.2695777600000024</v>
+        <v>-1.3904366640000003</v>
       </c>
       <c r="O6" s="1">
-        <v>-8.1415081066666666</v>
+        <v>-1.221226216</v>
       </c>
       <c r="P6" s="1">
-        <v>-8.2821245866666668</v>
+        <v>-1.2423186879999999</v>
       </c>
       <c r="Q6" s="1">
-        <v>-7.6118136599999993</v>
+        <v>-1.1417720489999998</v>
       </c>
       <c r="R6" s="1">
-        <v>-7.5370644266666682</v>
+        <v>-1.1305596640000002</v>
       </c>
       <c r="S6" s="1">
-        <v>-6.594958666666666</v>
+        <v>-0.9892437999999999</v>
       </c>
       <c r="T6" s="1">
-        <v>-6.0433346400000003</v>
+        <v>-0.90650019599999998</v>
       </c>
       <c r="U6" s="1">
-        <v>-5.2978163199999999</v>
+        <v>-0.79467244800000003</v>
       </c>
       <c r="V6" s="1">
-        <v>-3.5027926666666662</v>
+        <v>-0.52541889999999991</v>
       </c>
       <c r="W6" s="1">
-        <v>-3.8809491599999988</v>
+        <v>-0.5821423739999998</v>
       </c>
       <c r="X6" s="1">
-        <v>-4.0608965599999989</v>
+        <v>-0.60913448399999992</v>
       </c>
       <c r="Y6" s="1">
-        <v>-4.3152745666666661</v>
+        <v>-0.64729118499999994</v>
       </c>
       <c r="Z6" s="1">
-        <v>-3.6758661333333333</v>
+        <v>-0.55137992000000002</v>
       </c>
       <c r="AA6" s="1">
-        <v>-3.6055168000000002</v>
+        <v>-0.54082752000000001</v>
       </c>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.2">
@@ -74196,76 +74164,76 @@
         <v>2</v>
       </c>
       <c r="D7" s="1">
-        <v>3.8942380999999995</v>
+        <v>0.58413571499999994</v>
       </c>
       <c r="E7" s="1">
-        <v>4.5170196799999989</v>
+        <v>0.67755295199999988</v>
       </c>
       <c r="F7" s="1">
-        <v>4.7204243199999993</v>
+        <v>0.70806364799999988</v>
       </c>
       <c r="G7" s="1">
-        <v>5.0263885666666672</v>
+        <v>0.75395828500000006</v>
       </c>
       <c r="H7" s="1">
-        <v>5.4627522333333323</v>
+        <v>0.81941283499999984</v>
       </c>
       <c r="I7" s="1">
-        <v>6.3339163333333346</v>
+        <v>0.95008745000000017</v>
       </c>
       <c r="J7" s="1">
-        <v>5.6281919999999994</v>
+        <v>0.8442288</v>
       </c>
       <c r="K7" s="1">
-        <v>6.3513708800000011</v>
+        <v>0.95270563200000014</v>
       </c>
       <c r="L7" s="1">
-        <v>6.1207797800000003</v>
+        <v>0.91811696700000012</v>
       </c>
       <c r="M7" s="1">
-        <v>6.7076651066666662</v>
+        <v>1.0061497659999998</v>
       </c>
       <c r="N7" s="1">
-        <v>6.969567333333333</v>
+        <v>1.0454351</v>
       </c>
       <c r="O7" s="1">
-        <v>6.6546792399999992</v>
+        <v>0.99820188599999982</v>
       </c>
       <c r="P7" s="1">
-        <v>6.0521280000000006</v>
+        <v>0.90781920000000016</v>
       </c>
       <c r="Q7" s="1">
-        <v>6.2651024799999986</v>
+        <v>0.93976537199999977</v>
       </c>
       <c r="R7" s="1">
-        <v>6.0440688000000016</v>
+        <v>0.90661032000000019</v>
       </c>
       <c r="S7" s="1">
-        <v>5.3979560200000014</v>
+        <v>0.80969340300000014</v>
       </c>
       <c r="T7" s="1">
-        <v>4.7356842066666651</v>
+        <v>0.71035263099999979</v>
       </c>
       <c r="U7" s="1">
-        <v>4.537974826666666</v>
+        <v>0.68069622399999985</v>
       </c>
       <c r="V7" s="1">
-        <v>3.5860173999999994</v>
+        <v>0.53790260999999995</v>
       </c>
       <c r="W7" s="1">
-        <v>3.822661333333333</v>
+        <v>0.5733992</v>
       </c>
       <c r="X7" s="1">
-        <v>3.8589139333333335</v>
+        <v>0.57883709000000005</v>
       </c>
       <c r="Y7" s="1">
-        <v>4.5943604000000002</v>
+        <v>0.68915406000000012</v>
       </c>
       <c r="Z7" s="1">
-        <v>3.3707189999999994</v>
+        <v>0.50560784999999986</v>
       </c>
       <c r="AA7" s="1">
-        <v>3.6205066666666674</v>
+        <v>0.54307600000000011</v>
       </c>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.2">
@@ -74279,76 +74247,76 @@
         <v>3</v>
       </c>
       <c r="D8" s="1">
-        <v>1.8284583240000003</v>
+        <v>0.27426874860000006</v>
       </c>
       <c r="E8" s="1">
-        <v>1.9864363999999999</v>
+        <v>0.29796546000000002</v>
       </c>
       <c r="F8" s="1">
-        <v>1.8317505439999999</v>
+        <v>0.2747625816</v>
       </c>
       <c r="G8" s="1">
-        <v>1.6185523199999998</v>
+        <v>0.24278284799999997</v>
       </c>
       <c r="H8" s="1">
-        <v>1.2607974399999999</v>
+        <v>0.18911961599999999</v>
       </c>
       <c r="I8" s="1">
-        <v>1.1144453120000002</v>
+        <v>0.16716679680000002</v>
       </c>
       <c r="J8" s="1">
-        <v>1.4054661060000002</v>
+        <v>0.21081991590000002</v>
       </c>
       <c r="K8" s="1">
-        <v>0.24879351466666666</v>
+        <v>3.73190272E-2</v>
       </c>
       <c r="L8" s="1">
-        <v>0.22325333333333339</v>
+        <v>3.3488000000000004E-2</v>
       </c>
       <c r="M8" s="1">
-        <v>0.31217095</v>
+        <v>4.68256425E-2</v>
       </c>
       <c r="N8" s="1">
-        <v>0.18242673866666667</v>
+        <v>2.7364010799999998E-2</v>
       </c>
       <c r="O8" s="1">
-        <v>0.23260973333333332</v>
+        <v>3.4891459999999999E-2</v>
       </c>
       <c r="P8" s="1">
-        <v>0.36325740000000012</v>
+        <v>5.4488610000000014E-2</v>
       </c>
       <c r="Q8" s="1">
-        <v>0.67435655000000005</v>
+        <v>0.1011534825</v>
       </c>
       <c r="R8" s="1">
-        <v>0.69964159999999997</v>
+        <v>0.10494624</v>
       </c>
       <c r="S8" s="1">
-        <v>0.7018012079999999</v>
+        <v>0.10527018119999998</v>
       </c>
       <c r="T8" s="1">
-        <v>0.37800499999999998</v>
+        <v>5.6700750000000001E-2</v>
       </c>
       <c r="U8" s="1">
-        <v>0.82551461999999975</v>
+        <v>0.12382719299999996</v>
       </c>
       <c r="V8" s="1">
-        <v>0.47078847199999996</v>
+        <v>7.0618270799999994E-2</v>
       </c>
       <c r="W8" s="1">
-        <v>0.3616752299999999</v>
+        <v>5.4251284499999983E-2</v>
       </c>
       <c r="X8" s="1">
-        <v>0.51291840000000011</v>
+        <v>7.6937760000000008E-2</v>
       </c>
       <c r="Y8" s="1">
-        <v>0.31010685333333332</v>
+        <v>4.6516028000000001E-2</v>
       </c>
       <c r="Z8" s="1">
-        <v>1.4320202960000001</v>
+        <v>0.21480304440000003</v>
       </c>
       <c r="AA8" s="1">
-        <v>1.6579135999999999</v>
+        <v>0.24868704</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.2">
@@ -74362,76 +74330,76 @@
         <v>3</v>
       </c>
       <c r="D9" s="1">
-        <v>-4.0422500000000001</v>
+        <v>-0.60633750000000008</v>
       </c>
       <c r="E9" s="1">
-        <v>-4.5045131999999999</v>
+        <v>-0.67567697999999998</v>
       </c>
       <c r="F9" s="1">
-        <v>-4.8614793333333344</v>
+        <v>-0.72922190000000009</v>
       </c>
       <c r="G9" s="1">
-        <v>-5.2441456666666664</v>
+        <v>-0.78662184999999996</v>
       </c>
       <c r="H9" s="1">
-        <v>-5.9521890133333342</v>
+        <v>-0.8928283520000001</v>
       </c>
       <c r="I9" s="1">
-        <v>-6.0580307200000005</v>
+        <v>-0.90870460800000008</v>
       </c>
       <c r="J9" s="1">
-        <v>-6.3918320660000001</v>
+        <v>-0.95877480990000008</v>
       </c>
       <c r="K9" s="1">
-        <v>-6.7543965066666658</v>
+        <v>-1.0131594759999998</v>
       </c>
       <c r="L9" s="1">
-        <v>-6.5637123999999973</v>
+        <v>-0.98455685999999965</v>
       </c>
       <c r="M9" s="1">
-        <v>-9.181003807799998</v>
+        <v>-1.3771505711699996</v>
       </c>
       <c r="N9" s="1">
-        <v>-8.9914904272000022</v>
+        <v>-1.3487235640800004</v>
       </c>
       <c r="O9" s="1">
-        <v>-8.3857533498666665</v>
+        <v>-1.2578630024800002</v>
       </c>
       <c r="P9" s="1">
-        <v>-8.199303340800002</v>
+        <v>-1.2298955011200001</v>
       </c>
       <c r="Q9" s="1">
-        <v>-7.9924043429999996</v>
+        <v>-1.19886065145</v>
       </c>
       <c r="R9" s="1">
-        <v>-7.4616937824000011</v>
+        <v>-1.1192540673600002</v>
       </c>
       <c r="S9" s="1">
-        <v>-6.594958666666666</v>
+        <v>-0.9892437999999999</v>
       </c>
       <c r="T9" s="1">
-        <v>-5.9829012936000003</v>
+        <v>-0.89743519404000005</v>
       </c>
       <c r="U9" s="1">
-        <v>-5.5097289728000005</v>
+        <v>-0.82645934592000003</v>
       </c>
       <c r="V9" s="1">
-        <v>-3.6078764466666668</v>
+        <v>-0.54118146700000003</v>
       </c>
       <c r="W9" s="1">
-        <v>-3.8421396683999984</v>
+        <v>-0.57632095025999974</v>
       </c>
       <c r="X9" s="1">
-        <v>-4.0608965599999989</v>
+        <v>-0.60913448399999992</v>
       </c>
       <c r="Y9" s="1">
-        <v>-4.099510838333333</v>
+        <v>-0.6149266257499999</v>
       </c>
       <c r="Z9" s="1">
-        <v>-3.6391074719999996</v>
+        <v>-0.54586612079999997</v>
       </c>
       <c r="AA9" s="1">
-        <v>-3.7857926399999999</v>
+        <v>-0.56786889600000001</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.2">
@@ -74445,76 +74413,76 @@
         <v>3</v>
       </c>
       <c r="D10" s="1">
-        <v>3.9721228619999995</v>
+        <v>0.59581842929999995</v>
       </c>
       <c r="E10" s="1">
-        <v>4.2911686959999988</v>
+        <v>0.64367530439999987</v>
       </c>
       <c r="F10" s="1">
-        <v>4.7204243199999993</v>
+        <v>0.70806364799999988</v>
       </c>
       <c r="G10" s="1">
-        <v>4.8755969096666671</v>
+        <v>0.73133953645000005</v>
       </c>
       <c r="H10" s="1">
-        <v>5.1896146216666645</v>
+        <v>0.77844219324999975</v>
       </c>
       <c r="I10" s="1">
-        <v>6.0172205166666677</v>
+        <v>0.90258307750000011</v>
       </c>
       <c r="J10" s="1">
-        <v>5.3467823999999986</v>
+        <v>0.80201735999999979</v>
       </c>
       <c r="K10" s="1">
-        <v>6.0338023360000008</v>
+        <v>0.90507035040000017</v>
       </c>
       <c r="L10" s="1">
-        <v>5.9983641844000006</v>
+        <v>0.89975462766000014</v>
       </c>
       <c r="M10" s="1">
-        <v>6.8418184088000009</v>
+        <v>1.02627276132</v>
       </c>
       <c r="N10" s="1">
-        <v>7.1089586799999998</v>
+        <v>1.066343802</v>
       </c>
       <c r="O10" s="1">
-        <v>6.3219452780000003</v>
+        <v>0.9482917917</v>
       </c>
       <c r="P10" s="1">
-        <v>6.2942131200000011</v>
+        <v>0.9441319680000001</v>
       </c>
       <c r="Q10" s="1">
-        <v>6.3277535047999995</v>
+        <v>0.94916302571999989</v>
       </c>
       <c r="R10" s="1">
-        <v>6.1649501760000014</v>
+        <v>0.92474252640000021</v>
       </c>
       <c r="S10" s="1">
-        <v>5.1820377792000007</v>
+        <v>0.77730566688000013</v>
       </c>
       <c r="T10" s="1">
-        <v>4.9251115749333314</v>
+        <v>0.73876673623999978</v>
       </c>
       <c r="U10" s="1">
-        <v>4.3564558335999992</v>
+        <v>0.65346837503999988</v>
       </c>
       <c r="V10" s="1">
-        <v>3.7653182699999994</v>
+        <v>0.56479774049999987</v>
       </c>
       <c r="W10" s="1">
-        <v>3.8608879466666668</v>
+        <v>0.57913319200000002</v>
       </c>
       <c r="X10" s="1">
-        <v>4.0132704906666667</v>
+        <v>0.60199057359999997</v>
       </c>
       <c r="Y10" s="1">
-        <v>4.7321912120000009</v>
+        <v>0.70982868180000014</v>
       </c>
       <c r="Z10" s="1">
-        <v>3.4044261899999992</v>
+        <v>0.51066392849999986</v>
       </c>
       <c r="AA10" s="1">
-        <v>3.8015320000000012</v>
+        <v>0.57022980000000012</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.2">
@@ -74528,76 +74496,76 @@
         <v>1</v>
       </c>
       <c r="D11" s="1">
-        <v>1.7903890000000002</v>
+        <v>0.26855835000000006</v>
       </c>
       <c r="E11" s="1">
-        <v>1.8501123333333334</v>
+        <v>0.27751684999999998</v>
       </c>
       <c r="F11" s="1">
-        <v>1.6566669999999999</v>
+        <v>0.24850005</v>
       </c>
       <c r="G11" s="1">
-        <v>1.5702866666666662</v>
+        <v>0.23554299999999992</v>
       </c>
       <c r="H11" s="1">
-        <v>1.2865279999999999</v>
+        <v>0.19297919999999999</v>
       </c>
       <c r="I11" s="1">
-        <v>1.0919173333333334</v>
+        <v>0.16378760000000001</v>
       </c>
       <c r="J11" s="1">
-        <v>1.3353263333333334</v>
+        <v>0.20029895</v>
       </c>
       <c r="K11" s="1">
-        <v>0.23190133333333332</v>
+        <v>3.4785200000000002E-2</v>
       </c>
       <c r="L11" s="1">
-        <v>0.20393333333333333</v>
+        <v>3.0589999999999999E-2</v>
       </c>
       <c r="M11" s="1">
-        <v>0.29730566666666658</v>
+        <v>4.4595849999999986E-2</v>
       </c>
       <c r="N11" s="1">
-        <v>0.17509133333333335</v>
+        <v>2.6263700000000001E-2</v>
       </c>
       <c r="O11" s="1">
-        <v>0.21879133333333331</v>
+        <v>3.2818699999999992E-2</v>
       </c>
       <c r="P11" s="1">
-        <v>0.34858033333333344</v>
+        <v>5.2287050000000015E-2</v>
       </c>
       <c r="Q11" s="1">
-        <v>0.64224433333333331</v>
+        <v>9.6336649999999996E-2</v>
       </c>
       <c r="R11" s="1">
-        <v>0.68521599999999994</v>
+        <v>0.10278239999999998</v>
       </c>
       <c r="S11" s="1">
-        <v>0.67385399999999984</v>
+        <v>0.10107809999999998</v>
       </c>
       <c r="T11" s="1">
-        <v>0.37800499999999998</v>
+        <v>5.6700750000000001E-2</v>
       </c>
       <c r="U11" s="1">
-        <v>0.76999399999999973</v>
+        <v>0.11549909999999997</v>
       </c>
       <c r="V11" s="1">
-        <v>0.45185799999999993</v>
+        <v>6.7778699999999997E-2</v>
       </c>
       <c r="W11" s="1">
-        <v>0.3176989999999999</v>
+        <v>4.7654849999999985E-2</v>
       </c>
       <c r="X11" s="1">
-        <v>0.48244799999999999</v>
+        <v>7.2367199999999993E-2</v>
       </c>
       <c r="Y11" s="1">
-        <v>0.29817966666666668</v>
+        <v>4.4726950000000001E-2</v>
       </c>
       <c r="Z11" s="1">
-        <v>1.3609636666666667</v>
+        <v>0.20414455000000001</v>
       </c>
       <c r="AA11" s="1">
-        <v>1.6406436666666666</v>
+        <v>0.24609655</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.2">
@@ -74611,76 +74579,76 @@
         <v>1</v>
       </c>
       <c r="D12" s="1">
-        <v>-4.2039400000000002</v>
+        <v>-0.63059100000000012</v>
       </c>
       <c r="E12" s="1">
-        <v>-4.5045131999999999</v>
+        <v>-0.67567697999999998</v>
       </c>
       <c r="F12" s="1">
-        <v>-4.6184053666666669</v>
+        <v>-0.69276080500000004</v>
       </c>
       <c r="G12" s="1">
-        <v>-5.2441456666666664</v>
+        <v>-0.78662184999999996</v>
       </c>
       <c r="H12" s="1">
-        <v>-5.8926671231999999</v>
+        <v>-0.88390006848000002</v>
       </c>
       <c r="I12" s="1">
-        <v>-6.3003519487999995</v>
+        <v>-0.94505279231999995</v>
       </c>
       <c r="J12" s="1">
-        <v>-6.2000771040200009</v>
+        <v>-0.93001156560300013</v>
       </c>
       <c r="K12" s="1">
-        <v>-6.6868525415999978</v>
+        <v>-1.0030278812399998</v>
       </c>
       <c r="L12" s="1">
-        <v>-6.6949866479999978</v>
+        <v>-1.0042479971999998</v>
       </c>
       <c r="M12" s="1">
-        <v>-8.8137636554879979</v>
+        <v>-1.3220645483231999</v>
       </c>
       <c r="N12" s="1">
-        <v>-9.0814053314720038</v>
+        <v>-1.3622107997208006</v>
       </c>
       <c r="O12" s="1">
-        <v>-8.6373259503626674</v>
+        <v>-1.2955988925544002</v>
       </c>
       <c r="P12" s="1">
-        <v>-7.9533242405759994</v>
+        <v>-1.1929986360864</v>
       </c>
       <c r="Q12" s="1">
-        <v>-7.5927841258499988</v>
+        <v>-1.1389176188774999</v>
       </c>
       <c r="R12" s="1">
-        <v>-7.3870768445760016</v>
+        <v>-1.1080615266864002</v>
       </c>
       <c r="S12" s="1">
-        <v>-6.594958666666666</v>
+        <v>-0.9892437999999999</v>
       </c>
       <c r="T12" s="1">
-        <v>-6.2222173453440002</v>
+        <v>-0.93333260180160005</v>
       </c>
       <c r="U12" s="1">
-        <v>-5.3995343933439992</v>
+        <v>-0.80993015900159993</v>
       </c>
       <c r="V12" s="1">
-        <v>-3.4635613888000001</v>
+        <v>-0.51953420831999997</v>
       </c>
       <c r="W12" s="1">
-        <v>-3.8805610650839988</v>
+        <v>-0.58208415976259986</v>
       </c>
       <c r="X12" s="1">
-        <v>-4.2639413879999992</v>
+        <v>-0.63959120819999993</v>
       </c>
       <c r="Y12" s="1">
-        <v>-4.099510838333333</v>
+        <v>-0.6149266257499999</v>
       </c>
       <c r="Z12" s="1">
-        <v>-3.52993424784</v>
+        <v>-0.52949013717600002</v>
       </c>
       <c r="AA12" s="1">
-        <v>-3.7100767871999998</v>
+        <v>-0.55651151807999999</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.2">
@@ -74694,76 +74662,76 @@
         <v>1</v>
       </c>
       <c r="D13" s="1">
-        <v>3.7735167188999998</v>
+        <v>0.566027507835</v>
       </c>
       <c r="E13" s="1">
-        <v>4.1624336351200002</v>
+        <v>0.62436504526799996</v>
       </c>
       <c r="F13" s="1">
-        <v>4.7676285631999988</v>
+        <v>0.71514428447999978</v>
       </c>
       <c r="G13" s="1">
-        <v>4.7780849714733344</v>
+        <v>0.71671274572100008</v>
       </c>
       <c r="H13" s="1">
-        <v>5.137718475449998</v>
+        <v>0.7706577713174998</v>
       </c>
       <c r="I13" s="1">
-        <v>6.0773927218333341</v>
+        <v>0.91160890827500007</v>
       </c>
       <c r="J13" s="1">
-        <v>5.3467823999999986</v>
+        <v>0.80201735999999979</v>
       </c>
       <c r="K13" s="1">
-        <v>6.0941403593599999</v>
+        <v>0.91412105390399989</v>
       </c>
       <c r="L13" s="1">
-        <v>5.9983641844000006</v>
+        <v>0.89975462766000014</v>
       </c>
       <c r="M13" s="1">
-        <v>7.0470729610640008</v>
+        <v>1.0570609441596002</v>
       </c>
       <c r="N13" s="1">
-        <v>6.7535107459999999</v>
+        <v>1.0130266119</v>
       </c>
       <c r="O13" s="1">
-        <v>6.0058480140999997</v>
+        <v>0.900877202115</v>
       </c>
       <c r="P13" s="1">
-        <v>6.4830395136000005</v>
+        <v>0.97245592704000006</v>
       </c>
       <c r="Q13" s="1">
-        <v>6.2644759697519996</v>
+        <v>0.93967139546279999</v>
       </c>
       <c r="R13" s="1">
-        <v>6.0416511724800017</v>
+        <v>0.90624767587200028</v>
       </c>
       <c r="S13" s="1">
-        <v>4.9229358902400007</v>
+        <v>0.73844038353600017</v>
       </c>
       <c r="T13" s="1">
-        <v>5.1713671536799986</v>
+        <v>0.77570507305199976</v>
       </c>
       <c r="U13" s="1">
-        <v>4.5307140669439994</v>
+        <v>0.6796071100415999</v>
       </c>
       <c r="V13" s="1">
-        <v>3.8029714526999996</v>
+        <v>0.57044571790499998</v>
       </c>
       <c r="W13" s="1">
-        <v>3.976714585066667</v>
+        <v>0.59650718776000011</v>
       </c>
       <c r="X13" s="1">
-        <v>3.9731377857600005</v>
+        <v>0.5959706678640001</v>
       </c>
       <c r="Y13" s="1">
-        <v>4.9214788604800015</v>
+        <v>0.73822182907200018</v>
       </c>
       <c r="Z13" s="1">
-        <v>3.4044261899999992</v>
+        <v>0.51066392849999986</v>
       </c>
       <c r="AA13" s="1">
-        <v>3.8775626400000012</v>
+        <v>0.58163439600000022</v>
       </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.2">
@@ -74777,76 +74745,76 @@
         <v>2</v>
       </c>
       <c r="D14" s="1">
-        <v>1.8620045600000001</v>
+        <v>0.27930068400000002</v>
       </c>
       <c r="E14" s="1">
-        <v>1.8686134566666668</v>
+        <v>0.28029201850000002</v>
       </c>
       <c r="F14" s="1">
-        <v>1.6566669999999999</v>
+        <v>0.24850005</v>
       </c>
       <c r="G14" s="1">
-        <v>1.6016923999999992</v>
+        <v>0.24025385999999987</v>
       </c>
       <c r="H14" s="1">
-        <v>1.2993932799999999</v>
+        <v>0.19490899199999998</v>
       </c>
       <c r="I14" s="1">
-        <v>1.0591598133333333</v>
+        <v>0.158873972</v>
       </c>
       <c r="J14" s="1">
-        <v>1.3887393866666666</v>
+        <v>0.20831090799999999</v>
       </c>
       <c r="K14" s="1">
-        <v>0.22958232000000001</v>
+        <v>3.4437348E-2</v>
       </c>
       <c r="L14" s="1">
-        <v>0.21005133333333337</v>
+        <v>3.1507700000000007E-2</v>
       </c>
       <c r="M14" s="1">
-        <v>0.29433260999999994</v>
+        <v>4.4149891499999989E-2</v>
       </c>
       <c r="N14" s="1">
-        <v>0.18034407333333333</v>
+        <v>2.7051610999999996E-2</v>
       </c>
       <c r="O14" s="1">
-        <v>0.20785176666666663</v>
+        <v>3.1177764999999996E-2</v>
       </c>
       <c r="P14" s="1">
-        <v>0.34858033333333344</v>
+        <v>5.2287050000000015E-2</v>
       </c>
       <c r="Q14" s="1">
-        <v>0.66151166333333333</v>
+        <v>9.9226749500000003E-2</v>
       </c>
       <c r="R14" s="1">
-        <v>0.67151167999999994</v>
+        <v>0.10072675199999999</v>
       </c>
       <c r="S14" s="1">
-        <v>0.68733107999999976</v>
+        <v>0.10309966199999995</v>
       </c>
       <c r="T14" s="1">
-        <v>0.36288479999999995</v>
+        <v>5.443271999999999E-2</v>
       </c>
       <c r="U14" s="1">
-        <v>0.73919423999999978</v>
+        <v>0.11087913599999996</v>
       </c>
       <c r="V14" s="1">
-        <v>0.43378367999999995</v>
+        <v>6.5067552000000001E-2</v>
       </c>
       <c r="W14" s="1">
-        <v>0.33358394999999991</v>
+        <v>5.0037592499999985E-2</v>
       </c>
       <c r="X14" s="1">
-        <v>0.46797456000000004</v>
+        <v>7.0196184000000009E-2</v>
       </c>
       <c r="Y14" s="1">
-        <v>0.30712505666666662</v>
+        <v>4.6068758499999994E-2</v>
       </c>
       <c r="Z14" s="1">
-        <v>1.3745733033333334</v>
+        <v>0.2061859955</v>
       </c>
       <c r="AA14" s="1">
-        <v>1.6078307933333333</v>
+        <v>0.24117461900000001</v>
       </c>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.2">
@@ -74860,76 +74828,76 @@
         <v>2</v>
       </c>
       <c r="D15" s="1">
-        <v>-4.2459794000000004</v>
+        <v>-0.63689691000000015</v>
       </c>
       <c r="E15" s="1">
-        <v>-4.4144229360000002</v>
+        <v>-0.66216344039999997</v>
       </c>
       <c r="F15" s="1">
-        <v>-4.4336691520000002</v>
+        <v>-0.66505037280000001</v>
       </c>
       <c r="G15" s="1">
-        <v>-5.0343798399999988</v>
+        <v>-0.75515697599999987</v>
       </c>
       <c r="H15" s="1">
-        <v>-6.1283738081280008</v>
+        <v>-0.91925607121920017</v>
       </c>
       <c r="I15" s="1">
-        <v>-6.1743449098239997</v>
+        <v>-0.92615173647359994</v>
       </c>
       <c r="J15" s="1">
-        <v>-6.0760755619396001</v>
+        <v>-0.91141133429094001</v>
       </c>
       <c r="K15" s="1">
-        <v>-6.419378439935997</v>
+        <v>-0.96290676599039959</v>
       </c>
       <c r="L15" s="1">
-        <v>-6.7619365144799986</v>
+        <v>-1.0142904771719998</v>
       </c>
       <c r="M15" s="1">
-        <v>-8.7256260189331183</v>
+        <v>-1.3088439028399679</v>
       </c>
       <c r="N15" s="1">
-        <v>-9.4446615447308826</v>
+        <v>-1.4166992317096325</v>
       </c>
       <c r="O15" s="1">
-        <v>-8.4645794313554159</v>
+        <v>-1.2696869147033123</v>
       </c>
       <c r="P15" s="1">
-        <v>-7.8737909981702403</v>
+        <v>-1.181068649725536</v>
       </c>
       <c r="Q15" s="1">
-        <v>-7.2890727608159978</v>
+        <v>-1.0933609141223997</v>
       </c>
       <c r="R15" s="1">
-        <v>-7.2393353076844811</v>
+        <v>-1.0859002961526723</v>
       </c>
       <c r="S15" s="1">
-        <v>-6.2652107333333324</v>
+        <v>-0.93978160999999982</v>
       </c>
       <c r="T15" s="1">
-        <v>-6.2222173453440002</v>
+        <v>-0.93333260180160005</v>
       </c>
       <c r="U15" s="1">
-        <v>-5.3455390494105588</v>
+        <v>-0.80183085741158389</v>
       </c>
       <c r="V15" s="1">
-        <v>-3.4635613888000001</v>
+        <v>-0.51953420831999997</v>
       </c>
       <c r="W15" s="1">
-        <v>-3.958172286385679</v>
+        <v>-0.5937258429578518</v>
       </c>
       <c r="X15" s="1">
-        <v>-4.3065808018799991</v>
+        <v>-0.64598712028199989</v>
       </c>
       <c r="Y15" s="1">
-        <v>-4.1405059467166661</v>
+        <v>-0.62107589200749991</v>
       </c>
       <c r="Z15" s="1">
-        <v>-3.3887368779263998</v>
+        <v>-0.50831053168896001</v>
       </c>
       <c r="AA15" s="1">
-        <v>-3.8584798586879998</v>
+        <v>-0.57877197880319997</v>
       </c>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.2">
@@ -74943,76 +74911,76 @@
         <v>2</v>
       </c>
       <c r="D16" s="1">
-        <v>3.5848408829549996</v>
+        <v>0.53772613244324996</v>
       </c>
       <c r="E16" s="1">
-        <v>3.9959362897151998</v>
+        <v>0.59939044345727999</v>
       </c>
       <c r="F16" s="1">
-        <v>5.0060099913599991</v>
+        <v>0.75090149870399991</v>
       </c>
       <c r="G16" s="1">
-        <v>4.5869615726144</v>
+        <v>0.68804423589216002</v>
       </c>
       <c r="H16" s="1">
-        <v>5.3946043992224979</v>
+        <v>0.80919065988337469</v>
       </c>
       <c r="I16" s="1">
-        <v>5.8342970129600005</v>
+        <v>0.87514455194400009</v>
       </c>
       <c r="J16" s="1">
-        <v>5.4002502239999997</v>
+        <v>0.81003753359999986</v>
       </c>
       <c r="K16" s="1">
-        <v>6.0941403593599999</v>
+        <v>0.91412105390399989</v>
       </c>
       <c r="L16" s="1">
-        <v>5.6984459751800012</v>
+        <v>0.8547668962770002</v>
       </c>
       <c r="M16" s="1">
-        <v>7.1880144202852811</v>
+        <v>1.0782021630427923</v>
       </c>
       <c r="N16" s="1">
-        <v>6.6184405310800001</v>
+        <v>0.99276607966199992</v>
       </c>
       <c r="O16" s="1">
-        <v>6.2460819346639989</v>
+        <v>0.93691229019959987</v>
       </c>
       <c r="P16" s="1">
-        <v>6.2237179330560002</v>
+        <v>0.93355768995839994</v>
       </c>
       <c r="Q16" s="1">
-        <v>6.4524102488445587</v>
+        <v>0.9678615373266839</v>
       </c>
       <c r="R16" s="1">
-        <v>6.1624841959296015</v>
+        <v>0.92437262938944031</v>
       </c>
       <c r="S16" s="1">
-        <v>4.9721652491424004</v>
+        <v>0.74582478737136015</v>
       </c>
       <c r="T16" s="1">
-        <v>5.2747944967535982</v>
+        <v>0.79121917451303969</v>
       </c>
       <c r="U16" s="1">
-        <v>4.4400997856051196</v>
+        <v>0.66601496784076786</v>
       </c>
       <c r="V16" s="1">
-        <v>3.8410011672269992</v>
+        <v>0.57615017508404986</v>
       </c>
       <c r="W16" s="1">
-        <v>3.976714585066667</v>
+        <v>0.59650718776000011</v>
       </c>
       <c r="X16" s="1">
-        <v>4.1320632971903999</v>
+        <v>0.61980949457856005</v>
       </c>
       <c r="Y16" s="1">
-        <v>5.0199084376896019</v>
+        <v>0.75298626565344029</v>
       </c>
       <c r="Z16" s="1">
-        <v>3.4384704518999993</v>
+        <v>0.51577056778499997</v>
       </c>
       <c r="AA16" s="1">
-        <v>3.7224601344000017</v>
+        <v>0.55836902016000023</v>
       </c>
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.2">
@@ -75026,76 +74994,76 @@
         <v>3</v>
       </c>
       <c r="D17" s="1">
-        <v>1.7689043320000002</v>
+        <v>0.26533564980000002</v>
       </c>
       <c r="E17" s="1">
-        <v>1.9433579949333335</v>
+        <v>0.29150369924000002</v>
       </c>
       <c r="F17" s="1">
-        <v>1.6401003299999999</v>
+        <v>0.24601504949999997</v>
       </c>
       <c r="G17" s="1">
-        <v>1.6817770199999993</v>
+        <v>0.25226655299999989</v>
       </c>
       <c r="H17" s="1">
-        <v>1.3123872127999998</v>
+        <v>0.19685808191999998</v>
       </c>
       <c r="I17" s="1">
-        <v>1.0485682152000002</v>
+        <v>0.15728523228000002</v>
       </c>
       <c r="J17" s="1">
-        <v>1.3470772050666664</v>
+        <v>0.20206158075999997</v>
       </c>
       <c r="K17" s="1">
-        <v>0.2318781432</v>
+        <v>3.478172148E-2</v>
       </c>
       <c r="L17" s="1">
-        <v>0.21005133333333337</v>
+        <v>3.1507700000000007E-2</v>
       </c>
       <c r="M17" s="1">
-        <v>0.28550263169999995</v>
+        <v>4.2825394754999989E-2</v>
       </c>
       <c r="N17" s="1">
-        <v>0.1785406326</v>
+        <v>2.6781094890000003E-2</v>
       </c>
       <c r="O17" s="1">
-        <v>0.20577324899999996</v>
+        <v>3.0865987349999995E-2</v>
       </c>
       <c r="P17" s="1">
-        <v>0.34858033333333344</v>
+        <v>5.2287050000000015E-2</v>
       </c>
       <c r="Q17" s="1">
-        <v>0.6681267799666667</v>
+        <v>0.10021901699499999</v>
       </c>
       <c r="R17" s="1">
-        <v>0.70508726399999988</v>
+        <v>0.10576308959999998</v>
       </c>
       <c r="S17" s="1">
-        <v>0.65296452599999966</v>
+        <v>9.7944678899999943E-2</v>
       </c>
       <c r="T17" s="1">
-        <v>0.35199825599999995</v>
+        <v>5.2799738399999997E-2</v>
       </c>
       <c r="U17" s="1">
-        <v>0.73180229759999982</v>
+        <v>0.10977034463999998</v>
       </c>
       <c r="V17" s="1">
-        <v>0.44245935359999988</v>
+        <v>6.6368903039999982E-2</v>
       </c>
       <c r="W17" s="1">
-        <v>0.33358394999999991</v>
+        <v>5.0037592499999985E-2</v>
       </c>
       <c r="X17" s="1">
-        <v>0.45861506880000008</v>
+        <v>6.8792260320000007E-2</v>
       </c>
       <c r="Y17" s="1">
-        <v>0.30712505666666662</v>
+        <v>4.6068758499999994E-2</v>
       </c>
       <c r="Z17" s="1">
-        <v>1.3195903712000001</v>
+        <v>0.19793855568000002</v>
       </c>
       <c r="AA17" s="1">
-        <v>1.5756741774666665</v>
+        <v>0.23635112661999996</v>
       </c>
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.2">
@@ -75109,76 +75077,76 @@
         <v>3</v>
       </c>
       <c r="D18" s="1">
-        <v>-4.2035196060000013</v>
+        <v>-0.63052794090000019</v>
       </c>
       <c r="E18" s="1">
-        <v>-4.5909998534400005</v>
+        <v>-0.68864997801600003</v>
       </c>
       <c r="F18" s="1">
-        <v>-4.2119856944</v>
+        <v>-0.63179785416000001</v>
       </c>
       <c r="G18" s="1">
-        <v>-5.084723638399999</v>
+        <v>-0.76270854575999991</v>
       </c>
       <c r="H18" s="1">
-        <v>-6.3122250223718401</v>
+        <v>-0.94683375335577602</v>
       </c>
       <c r="I18" s="1">
-        <v>-6.2360883589222382</v>
+        <v>-0.93541325383833573</v>
       </c>
       <c r="J18" s="1">
-        <v>-5.8330325394620166</v>
+        <v>-0.8749548809193024</v>
       </c>
       <c r="K18" s="1">
-        <v>-6.5477660087347163</v>
+        <v>-0.98216490131020751</v>
       </c>
       <c r="L18" s="1">
-        <v>-6.8295558796247988</v>
+        <v>-1.0244333819437199</v>
       </c>
       <c r="M18" s="1">
-        <v>-8.3766009781757944</v>
+        <v>-1.2564901467263692</v>
       </c>
       <c r="N18" s="1">
-        <v>-9.6335547756255</v>
+        <v>-1.4450332163438251</v>
       </c>
       <c r="O18" s="1">
-        <v>-8.3799336370418605</v>
+        <v>-1.2569900455562792</v>
       </c>
       <c r="P18" s="1">
-        <v>-8.1100047281153476</v>
+        <v>-1.2165007092173021</v>
       </c>
       <c r="Q18" s="1">
-        <v>-7.5077449436404775</v>
+        <v>-1.1261617415460716</v>
       </c>
       <c r="R18" s="1">
-        <v>-7.6013020730687053</v>
+        <v>-1.1401953109603058</v>
       </c>
       <c r="S18" s="1">
-        <v>-6.5158191626666655</v>
+        <v>-0.97737287439999976</v>
       </c>
       <c r="T18" s="1">
-        <v>-6.0355508249836802</v>
+        <v>-0.90533262374755208</v>
       </c>
       <c r="U18" s="1">
-        <v>-5.5059052208928767</v>
+        <v>-0.82588578313393146</v>
       </c>
       <c r="V18" s="1">
-        <v>-3.2903833193600001</v>
+        <v>-0.493557497904</v>
       </c>
       <c r="W18" s="1">
-        <v>-3.8790088406579653</v>
+        <v>-0.58185132609869483</v>
       </c>
       <c r="X18" s="1">
-        <v>-4.2635149938611994</v>
+        <v>-0.6395272490791799</v>
       </c>
       <c r="Y18" s="1">
-        <v>-4.0162907683151667</v>
+        <v>-0.60244361524727497</v>
       </c>
       <c r="Z18" s="1">
-        <v>-3.3209621403678717</v>
+        <v>-0.49814432105518075</v>
       </c>
       <c r="AA18" s="1">
-        <v>-3.8584798586879998</v>
+        <v>-0.57877197880319997</v>
       </c>
     </row>
     <row r="19" spans="1:27" x14ac:dyDescent="0.2">
@@ -75192,76 +75160,76 @@
         <v>3</v>
       </c>
       <c r="D19" s="1">
-        <v>3.4055988388072493</v>
+        <v>0.51083982582108745</v>
       </c>
       <c r="E19" s="1">
-        <v>4.0758550155095037</v>
+        <v>0.61137825232642551</v>
       </c>
       <c r="F19" s="1">
-        <v>5.2062503910143993</v>
+        <v>0.78093755865215986</v>
       </c>
       <c r="G19" s="1">
-        <v>4.8163096512451204</v>
+        <v>0.72244644768676802</v>
       </c>
       <c r="H19" s="1">
-        <v>5.6103885751913971</v>
+        <v>0.84155828627870954</v>
       </c>
       <c r="I19" s="1">
-        <v>5.6592681025712004</v>
+        <v>0.8488902153856801</v>
       </c>
       <c r="J19" s="1">
-        <v>5.6702627351999988</v>
+        <v>0.85053941027999991</v>
       </c>
       <c r="K19" s="1">
-        <v>6.3988473773279999</v>
+        <v>0.95982710659920001</v>
       </c>
       <c r="L19" s="1">
-        <v>5.5274925959246017</v>
+        <v>0.82912388938869019</v>
       </c>
       <c r="M19" s="1">
-        <v>7.1880144202852811</v>
+        <v>1.0782021630427923</v>
       </c>
       <c r="N19" s="1">
-        <v>6.6846249363907999</v>
+        <v>1.00269374045862</v>
       </c>
       <c r="O19" s="1">
-        <v>6.1211602959707205</v>
+        <v>0.91817404439560801</v>
       </c>
       <c r="P19" s="1">
-        <v>6.5349038297088002</v>
+        <v>0.98023557445632004</v>
       </c>
       <c r="Q19" s="1">
-        <v>6.2588379413792232</v>
+        <v>0.93882569120688353</v>
       </c>
       <c r="R19" s="1">
-        <v>5.8543599861331224</v>
+        <v>0.8781539979199684</v>
       </c>
       <c r="S19" s="1">
-        <v>4.922443596650977</v>
+        <v>0.73836653949764652</v>
       </c>
       <c r="T19" s="1">
-        <v>5.2747944967535982</v>
+        <v>0.79121917451303969</v>
       </c>
       <c r="U19" s="1">
-        <v>4.528901781317221</v>
+        <v>0.67933526719758319</v>
       </c>
       <c r="V19" s="1">
-        <v>3.9946412139160792</v>
+        <v>0.59919618208741188</v>
       </c>
       <c r="W19" s="1">
-        <v>4.0960160226186675</v>
+        <v>0.61440240339280017</v>
       </c>
       <c r="X19" s="1">
-        <v>4.1320632971903999</v>
+        <v>0.61980949457856005</v>
       </c>
       <c r="Y19" s="1">
-        <v>4.9195102689358094</v>
+        <v>0.73792654034037142</v>
       </c>
       <c r="Z19" s="1">
-        <v>3.3009316338239993</v>
+        <v>0.49513974507359987</v>
       </c>
       <c r="AA19" s="1">
-        <v>3.610786330368001</v>
+        <v>0.54161794955520015</v>
       </c>
     </row>
     <row r="20" spans="1:27" x14ac:dyDescent="0.2">
@@ -75275,76 +75243,76 @@
         <v>1</v>
       </c>
       <c r="D20" s="1">
-        <v>1.9694279000000006</v>
+        <v>0.29541418500000011</v>
       </c>
       <c r="E20" s="1">
-        <v>2.0351235666666669</v>
+        <v>0.30526853500000006</v>
       </c>
       <c r="F20" s="1">
-        <v>1.8223337000000004</v>
+        <v>0.27335005500000004</v>
       </c>
       <c r="G20" s="1">
-        <v>1.7273153333333331</v>
+        <v>0.25909729999999997</v>
       </c>
       <c r="H20" s="1">
-        <v>1.4151807999999999</v>
+        <v>0.21227711999999999</v>
       </c>
       <c r="I20" s="1">
-        <v>1.2011090666666668</v>
+        <v>0.18016636000000003</v>
       </c>
       <c r="J20" s="1">
-        <v>1.4688589666666667</v>
+        <v>0.220328845</v>
       </c>
       <c r="K20" s="1">
-        <v>0.25509146666666671</v>
+        <v>3.8263720000000008E-2</v>
       </c>
       <c r="L20" s="1">
-        <v>0.22432666666666667</v>
+        <v>3.3648999999999998E-2</v>
       </c>
       <c r="M20" s="1">
-        <v>0.32703623333333326</v>
+        <v>4.9055434999999988E-2</v>
       </c>
       <c r="N20" s="1">
-        <v>0.19260046666666666</v>
+        <v>2.889007E-2</v>
       </c>
       <c r="O20" s="1">
-        <v>0.24067046666666661</v>
+        <v>3.6100569999999992E-2</v>
       </c>
       <c r="P20" s="1">
-        <v>0.38343836666666675</v>
+        <v>5.7515755000000016E-2</v>
       </c>
       <c r="Q20" s="1">
-        <v>0.70646876666666669</v>
+        <v>0.10597031500000001</v>
       </c>
       <c r="R20" s="1">
-        <v>0.75373760000000001</v>
+        <v>0.11306064</v>
       </c>
       <c r="S20" s="1">
-        <v>0.74123939999999988</v>
+        <v>0.11118590999999997</v>
       </c>
       <c r="T20" s="1">
-        <v>0.41580549999999999</v>
+        <v>6.2370824999999998E-2</v>
       </c>
       <c r="U20" s="1">
-        <v>0.84699339999999979</v>
+        <v>0.12704900999999996</v>
       </c>
       <c r="V20" s="1">
-        <v>0.49704379999999998</v>
+        <v>7.4556570000000003E-2</v>
       </c>
       <c r="W20" s="1">
-        <v>0.34946889999999992</v>
+        <v>5.2420334999999985E-2</v>
       </c>
       <c r="X20" s="1">
-        <v>0.53069280000000008</v>
+        <v>7.9603920000000022E-2</v>
       </c>
       <c r="Y20" s="1">
-        <v>0.32799763333333332</v>
+        <v>4.9199645E-2</v>
       </c>
       <c r="Z20" s="1">
-        <v>1.4970600333333335</v>
+        <v>0.22455900500000001</v>
       </c>
       <c r="AA20" s="1">
-        <v>1.8047080333333332</v>
+        <v>0.27070620499999998</v>
       </c>
     </row>
     <row r="21" spans="1:27" x14ac:dyDescent="0.2">
@@ -75358,76 +75326,76 @@
         <v>1</v>
       </c>
       <c r="D21" s="1">
-        <v>-4.0774140178200016</v>
+        <v>-0.61161210267300015</v>
       </c>
       <c r="E21" s="1">
-        <v>-4.8205498461120007</v>
+        <v>-0.72308247691680005</v>
       </c>
       <c r="F21" s="1">
-        <v>-4.0856261235679989</v>
+        <v>-0.61284391853519993</v>
       </c>
       <c r="G21" s="1">
-        <v>-5.186418111167999</v>
+        <v>-0.77796271667519989</v>
       </c>
       <c r="H21" s="1">
-        <v>-6.5647140232667143</v>
+        <v>-0.98470710349000723</v>
       </c>
       <c r="I21" s="1">
-        <v>-6.2360883589222382</v>
+        <v>-0.93541325383833573</v>
       </c>
       <c r="J21" s="1">
-        <v>-5.8913628648566378</v>
+        <v>-0.88370442972849561</v>
       </c>
       <c r="K21" s="1">
-        <v>-6.4822883486473692</v>
+        <v>-0.97234325229710539</v>
       </c>
       <c r="L21" s="1">
-        <v>-6.8978514384210454</v>
+        <v>-1.0346777157631568</v>
       </c>
       <c r="M21" s="1">
-        <v>-8.3766009781757944</v>
+        <v>-1.2564901467263692</v>
       </c>
       <c r="N21" s="1">
-        <v>-9.5372192278692456</v>
+        <v>-1.4305828841803867</v>
       </c>
       <c r="O21" s="1">
-        <v>-8.7151309825235366</v>
+        <v>-1.3072696473785306</v>
       </c>
       <c r="P21" s="1">
-        <v>-8.1100047281153476</v>
+        <v>-1.2165007092173021</v>
       </c>
       <c r="Q21" s="1">
-        <v>-7.7329772919496911</v>
+        <v>-1.1599465937924536</v>
       </c>
       <c r="R21" s="1">
-        <v>-7.3732630108766442</v>
+        <v>-1.1059894516314965</v>
       </c>
       <c r="S21" s="1">
-        <v>-6.3855027794133319</v>
+        <v>-0.95782541691199974</v>
       </c>
       <c r="T21" s="1">
-        <v>-5.7337732837344966</v>
+        <v>-0.86006599256017446</v>
       </c>
       <c r="U21" s="1">
-        <v>-5.5059052208928767</v>
+        <v>-0.82588578313393146</v>
       </c>
       <c r="V21" s="1">
-        <v>-3.3561909857471997</v>
+        <v>-0.50342864786207997</v>
       </c>
       <c r="W21" s="1">
-        <v>-3.9953791058777042</v>
+        <v>-0.5993068658816556</v>
       </c>
       <c r="X21" s="1">
-        <v>-4.4340555936156472</v>
+        <v>-0.66510833904234712</v>
       </c>
       <c r="Y21" s="1">
-        <v>-3.9359649529488636</v>
+        <v>-0.59039474294232952</v>
       </c>
       <c r="Z21" s="1">
-        <v>-3.3209621403678717</v>
+        <v>-0.49814432105518075</v>
       </c>
       <c r="AA21" s="1">
-        <v>-3.9742342544486391</v>
+        <v>-0.59613513816729591</v>
       </c>
     </row>
     <row r="22" spans="1:27" x14ac:dyDescent="0.2">
@@ -75441,76 +75409,76 @@
         <v>1</v>
       </c>
       <c r="D22" s="1">
-        <v>3.2353188968668873</v>
+        <v>0.48529783453003306</v>
       </c>
       <c r="E22" s="1">
-        <v>4.157372115819693</v>
+        <v>0.62360581737295395</v>
       </c>
       <c r="F22" s="1">
-        <v>5.3624379027448308</v>
+        <v>0.80436568541172471</v>
       </c>
       <c r="G22" s="1">
-        <v>4.7199834582202174</v>
+        <v>0.70799751873303252</v>
       </c>
       <c r="H22" s="1">
-        <v>5.7225963466952257</v>
+        <v>0.85838945200428385</v>
       </c>
       <c r="I22" s="1">
-        <v>5.6026754215454879</v>
+        <v>0.84040131323182321</v>
       </c>
       <c r="J22" s="1">
-        <v>5.5001548531439992</v>
+        <v>0.82502322797159988</v>
       </c>
       <c r="K22" s="1">
-        <v>6.5908127986478391</v>
+        <v>0.98862191979717584</v>
       </c>
       <c r="L22" s="1">
-        <v>5.8038672257208317</v>
+        <v>0.87058008385812469</v>
       </c>
       <c r="M22" s="1">
-        <v>7.4036548528938404</v>
+        <v>1.1105482279340761</v>
       </c>
       <c r="N22" s="1">
-        <v>6.5509324376629827</v>
+        <v>0.98263986564944739</v>
       </c>
       <c r="O22" s="1">
-        <v>6.2435835018901349</v>
+        <v>0.93653752528352019</v>
       </c>
       <c r="P22" s="1">
-        <v>6.7962999828971524</v>
+        <v>1.0194449974345727</v>
       </c>
       <c r="Q22" s="1">
-        <v>6.4466030796205986</v>
+        <v>0.9669904619430898</v>
       </c>
       <c r="R22" s="1">
-        <v>5.6787291865491278</v>
+        <v>0.85180937798236922</v>
       </c>
       <c r="S22" s="1">
-        <v>4.8732191606844664</v>
+        <v>0.73098287410267004</v>
       </c>
       <c r="T22" s="1">
-        <v>5.38029038668867</v>
+        <v>0.80704355800330041</v>
       </c>
       <c r="U22" s="1">
-        <v>4.3930347278777058</v>
+        <v>0.65895520918165584</v>
       </c>
       <c r="V22" s="1">
-        <v>4.1144804503335619</v>
+        <v>0.61717206755003429</v>
       </c>
       <c r="W22" s="1">
-        <v>4.2598566635234141</v>
+        <v>0.63897849952851205</v>
       </c>
       <c r="X22" s="1">
-        <v>4.0907426642184967</v>
+        <v>0.61361139963277445</v>
       </c>
       <c r="Y22" s="1">
-        <v>4.870315166246451</v>
+        <v>0.73054727493696769</v>
       </c>
       <c r="Z22" s="1">
-        <v>3.3669502665004791</v>
+        <v>0.50504253997507187</v>
       </c>
       <c r="AA22" s="1">
-        <v>3.646894193671681</v>
+        <v>0.5470341290507521</v>
       </c>
     </row>
     <row r="23" spans="1:27" x14ac:dyDescent="0.2">
@@ -75524,76 +75492,76 @@
         <v>2</v>
       </c>
       <c r="D23" s="1">
-        <v>2.0678992950000006</v>
+        <v>0.31018489425000006</v>
       </c>
       <c r="E23" s="1">
-        <v>2.1368797449999999</v>
+        <v>0.32053196174999998</v>
       </c>
       <c r="F23" s="1">
-        <v>1.7494403519999999</v>
+        <v>0.26241605280000002</v>
       </c>
       <c r="G23" s="1">
-        <v>1.6754958733333332</v>
+        <v>0.25132438099999999</v>
       </c>
       <c r="H23" s="1">
-        <v>1.4010289919999999</v>
+        <v>0.2101543488</v>
       </c>
       <c r="I23" s="1">
-        <v>1.1770868853333336</v>
+        <v>0.17656303280000002</v>
       </c>
       <c r="J23" s="1">
-        <v>1.4541703769999998</v>
+        <v>0.21812555654999999</v>
       </c>
       <c r="K23" s="1">
-        <v>0.25764238133333334</v>
+        <v>3.8646357200000002E-2</v>
       </c>
       <c r="L23" s="1">
-        <v>0.21984013333333333</v>
+        <v>3.2976020000000002E-2</v>
       </c>
       <c r="M23" s="1">
-        <v>0.33030659566666659</v>
+        <v>4.9545989349999993E-2</v>
       </c>
       <c r="N23" s="1">
-        <v>0.20030448533333337</v>
+        <v>3.0045672800000006E-2</v>
       </c>
       <c r="O23" s="1">
-        <v>0.25029728533333334</v>
+        <v>3.7544592799999998E-2</v>
       </c>
       <c r="P23" s="1">
-        <v>0.37576959933333343</v>
+        <v>5.6365439900000015E-2</v>
       </c>
       <c r="Q23" s="1">
-        <v>0.73472751733333341</v>
+        <v>0.11020912760000001</v>
       </c>
       <c r="R23" s="1">
-        <v>0.79142447999999987</v>
+        <v>0.11871367199999998</v>
       </c>
       <c r="S23" s="1">
-        <v>0.70417742999999999</v>
+        <v>0.10562661449999999</v>
       </c>
       <c r="T23" s="1">
-        <v>0.42827966500000003</v>
+        <v>6.4241949749999999E-2</v>
       </c>
       <c r="U23" s="1">
-        <v>0.88087313599999983</v>
+        <v>0.13213097039999996</v>
       </c>
       <c r="V23" s="1">
-        <v>0.48710292400000005</v>
+        <v>7.3065438600000004E-2</v>
       </c>
       <c r="W23" s="1">
-        <v>0.34597421099999992</v>
+        <v>5.1896131649999989E-2</v>
       </c>
       <c r="X23" s="1">
-        <v>0.53069280000000008</v>
+        <v>7.9603920000000022E-2</v>
       </c>
       <c r="Y23" s="1">
-        <v>0.33783756233333334</v>
+        <v>5.0675634349999998E-2</v>
       </c>
       <c r="Z23" s="1">
-        <v>1.5719130350000003</v>
+        <v>0.23578695525000004</v>
       </c>
       <c r="AA23" s="1">
-        <v>1.8408021940000001</v>
+        <v>0.27612032910000001</v>
       </c>
     </row>
     <row r="24" spans="1:27" x14ac:dyDescent="0.2">
@@ -75607,76 +75575,76 @@
         <v>2</v>
       </c>
       <c r="D24" s="1">
-        <v>-4.118188157998202</v>
+        <v>-0.61772822369973024</v>
       </c>
       <c r="E24" s="1">
-        <v>-4.9651663414953608</v>
+        <v>-0.74477495122430404</v>
       </c>
       <c r="F24" s="1">
-        <v>-4.003913601096639</v>
+        <v>-0.60058704016449593</v>
       </c>
       <c r="G24" s="1">
-        <v>-5.082689748944639</v>
+        <v>-0.76240346234169576</v>
       </c>
       <c r="H24" s="1">
-        <v>-6.6303611634993826</v>
+        <v>-0.99455417452490735</v>
       </c>
       <c r="I24" s="1">
-        <v>-6.0490057081545707</v>
+        <v>-0.90735085622318556</v>
       </c>
       <c r="J24" s="1">
-        <v>-5.7735356075595057</v>
+        <v>-0.86603034113392585</v>
       </c>
       <c r="K24" s="1">
-        <v>-6.6119341156203157</v>
+        <v>-0.99179011734304745</v>
       </c>
       <c r="L24" s="1">
-        <v>-7.1737654959578876</v>
+        <v>-1.0760648243936832</v>
       </c>
       <c r="M24" s="1">
-        <v>-8.6278990075210675</v>
+        <v>-1.2941848511281602</v>
       </c>
       <c r="N24" s="1">
-        <v>-9.1557304587544763</v>
+        <v>-1.3733595688131714</v>
       </c>
       <c r="O24" s="1">
-        <v>-8.9765849119992431</v>
+        <v>-1.3464877367998864</v>
       </c>
       <c r="P24" s="1">
-        <v>-7.8667045862718892</v>
+        <v>-1.1800056879407834</v>
       </c>
       <c r="Q24" s="1">
-        <v>-7.5783177461106979</v>
+        <v>-1.1367476619166046</v>
       </c>
       <c r="R24" s="1">
-        <v>-7.3732630108766442</v>
+        <v>-1.1059894516314965</v>
       </c>
       <c r="S24" s="1">
-        <v>-6.1300826682367981</v>
+        <v>-0.91951240023551972</v>
       </c>
       <c r="T24" s="1">
-        <v>-5.7911110165718407</v>
+        <v>-0.86866665248577613</v>
       </c>
       <c r="U24" s="1">
-        <v>-5.2306099598482332</v>
+        <v>-0.78459149397723493</v>
       </c>
       <c r="V24" s="1">
-        <v>-3.2219433463173122</v>
+        <v>-0.48329150194759685</v>
       </c>
       <c r="W24" s="1">
-        <v>-3.9953791058777042</v>
+        <v>-0.5993068658816556</v>
       </c>
       <c r="X24" s="1">
-        <v>-4.6114178173602731</v>
+        <v>-0.69171267260404101</v>
       </c>
       <c r="Y24" s="1">
-        <v>-3.8178860043603975</v>
+        <v>-0.57268290065405958</v>
       </c>
       <c r="Z24" s="1">
-        <v>-3.3873813831752297</v>
+        <v>-0.50810720747628446</v>
       </c>
       <c r="AA24" s="1">
-        <v>-3.934491911904153</v>
+        <v>-0.59017378678562293</v>
       </c>
     </row>
     <row r="25" spans="1:27" x14ac:dyDescent="0.2">
@@ -75690,76 +75658,76 @@
         <v>2</v>
       </c>
       <c r="D25" s="1">
-        <v>3.2029657078982186</v>
+        <v>0.48044485618473276</v>
       </c>
       <c r="E25" s="1">
-        <v>4.157372115819693</v>
+        <v>0.62360581737295395</v>
       </c>
       <c r="F25" s="1">
-        <v>5.0943160076075893</v>
+        <v>0.76414740114113844</v>
       </c>
       <c r="G25" s="1">
-        <v>4.8143831273846223</v>
+        <v>0.7221574691076933</v>
       </c>
       <c r="H25" s="1">
-        <v>5.8370482736291303</v>
+        <v>0.87555724104436961</v>
       </c>
       <c r="I25" s="1">
-        <v>5.7707556841918519</v>
+        <v>0.86561335262877781</v>
       </c>
       <c r="J25" s="1">
-        <v>5.5551564016754389</v>
+        <v>0.83327346025131577</v>
       </c>
       <c r="K25" s="1">
-        <v>6.5908127986478391</v>
+        <v>0.98862191979717584</v>
       </c>
       <c r="L25" s="1">
-        <v>5.5136738644347894</v>
+        <v>0.8270510796652184</v>
       </c>
       <c r="M25" s="1">
-        <v>7.6998010470095934</v>
+        <v>1.154970157051439</v>
       </c>
       <c r="N25" s="1">
-        <v>6.7474604107928728</v>
+        <v>1.0121190616189311</v>
       </c>
       <c r="O25" s="1">
-        <v>6.3060193369090358</v>
+        <v>0.9459029005363554</v>
       </c>
       <c r="P25" s="1">
-        <v>6.7962999828971524</v>
+        <v>1.0194449974345727</v>
       </c>
       <c r="Q25" s="1">
-        <v>6.3821370488243936</v>
+        <v>0.95732055732365906</v>
       </c>
       <c r="R25" s="1">
-        <v>5.3947927272216711</v>
+        <v>0.80921890908325067</v>
       </c>
       <c r="S25" s="1">
-        <v>4.6295582026502426</v>
+        <v>0.69443373039753642</v>
       </c>
       <c r="T25" s="1">
-        <v>5.2188816750880092</v>
+        <v>0.78283225126320144</v>
       </c>
       <c r="U25" s="1">
-        <v>4.305174033320152</v>
+        <v>0.64577610499802274</v>
       </c>
       <c r="V25" s="1">
-        <v>4.1144804503335619</v>
+        <v>0.61717206755003429</v>
       </c>
       <c r="W25" s="1">
-        <v>4.3876523634291162</v>
+        <v>0.65814785451436753</v>
       </c>
       <c r="X25" s="1">
-        <v>3.8862055310075712</v>
+        <v>0.58293082965113574</v>
       </c>
       <c r="Y25" s="1">
-        <v>5.1138309245587736</v>
+        <v>0.76707463868381598</v>
       </c>
       <c r="Z25" s="1">
-        <v>3.2996112611704693</v>
+        <v>0.49494168917557041</v>
       </c>
       <c r="AA25" s="1">
-        <v>3.7563010194818314</v>
+        <v>0.56344515292227471</v>
       </c>
     </row>
     <row r="26" spans="1:27" x14ac:dyDescent="0.2">
@@ -75773,76 +75741,76 @@
         <v>3</v>
       </c>
       <c r="D26" s="1">
-        <v>2.1299362738500007</v>
+        <v>0.31949044107750008</v>
       </c>
       <c r="E26" s="1">
-        <v>2.15824854245</v>
+        <v>0.32373728136750002</v>
       </c>
       <c r="F26" s="1">
-        <v>1.7319459484800002</v>
+        <v>0.25979189227200006</v>
       </c>
       <c r="G26" s="1">
-        <v>1.7592706669999998</v>
+        <v>0.26389060004999998</v>
       </c>
       <c r="H26" s="1">
-        <v>1.4150392819200002</v>
+        <v>0.21225589228800001</v>
       </c>
       <c r="I26" s="1">
-        <v>1.1770868853333336</v>
+        <v>0.17656303280000002</v>
       </c>
       <c r="J26" s="1">
-        <v>1.3814618581499998</v>
+        <v>0.20721927872249996</v>
       </c>
       <c r="K26" s="1">
-        <v>0.24476026226666669</v>
+        <v>3.6714039340000004E-2</v>
       </c>
       <c r="L26" s="1">
-        <v>0.20884812666666666</v>
+        <v>3.1327219000000003E-2</v>
       </c>
       <c r="M26" s="1">
-        <v>0.32039739779666659</v>
+        <v>4.8059609669499993E-2</v>
       </c>
       <c r="N26" s="1">
-        <v>0.19830144048000001</v>
+        <v>2.9745216072000001E-2</v>
       </c>
       <c r="O26" s="1">
-        <v>0.25530323103999997</v>
+        <v>3.8295484655999995E-2</v>
       </c>
       <c r="P26" s="1">
-        <v>0.36825420734666675</v>
+        <v>5.5238131102000008E-2</v>
       </c>
       <c r="Q26" s="1">
-        <v>0.77146389320000008</v>
+        <v>0.11571958398000001</v>
       </c>
       <c r="R26" s="1">
-        <v>0.83099570399999989</v>
+        <v>0.12464935559999998</v>
       </c>
       <c r="S26" s="1">
-        <v>0.73938630149999984</v>
+        <v>0.11090794522499998</v>
       </c>
       <c r="T26" s="1">
-        <v>0.43256246165000006</v>
+        <v>6.4884369247500004E-2</v>
       </c>
       <c r="U26" s="1">
-        <v>0.88087313599999983</v>
+        <v>0.13213097039999996</v>
       </c>
       <c r="V26" s="1">
-        <v>0.48710292400000005</v>
+        <v>7.3065438600000004E-2</v>
       </c>
       <c r="W26" s="1">
-        <v>0.33213524255999993</v>
+        <v>4.982028638399999E-2</v>
       </c>
       <c r="X26" s="1">
-        <v>0.51477201600000011</v>
+        <v>7.7215802400000005E-2</v>
       </c>
       <c r="Y26" s="1">
-        <v>0.34121593795666666</v>
+        <v>5.1182390693500002E-2</v>
       </c>
       <c r="Z26" s="1">
-        <v>1.5247556439500001</v>
+        <v>0.22871334659250003</v>
       </c>
       <c r="AA26" s="1">
-        <v>1.8960262598199999</v>
+        <v>0.28440393897299998</v>
       </c>
     </row>
     <row r="27" spans="1:27" x14ac:dyDescent="0.2">
@@ -75856,76 +75824,76 @@
         <v>3</v>
       </c>
       <c r="D27" s="1">
-        <v>-4.3240975658981116</v>
+        <v>-0.64861463488471682</v>
       </c>
       <c r="E27" s="1">
-        <v>-4.9155146780804069</v>
+        <v>-0.73732720171206112</v>
       </c>
       <c r="F27" s="1">
-        <v>-3.9638744650856732</v>
+        <v>-0.59458116976285091</v>
       </c>
       <c r="G27" s="1">
-        <v>-4.9302090564762997</v>
+        <v>-0.73953135847144491</v>
       </c>
       <c r="H27" s="1">
-        <v>-6.5640575518643898</v>
+        <v>-0.98460863277965838</v>
       </c>
       <c r="I27" s="1">
-        <v>-6.2304758793992088</v>
+        <v>-0.93457138190988132</v>
       </c>
       <c r="J27" s="1">
-        <v>-5.4848588271815295</v>
+        <v>-0.82272882407722947</v>
       </c>
       <c r="K27" s="1">
-        <v>-6.5458147744641133</v>
+        <v>-0.98187221616961706</v>
       </c>
       <c r="L27" s="1">
-        <v>-6.9585525310791505</v>
+        <v>-1.0437828796618727</v>
       </c>
       <c r="M27" s="1">
-        <v>-8.8867359777467012</v>
+        <v>-1.333010396662005</v>
       </c>
       <c r="N27" s="1">
-        <v>-9.1557304587544763</v>
+        <v>-1.3733595688131714</v>
       </c>
       <c r="O27" s="1">
-        <v>-8.9765849119992431</v>
+        <v>-1.3464877367998864</v>
       </c>
       <c r="P27" s="1">
-        <v>-7.7093704945464516</v>
+        <v>-1.1564055741819677</v>
       </c>
       <c r="Q27" s="1">
-        <v>-7.5783177461106979</v>
+        <v>-1.1367476619166046</v>
       </c>
       <c r="R27" s="1">
-        <v>-7.5207282710941774</v>
+        <v>-1.1281092406641267</v>
       </c>
       <c r="S27" s="1">
-        <v>-6.2526843216015342</v>
+        <v>-0.93790264824023006</v>
       </c>
       <c r="T27" s="1">
-        <v>-5.9648443470689969</v>
+        <v>-0.89472665206034951</v>
       </c>
       <c r="U27" s="1">
-        <v>-5.2306099598482332</v>
+        <v>-0.78459149397723493</v>
       </c>
       <c r="V27" s="1">
-        <v>-3.2863822132436589</v>
+        <v>-0.49295733198654884</v>
       </c>
       <c r="W27" s="1">
-        <v>-4.1551942701128128</v>
+        <v>-0.6232791405169219</v>
       </c>
       <c r="X27" s="1">
-        <v>-4.4730752828394653</v>
+        <v>-0.67096129242591984</v>
       </c>
       <c r="Y27" s="1">
-        <v>-3.8560648644040008</v>
+        <v>-0.57840972966060011</v>
       </c>
       <c r="Z27" s="1">
-        <v>-3.2180123140164683</v>
+        <v>-0.48270184710247027</v>
       </c>
       <c r="AA27" s="1">
-        <v>-4.0131817501422367</v>
+        <v>-0.60197726252133543</v>
       </c>
     </row>
     <row r="28" spans="1:27" x14ac:dyDescent="0.2">
@@ -75939,76 +75907,76 @@
         <v>3</v>
       </c>
       <c r="D28" s="1">
-        <v>3.1068767366612722</v>
+        <v>0.46603151049919084</v>
       </c>
       <c r="E28" s="1">
-        <v>4.0326509523451035</v>
+        <v>0.6048976428517655</v>
       </c>
       <c r="F28" s="1">
-        <v>5.0943160076075893</v>
+        <v>0.76414740114113844</v>
       </c>
       <c r="G28" s="1">
-        <v>4.9588146212061597</v>
+        <v>0.74382219318092402</v>
       </c>
       <c r="H28" s="1">
-        <v>6.1289006873105869</v>
+        <v>0.91933510309658806</v>
       </c>
       <c r="I28" s="1">
-        <v>5.7130481273499329</v>
+        <v>0.85695721910249001</v>
       </c>
       <c r="J28" s="1">
-        <v>5.8329142217592107</v>
+        <v>0.87493713326388156</v>
       </c>
       <c r="K28" s="1">
-        <v>6.4589965426748828</v>
+        <v>0.9688494814012325</v>
       </c>
       <c r="L28" s="1">
-        <v>5.4585371257904418</v>
+        <v>0.81878056886856621</v>
       </c>
       <c r="M28" s="1">
-        <v>8.0847910993600749</v>
+        <v>1.2127186649040111</v>
       </c>
       <c r="N28" s="1">
-        <v>7.0173588272245881</v>
+        <v>1.0526038240836884</v>
       </c>
       <c r="O28" s="1">
-        <v>6.1168387568017657</v>
+        <v>0.91752581352026485</v>
       </c>
       <c r="P28" s="1">
-        <v>6.7962999828971524</v>
+        <v>1.0194449974345727</v>
       </c>
       <c r="Q28" s="1">
-        <v>6.6374225307773678</v>
+        <v>0.99561337961660512</v>
       </c>
       <c r="R28" s="1">
-        <v>5.3947927272216711</v>
+        <v>0.80921890908325067</v>
       </c>
       <c r="S28" s="1">
-        <v>4.5369670385972372</v>
+        <v>0.68054505578958557</v>
       </c>
       <c r="T28" s="1">
-        <v>5.0623152248353689</v>
+        <v>0.75934728372530536</v>
       </c>
       <c r="U28" s="1">
-        <v>4.5204327349861595</v>
+        <v>0.67806491024792392</v>
       </c>
       <c r="V28" s="1">
-        <v>4.1144804503335619</v>
+        <v>0.61717206755003429</v>
       </c>
       <c r="W28" s="1">
-        <v>4.3437758397948256</v>
+        <v>0.65156637596922384</v>
       </c>
       <c r="X28" s="1">
-        <v>4.0416537522478739</v>
+        <v>0.60624806283718102</v>
       </c>
       <c r="Y28" s="1">
-        <v>4.9604159968220101</v>
+        <v>0.74406239952330155</v>
       </c>
       <c r="Z28" s="1">
-        <v>3.3985995990055833</v>
+        <v>0.50978993985083743</v>
       </c>
       <c r="AA28" s="1">
-        <v>3.6436119888973764</v>
+        <v>0.54654179833460648</v>
       </c>
     </row>
     <row r="29" spans="1:27" x14ac:dyDescent="0.2">
@@ -76022,76 +75990,76 @@
         <v>1</v>
       </c>
       <c r="D29" s="1">
-        <v>1.8709565050000003</v>
+        <v>0.28064347575000004</v>
       </c>
       <c r="E29" s="1">
-        <v>1.9333673883333333</v>
+        <v>0.29000510825000003</v>
       </c>
       <c r="F29" s="1">
-        <v>1.7312170150000001</v>
+        <v>0.25968255225000003</v>
       </c>
       <c r="G29" s="1">
-        <v>1.6409495666666665</v>
+        <v>0.24614243499999997</v>
       </c>
       <c r="H29" s="1">
-        <v>1.3444217600000001</v>
+        <v>0.20166326400000001</v>
       </c>
       <c r="I29" s="1">
-        <v>1.1410536133333333</v>
+        <v>0.17115804200000001</v>
       </c>
       <c r="J29" s="1">
-        <v>1.3954160183333333</v>
+        <v>0.20931240275000002</v>
       </c>
       <c r="K29" s="1">
-        <v>0.24233689333333339</v>
+        <v>3.6350534000000004E-2</v>
       </c>
       <c r="L29" s="1">
-        <v>0.21311033333333332</v>
+        <v>3.1966549999999996E-2</v>
       </c>
       <c r="M29" s="1">
-        <v>0.3106844216666666</v>
+        <v>4.6602663249999988E-2</v>
       </c>
       <c r="N29" s="1">
-        <v>0.18297044333333334</v>
+        <v>2.7445566500000001E-2</v>
       </c>
       <c r="O29" s="1">
-        <v>0.22863694333333326</v>
+        <v>3.4295541499999985E-2</v>
       </c>
       <c r="P29" s="1">
-        <v>0.36426644833333338</v>
+        <v>5.4639967250000011E-2</v>
       </c>
       <c r="Q29" s="1">
-        <v>0.6711453283333334</v>
+        <v>0.10067179925</v>
       </c>
       <c r="R29" s="1">
-        <v>0.71605072000000003</v>
+        <v>0.107407608</v>
       </c>
       <c r="S29" s="1">
-        <v>0.70417742999999977</v>
+        <v>0.10562661449999997</v>
       </c>
       <c r="T29" s="1">
-        <v>0.39501522499999991</v>
+        <v>5.9252283749999989E-2</v>
       </c>
       <c r="U29" s="1">
-        <v>0.80464372999999989</v>
+        <v>0.12069655949999998</v>
       </c>
       <c r="V29" s="1">
-        <v>0.47219160999999993</v>
+        <v>7.0828741499999986E-2</v>
       </c>
       <c r="W29" s="1">
-        <v>0.33199545499999994</v>
+        <v>4.9799318249999988E-2</v>
       </c>
       <c r="X29" s="1">
-        <v>0.50415816000000002</v>
+        <v>7.5623724000000003E-2</v>
       </c>
       <c r="Y29" s="1">
-        <v>0.31159775166666664</v>
+        <v>4.6739662749999994E-2</v>
       </c>
       <c r="Z29" s="1">
-        <v>1.4222070316666668</v>
+        <v>0.21333105475000003</v>
       </c>
       <c r="AA29" s="1">
-        <v>1.7144726316666665</v>
+        <v>0.25717089474999999</v>
       </c>
     </row>
     <row r="30" spans="1:27" x14ac:dyDescent="0.2">
@@ -76105,76 +76073,76 @@
         <v>1</v>
       </c>
       <c r="D30" s="1">
-        <v>-4.2808565902391305</v>
+        <v>-0.64212848853586957</v>
       </c>
       <c r="E30" s="1">
-        <v>-4.9155146780804069</v>
+        <v>-0.73732720171206112</v>
       </c>
       <c r="F30" s="1">
-        <v>-3.8449582311331034</v>
+        <v>-0.57674373466996554</v>
       </c>
       <c r="G30" s="1">
-        <v>-5.1274174187353516</v>
+        <v>-0.76911261281030274</v>
       </c>
       <c r="H30" s="1">
-        <v>-6.8266198539389658</v>
+        <v>-1.023992978090845</v>
       </c>
       <c r="I30" s="1">
-        <v>-6.4796949145751768</v>
+        <v>-0.97195423718627649</v>
       </c>
       <c r="J30" s="1">
-        <v>-5.7591017685406056</v>
+        <v>-0.86386526528109076</v>
       </c>
       <c r="K30" s="1">
-        <v>-6.807647365442679</v>
+        <v>-1.0211471048164018</v>
       </c>
       <c r="L30" s="1">
-        <v>-7.1673091070115262</v>
+        <v>-1.075096366051729</v>
       </c>
       <c r="M30" s="1">
-        <v>-9.0644706973016351</v>
+        <v>-1.3596706045952451</v>
       </c>
       <c r="N30" s="1">
-        <v>-9.2472877633420207</v>
+        <v>-1.3870931645013029</v>
       </c>
       <c r="O30" s="1">
-        <v>-9.0663507611192351</v>
+        <v>-1.3599526141678853</v>
       </c>
       <c r="P30" s="1">
-        <v>-7.4009956747645935</v>
+        <v>-1.1101493512146889</v>
       </c>
       <c r="Q30" s="1">
-        <v>-7.2751850362662696</v>
+        <v>-1.0912777554399404</v>
       </c>
       <c r="R30" s="1">
-        <v>-7.6711428365160605</v>
+        <v>-1.1506714254774091</v>
       </c>
       <c r="S30" s="1">
-        <v>-6.3152111648175504</v>
+        <v>-0.94728167472263247</v>
       </c>
       <c r="T30" s="1">
-        <v>-6.0244927905396866</v>
+        <v>-0.90367391858095303</v>
       </c>
       <c r="U30" s="1">
-        <v>-5.3875282586436795</v>
+        <v>-0.80812923879655185</v>
       </c>
       <c r="V30" s="1">
-        <v>-3.1220631025814751</v>
+        <v>-0.46830946538722129</v>
       </c>
       <c r="W30" s="1">
-        <v>-4.1967462128139408</v>
+        <v>-0.62951193192209109</v>
       </c>
       <c r="X30" s="1">
-        <v>-4.2941522715258866</v>
+        <v>-0.64412284072888304</v>
       </c>
       <c r="Y30" s="1">
-        <v>-3.9717468103361209</v>
+        <v>-0.59576202155041813</v>
       </c>
       <c r="Z30" s="1">
-        <v>-3.2823725602967979</v>
+        <v>-0.49235588404451969</v>
       </c>
       <c r="AA30" s="1">
-        <v>-4.2138408376493484</v>
+        <v>-0.63207612564740223</v>
       </c>
     </row>
     <row r="31" spans="1:27" x14ac:dyDescent="0.2">
@@ -76188,76 +76156,76 @@
         <v>1</v>
       </c>
       <c r="D31" s="1">
-        <v>3.2311518061277229</v>
+        <v>0.48467277091915839</v>
       </c>
       <c r="E31" s="1">
-        <v>4.0729774618685539</v>
+        <v>0.61094661928028304</v>
       </c>
       <c r="F31" s="1">
-        <v>5.2980886479118929</v>
+        <v>0.79471329718678396</v>
       </c>
       <c r="G31" s="1">
-        <v>5.0579909136302827</v>
+        <v>0.75869863704454243</v>
       </c>
       <c r="H31" s="1">
-        <v>6.312767707929904</v>
+        <v>0.94691515618948563</v>
       </c>
       <c r="I31" s="1">
-        <v>5.5987871648029355</v>
+        <v>0.83981807472044034</v>
       </c>
       <c r="J31" s="1">
-        <v>5.5412685106712489</v>
+        <v>0.83119027660068734</v>
       </c>
       <c r="K31" s="1">
-        <v>6.4589965426748828</v>
+        <v>0.9688494814012325</v>
       </c>
       <c r="L31" s="1">
-        <v>5.5677078683062513</v>
+        <v>0.83515618024593774</v>
       </c>
       <c r="M31" s="1">
-        <v>8.4890306543280776</v>
+        <v>1.2733545981492116</v>
       </c>
       <c r="N31" s="1">
-        <v>6.8770116506800969</v>
+        <v>1.0315517476020146</v>
       </c>
       <c r="O31" s="1">
-        <v>6.1168387568017657</v>
+        <v>0.91752581352026485</v>
       </c>
       <c r="P31" s="1">
-        <v>7.0681519822130374</v>
+        <v>1.0602227973319556</v>
       </c>
       <c r="Q31" s="1">
-        <v>6.305551404238499</v>
+        <v>0.94583271063577479</v>
       </c>
       <c r="R31" s="1">
-        <v>5.3947927272216711</v>
+        <v>0.80921890908325067</v>
       </c>
       <c r="S31" s="1">
-        <v>4.7638153905270988</v>
+        <v>0.71457230857906484</v>
       </c>
       <c r="T31" s="1">
-        <v>5.0116920725870155</v>
+        <v>0.75175381088805238</v>
       </c>
       <c r="U31" s="1">
-        <v>4.4300240802864357</v>
+        <v>0.66450361204296537</v>
       </c>
       <c r="V31" s="1">
-        <v>4.1967700593402339</v>
+        <v>0.62951550890103503</v>
       </c>
       <c r="W31" s="1">
-        <v>4.4740891149886695</v>
+        <v>0.6711133672483004</v>
       </c>
       <c r="X31" s="1">
-        <v>4.1224868272928319</v>
+        <v>0.61837302409392481</v>
       </c>
       <c r="Y31" s="1">
-        <v>4.8116035169173497</v>
+        <v>0.72174052753760243</v>
       </c>
       <c r="Z31" s="1">
-        <v>3.4325855949956394</v>
+        <v>0.51488783924934589</v>
       </c>
       <c r="AA31" s="1">
-        <v>3.6800481087863499</v>
+        <v>0.55200721631795246</v>
       </c>
     </row>
     <row r="32" spans="1:27" x14ac:dyDescent="0.2">
@@ -76271,76 +76239,76 @@
         <v>2</v>
       </c>
       <c r="D32" s="1">
-        <v>1.8522469399500003</v>
+        <v>0.27783704099250006</v>
       </c>
       <c r="E32" s="1">
-        <v>2.0300357577500003</v>
+        <v>0.30450536366250003</v>
       </c>
       <c r="F32" s="1">
-        <v>1.7312170150000001</v>
+        <v>0.25968255225000003</v>
       </c>
       <c r="G32" s="1">
-        <v>1.5589020883333331</v>
+        <v>0.23383531324999995</v>
       </c>
       <c r="H32" s="1">
-        <v>1.3309775424000001</v>
+        <v>0.19964663136000002</v>
       </c>
       <c r="I32" s="1">
-        <v>1.0840009326666669</v>
+        <v>0.16260013990000002</v>
       </c>
       <c r="J32" s="1">
-        <v>1.3395993775999999</v>
+        <v>0.20093990664</v>
       </c>
       <c r="K32" s="1">
-        <v>0.2496070001333334</v>
+        <v>3.7441050020000012E-2</v>
       </c>
       <c r="L32" s="1">
-        <v>0.21311033333333332</v>
+        <v>3.1966549999999996E-2</v>
       </c>
       <c r="M32" s="1">
-        <v>0.30447073323333324</v>
+        <v>4.5670609984999985E-2</v>
       </c>
       <c r="N32" s="1">
-        <v>0.18114073890000001</v>
+        <v>2.7171110835000001E-2</v>
       </c>
       <c r="O32" s="1">
-        <v>0.23092331276666658</v>
+        <v>3.463849691499999E-2</v>
       </c>
       <c r="P32" s="1">
-        <v>0.3606237838500001</v>
+        <v>5.4093567577500015E-2</v>
       </c>
       <c r="Q32" s="1">
-        <v>0.66443387504999996</v>
+        <v>9.9665081257499982E-2</v>
       </c>
       <c r="R32" s="1">
-        <v>0.72321122719999986</v>
+        <v>0.10848168407999999</v>
       </c>
       <c r="S32" s="1">
-        <v>0.67601033279999989</v>
+        <v>0.10140154991999999</v>
       </c>
       <c r="T32" s="1">
-        <v>0.39501522499999991</v>
+        <v>5.9252283749999989E-2</v>
       </c>
       <c r="U32" s="1">
-        <v>0.84487591649999982</v>
+        <v>0.12673138747499996</v>
       </c>
       <c r="V32" s="1">
-        <v>0.45330394560000004</v>
+        <v>6.7995591840000008E-2</v>
       </c>
       <c r="W32" s="1">
-        <v>0.33863536409999989</v>
+        <v>5.0795304614999981E-2</v>
       </c>
       <c r="X32" s="1">
-        <v>0.48399183360000003</v>
+        <v>7.2598775040000008E-2</v>
       </c>
       <c r="Y32" s="1">
-        <v>0.29913384159999995</v>
+        <v>4.4870076239999994E-2</v>
       </c>
       <c r="Z32" s="1">
-        <v>1.4079849613500002</v>
+        <v>0.21119774420250001</v>
       </c>
       <c r="AA32" s="1">
-        <v>1.7144726316666665</v>
+        <v>0.25717089474999999</v>
       </c>
     </row>
     <row r="33" spans="1:27" x14ac:dyDescent="0.2">
@@ -76354,76 +76322,76 @@
         <v>2</v>
       </c>
       <c r="D33" s="1">
-        <v>-4.1952394584343473</v>
+        <v>-0.62928591876515205</v>
       </c>
       <c r="E33" s="1">
-        <v>-4.8172043845187993</v>
+        <v>-0.72258065767781987</v>
       </c>
       <c r="F33" s="1">
-        <v>-3.7680590665104408</v>
+        <v>-0.56520885997656611</v>
       </c>
       <c r="G33" s="1">
-        <v>-4.9735948961732896</v>
+        <v>-0.74603923442599351</v>
       </c>
       <c r="H33" s="1">
-        <v>-7.1679508466359136</v>
+        <v>-1.0751926269953871</v>
       </c>
       <c r="I33" s="1">
-        <v>-6.2853040671379219</v>
+        <v>-0.94279561007068824</v>
       </c>
       <c r="J33" s="1">
-        <v>-5.8742838039114176</v>
+        <v>-0.88114257058671264</v>
       </c>
       <c r="K33" s="1">
-        <v>-6.7395708917882517</v>
+        <v>-1.0109356337682378</v>
       </c>
       <c r="L33" s="1">
-        <v>-6.9522898338011805</v>
+        <v>-1.0428434750701769</v>
       </c>
       <c r="M33" s="1">
-        <v>-8.7925365763825862</v>
+        <v>-1.3188804864573878</v>
       </c>
       <c r="N33" s="1">
-        <v>-8.7849233751749178</v>
+        <v>-1.3177385062762377</v>
       </c>
       <c r="O33" s="1">
-        <v>-9.5196682991751977</v>
+        <v>-1.4279502448762798</v>
       </c>
       <c r="P33" s="1">
-        <v>-7.6230255450075317</v>
+        <v>-1.1434538317511298</v>
       </c>
       <c r="Q33" s="1">
-        <v>-7.4206887369915941</v>
+        <v>-1.1131033105487391</v>
       </c>
       <c r="R33" s="1">
-        <v>-7.977988549976704</v>
+        <v>-1.1966982824965056</v>
       </c>
       <c r="S33" s="1">
-        <v>-6.5678196114102514</v>
+        <v>-0.9851729417115378</v>
       </c>
       <c r="T33" s="1">
-        <v>-5.9642478626342905</v>
+        <v>-0.89463717939514353</v>
       </c>
       <c r="U33" s="1">
-        <v>-5.3336529760572438</v>
+        <v>-0.80004794640858656</v>
       </c>
       <c r="V33" s="1">
-        <v>-3.1532837336072901</v>
+        <v>-0.47299256004109347</v>
       </c>
       <c r="W33" s="1">
-        <v>-4.1967462128139408</v>
+        <v>-0.62951193192209109</v>
       </c>
       <c r="X33" s="1">
-        <v>-4.3800353169564046</v>
+        <v>-0.6570052975434606</v>
       </c>
       <c r="Y33" s="1">
-        <v>-4.170334150852927</v>
+        <v>-0.62555012262793908</v>
       </c>
       <c r="Z33" s="1">
-        <v>-3.4464911883116378</v>
+        <v>-0.51697367824674567</v>
       </c>
       <c r="AA33" s="1">
-        <v>-4.0452872041433752</v>
+        <v>-0.60679308062150628</v>
       </c>
     </row>
     <row r="34" spans="1:27" x14ac:dyDescent="0.2">
@@ -76437,76 +76405,76 @@
         <v>2</v>
       </c>
       <c r="D34" s="1">
-        <v>3.0695942158213367</v>
+        <v>0.46043913237320055</v>
       </c>
       <c r="E34" s="1">
-        <v>4.1951667857246102</v>
+        <v>0.62927501785869155</v>
       </c>
       <c r="F34" s="1">
-        <v>5.0331842155162985</v>
+        <v>0.75497763232744475</v>
       </c>
       <c r="G34" s="1">
-        <v>4.8556712770850723</v>
+        <v>0.72835069156276089</v>
       </c>
       <c r="H34" s="1">
-        <v>5.9971293225334099</v>
+        <v>0.89956939838001149</v>
       </c>
       <c r="I34" s="1">
-        <v>5.7667507797470234</v>
+        <v>0.86501261696205345</v>
       </c>
       <c r="J34" s="1">
-        <v>5.319617770244399</v>
+        <v>0.79794266553665982</v>
       </c>
       <c r="K34" s="1">
-        <v>6.1360467155411387</v>
+        <v>0.92040700733117087</v>
       </c>
       <c r="L34" s="1">
-        <v>5.7904161830385013</v>
+        <v>0.86856242745577517</v>
       </c>
       <c r="M34" s="1">
-        <v>8.0645791216116738</v>
+        <v>1.209686868241751</v>
       </c>
       <c r="N34" s="1">
-        <v>6.5331610681460921</v>
+        <v>0.97997416022191375</v>
       </c>
       <c r="O34" s="1">
-        <v>6.422680694641854</v>
+        <v>0.96340210419627803</v>
       </c>
       <c r="P34" s="1">
-        <v>7.209515021857297</v>
+        <v>1.0814272532785947</v>
       </c>
       <c r="Q34" s="1">
-        <v>6.431662432323269</v>
+        <v>0.96474936484849039</v>
       </c>
       <c r="R34" s="1">
-        <v>5.5026885817661055</v>
+        <v>0.82540328726491585</v>
       </c>
       <c r="S34" s="1">
-        <v>4.7638153905270988</v>
+        <v>0.71457230857906484</v>
       </c>
       <c r="T34" s="1">
-        <v>5.0618089933128854</v>
+        <v>0.75927134899693283</v>
       </c>
       <c r="U34" s="1">
-        <v>4.2971233578778429</v>
+        <v>0.64456850368167651</v>
       </c>
       <c r="V34" s="1">
-        <v>4.3226731611204405</v>
+        <v>0.64840097416806608</v>
       </c>
       <c r="W34" s="1">
-        <v>4.563570897288443</v>
+        <v>0.6845356345932665</v>
       </c>
       <c r="X34" s="1">
-        <v>3.91636248592819</v>
+        <v>0.58745437288922853</v>
       </c>
       <c r="Y34" s="1">
-        <v>4.763487481748176</v>
+        <v>0.71452312226222647</v>
       </c>
       <c r="Z34" s="1">
-        <v>3.2609563152458576</v>
+        <v>0.48914344728687864</v>
       </c>
       <c r="AA34" s="1">
-        <v>3.7904495520499402</v>
+        <v>0.568567432807491</v>
       </c>
     </row>
     <row r="35" spans="1:27" x14ac:dyDescent="0.2">
@@ -76520,76 +76488,76 @@
         <v>3</v>
       </c>
       <c r="D35" s="1">
-        <v>1.8522469399500003</v>
+        <v>0.27783704099250006</v>
       </c>
       <c r="E35" s="1">
-        <v>2.1112371880600005</v>
+        <v>0.31668557820900006</v>
       </c>
       <c r="F35" s="1">
-        <v>1.7312170150000001</v>
+        <v>0.25968255225000003</v>
       </c>
       <c r="G35" s="1">
-        <v>1.5277240465666664</v>
+        <v>0.22915860698499996</v>
       </c>
       <c r="H35" s="1">
-        <v>1.2644286652800003</v>
+        <v>0.18966429979200003</v>
       </c>
       <c r="I35" s="1">
-        <v>1.0623209140133334</v>
+        <v>0.15934813710200002</v>
       </c>
       <c r="J35" s="1">
-        <v>1.27261940872</v>
+        <v>0.19089291130799999</v>
       </c>
       <c r="K35" s="1">
-        <v>0.24461486013066677</v>
+        <v>3.6692229019600016E-2</v>
       </c>
       <c r="L35" s="1">
-        <v>0.21311033333333332</v>
+        <v>3.1966549999999996E-2</v>
       </c>
       <c r="M35" s="1">
-        <v>0.3075154405656666</v>
+        <v>4.612731608484999E-2</v>
       </c>
       <c r="N35" s="1">
-        <v>0.190197775845</v>
+        <v>2.8529666376750001E-2</v>
       </c>
       <c r="O35" s="1">
-        <v>0.22861407963899993</v>
+        <v>3.4292111945849989E-2</v>
       </c>
       <c r="P35" s="1">
-        <v>0.37865497304250012</v>
+        <v>5.6798245956375018E-2</v>
       </c>
       <c r="Q35" s="1">
-        <v>0.67772255255099989</v>
+        <v>0.10165838288264999</v>
       </c>
       <c r="R35" s="1">
-        <v>0.73767545174399984</v>
+        <v>0.11065131776159998</v>
       </c>
       <c r="S35" s="1">
-        <v>0.6557300228159999</v>
+        <v>9.8359503422399991E-2</v>
       </c>
       <c r="T35" s="1">
-        <v>0.40686568174999999</v>
+        <v>6.1029852262499996E-2</v>
       </c>
       <c r="U35" s="1">
-        <v>0.81952963900499975</v>
+        <v>0.12292944585074997</v>
       </c>
       <c r="V35" s="1">
-        <v>0.471436103424</v>
+        <v>7.07154155136E-2</v>
       </c>
       <c r="W35" s="1">
-        <v>0.32847630317699988</v>
+        <v>4.9271445476549984E-2</v>
       </c>
       <c r="X35" s="1">
-        <v>0.45979224192000001</v>
+        <v>6.8968836288000004E-2</v>
       </c>
       <c r="Y35" s="1">
-        <v>0.29614250318399998</v>
+        <v>4.44213754776E-2</v>
       </c>
       <c r="Z35" s="1">
-        <v>1.4361446605770001</v>
+        <v>0.21542169908655001</v>
       </c>
       <c r="AA35" s="1">
-        <v>1.6973279053500001</v>
+        <v>0.25459918580250002</v>
       </c>
     </row>
     <row r="36" spans="1:27" x14ac:dyDescent="0.2">
@@ -76603,76 +76571,76 @@
         <v>3</v>
       </c>
       <c r="D36" s="1">
-        <v>-4.405001431356065</v>
+        <v>-0.66075021470340967</v>
       </c>
       <c r="E36" s="1">
-        <v>-5.0580646037447394</v>
+        <v>-0.75870969056171089</v>
       </c>
       <c r="F36" s="1">
-        <v>-3.8811008385057537</v>
+        <v>-0.5821651257758631</v>
       </c>
       <c r="G36" s="1">
-        <v>-5.0730667940967562</v>
+        <v>-0.7609600191145135</v>
       </c>
       <c r="H36" s="1">
-        <v>-7.3113098635686322</v>
+        <v>-1.0966964795352949</v>
       </c>
       <c r="I36" s="1">
-        <v>-6.5995692704948183</v>
+        <v>-0.98993539057422275</v>
       </c>
       <c r="J36" s="1">
-        <v>-5.6980552897940742</v>
+        <v>-0.85470829346911115</v>
       </c>
       <c r="K36" s="1">
-        <v>-6.8743623096240176</v>
+        <v>-1.0311543464436026</v>
       </c>
       <c r="L36" s="1">
-        <v>-6.8827669354631693</v>
+        <v>-1.0324150403194754</v>
       </c>
       <c r="M36" s="1">
-        <v>-8.52876047909111</v>
+        <v>-1.2793140718636664</v>
       </c>
       <c r="N36" s="1">
-        <v>-8.3456772064161751</v>
+        <v>-1.2518515809624262</v>
       </c>
       <c r="O36" s="1">
-        <v>-9.3292749331916927</v>
+        <v>-1.399391239978754</v>
       </c>
       <c r="P36" s="1">
-        <v>-7.2418742677571544</v>
+        <v>-1.0862811401635732</v>
       </c>
       <c r="Q36" s="1">
-        <v>-7.3464818496216786</v>
+        <v>-1.1019722774432519</v>
       </c>
       <c r="R36" s="1">
-        <v>-8.3768879774755387</v>
+        <v>-1.2565331966213309</v>
       </c>
       <c r="S36" s="1">
-        <v>-6.76485419975256</v>
+        <v>-1.0147281299628841</v>
       </c>
       <c r="T36" s="1">
-        <v>-5.6660354695025745</v>
+        <v>-0.84990532042538613</v>
       </c>
       <c r="U36" s="1">
-        <v>-5.6003356248601044</v>
+        <v>-0.84005034372901566</v>
       </c>
       <c r="V36" s="1">
-        <v>-3.1848165709433629</v>
+        <v>-0.47772248564150444</v>
       </c>
       <c r="W36" s="1">
-        <v>-4.2806811370702187</v>
+        <v>-0.64210217056053276</v>
       </c>
       <c r="X36" s="1">
-        <v>-4.2486342574477112</v>
+        <v>-0.6372951386171567</v>
       </c>
       <c r="Y36" s="1">
-        <v>-4.0035207848188099</v>
+        <v>-0.60052811772282144</v>
       </c>
       <c r="Z36" s="1">
-        <v>-3.5843508358441034</v>
+        <v>-0.53765262537661551</v>
       </c>
       <c r="AA36" s="1">
-        <v>-3.964381460060507</v>
+        <v>-0.59465721900907609</v>
       </c>
     </row>
     <row r="37" spans="1:27" x14ac:dyDescent="0.2">
@@ -76686,77 +76654,1013 @@
         <v>3</v>
       </c>
       <c r="D37" s="1">
-        <v>3.0695942158213367</v>
+        <v>0.46043913237320055</v>
       </c>
       <c r="E37" s="1">
-        <v>4.1112634500101182</v>
+        <v>0.61668951750151779</v>
       </c>
       <c r="F37" s="1">
-        <v>5.0331842155162985</v>
+        <v>0.75497763232744475</v>
       </c>
       <c r="G37" s="1">
-        <v>4.6128877132308181</v>
+        <v>0.69193315698462277</v>
       </c>
       <c r="H37" s="1">
-        <v>6.1770432022094122</v>
+        <v>0.92655648033141191</v>
       </c>
       <c r="I37" s="1">
-        <v>6.0550883187343745</v>
+        <v>0.90826324781015622</v>
       </c>
       <c r="J37" s="1">
-        <v>5.5324024810541745</v>
+        <v>0.82986037215812625</v>
       </c>
       <c r="K37" s="1">
-        <v>6.2587676498519604</v>
+        <v>0.93881514747779404</v>
       </c>
       <c r="L37" s="1">
-        <v>5.7904161830385013</v>
+        <v>0.86856242745577517</v>
       </c>
       <c r="M37" s="1">
-        <v>8.2258707040439045</v>
+        <v>1.2338806056065859</v>
       </c>
       <c r="N37" s="1">
-        <v>6.794487510871936</v>
+        <v>1.0191731266307904</v>
       </c>
       <c r="O37" s="1">
-        <v>6.6153611154811083</v>
+        <v>0.99230416732216631</v>
       </c>
       <c r="P37" s="1">
-        <v>6.8490392707644334</v>
+        <v>1.0273558906146651</v>
       </c>
       <c r="Q37" s="1">
-        <v>6.1100793107071061</v>
+        <v>0.91651189660606591</v>
       </c>
       <c r="R37" s="1">
-        <v>5.6127423534014271</v>
+        <v>0.84191135301021414</v>
       </c>
       <c r="S37" s="1">
-        <v>4.6685390827165572</v>
+        <v>0.70028086240748366</v>
       </c>
       <c r="T37" s="1">
-        <v>5.1630451731791434</v>
+        <v>0.77445677597687146</v>
       </c>
       <c r="U37" s="1">
-        <v>4.1682096571415084</v>
+        <v>0.62523144857122626</v>
       </c>
       <c r="V37" s="1">
-        <v>4.4955800875652576</v>
+        <v>0.67433701313478855</v>
       </c>
       <c r="W37" s="1">
-        <v>4.4722994793426736</v>
+        <v>0.67084492190140099</v>
       </c>
       <c r="X37" s="1">
-        <v>3.8771988610689081</v>
+        <v>0.58157982916033624</v>
       </c>
       <c r="Y37" s="1">
-        <v>4.763487481748176</v>
+        <v>0.71452312226222647</v>
       </c>
       <c r="Z37" s="1">
-        <v>3.1305180626360229</v>
+        <v>0.46957770939540344</v>
       </c>
       <c r="AA37" s="1">
-        <v>3.7904495520499402</v>
-      </c>
+        <v>0.568567432807491</v>
+      </c>
+    </row>
+    <row r="38" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="D38" s="1"/>
+      <c r="E38" s="1"/>
+      <c r="F38" s="1"/>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
+      <c r="I38" s="1"/>
+      <c r="J38" s="1"/>
+      <c r="K38" s="1"/>
+      <c r="L38" s="1"/>
+      <c r="M38" s="1"/>
+      <c r="N38" s="1"/>
+      <c r="O38" s="1"/>
+      <c r="P38" s="1"/>
+      <c r="Q38" s="1"/>
+      <c r="R38" s="1"/>
+      <c r="S38" s="1"/>
+      <c r="T38" s="1"/>
+      <c r="U38" s="1"/>
+      <c r="V38" s="1"/>
+      <c r="W38" s="1"/>
+      <c r="X38" s="1"/>
+      <c r="Y38" s="1"/>
+      <c r="Z38" s="1"/>
+      <c r="AA38" s="1"/>
+    </row>
+    <row r="39" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="D39" s="1"/>
+      <c r="E39" s="1"/>
+      <c r="F39" s="1"/>
+      <c r="G39" s="1"/>
+      <c r="H39" s="1"/>
+      <c r="I39" s="1"/>
+      <c r="J39" s="1"/>
+      <c r="K39" s="1"/>
+      <c r="L39" s="1"/>
+      <c r="M39" s="1"/>
+      <c r="N39" s="1"/>
+      <c r="O39" s="1"/>
+      <c r="P39" s="1"/>
+      <c r="Q39" s="1"/>
+      <c r="R39" s="1"/>
+      <c r="S39" s="1"/>
+      <c r="T39" s="1"/>
+      <c r="U39" s="1"/>
+      <c r="V39" s="1"/>
+      <c r="W39" s="1"/>
+      <c r="X39" s="1"/>
+      <c r="Y39" s="1"/>
+      <c r="Z39" s="1"/>
+      <c r="AA39" s="1"/>
+    </row>
+    <row r="40" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="D40" s="1"/>
+      <c r="E40" s="1"/>
+      <c r="F40" s="1"/>
+      <c r="G40" s="1"/>
+      <c r="H40" s="1"/>
+      <c r="I40" s="1"/>
+      <c r="J40" s="1"/>
+      <c r="K40" s="1"/>
+      <c r="L40" s="1"/>
+      <c r="M40" s="1"/>
+      <c r="N40" s="1"/>
+      <c r="O40" s="1"/>
+      <c r="P40" s="1"/>
+      <c r="Q40" s="1"/>
+      <c r="R40" s="1"/>
+      <c r="S40" s="1"/>
+      <c r="T40" s="1"/>
+      <c r="U40" s="1"/>
+      <c r="V40" s="1"/>
+      <c r="W40" s="1"/>
+      <c r="X40" s="1"/>
+      <c r="Y40" s="1"/>
+      <c r="Z40" s="1"/>
+      <c r="AA40" s="1"/>
+    </row>
+    <row r="41" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="D41" s="1"/>
+      <c r="E41" s="1"/>
+      <c r="F41" s="1"/>
+      <c r="G41" s="1"/>
+      <c r="H41" s="1"/>
+      <c r="I41" s="1"/>
+      <c r="J41" s="1"/>
+      <c r="K41" s="1"/>
+      <c r="L41" s="1"/>
+      <c r="M41" s="1"/>
+      <c r="N41" s="1"/>
+      <c r="O41" s="1"/>
+      <c r="P41" s="1"/>
+      <c r="Q41" s="1"/>
+      <c r="R41" s="1"/>
+      <c r="S41" s="1"/>
+      <c r="T41" s="1"/>
+      <c r="U41" s="1"/>
+      <c r="V41" s="1"/>
+      <c r="W41" s="1"/>
+      <c r="X41" s="1"/>
+      <c r="Y41" s="1"/>
+      <c r="Z41" s="1"/>
+      <c r="AA41" s="1"/>
+    </row>
+    <row r="42" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="D42" s="1"/>
+      <c r="E42" s="1"/>
+      <c r="F42" s="1"/>
+      <c r="G42" s="1"/>
+      <c r="H42" s="1"/>
+      <c r="I42" s="1"/>
+      <c r="J42" s="1"/>
+      <c r="K42" s="1"/>
+      <c r="L42" s="1"/>
+      <c r="M42" s="1"/>
+      <c r="N42" s="1"/>
+      <c r="O42" s="1"/>
+      <c r="P42" s="1"/>
+      <c r="Q42" s="1"/>
+      <c r="R42" s="1"/>
+      <c r="S42" s="1"/>
+      <c r="T42" s="1"/>
+      <c r="U42" s="1"/>
+      <c r="V42" s="1"/>
+      <c r="W42" s="1"/>
+      <c r="X42" s="1"/>
+      <c r="Y42" s="1"/>
+      <c r="Z42" s="1"/>
+      <c r="AA42" s="1"/>
+    </row>
+    <row r="43" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="D43" s="1"/>
+      <c r="E43" s="1"/>
+      <c r="F43" s="1"/>
+      <c r="G43" s="1"/>
+      <c r="H43" s="1"/>
+      <c r="I43" s="1"/>
+      <c r="J43" s="1"/>
+      <c r="K43" s="1"/>
+      <c r="L43" s="1"/>
+      <c r="M43" s="1"/>
+      <c r="N43" s="1"/>
+      <c r="O43" s="1"/>
+      <c r="P43" s="1"/>
+      <c r="Q43" s="1"/>
+      <c r="R43" s="1"/>
+      <c r="S43" s="1"/>
+      <c r="T43" s="1"/>
+      <c r="U43" s="1"/>
+      <c r="V43" s="1"/>
+      <c r="W43" s="1"/>
+      <c r="X43" s="1"/>
+      <c r="Y43" s="1"/>
+      <c r="Z43" s="1"/>
+      <c r="AA43" s="1"/>
+    </row>
+    <row r="44" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="D44" s="1"/>
+      <c r="E44" s="1"/>
+      <c r="F44" s="1"/>
+      <c r="G44" s="1"/>
+      <c r="H44" s="1"/>
+      <c r="I44" s="1"/>
+      <c r="J44" s="1"/>
+      <c r="K44" s="1"/>
+      <c r="L44" s="1"/>
+      <c r="M44" s="1"/>
+      <c r="N44" s="1"/>
+      <c r="O44" s="1"/>
+      <c r="P44" s="1"/>
+      <c r="Q44" s="1"/>
+      <c r="R44" s="1"/>
+      <c r="S44" s="1"/>
+      <c r="T44" s="1"/>
+      <c r="U44" s="1"/>
+      <c r="V44" s="1"/>
+      <c r="W44" s="1"/>
+      <c r="X44" s="1"/>
+      <c r="Y44" s="1"/>
+      <c r="Z44" s="1"/>
+      <c r="AA44" s="1"/>
+    </row>
+    <row r="45" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="D45" s="1"/>
+      <c r="E45" s="1"/>
+      <c r="F45" s="1"/>
+      <c r="G45" s="1"/>
+      <c r="H45" s="1"/>
+      <c r="I45" s="1"/>
+      <c r="J45" s="1"/>
+      <c r="K45" s="1"/>
+      <c r="L45" s="1"/>
+      <c r="M45" s="1"/>
+      <c r="N45" s="1"/>
+      <c r="O45" s="1"/>
+      <c r="P45" s="1"/>
+      <c r="Q45" s="1"/>
+      <c r="R45" s="1"/>
+      <c r="S45" s="1"/>
+      <c r="T45" s="1"/>
+      <c r="U45" s="1"/>
+      <c r="V45" s="1"/>
+      <c r="W45" s="1"/>
+      <c r="X45" s="1"/>
+      <c r="Y45" s="1"/>
+      <c r="Z45" s="1"/>
+      <c r="AA45" s="1"/>
+    </row>
+    <row r="46" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="D46" s="1"/>
+      <c r="E46" s="1"/>
+      <c r="F46" s="1"/>
+      <c r="G46" s="1"/>
+      <c r="H46" s="1"/>
+      <c r="I46" s="1"/>
+      <c r="J46" s="1"/>
+      <c r="K46" s="1"/>
+      <c r="L46" s="1"/>
+      <c r="M46" s="1"/>
+      <c r="N46" s="1"/>
+      <c r="O46" s="1"/>
+      <c r="P46" s="1"/>
+      <c r="Q46" s="1"/>
+      <c r="R46" s="1"/>
+      <c r="S46" s="1"/>
+      <c r="T46" s="1"/>
+      <c r="U46" s="1"/>
+      <c r="V46" s="1"/>
+      <c r="W46" s="1"/>
+      <c r="X46" s="1"/>
+      <c r="Y46" s="1"/>
+      <c r="Z46" s="1"/>
+      <c r="AA46" s="1"/>
+    </row>
+    <row r="47" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="D47" s="1"/>
+      <c r="E47" s="1"/>
+      <c r="F47" s="1"/>
+      <c r="G47" s="1"/>
+      <c r="H47" s="1"/>
+      <c r="I47" s="1"/>
+      <c r="J47" s="1"/>
+      <c r="K47" s="1"/>
+      <c r="L47" s="1"/>
+      <c r="M47" s="1"/>
+      <c r="N47" s="1"/>
+      <c r="O47" s="1"/>
+      <c r="P47" s="1"/>
+      <c r="Q47" s="1"/>
+      <c r="R47" s="1"/>
+      <c r="S47" s="1"/>
+      <c r="T47" s="1"/>
+      <c r="U47" s="1"/>
+      <c r="V47" s="1"/>
+      <c r="W47" s="1"/>
+      <c r="X47" s="1"/>
+      <c r="Y47" s="1"/>
+      <c r="Z47" s="1"/>
+      <c r="AA47" s="1"/>
+    </row>
+    <row r="48" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="D48" s="1"/>
+      <c r="E48" s="1"/>
+      <c r="F48" s="1"/>
+      <c r="G48" s="1"/>
+      <c r="H48" s="1"/>
+      <c r="I48" s="1"/>
+      <c r="J48" s="1"/>
+      <c r="K48" s="1"/>
+      <c r="L48" s="1"/>
+      <c r="M48" s="1"/>
+      <c r="N48" s="1"/>
+      <c r="O48" s="1"/>
+      <c r="P48" s="1"/>
+      <c r="Q48" s="1"/>
+      <c r="R48" s="1"/>
+      <c r="S48" s="1"/>
+      <c r="T48" s="1"/>
+      <c r="U48" s="1"/>
+      <c r="V48" s="1"/>
+      <c r="W48" s="1"/>
+      <c r="X48" s="1"/>
+      <c r="Y48" s="1"/>
+      <c r="Z48" s="1"/>
+      <c r="AA48" s="1"/>
+    </row>
+    <row r="49" spans="4:27" x14ac:dyDescent="0.2">
+      <c r="D49" s="1"/>
+      <c r="E49" s="1"/>
+      <c r="F49" s="1"/>
+      <c r="G49" s="1"/>
+      <c r="H49" s="1"/>
+      <c r="I49" s="1"/>
+      <c r="J49" s="1"/>
+      <c r="K49" s="1"/>
+      <c r="L49" s="1"/>
+      <c r="M49" s="1"/>
+      <c r="N49" s="1"/>
+      <c r="O49" s="1"/>
+      <c r="P49" s="1"/>
+      <c r="Q49" s="1"/>
+      <c r="R49" s="1"/>
+      <c r="S49" s="1"/>
+      <c r="T49" s="1"/>
+      <c r="U49" s="1"/>
+      <c r="V49" s="1"/>
+      <c r="W49" s="1"/>
+      <c r="X49" s="1"/>
+      <c r="Y49" s="1"/>
+      <c r="Z49" s="1"/>
+      <c r="AA49" s="1"/>
+    </row>
+    <row r="50" spans="4:27" x14ac:dyDescent="0.2">
+      <c r="D50" s="1"/>
+      <c r="E50" s="1"/>
+      <c r="F50" s="1"/>
+      <c r="G50" s="1"/>
+      <c r="H50" s="1"/>
+      <c r="I50" s="1"/>
+      <c r="J50" s="1"/>
+      <c r="K50" s="1"/>
+      <c r="L50" s="1"/>
+      <c r="M50" s="1"/>
+      <c r="N50" s="1"/>
+      <c r="O50" s="1"/>
+      <c r="P50" s="1"/>
+      <c r="Q50" s="1"/>
+      <c r="R50" s="1"/>
+      <c r="S50" s="1"/>
+      <c r="T50" s="1"/>
+      <c r="U50" s="1"/>
+      <c r="V50" s="1"/>
+      <c r="W50" s="1"/>
+      <c r="X50" s="1"/>
+      <c r="Y50" s="1"/>
+      <c r="Z50" s="1"/>
+      <c r="AA50" s="1"/>
+    </row>
+    <row r="51" spans="4:27" x14ac:dyDescent="0.2">
+      <c r="D51" s="1"/>
+      <c r="E51" s="1"/>
+      <c r="F51" s="1"/>
+      <c r="G51" s="1"/>
+      <c r="H51" s="1"/>
+      <c r="I51" s="1"/>
+      <c r="J51" s="1"/>
+      <c r="K51" s="1"/>
+      <c r="L51" s="1"/>
+      <c r="M51" s="1"/>
+      <c r="N51" s="1"/>
+      <c r="O51" s="1"/>
+      <c r="P51" s="1"/>
+      <c r="Q51" s="1"/>
+      <c r="R51" s="1"/>
+      <c r="S51" s="1"/>
+      <c r="T51" s="1"/>
+      <c r="U51" s="1"/>
+      <c r="V51" s="1"/>
+      <c r="W51" s="1"/>
+      <c r="X51" s="1"/>
+      <c r="Y51" s="1"/>
+      <c r="Z51" s="1"/>
+      <c r="AA51" s="1"/>
+    </row>
+    <row r="52" spans="4:27" x14ac:dyDescent="0.2">
+      <c r="D52" s="1"/>
+      <c r="E52" s="1"/>
+      <c r="F52" s="1"/>
+      <c r="G52" s="1"/>
+      <c r="H52" s="1"/>
+      <c r="I52" s="1"/>
+      <c r="J52" s="1"/>
+      <c r="K52" s="1"/>
+      <c r="L52" s="1"/>
+      <c r="M52" s="1"/>
+      <c r="N52" s="1"/>
+      <c r="O52" s="1"/>
+      <c r="P52" s="1"/>
+      <c r="Q52" s="1"/>
+      <c r="R52" s="1"/>
+      <c r="S52" s="1"/>
+      <c r="T52" s="1"/>
+      <c r="U52" s="1"/>
+      <c r="V52" s="1"/>
+      <c r="W52" s="1"/>
+      <c r="X52" s="1"/>
+      <c r="Y52" s="1"/>
+      <c r="Z52" s="1"/>
+      <c r="AA52" s="1"/>
+    </row>
+    <row r="53" spans="4:27" x14ac:dyDescent="0.2">
+      <c r="D53" s="1"/>
+      <c r="E53" s="1"/>
+      <c r="F53" s="1"/>
+      <c r="G53" s="1"/>
+      <c r="H53" s="1"/>
+      <c r="I53" s="1"/>
+      <c r="J53" s="1"/>
+      <c r="K53" s="1"/>
+      <c r="L53" s="1"/>
+      <c r="M53" s="1"/>
+      <c r="N53" s="1"/>
+      <c r="O53" s="1"/>
+      <c r="P53" s="1"/>
+      <c r="Q53" s="1"/>
+      <c r="R53" s="1"/>
+      <c r="S53" s="1"/>
+      <c r="T53" s="1"/>
+      <c r="U53" s="1"/>
+      <c r="V53" s="1"/>
+      <c r="W53" s="1"/>
+      <c r="X53" s="1"/>
+      <c r="Y53" s="1"/>
+      <c r="Z53" s="1"/>
+      <c r="AA53" s="1"/>
+    </row>
+    <row r="54" spans="4:27" x14ac:dyDescent="0.2">
+      <c r="D54" s="1"/>
+      <c r="E54" s="1"/>
+      <c r="F54" s="1"/>
+      <c r="G54" s="1"/>
+      <c r="H54" s="1"/>
+      <c r="I54" s="1"/>
+      <c r="J54" s="1"/>
+      <c r="K54" s="1"/>
+      <c r="L54" s="1"/>
+      <c r="M54" s="1"/>
+      <c r="N54" s="1"/>
+      <c r="O54" s="1"/>
+      <c r="P54" s="1"/>
+      <c r="Q54" s="1"/>
+      <c r="R54" s="1"/>
+      <c r="S54" s="1"/>
+      <c r="T54" s="1"/>
+      <c r="U54" s="1"/>
+      <c r="V54" s="1"/>
+      <c r="W54" s="1"/>
+      <c r="X54" s="1"/>
+      <c r="Y54" s="1"/>
+      <c r="Z54" s="1"/>
+      <c r="AA54" s="1"/>
+    </row>
+    <row r="55" spans="4:27" x14ac:dyDescent="0.2">
+      <c r="D55" s="1"/>
+      <c r="E55" s="1"/>
+      <c r="F55" s="1"/>
+      <c r="G55" s="1"/>
+      <c r="H55" s="1"/>
+      <c r="I55" s="1"/>
+      <c r="J55" s="1"/>
+      <c r="K55" s="1"/>
+      <c r="L55" s="1"/>
+      <c r="M55" s="1"/>
+      <c r="N55" s="1"/>
+      <c r="O55" s="1"/>
+      <c r="P55" s="1"/>
+      <c r="Q55" s="1"/>
+      <c r="R55" s="1"/>
+      <c r="S55" s="1"/>
+      <c r="T55" s="1"/>
+      <c r="U55" s="1"/>
+      <c r="V55" s="1"/>
+      <c r="W55" s="1"/>
+      <c r="X55" s="1"/>
+      <c r="Y55" s="1"/>
+      <c r="Z55" s="1"/>
+      <c r="AA55" s="1"/>
+    </row>
+    <row r="56" spans="4:27" x14ac:dyDescent="0.2">
+      <c r="D56" s="1"/>
+      <c r="E56" s="1"/>
+      <c r="F56" s="1"/>
+      <c r="G56" s="1"/>
+      <c r="H56" s="1"/>
+      <c r="I56" s="1"/>
+      <c r="J56" s="1"/>
+      <c r="K56" s="1"/>
+      <c r="L56" s="1"/>
+      <c r="M56" s="1"/>
+      <c r="N56" s="1"/>
+      <c r="O56" s="1"/>
+      <c r="P56" s="1"/>
+      <c r="Q56" s="1"/>
+      <c r="R56" s="1"/>
+      <c r="S56" s="1"/>
+      <c r="T56" s="1"/>
+      <c r="U56" s="1"/>
+      <c r="V56" s="1"/>
+      <c r="W56" s="1"/>
+      <c r="X56" s="1"/>
+      <c r="Y56" s="1"/>
+      <c r="Z56" s="1"/>
+      <c r="AA56" s="1"/>
+    </row>
+    <row r="57" spans="4:27" x14ac:dyDescent="0.2">
+      <c r="D57" s="1"/>
+      <c r="E57" s="1"/>
+      <c r="F57" s="1"/>
+      <c r="G57" s="1"/>
+      <c r="H57" s="1"/>
+      <c r="I57" s="1"/>
+      <c r="J57" s="1"/>
+      <c r="K57" s="1"/>
+      <c r="L57" s="1"/>
+      <c r="M57" s="1"/>
+      <c r="N57" s="1"/>
+      <c r="O57" s="1"/>
+      <c r="P57" s="1"/>
+      <c r="Q57" s="1"/>
+      <c r="R57" s="1"/>
+      <c r="S57" s="1"/>
+      <c r="T57" s="1"/>
+      <c r="U57" s="1"/>
+      <c r="V57" s="1"/>
+      <c r="W57" s="1"/>
+      <c r="X57" s="1"/>
+      <c r="Y57" s="1"/>
+      <c r="Z57" s="1"/>
+      <c r="AA57" s="1"/>
+    </row>
+    <row r="58" spans="4:27" x14ac:dyDescent="0.2">
+      <c r="D58" s="1"/>
+      <c r="E58" s="1"/>
+      <c r="F58" s="1"/>
+      <c r="G58" s="1"/>
+      <c r="H58" s="1"/>
+      <c r="I58" s="1"/>
+      <c r="J58" s="1"/>
+      <c r="K58" s="1"/>
+      <c r="L58" s="1"/>
+      <c r="M58" s="1"/>
+      <c r="N58" s="1"/>
+      <c r="O58" s="1"/>
+      <c r="P58" s="1"/>
+      <c r="Q58" s="1"/>
+      <c r="R58" s="1"/>
+      <c r="S58" s="1"/>
+      <c r="T58" s="1"/>
+      <c r="U58" s="1"/>
+      <c r="V58" s="1"/>
+      <c r="W58" s="1"/>
+      <c r="X58" s="1"/>
+      <c r="Y58" s="1"/>
+      <c r="Z58" s="1"/>
+      <c r="AA58" s="1"/>
+    </row>
+    <row r="59" spans="4:27" x14ac:dyDescent="0.2">
+      <c r="D59" s="1"/>
+      <c r="E59" s="1"/>
+      <c r="F59" s="1"/>
+      <c r="G59" s="1"/>
+      <c r="H59" s="1"/>
+      <c r="I59" s="1"/>
+      <c r="J59" s="1"/>
+      <c r="K59" s="1"/>
+      <c r="L59" s="1"/>
+      <c r="M59" s="1"/>
+      <c r="N59" s="1"/>
+      <c r="O59" s="1"/>
+      <c r="P59" s="1"/>
+      <c r="Q59" s="1"/>
+      <c r="R59" s="1"/>
+      <c r="S59" s="1"/>
+      <c r="T59" s="1"/>
+      <c r="U59" s="1"/>
+      <c r="V59" s="1"/>
+      <c r="W59" s="1"/>
+      <c r="X59" s="1"/>
+      <c r="Y59" s="1"/>
+      <c r="Z59" s="1"/>
+      <c r="AA59" s="1"/>
+    </row>
+    <row r="60" spans="4:27" x14ac:dyDescent="0.2">
+      <c r="D60" s="1"/>
+      <c r="E60" s="1"/>
+      <c r="F60" s="1"/>
+      <c r="G60" s="1"/>
+      <c r="H60" s="1"/>
+      <c r="I60" s="1"/>
+      <c r="J60" s="1"/>
+      <c r="K60" s="1"/>
+      <c r="L60" s="1"/>
+      <c r="M60" s="1"/>
+      <c r="N60" s="1"/>
+      <c r="O60" s="1"/>
+      <c r="P60" s="1"/>
+      <c r="Q60" s="1"/>
+      <c r="R60" s="1"/>
+      <c r="S60" s="1"/>
+      <c r="T60" s="1"/>
+      <c r="U60" s="1"/>
+      <c r="V60" s="1"/>
+      <c r="W60" s="1"/>
+      <c r="X60" s="1"/>
+      <c r="Y60" s="1"/>
+      <c r="Z60" s="1"/>
+      <c r="AA60" s="1"/>
+    </row>
+    <row r="61" spans="4:27" x14ac:dyDescent="0.2">
+      <c r="D61" s="1"/>
+      <c r="E61" s="1"/>
+      <c r="F61" s="1"/>
+      <c r="G61" s="1"/>
+      <c r="H61" s="1"/>
+      <c r="I61" s="1"/>
+      <c r="J61" s="1"/>
+      <c r="K61" s="1"/>
+      <c r="L61" s="1"/>
+      <c r="M61" s="1"/>
+      <c r="N61" s="1"/>
+      <c r="O61" s="1"/>
+      <c r="P61" s="1"/>
+      <c r="Q61" s="1"/>
+      <c r="R61" s="1"/>
+      <c r="S61" s="1"/>
+      <c r="T61" s="1"/>
+      <c r="U61" s="1"/>
+      <c r="V61" s="1"/>
+      <c r="W61" s="1"/>
+      <c r="X61" s="1"/>
+      <c r="Y61" s="1"/>
+      <c r="Z61" s="1"/>
+      <c r="AA61" s="1"/>
+    </row>
+    <row r="62" spans="4:27" x14ac:dyDescent="0.2">
+      <c r="D62" s="1"/>
+      <c r="E62" s="1"/>
+      <c r="F62" s="1"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
+      <c r="I62" s="1"/>
+      <c r="J62" s="1"/>
+      <c r="K62" s="1"/>
+      <c r="L62" s="1"/>
+      <c r="M62" s="1"/>
+      <c r="N62" s="1"/>
+      <c r="O62" s="1"/>
+      <c r="P62" s="1"/>
+      <c r="Q62" s="1"/>
+      <c r="R62" s="1"/>
+      <c r="S62" s="1"/>
+      <c r="T62" s="1"/>
+      <c r="U62" s="1"/>
+      <c r="V62" s="1"/>
+      <c r="W62" s="1"/>
+      <c r="X62" s="1"/>
+      <c r="Y62" s="1"/>
+      <c r="Z62" s="1"/>
+      <c r="AA62" s="1"/>
+    </row>
+    <row r="63" spans="4:27" x14ac:dyDescent="0.2">
+      <c r="D63" s="1"/>
+      <c r="E63" s="1"/>
+      <c r="F63" s="1"/>
+      <c r="G63" s="1"/>
+      <c r="H63" s="1"/>
+      <c r="I63" s="1"/>
+      <c r="J63" s="1"/>
+      <c r="K63" s="1"/>
+      <c r="L63" s="1"/>
+      <c r="M63" s="1"/>
+      <c r="N63" s="1"/>
+      <c r="O63" s="1"/>
+      <c r="P63" s="1"/>
+      <c r="Q63" s="1"/>
+      <c r="R63" s="1"/>
+      <c r="S63" s="1"/>
+      <c r="T63" s="1"/>
+      <c r="U63" s="1"/>
+      <c r="V63" s="1"/>
+      <c r="W63" s="1"/>
+      <c r="X63" s="1"/>
+      <c r="Y63" s="1"/>
+      <c r="Z63" s="1"/>
+      <c r="AA63" s="1"/>
+    </row>
+    <row r="64" spans="4:27" x14ac:dyDescent="0.2">
+      <c r="D64" s="1"/>
+      <c r="E64" s="1"/>
+      <c r="F64" s="1"/>
+      <c r="G64" s="1"/>
+      <c r="H64" s="1"/>
+      <c r="I64" s="1"/>
+      <c r="J64" s="1"/>
+      <c r="K64" s="1"/>
+      <c r="L64" s="1"/>
+      <c r="M64" s="1"/>
+      <c r="N64" s="1"/>
+      <c r="O64" s="1"/>
+      <c r="P64" s="1"/>
+      <c r="Q64" s="1"/>
+      <c r="R64" s="1"/>
+      <c r="S64" s="1"/>
+      <c r="T64" s="1"/>
+      <c r="U64" s="1"/>
+      <c r="V64" s="1"/>
+      <c r="W64" s="1"/>
+      <c r="X64" s="1"/>
+      <c r="Y64" s="1"/>
+      <c r="Z64" s="1"/>
+      <c r="AA64" s="1"/>
+    </row>
+    <row r="65" spans="4:27" x14ac:dyDescent="0.2">
+      <c r="D65" s="1"/>
+      <c r="E65" s="1"/>
+      <c r="F65" s="1"/>
+      <c r="G65" s="1"/>
+      <c r="H65" s="1"/>
+      <c r="I65" s="1"/>
+      <c r="J65" s="1"/>
+      <c r="K65" s="1"/>
+      <c r="L65" s="1"/>
+      <c r="M65" s="1"/>
+      <c r="N65" s="1"/>
+      <c r="O65" s="1"/>
+      <c r="P65" s="1"/>
+      <c r="Q65" s="1"/>
+      <c r="R65" s="1"/>
+      <c r="S65" s="1"/>
+      <c r="T65" s="1"/>
+      <c r="U65" s="1"/>
+      <c r="V65" s="1"/>
+      <c r="W65" s="1"/>
+      <c r="X65" s="1"/>
+      <c r="Y65" s="1"/>
+      <c r="Z65" s="1"/>
+      <c r="AA65" s="1"/>
+    </row>
+    <row r="66" spans="4:27" x14ac:dyDescent="0.2">
+      <c r="D66" s="1"/>
+      <c r="E66" s="1"/>
+      <c r="F66" s="1"/>
+      <c r="G66" s="1"/>
+      <c r="H66" s="1"/>
+      <c r="I66" s="1"/>
+      <c r="J66" s="1"/>
+      <c r="K66" s="1"/>
+      <c r="L66" s="1"/>
+      <c r="M66" s="1"/>
+      <c r="N66" s="1"/>
+      <c r="O66" s="1"/>
+      <c r="P66" s="1"/>
+      <c r="Q66" s="1"/>
+      <c r="R66" s="1"/>
+      <c r="S66" s="1"/>
+      <c r="T66" s="1"/>
+      <c r="U66" s="1"/>
+      <c r="V66" s="1"/>
+      <c r="W66" s="1"/>
+      <c r="X66" s="1"/>
+      <c r="Y66" s="1"/>
+      <c r="Z66" s="1"/>
+      <c r="AA66" s="1"/>
+    </row>
+    <row r="67" spans="4:27" x14ac:dyDescent="0.2">
+      <c r="D67" s="1"/>
+      <c r="E67" s="1"/>
+      <c r="F67" s="1"/>
+      <c r="G67" s="1"/>
+      <c r="H67" s="1"/>
+      <c r="I67" s="1"/>
+      <c r="J67" s="1"/>
+      <c r="K67" s="1"/>
+      <c r="L67" s="1"/>
+      <c r="M67" s="1"/>
+      <c r="N67" s="1"/>
+      <c r="O67" s="1"/>
+      <c r="P67" s="1"/>
+      <c r="Q67" s="1"/>
+      <c r="R67" s="1"/>
+      <c r="S67" s="1"/>
+      <c r="T67" s="1"/>
+      <c r="U67" s="1"/>
+      <c r="V67" s="1"/>
+      <c r="W67" s="1"/>
+      <c r="X67" s="1"/>
+      <c r="Y67" s="1"/>
+      <c r="Z67" s="1"/>
+      <c r="AA67" s="1"/>
+    </row>
+    <row r="68" spans="4:27" x14ac:dyDescent="0.2">
+      <c r="D68" s="1"/>
+      <c r="E68" s="1"/>
+      <c r="F68" s="1"/>
+      <c r="G68" s="1"/>
+      <c r="H68" s="1"/>
+      <c r="I68" s="1"/>
+      <c r="J68" s="1"/>
+      <c r="K68" s="1"/>
+      <c r="L68" s="1"/>
+      <c r="M68" s="1"/>
+      <c r="N68" s="1"/>
+      <c r="O68" s="1"/>
+      <c r="P68" s="1"/>
+      <c r="Q68" s="1"/>
+      <c r="R68" s="1"/>
+      <c r="S68" s="1"/>
+      <c r="T68" s="1"/>
+      <c r="U68" s="1"/>
+      <c r="V68" s="1"/>
+      <c r="W68" s="1"/>
+      <c r="X68" s="1"/>
+      <c r="Y68" s="1"/>
+      <c r="Z68" s="1"/>
+      <c r="AA68" s="1"/>
+    </row>
+    <row r="69" spans="4:27" x14ac:dyDescent="0.2">
+      <c r="D69" s="1"/>
+      <c r="E69" s="1"/>
+      <c r="F69" s="1"/>
+      <c r="G69" s="1"/>
+      <c r="H69" s="1"/>
+      <c r="I69" s="1"/>
+      <c r="J69" s="1"/>
+      <c r="K69" s="1"/>
+      <c r="L69" s="1"/>
+      <c r="M69" s="1"/>
+      <c r="N69" s="1"/>
+      <c r="O69" s="1"/>
+      <c r="P69" s="1"/>
+      <c r="Q69" s="1"/>
+      <c r="R69" s="1"/>
+      <c r="S69" s="1"/>
+      <c r="T69" s="1"/>
+      <c r="U69" s="1"/>
+      <c r="V69" s="1"/>
+      <c r="W69" s="1"/>
+      <c r="X69" s="1"/>
+      <c r="Y69" s="1"/>
+      <c r="Z69" s="1"/>
+      <c r="AA69" s="1"/>
+    </row>
+    <row r="70" spans="4:27" x14ac:dyDescent="0.2">
+      <c r="D70" s="1"/>
+      <c r="E70" s="1"/>
+      <c r="F70" s="1"/>
+      <c r="G70" s="1"/>
+      <c r="H70" s="1"/>
+      <c r="I70" s="1"/>
+      <c r="J70" s="1"/>
+      <c r="K70" s="1"/>
+      <c r="L70" s="1"/>
+      <c r="M70" s="1"/>
+      <c r="N70" s="1"/>
+      <c r="O70" s="1"/>
+      <c r="P70" s="1"/>
+      <c r="Q70" s="1"/>
+      <c r="R70" s="1"/>
+      <c r="S70" s="1"/>
+      <c r="T70" s="1"/>
+      <c r="U70" s="1"/>
+      <c r="V70" s="1"/>
+      <c r="W70" s="1"/>
+      <c r="X70" s="1"/>
+      <c r="Y70" s="1"/>
+      <c r="Z70" s="1"/>
+      <c r="AA70" s="1"/>
+    </row>
+    <row r="71" spans="4:27" x14ac:dyDescent="0.2">
+      <c r="D71" s="1"/>
+      <c r="E71" s="1"/>
+      <c r="F71" s="1"/>
+      <c r="G71" s="1"/>
+      <c r="H71" s="1"/>
+      <c r="I71" s="1"/>
+      <c r="J71" s="1"/>
+      <c r="K71" s="1"/>
+      <c r="L71" s="1"/>
+      <c r="M71" s="1"/>
+      <c r="N71" s="1"/>
+      <c r="O71" s="1"/>
+      <c r="P71" s="1"/>
+      <c r="Q71" s="1"/>
+      <c r="R71" s="1"/>
+      <c r="S71" s="1"/>
+      <c r="T71" s="1"/>
+      <c r="U71" s="1"/>
+      <c r="V71" s="1"/>
+      <c r="W71" s="1"/>
+      <c r="X71" s="1"/>
+      <c r="Y71" s="1"/>
+      <c r="Z71" s="1"/>
+      <c r="AA71" s="1"/>
+    </row>
+    <row r="72" spans="4:27" x14ac:dyDescent="0.2">
+      <c r="D72" s="1"/>
+      <c r="E72" s="1"/>
+      <c r="F72" s="1"/>
+      <c r="G72" s="1"/>
+      <c r="H72" s="1"/>
+      <c r="I72" s="1"/>
+      <c r="J72" s="1"/>
+      <c r="K72" s="1"/>
+      <c r="L72" s="1"/>
+      <c r="M72" s="1"/>
+      <c r="N72" s="1"/>
+      <c r="O72" s="1"/>
+      <c r="P72" s="1"/>
+      <c r="Q72" s="1"/>
+      <c r="R72" s="1"/>
+      <c r="S72" s="1"/>
+      <c r="T72" s="1"/>
+      <c r="U72" s="1"/>
+      <c r="V72" s="1"/>
+      <c r="W72" s="1"/>
+      <c r="X72" s="1"/>
+      <c r="Y72" s="1"/>
+      <c r="Z72" s="1"/>
+      <c r="AA72" s="1"/>
+    </row>
+    <row r="73" spans="4:27" x14ac:dyDescent="0.2">
+      <c r="D73" s="1"/>
+      <c r="E73" s="1"/>
+      <c r="F73" s="1"/>
+      <c r="G73" s="1"/>
+      <c r="H73" s="1"/>
+      <c r="I73" s="1"/>
+      <c r="J73" s="1"/>
+      <c r="K73" s="1"/>
+      <c r="L73" s="1"/>
+      <c r="M73" s="1"/>
+      <c r="N73" s="1"/>
+      <c r="O73" s="1"/>
+      <c r="P73" s="1"/>
+      <c r="Q73" s="1"/>
+      <c r="R73" s="1"/>
+      <c r="S73" s="1"/>
+      <c r="T73" s="1"/>
+      <c r="U73" s="1"/>
+      <c r="V73" s="1"/>
+      <c r="W73" s="1"/>
+      <c r="X73" s="1"/>
+      <c r="Y73" s="1"/>
+      <c r="Z73" s="1"/>
+      <c r="AA73" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/CS1/case33_1/case33_operational_data.xlsx
+++ b/data/CS1/case33_1/case33_operational_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/micaelsimoes/PycharmProjects/shared-resources-planning/data/CS1/case33_1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A166F70-7DFC-0D40-80A0-A93C8AE5AD29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D231ED70-D9DE-1B4F-B199-E41F7211EACD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1000" yWindow="680" windowWidth="28400" windowHeight="18440" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1000" yWindow="680" windowWidth="28400" windowHeight="18440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Characterization" sheetId="2" r:id="rId1"/>
@@ -454,19 +454,21 @@
         <v>1</v>
       </c>
       <c r="B2" s="1">
-        <v>0.1</v>
+        <f>E2*2</f>
+        <v>0.2</v>
       </c>
       <c r="C2" s="1">
+        <f>F2</f>
         <v>0.06</v>
       </c>
       <c r="D2" s="2">
         <f>B2/SUM(B$2:B$33)</f>
         <v>2.6917900403768499E-2</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="1">
         <v>0.1</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="1">
         <v>0.06</v>
       </c>
     </row>
@@ -475,19 +477,21 @@
         <v>2</v>
       </c>
       <c r="B3" s="1">
+        <f t="shared" ref="B3:B33" si="0">E3*2</f>
+        <v>0.18</v>
+      </c>
+      <c r="C3" s="1">
+        <f t="shared" ref="C3:C33" si="1">F3</f>
+        <v>0.04</v>
+      </c>
+      <c r="D3" s="2">
+        <f t="shared" ref="D3:D33" si="2">B3/SUM(B$2:B$33)</f>
+        <v>2.4226110363391645E-2</v>
+      </c>
+      <c r="E3" s="1">
         <v>0.09</v>
       </c>
-      <c r="C3" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="D3" s="2">
-        <f t="shared" ref="D3:D33" si="0">B3/SUM(B$2:B$33)</f>
-        <v>2.4226110363391645E-2</v>
-      </c>
-      <c r="E3">
-        <v>0.09</v>
-      </c>
-      <c r="F3">
+      <c r="F3" s="1">
         <v>0.04</v>
       </c>
     </row>
@@ -496,19 +500,21 @@
         <v>3</v>
       </c>
       <c r="B4" s="1">
+        <f t="shared" si="0"/>
+        <v>0.24</v>
+      </c>
+      <c r="C4" s="1">
+        <f t="shared" si="1"/>
+        <v>0.08</v>
+      </c>
+      <c r="D4" s="2">
+        <f t="shared" si="2"/>
+        <v>3.2301480484522194E-2</v>
+      </c>
+      <c r="E4" s="1">
         <v>0.12</v>
       </c>
-      <c r="C4" s="1">
-        <v>0.08</v>
-      </c>
-      <c r="D4" s="2">
-        <f t="shared" si="0"/>
-        <v>3.2301480484522194E-2</v>
-      </c>
-      <c r="E4">
-        <v>0.12</v>
-      </c>
-      <c r="F4">
+      <c r="F4" s="1">
         <v>0.08</v>
       </c>
     </row>
@@ -517,19 +523,21 @@
         <v>4</v>
       </c>
       <c r="B5" s="1">
+        <f t="shared" si="0"/>
+        <v>0.12</v>
+      </c>
+      <c r="C5" s="1">
+        <f t="shared" si="1"/>
+        <v>0.03</v>
+      </c>
+      <c r="D5" s="2">
+        <f t="shared" si="2"/>
+        <v>1.6150740242261097E-2</v>
+      </c>
+      <c r="E5" s="1">
         <v>0.06</v>
       </c>
-      <c r="C5" s="1">
-        <v>0.03</v>
-      </c>
-      <c r="D5" s="2">
-        <f t="shared" si="0"/>
-        <v>1.6150740242261097E-2</v>
-      </c>
-      <c r="E5">
-        <v>0.06</v>
-      </c>
-      <c r="F5">
+      <c r="F5" s="1">
         <v>0.03</v>
       </c>
     </row>
@@ -538,19 +546,21 @@
         <v>5</v>
       </c>
       <c r="B6" s="1">
+        <f t="shared" si="0"/>
+        <v>0.12</v>
+      </c>
+      <c r="C6" s="1">
+        <f t="shared" si="1"/>
+        <v>0.02</v>
+      </c>
+      <c r="D6" s="2">
+        <f t="shared" si="2"/>
+        <v>1.6150740242261097E-2</v>
+      </c>
+      <c r="E6" s="1">
         <v>0.06</v>
       </c>
-      <c r="C6" s="1">
-        <v>0.02</v>
-      </c>
-      <c r="D6" s="2">
-        <f t="shared" si="0"/>
-        <v>1.6150740242261097E-2</v>
-      </c>
-      <c r="E6">
-        <v>0.06</v>
-      </c>
-      <c r="F6">
+      <c r="F6" s="1">
         <v>0.02</v>
       </c>
     </row>
@@ -559,19 +569,21 @@
         <v>6</v>
       </c>
       <c r="B7" s="1">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+      <c r="C7" s="1">
+        <f t="shared" si="1"/>
+        <v>0.1</v>
+      </c>
+      <c r="D7" s="2">
+        <f t="shared" si="2"/>
+        <v>5.3835800807536999E-2</v>
+      </c>
+      <c r="E7" s="1">
         <v>0.2</v>
       </c>
-      <c r="C7" s="1">
-        <v>0.1</v>
-      </c>
-      <c r="D7" s="2">
-        <f t="shared" si="0"/>
-        <v>5.3835800807536999E-2</v>
-      </c>
-      <c r="E7">
-        <v>0.2</v>
-      </c>
-      <c r="F7">
+      <c r="F7" s="1">
         <v>0.1</v>
       </c>
     </row>
@@ -580,19 +592,21 @@
         <v>7</v>
       </c>
       <c r="B8" s="1">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+      <c r="C8" s="1">
+        <f t="shared" si="1"/>
+        <v>0.1</v>
+      </c>
+      <c r="D8" s="2">
+        <f t="shared" si="2"/>
+        <v>5.3835800807536999E-2</v>
+      </c>
+      <c r="E8" s="1">
         <v>0.2</v>
       </c>
-      <c r="C8" s="1">
-        <v>0.1</v>
-      </c>
-      <c r="D8" s="2">
-        <f t="shared" si="0"/>
-        <v>5.3835800807536999E-2</v>
-      </c>
-      <c r="E8">
-        <v>0.2</v>
-      </c>
-      <c r="F8">
+      <c r="F8" s="1">
         <v>0.1</v>
       </c>
     </row>
@@ -601,19 +615,21 @@
         <v>8</v>
       </c>
       <c r="B9" s="1">
+        <f t="shared" si="0"/>
+        <v>0.12</v>
+      </c>
+      <c r="C9" s="1">
+        <f t="shared" si="1"/>
+        <v>0.02</v>
+      </c>
+      <c r="D9" s="2">
+        <f t="shared" si="2"/>
+        <v>1.6150740242261097E-2</v>
+      </c>
+      <c r="E9" s="1">
         <v>0.06</v>
       </c>
-      <c r="C9" s="1">
-        <v>0.02</v>
-      </c>
-      <c r="D9" s="2">
-        <f t="shared" si="0"/>
-        <v>1.6150740242261097E-2</v>
-      </c>
-      <c r="E9">
-        <v>0.06</v>
-      </c>
-      <c r="F9">
+      <c r="F9" s="1">
         <v>0.02</v>
       </c>
     </row>
@@ -622,19 +638,21 @@
         <v>9</v>
       </c>
       <c r="B10" s="1">
+        <f t="shared" si="0"/>
+        <v>0.12</v>
+      </c>
+      <c r="C10" s="1">
+        <f t="shared" si="1"/>
+        <v>0.02</v>
+      </c>
+      <c r="D10" s="2">
+        <f t="shared" si="2"/>
+        <v>1.6150740242261097E-2</v>
+      </c>
+      <c r="E10" s="1">
         <v>0.06</v>
       </c>
-      <c r="C10" s="1">
-        <v>0.02</v>
-      </c>
-      <c r="D10" s="2">
-        <f t="shared" si="0"/>
-        <v>1.6150740242261097E-2</v>
-      </c>
-      <c r="E10">
-        <v>0.06</v>
-      </c>
-      <c r="F10">
+      <c r="F10" s="1">
         <v>0.02</v>
       </c>
     </row>
@@ -643,19 +661,21 @@
         <v>10</v>
       </c>
       <c r="B11" s="1">
+        <f t="shared" si="0"/>
+        <v>0.09</v>
+      </c>
+      <c r="C11" s="1">
+        <f t="shared" si="1"/>
+        <v>0.03</v>
+      </c>
+      <c r="D11" s="2">
+        <f t="shared" si="2"/>
+        <v>1.2113055181695823E-2</v>
+      </c>
+      <c r="E11" s="1">
         <v>4.4999999999999998E-2</v>
       </c>
-      <c r="C11" s="1">
-        <v>0.03</v>
-      </c>
-      <c r="D11" s="2">
-        <f t="shared" si="0"/>
-        <v>1.2113055181695823E-2</v>
-      </c>
-      <c r="E11">
-        <v>4.4999999999999998E-2</v>
-      </c>
-      <c r="F11">
+      <c r="F11" s="1">
         <v>0.03</v>
       </c>
     </row>
@@ -664,19 +684,21 @@
         <v>11</v>
       </c>
       <c r="B12" s="1">
+        <f t="shared" si="0"/>
+        <v>0.12</v>
+      </c>
+      <c r="C12" s="1">
+        <f t="shared" si="1"/>
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="D12" s="2">
+        <f t="shared" si="2"/>
+        <v>1.6150740242261097E-2</v>
+      </c>
+      <c r="E12" s="1">
         <v>0.06</v>
       </c>
-      <c r="C12" s="1">
-        <v>3.5000000000000003E-2</v>
-      </c>
-      <c r="D12" s="2">
-        <f t="shared" si="0"/>
-        <v>1.6150740242261097E-2</v>
-      </c>
-      <c r="E12">
-        <v>0.06</v>
-      </c>
-      <c r="F12">
+      <c r="F12" s="1">
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
@@ -685,19 +707,21 @@
         <v>12</v>
       </c>
       <c r="B13" s="1">
+        <f t="shared" si="0"/>
+        <v>0.12</v>
+      </c>
+      <c r="C13" s="1">
+        <f t="shared" si="1"/>
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="D13" s="2">
+        <f t="shared" si="2"/>
+        <v>1.6150740242261097E-2</v>
+      </c>
+      <c r="E13" s="1">
         <v>0.06</v>
       </c>
-      <c r="C13" s="1">
-        <v>3.5000000000000003E-2</v>
-      </c>
-      <c r="D13" s="2">
-        <f t="shared" si="0"/>
-        <v>1.6150740242261097E-2</v>
-      </c>
-      <c r="E13">
-        <v>0.06</v>
-      </c>
-      <c r="F13">
+      <c r="F13" s="1">
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
@@ -706,19 +730,21 @@
         <v>13</v>
       </c>
       <c r="B14" s="1">
+        <f t="shared" si="0"/>
+        <v>0.24</v>
+      </c>
+      <c r="C14" s="1">
+        <f t="shared" si="1"/>
+        <v>0.08</v>
+      </c>
+      <c r="D14" s="2">
+        <f t="shared" si="2"/>
+        <v>3.2301480484522194E-2</v>
+      </c>
+      <c r="E14" s="1">
         <v>0.12</v>
       </c>
-      <c r="C14" s="1">
-        <v>0.08</v>
-      </c>
-      <c r="D14" s="2">
-        <f t="shared" si="0"/>
-        <v>3.2301480484522194E-2</v>
-      </c>
-      <c r="E14">
-        <v>0.12</v>
-      </c>
-      <c r="F14">
+      <c r="F14" s="1">
         <v>0.08</v>
       </c>
     </row>
@@ -727,19 +753,21 @@
         <v>14</v>
       </c>
       <c r="B15" s="1">
+        <f t="shared" si="0"/>
+        <v>0.12</v>
+      </c>
+      <c r="C15" s="1">
+        <f t="shared" si="1"/>
+        <v>0.01</v>
+      </c>
+      <c r="D15" s="2">
+        <f t="shared" si="2"/>
+        <v>1.6150740242261097E-2</v>
+      </c>
+      <c r="E15" s="1">
         <v>0.06</v>
       </c>
-      <c r="C15" s="1">
-        <v>0.01</v>
-      </c>
-      <c r="D15" s="2">
-        <f t="shared" si="0"/>
-        <v>1.6150740242261097E-2</v>
-      </c>
-      <c r="E15">
-        <v>0.06</v>
-      </c>
-      <c r="F15">
+      <c r="F15" s="1">
         <v>0.01</v>
       </c>
     </row>
@@ -748,19 +776,21 @@
         <v>15</v>
       </c>
       <c r="B16" s="1">
+        <f t="shared" si="0"/>
+        <v>0.12</v>
+      </c>
+      <c r="C16" s="1">
+        <f t="shared" si="1"/>
+        <v>0.02</v>
+      </c>
+      <c r="D16" s="2">
+        <f t="shared" si="2"/>
+        <v>1.6150740242261097E-2</v>
+      </c>
+      <c r="E16" s="1">
         <v>0.06</v>
       </c>
-      <c r="C16" s="1">
-        <v>0.02</v>
-      </c>
-      <c r="D16" s="2">
-        <f t="shared" si="0"/>
-        <v>1.6150740242261097E-2</v>
-      </c>
-      <c r="E16">
-        <v>0.06</v>
-      </c>
-      <c r="F16">
+      <c r="F16" s="1">
         <v>0.02</v>
       </c>
     </row>
@@ -769,19 +799,21 @@
         <v>16</v>
       </c>
       <c r="B17" s="1">
+        <f t="shared" si="0"/>
+        <v>0.12</v>
+      </c>
+      <c r="C17" s="1">
+        <f t="shared" si="1"/>
+        <v>0.02</v>
+      </c>
+      <c r="D17" s="2">
+        <f t="shared" si="2"/>
+        <v>1.6150740242261097E-2</v>
+      </c>
+      <c r="E17" s="1">
         <v>0.06</v>
       </c>
-      <c r="C17" s="1">
-        <v>0.02</v>
-      </c>
-      <c r="D17" s="2">
-        <f t="shared" si="0"/>
-        <v>1.6150740242261097E-2</v>
-      </c>
-      <c r="E17">
-        <v>0.06</v>
-      </c>
-      <c r="F17">
+      <c r="F17" s="1">
         <v>0.02</v>
       </c>
     </row>
@@ -790,19 +822,21 @@
         <v>17</v>
       </c>
       <c r="B18" s="1">
+        <f t="shared" si="0"/>
+        <v>0.18</v>
+      </c>
+      <c r="C18" s="1">
+        <f t="shared" si="1"/>
+        <v>0.04</v>
+      </c>
+      <c r="D18" s="2">
+        <f t="shared" si="2"/>
+        <v>2.4226110363391645E-2</v>
+      </c>
+      <c r="E18" s="1">
         <v>0.09</v>
       </c>
-      <c r="C18" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="D18" s="2">
-        <f t="shared" si="0"/>
-        <v>2.4226110363391645E-2</v>
-      </c>
-      <c r="E18">
-        <v>0.09</v>
-      </c>
-      <c r="F18">
+      <c r="F18" s="1">
         <v>0.04</v>
       </c>
     </row>
@@ -811,19 +845,21 @@
         <v>18</v>
       </c>
       <c r="B19" s="1">
+        <f t="shared" si="0"/>
+        <v>0.18</v>
+      </c>
+      <c r="C19" s="1">
+        <f t="shared" si="1"/>
+        <v>0.04</v>
+      </c>
+      <c r="D19" s="2">
+        <f t="shared" si="2"/>
+        <v>2.4226110363391645E-2</v>
+      </c>
+      <c r="E19" s="1">
         <v>0.09</v>
       </c>
-      <c r="C19" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="D19" s="2">
-        <f t="shared" si="0"/>
-        <v>2.4226110363391645E-2</v>
-      </c>
-      <c r="E19">
-        <v>0.09</v>
-      </c>
-      <c r="F19">
+      <c r="F19" s="1">
         <v>0.04</v>
       </c>
     </row>
@@ -832,19 +868,21 @@
         <v>19</v>
       </c>
       <c r="B20" s="1">
+        <f t="shared" si="0"/>
+        <v>0.18</v>
+      </c>
+      <c r="C20" s="1">
+        <f t="shared" si="1"/>
+        <v>0.04</v>
+      </c>
+      <c r="D20" s="2">
+        <f t="shared" si="2"/>
+        <v>2.4226110363391645E-2</v>
+      </c>
+      <c r="E20" s="1">
         <v>0.09</v>
       </c>
-      <c r="C20" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="D20" s="2">
-        <f t="shared" si="0"/>
-        <v>2.4226110363391645E-2</v>
-      </c>
-      <c r="E20">
-        <v>0.09</v>
-      </c>
-      <c r="F20">
+      <c r="F20" s="1">
         <v>0.04</v>
       </c>
     </row>
@@ -853,19 +891,21 @@
         <v>20</v>
       </c>
       <c r="B21" s="1">
+        <f t="shared" si="0"/>
+        <v>0.18</v>
+      </c>
+      <c r="C21" s="1">
+        <f t="shared" si="1"/>
+        <v>0.04</v>
+      </c>
+      <c r="D21" s="2">
+        <f t="shared" si="2"/>
+        <v>2.4226110363391645E-2</v>
+      </c>
+      <c r="E21" s="1">
         <v>0.09</v>
       </c>
-      <c r="C21" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="D21" s="2">
-        <f t="shared" si="0"/>
-        <v>2.4226110363391645E-2</v>
-      </c>
-      <c r="E21">
-        <v>0.09</v>
-      </c>
-      <c r="F21">
+      <c r="F21" s="1">
         <v>0.04</v>
       </c>
     </row>
@@ -874,19 +914,21 @@
         <v>21</v>
       </c>
       <c r="B22" s="1">
+        <f t="shared" si="0"/>
+        <v>0.18</v>
+      </c>
+      <c r="C22" s="1">
+        <f t="shared" si="1"/>
+        <v>0.04</v>
+      </c>
+      <c r="D22" s="2">
+        <f t="shared" si="2"/>
+        <v>2.4226110363391645E-2</v>
+      </c>
+      <c r="E22" s="1">
         <v>0.09</v>
       </c>
-      <c r="C22" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="D22" s="2">
-        <f t="shared" si="0"/>
-        <v>2.4226110363391645E-2</v>
-      </c>
-      <c r="E22">
-        <v>0.09</v>
-      </c>
-      <c r="F22">
+      <c r="F22" s="1">
         <v>0.04</v>
       </c>
     </row>
@@ -895,19 +937,21 @@
         <v>22</v>
       </c>
       <c r="B23" s="1">
+        <f t="shared" si="0"/>
+        <v>0.18</v>
+      </c>
+      <c r="C23" s="1">
+        <f t="shared" si="1"/>
+        <v>0.05</v>
+      </c>
+      <c r="D23" s="2">
+        <f t="shared" si="2"/>
+        <v>2.4226110363391645E-2</v>
+      </c>
+      <c r="E23" s="1">
         <v>0.09</v>
       </c>
-      <c r="C23" s="1">
-        <v>0.05</v>
-      </c>
-      <c r="D23" s="2">
-        <f t="shared" si="0"/>
-        <v>2.4226110363391645E-2</v>
-      </c>
-      <c r="E23">
-        <v>0.09</v>
-      </c>
-      <c r="F23">
+      <c r="F23" s="1">
         <v>0.05</v>
       </c>
     </row>
@@ -916,19 +960,21 @@
         <v>23</v>
       </c>
       <c r="B24" s="1">
+        <f t="shared" si="0"/>
+        <v>0.84</v>
+      </c>
+      <c r="C24" s="1">
+        <f t="shared" si="1"/>
+        <v>0.2</v>
+      </c>
+      <c r="D24" s="2">
+        <f t="shared" si="2"/>
+        <v>0.11305518169582769</v>
+      </c>
+      <c r="E24" s="1">
         <v>0.42</v>
       </c>
-      <c r="C24" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="D24" s="2">
-        <f t="shared" si="0"/>
-        <v>0.11305518169582769</v>
-      </c>
-      <c r="E24">
-        <v>0.42</v>
-      </c>
-      <c r="F24">
+      <c r="F24" s="1">
         <v>0.2</v>
       </c>
     </row>
@@ -937,19 +983,21 @@
         <v>24</v>
       </c>
       <c r="B25" s="1">
+        <f t="shared" si="0"/>
+        <v>0.84</v>
+      </c>
+      <c r="C25" s="1">
+        <f t="shared" si="1"/>
+        <v>0.2</v>
+      </c>
+      <c r="D25" s="2">
+        <f t="shared" si="2"/>
+        <v>0.11305518169582769</v>
+      </c>
+      <c r="E25" s="1">
         <v>0.42</v>
       </c>
-      <c r="C25" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="D25" s="2">
-        <f t="shared" si="0"/>
-        <v>0.11305518169582769</v>
-      </c>
-      <c r="E25">
-        <v>0.42</v>
-      </c>
-      <c r="F25">
+      <c r="F25" s="1">
         <v>0.2</v>
       </c>
     </row>
@@ -958,19 +1006,21 @@
         <v>25</v>
       </c>
       <c r="B26" s="1">
+        <f t="shared" si="0"/>
+        <v>0.12</v>
+      </c>
+      <c r="C26" s="1">
+        <f t="shared" si="1"/>
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="D26" s="2">
+        <f t="shared" si="2"/>
+        <v>1.6150740242261097E-2</v>
+      </c>
+      <c r="E26" s="1">
         <v>0.06</v>
       </c>
-      <c r="C26" s="1">
-        <v>2.5000000000000001E-2</v>
-      </c>
-      <c r="D26" s="2">
-        <f t="shared" si="0"/>
-        <v>1.6150740242261097E-2</v>
-      </c>
-      <c r="E26">
-        <v>0.06</v>
-      </c>
-      <c r="F26">
+      <c r="F26" s="1">
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
@@ -979,19 +1029,21 @@
         <v>26</v>
       </c>
       <c r="B27" s="1">
+        <f t="shared" si="0"/>
+        <v>0.12</v>
+      </c>
+      <c r="C27" s="1">
+        <f t="shared" si="1"/>
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="D27" s="2">
+        <f t="shared" si="2"/>
+        <v>1.6150740242261097E-2</v>
+      </c>
+      <c r="E27" s="1">
         <v>0.06</v>
       </c>
-      <c r="C27" s="1">
-        <v>2.5000000000000001E-2</v>
-      </c>
-      <c r="D27" s="2">
-        <f t="shared" si="0"/>
-        <v>1.6150740242261097E-2</v>
-      </c>
-      <c r="E27">
-        <v>0.06</v>
-      </c>
-      <c r="F27">
+      <c r="F27" s="1">
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
@@ -1000,19 +1052,21 @@
         <v>27</v>
       </c>
       <c r="B28" s="1">
+        <f t="shared" si="0"/>
+        <v>0.12</v>
+      </c>
+      <c r="C28" s="1">
+        <f t="shared" si="1"/>
+        <v>0.02</v>
+      </c>
+      <c r="D28" s="2">
+        <f t="shared" si="2"/>
+        <v>1.6150740242261097E-2</v>
+      </c>
+      <c r="E28" s="1">
         <v>0.06</v>
       </c>
-      <c r="C28" s="1">
-        <v>0.02</v>
-      </c>
-      <c r="D28" s="2">
-        <f t="shared" si="0"/>
-        <v>1.6150740242261097E-2</v>
-      </c>
-      <c r="E28">
-        <v>0.06</v>
-      </c>
-      <c r="F28">
+      <c r="F28" s="1">
         <v>0.02</v>
       </c>
     </row>
@@ -1021,19 +1075,21 @@
         <v>28</v>
       </c>
       <c r="B29" s="1">
+        <f t="shared" si="0"/>
+        <v>0.24</v>
+      </c>
+      <c r="C29" s="1">
+        <f t="shared" si="1"/>
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D29" s="2">
+        <f t="shared" si="2"/>
+        <v>3.2301480484522194E-2</v>
+      </c>
+      <c r="E29" s="1">
         <v>0.12</v>
       </c>
-      <c r="C29" s="1">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="D29" s="2">
-        <f t="shared" si="0"/>
-        <v>3.2301480484522194E-2</v>
-      </c>
-      <c r="E29">
-        <v>0.12</v>
-      </c>
-      <c r="F29">
+      <c r="F29" s="1">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
@@ -1042,19 +1098,21 @@
         <v>29</v>
       </c>
       <c r="B30" s="1">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+      <c r="C30" s="1">
+        <f t="shared" si="1"/>
+        <v>0.6</v>
+      </c>
+      <c r="D30" s="2">
+        <f t="shared" si="2"/>
+        <v>5.3835800807536999E-2</v>
+      </c>
+      <c r="E30" s="1">
         <v>0.2</v>
       </c>
-      <c r="C30" s="1">
-        <v>0.6</v>
-      </c>
-      <c r="D30" s="2">
-        <f t="shared" si="0"/>
-        <v>5.3835800807536999E-2</v>
-      </c>
-      <c r="E30">
-        <v>0.2</v>
-      </c>
-      <c r="F30">
+      <c r="F30" s="1">
         <v>0.6</v>
       </c>
     </row>
@@ -1063,19 +1121,21 @@
         <v>30</v>
       </c>
       <c r="B31" s="1">
+        <f t="shared" si="0"/>
+        <v>0.3</v>
+      </c>
+      <c r="C31" s="1">
+        <f t="shared" si="1"/>
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D31" s="2">
+        <f t="shared" si="2"/>
+        <v>4.0376850605652742E-2</v>
+      </c>
+      <c r="E31" s="1">
         <v>0.15</v>
       </c>
-      <c r="C31" s="1">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="D31" s="2">
-        <f t="shared" si="0"/>
-        <v>4.0376850605652742E-2</v>
-      </c>
-      <c r="E31">
-        <v>0.15</v>
-      </c>
-      <c r="F31">
+      <c r="F31" s="1">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
@@ -1084,19 +1144,21 @@
         <v>31</v>
       </c>
       <c r="B32" s="1">
+        <f t="shared" si="0"/>
+        <v>0.42</v>
+      </c>
+      <c r="C32" s="1">
+        <f t="shared" si="1"/>
+        <v>0.1</v>
+      </c>
+      <c r="D32" s="2">
+        <f t="shared" si="2"/>
+        <v>5.6527590847913846E-2</v>
+      </c>
+      <c r="E32" s="1">
         <v>0.21</v>
       </c>
-      <c r="C32" s="1">
-        <v>0.1</v>
-      </c>
-      <c r="D32" s="2">
-        <f t="shared" si="0"/>
-        <v>5.6527590847913846E-2</v>
-      </c>
-      <c r="E32">
-        <v>0.21</v>
-      </c>
-      <c r="F32">
+      <c r="F32" s="1">
         <v>0.1</v>
       </c>
     </row>
@@ -1105,19 +1167,21 @@
         <v>32</v>
       </c>
       <c r="B33" s="1">
+        <f t="shared" si="0"/>
+        <v>0.12</v>
+      </c>
+      <c r="C33" s="1">
+        <f t="shared" si="1"/>
+        <v>0.04</v>
+      </c>
+      <c r="D33" s="2">
+        <f t="shared" si="2"/>
+        <v>1.6150740242261097E-2</v>
+      </c>
+      <c r="E33" s="1">
         <v>0.06</v>
       </c>
-      <c r="C33" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="D33" s="2">
-        <f t="shared" si="0"/>
-        <v>1.6150740242261097E-2</v>
-      </c>
-      <c r="E33">
-        <v>0.06</v>
-      </c>
-      <c r="F33">
+      <c r="F33" s="1">
         <v>0.04</v>
       </c>
     </row>
@@ -73648,7 +73712,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8D12B52-98C9-449E-BF4A-23F7CAD72921}">
-  <dimension ref="A1:AA73"/>
+  <dimension ref="A1:AA37"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="27.83203125" bestFit="1" customWidth="1"/>
@@ -73749,76 +73813,76 @@
         <v>1</v>
       </c>
       <c r="D2" s="1">
-        <v>0.28269300000000003</v>
+        <v>0.56538600000000006</v>
       </c>
       <c r="E2" s="1">
-        <v>0.29212300000000002</v>
+        <v>0.58424600000000004</v>
       </c>
       <c r="F2" s="1">
-        <v>0.26157899999999995</v>
+        <v>0.5231579999999999</v>
       </c>
       <c r="G2" s="1">
-        <v>0.24793999999999997</v>
+        <v>0.49587999999999993</v>
       </c>
       <c r="H2" s="1">
-        <v>0.20313600000000004</v>
+        <v>0.40627200000000008</v>
       </c>
       <c r="I2" s="1">
-        <v>0.17240800000000003</v>
+        <v>0.34481600000000007</v>
       </c>
       <c r="J2" s="1">
-        <v>0.210841</v>
+        <v>0.421682</v>
       </c>
       <c r="K2" s="1">
-        <v>3.6615999999999996E-2</v>
+        <v>7.3231999999999992E-2</v>
       </c>
       <c r="L2" s="1">
-        <v>3.2199999999999999E-2</v>
+        <v>6.4399999999999999E-2</v>
       </c>
       <c r="M2" s="1">
-        <v>4.6942999999999992E-2</v>
+        <v>9.3885999999999983E-2</v>
       </c>
       <c r="N2" s="1">
-        <v>2.7646000000000004E-2</v>
+        <v>5.5292000000000008E-2</v>
       </c>
       <c r="O2" s="1">
-        <v>3.4546E-2</v>
+        <v>6.9092000000000001E-2</v>
       </c>
       <c r="P2" s="1">
-        <v>5.5039000000000018E-2</v>
+        <v>0.11007800000000004</v>
       </c>
       <c r="Q2" s="1">
-        <v>0.101407</v>
+        <v>0.20281399999999999</v>
       </c>
       <c r="R2" s="1">
-        <v>0.10819199999999998</v>
+        <v>0.21638399999999997</v>
       </c>
       <c r="S2" s="1">
-        <v>0.10639799999999999</v>
+        <v>0.21279599999999999</v>
       </c>
       <c r="T2" s="1">
-        <v>5.9685000000000002E-2</v>
+        <v>0.11937</v>
       </c>
       <c r="U2" s="1">
-        <v>0.12157799999999999</v>
+        <v>0.24315599999999998</v>
       </c>
       <c r="V2" s="1">
-        <v>7.1345999999999993E-2</v>
+        <v>0.14269199999999999</v>
       </c>
       <c r="W2" s="1">
-        <v>5.0162999999999992E-2</v>
+        <v>0.10032599999999998</v>
       </c>
       <c r="X2" s="1">
-        <v>7.6176000000000008E-2</v>
+        <v>0.15235200000000002</v>
       </c>
       <c r="Y2" s="1">
-        <v>4.7080999999999998E-2</v>
+        <v>9.4161999999999996E-2</v>
       </c>
       <c r="Z2" s="1">
-        <v>0.21488900000000002</v>
+        <v>0.42977800000000005</v>
       </c>
       <c r="AA2" s="1">
-        <v>0.25904899999999997</v>
+        <v>0.51809799999999995</v>
       </c>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.2">
@@ -73832,76 +73896,76 @@
         <v>1</v>
       </c>
       <c r="D3" s="1">
-        <v>-0.63824999999999998</v>
+        <v>-1.2765</v>
       </c>
       <c r="E3" s="1">
-        <v>-0.68250199999999994</v>
+        <v>-1.3650039999999999</v>
       </c>
       <c r="F3" s="1">
-        <v>-0.76760200000000012</v>
+        <v>-1.5352040000000002</v>
       </c>
       <c r="G3" s="1">
-        <v>-0.82802299999999995</v>
+        <v>-1.6560459999999999</v>
       </c>
       <c r="H3" s="1">
-        <v>-0.88504000000000005</v>
+        <v>-1.7700800000000001</v>
       </c>
       <c r="I3" s="1">
-        <v>-0.9658850000000001</v>
+        <v>-1.9317700000000002</v>
       </c>
       <c r="J3" s="1">
-        <v>-0.92163299999999992</v>
+        <v>-1.8432659999999998</v>
       </c>
       <c r="K3" s="1">
-        <v>-1.0338361999999999</v>
+        <v>-2.0676723999999997</v>
       </c>
       <c r="L3" s="1">
-        <v>-0.93767319999999965</v>
+        <v>-1.8753463999999993</v>
       </c>
       <c r="M3" s="1">
-        <v>-1.3772882999999998</v>
+        <v>-2.7545765999999996</v>
       </c>
       <c r="N3" s="1">
-        <v>-1.3631732000000001</v>
+        <v>-2.7263464000000002</v>
       </c>
       <c r="O3" s="1">
-        <v>-1.2461492000000001</v>
+        <v>-2.4922984000000001</v>
       </c>
       <c r="P3" s="1">
-        <v>-1.1945371999999999</v>
+        <v>-2.3890743999999997</v>
       </c>
       <c r="Q3" s="1">
-        <v>-1.1533051000000001</v>
+        <v>-2.3066102000000002</v>
       </c>
       <c r="R3" s="1">
-        <v>-1.0870766000000001</v>
+        <v>-2.1741532000000001</v>
       </c>
       <c r="S3" s="1">
-        <v>-0.9892437999999999</v>
+        <v>-1.9784875999999998</v>
       </c>
       <c r="T3" s="1">
-        <v>-0.92500020000000005</v>
+        <v>-1.8500004000000001</v>
       </c>
       <c r="U3" s="1">
-        <v>-0.82778380000000007</v>
+        <v>-1.6555676000000001</v>
       </c>
       <c r="V3" s="1">
-        <v>-0.52541889999999991</v>
+        <v>-1.0508377999999998</v>
       </c>
       <c r="W3" s="1">
-        <v>-0.58802259999999984</v>
+        <v>-1.1760451999999997</v>
       </c>
       <c r="X3" s="1">
-        <v>-0.62156579999999995</v>
+        <v>-1.2431315999999999</v>
       </c>
       <c r="Y3" s="1">
-        <v>-0.66731049999999992</v>
+        <v>-1.3346209999999998</v>
       </c>
       <c r="Z3" s="1">
-        <v>-0.53017300000000001</v>
+        <v>-1.060346</v>
       </c>
       <c r="AA3" s="1">
-        <v>-0.56336200000000003</v>
+        <v>-1.1267240000000001</v>
       </c>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.2">
@@ -73915,76 +73979,76 @@
         <v>1</v>
       </c>
       <c r="D4" s="1">
-        <v>0.61487969999999992</v>
+        <v>1.2297593999999998</v>
       </c>
       <c r="E4" s="1">
-        <v>0.6578183999999998</v>
+        <v>1.3156367999999996</v>
       </c>
       <c r="F4" s="1">
-        <v>0.7375662999999999</v>
+        <v>1.4751325999999998</v>
       </c>
       <c r="G4" s="1">
-        <v>0.79364030000000008</v>
+        <v>1.5872806000000002</v>
       </c>
       <c r="H4" s="1">
-        <v>0.84475549999999977</v>
+        <v>1.6895109999999995</v>
       </c>
       <c r="I4" s="1">
-        <v>0.92241499999999998</v>
+        <v>1.84483</v>
       </c>
       <c r="J4" s="1">
-        <v>0.87940499999999988</v>
+        <v>1.7588099999999998</v>
       </c>
       <c r="K4" s="1">
-        <v>0.99240169999999994</v>
+        <v>1.9848033999999999</v>
       </c>
       <c r="L4" s="1">
-        <v>0.90902670000000008</v>
+        <v>1.8180534000000002</v>
       </c>
       <c r="M4" s="1">
-        <v>1.0372678</v>
+        <v>2.0745355999999999</v>
       </c>
       <c r="N4" s="1">
-        <v>1.0454351</v>
+        <v>2.0908701999999999</v>
       </c>
       <c r="O4" s="1">
-        <v>0.97862929999999992</v>
+        <v>1.9572585999999998</v>
       </c>
       <c r="P4" s="1">
-        <v>0.94564500000000007</v>
+        <v>1.8912900000000001</v>
       </c>
       <c r="Q4" s="1">
-        <v>0.92133860000000001</v>
+        <v>1.8426772</v>
       </c>
       <c r="R4" s="1">
-        <v>0.86343840000000005</v>
+        <v>1.7268768000000001</v>
       </c>
       <c r="S4" s="1">
-        <v>0.78611010000000003</v>
+        <v>1.5722202000000001</v>
       </c>
       <c r="T4" s="1">
-        <v>0.73232229999999976</v>
+        <v>1.4646445999999995</v>
       </c>
       <c r="U4" s="1">
-        <v>0.65451559999999998</v>
+        <v>1.3090312</v>
       </c>
       <c r="V4" s="1">
-        <v>0.51228819999999997</v>
+        <v>1.0245763999999999</v>
       </c>
       <c r="W4" s="1">
-        <v>0.5733992</v>
+        <v>1.1467984</v>
       </c>
       <c r="X4" s="1">
-        <v>0.60930220000000002</v>
+        <v>1.2186044</v>
       </c>
       <c r="Y4" s="1">
-        <v>0.65633720000000007</v>
+        <v>1.3126744000000001</v>
       </c>
       <c r="Z4" s="1">
-        <v>0.51071500000000003</v>
+        <v>1.0214300000000001</v>
       </c>
       <c r="AA4" s="1">
-        <v>0.54307600000000011</v>
+        <v>1.0861520000000002</v>
       </c>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.2">
@@ -73998,76 +74062,76 @@
         <v>2</v>
       </c>
       <c r="D5" s="1">
-        <v>0.27986607000000008</v>
+        <v>0.55973214000000016</v>
       </c>
       <c r="E5" s="1">
-        <v>0.29212300000000002</v>
+        <v>0.58424600000000004</v>
       </c>
       <c r="F5" s="1">
-        <v>0.27204215999999998</v>
+        <v>0.54408431999999995</v>
       </c>
       <c r="G5" s="1">
-        <v>0.25289879999999998</v>
+        <v>0.50579759999999996</v>
       </c>
       <c r="H5" s="1">
-        <v>0.19907327999999999</v>
+        <v>0.39814655999999998</v>
       </c>
       <c r="I5" s="1">
-        <v>0.16551168000000002</v>
+        <v>0.33102336000000004</v>
       </c>
       <c r="J5" s="1">
-        <v>0.21294941000000001</v>
+        <v>0.42589882000000001</v>
       </c>
       <c r="K5" s="1">
-        <v>3.5883680000000001E-2</v>
+        <v>7.1767360000000002E-2</v>
       </c>
       <c r="L5" s="1">
-        <v>3.3488000000000004E-2</v>
+        <v>6.6976000000000008E-2</v>
       </c>
       <c r="M5" s="1">
-        <v>4.9290149999999991E-2</v>
+        <v>9.8580299999999982E-2</v>
       </c>
       <c r="N5" s="1">
-        <v>2.7093080000000002E-2</v>
+        <v>5.4186160000000004E-2</v>
       </c>
       <c r="O5" s="1">
-        <v>3.4891459999999999E-2</v>
+        <v>6.9782919999999998E-2</v>
       </c>
       <c r="P5" s="1">
-        <v>5.5039000000000018E-2</v>
+        <v>0.11007800000000004</v>
       </c>
       <c r="Q5" s="1">
-        <v>0.10647735</v>
+        <v>0.2129547</v>
       </c>
       <c r="R5" s="1">
-        <v>0.10819199999999998</v>
+        <v>0.21638399999999997</v>
       </c>
       <c r="S5" s="1">
-        <v>0.10852595999999999</v>
+        <v>0.21705191999999998</v>
       </c>
       <c r="T5" s="1">
-        <v>5.6700750000000001E-2</v>
+        <v>0.1134015</v>
       </c>
       <c r="U5" s="1">
-        <v>0.12765689999999996</v>
+        <v>0.25531379999999992</v>
       </c>
       <c r="V5" s="1">
-        <v>7.2059459999999992E-2</v>
+        <v>0.14411891999999998</v>
       </c>
       <c r="W5" s="1">
-        <v>5.166788999999998E-2</v>
+        <v>0.10333577999999996</v>
       </c>
       <c r="X5" s="1">
-        <v>7.6937760000000008E-2</v>
+        <v>0.15387552000000002</v>
       </c>
       <c r="Y5" s="1">
-        <v>4.4726950000000001E-2</v>
+        <v>8.9453900000000003E-2</v>
       </c>
       <c r="Z5" s="1">
-        <v>0.21918678000000003</v>
+        <v>0.43837356000000005</v>
       </c>
       <c r="AA5" s="1">
-        <v>0.25904899999999997</v>
+        <v>0.51809799999999995</v>
       </c>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.2">
@@ -74081,76 +74145,76 @@
         <v>2</v>
       </c>
       <c r="D6" s="1">
-        <v>-0.63824999999999998</v>
+        <v>-1.2765</v>
       </c>
       <c r="E6" s="1">
-        <v>-0.67567697999999998</v>
+        <v>-1.35135396</v>
       </c>
       <c r="F6" s="1">
-        <v>-0.76760200000000012</v>
+        <v>-1.5352040000000002</v>
       </c>
       <c r="G6" s="1">
-        <v>-0.78662184999999996</v>
+        <v>-1.5732436999999999</v>
       </c>
       <c r="H6" s="1">
-        <v>-0.85848879999999994</v>
+        <v>-1.7169775999999999</v>
       </c>
       <c r="I6" s="1">
-        <v>-0.92724960000000001</v>
+        <v>-1.8544992</v>
       </c>
       <c r="J6" s="1">
-        <v>-0.93084933000000003</v>
+        <v>-1.8616986600000001</v>
       </c>
       <c r="K6" s="1">
-        <v>-1.0338361999999999</v>
+        <v>-2.0676723999999997</v>
       </c>
       <c r="L6" s="1">
-        <v>-0.93767319999999965</v>
+        <v>-1.8753463999999993</v>
       </c>
       <c r="M6" s="1">
-        <v>-1.3635154169999999</v>
+        <v>-2.7270308339999998</v>
       </c>
       <c r="N6" s="1">
-        <v>-1.3904366640000003</v>
+        <v>-2.7808733280000006</v>
       </c>
       <c r="O6" s="1">
-        <v>-1.221226216</v>
+        <v>-2.4424524320000001</v>
       </c>
       <c r="P6" s="1">
-        <v>-1.2423186879999999</v>
+        <v>-2.4846373759999998</v>
       </c>
       <c r="Q6" s="1">
-        <v>-1.1417720489999998</v>
+        <v>-2.2835440979999997</v>
       </c>
       <c r="R6" s="1">
-        <v>-1.1305596640000002</v>
+        <v>-2.2611193280000004</v>
       </c>
       <c r="S6" s="1">
-        <v>-0.9892437999999999</v>
+        <v>-1.9784875999999998</v>
       </c>
       <c r="T6" s="1">
-        <v>-0.90650019599999998</v>
+        <v>-1.813000392</v>
       </c>
       <c r="U6" s="1">
-        <v>-0.79467244800000003</v>
+        <v>-1.5893448960000001</v>
       </c>
       <c r="V6" s="1">
-        <v>-0.52541889999999991</v>
+        <v>-1.0508377999999998</v>
       </c>
       <c r="W6" s="1">
-        <v>-0.5821423739999998</v>
+        <v>-1.1642847479999996</v>
       </c>
       <c r="X6" s="1">
-        <v>-0.60913448399999992</v>
+        <v>-1.2182689679999998</v>
       </c>
       <c r="Y6" s="1">
-        <v>-0.64729118499999994</v>
+        <v>-1.2945823699999999</v>
       </c>
       <c r="Z6" s="1">
-        <v>-0.55137992000000002</v>
+        <v>-1.10275984</v>
       </c>
       <c r="AA6" s="1">
-        <v>-0.54082752000000001</v>
+        <v>-1.08165504</v>
       </c>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.2">
@@ -74164,76 +74228,76 @@
         <v>2</v>
       </c>
       <c r="D7" s="1">
-        <v>0.58413571499999994</v>
+        <v>1.1682714299999999</v>
       </c>
       <c r="E7" s="1">
-        <v>0.67755295199999988</v>
+        <v>1.3551059039999998</v>
       </c>
       <c r="F7" s="1">
-        <v>0.70806364799999988</v>
+        <v>1.4161272959999998</v>
       </c>
       <c r="G7" s="1">
-        <v>0.75395828500000006</v>
+        <v>1.5079165700000001</v>
       </c>
       <c r="H7" s="1">
-        <v>0.81941283499999984</v>
+        <v>1.6388256699999997</v>
       </c>
       <c r="I7" s="1">
-        <v>0.95008745000000017</v>
+        <v>1.9001749000000003</v>
       </c>
       <c r="J7" s="1">
-        <v>0.8442288</v>
+        <v>1.6884576</v>
       </c>
       <c r="K7" s="1">
-        <v>0.95270563200000014</v>
+        <v>1.9054112640000003</v>
       </c>
       <c r="L7" s="1">
-        <v>0.91811696700000012</v>
+        <v>1.8362339340000002</v>
       </c>
       <c r="M7" s="1">
-        <v>1.0061497659999998</v>
+        <v>2.0122995319999997</v>
       </c>
       <c r="N7" s="1">
-        <v>1.0454351</v>
+        <v>2.0908701999999999</v>
       </c>
       <c r="O7" s="1">
-        <v>0.99820188599999982</v>
+        <v>1.9964037719999996</v>
       </c>
       <c r="P7" s="1">
-        <v>0.90781920000000016</v>
+        <v>1.8156384000000003</v>
       </c>
       <c r="Q7" s="1">
-        <v>0.93976537199999977</v>
+        <v>1.8795307439999995</v>
       </c>
       <c r="R7" s="1">
-        <v>0.90661032000000019</v>
+        <v>1.8132206400000004</v>
       </c>
       <c r="S7" s="1">
-        <v>0.80969340300000014</v>
+        <v>1.6193868060000003</v>
       </c>
       <c r="T7" s="1">
-        <v>0.71035263099999979</v>
+        <v>1.4207052619999996</v>
       </c>
       <c r="U7" s="1">
-        <v>0.68069622399999985</v>
+        <v>1.3613924479999997</v>
       </c>
       <c r="V7" s="1">
-        <v>0.53790260999999995</v>
+        <v>1.0758052199999999</v>
       </c>
       <c r="W7" s="1">
-        <v>0.5733992</v>
+        <v>1.1467984</v>
       </c>
       <c r="X7" s="1">
-        <v>0.57883709000000005</v>
+        <v>1.1576741800000001</v>
       </c>
       <c r="Y7" s="1">
-        <v>0.68915406000000012</v>
+        <v>1.3783081200000002</v>
       </c>
       <c r="Z7" s="1">
-        <v>0.50560784999999986</v>
+        <v>1.0112156999999997</v>
       </c>
       <c r="AA7" s="1">
-        <v>0.54307600000000011</v>
+        <v>1.0861520000000002</v>
       </c>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.2">
@@ -74247,76 +74311,76 @@
         <v>3</v>
       </c>
       <c r="D8" s="1">
-        <v>0.27426874860000006</v>
+        <v>0.54853749720000011</v>
       </c>
       <c r="E8" s="1">
-        <v>0.29796546000000002</v>
+        <v>0.59593092000000003</v>
       </c>
       <c r="F8" s="1">
-        <v>0.2747625816</v>
+        <v>0.5495251632</v>
       </c>
       <c r="G8" s="1">
-        <v>0.24278284799999997</v>
+        <v>0.48556569599999994</v>
       </c>
       <c r="H8" s="1">
-        <v>0.18911961599999999</v>
+        <v>0.37823923199999998</v>
       </c>
       <c r="I8" s="1">
-        <v>0.16716679680000002</v>
+        <v>0.33433359360000003</v>
       </c>
       <c r="J8" s="1">
-        <v>0.21081991590000002</v>
+        <v>0.42163983180000003</v>
       </c>
       <c r="K8" s="1">
-        <v>3.73190272E-2</v>
+        <v>7.4638054400000001E-2</v>
       </c>
       <c r="L8" s="1">
-        <v>3.3488000000000004E-2</v>
+        <v>6.6976000000000008E-2</v>
       </c>
       <c r="M8" s="1">
-        <v>4.68256425E-2</v>
+        <v>9.3651285000000001E-2</v>
       </c>
       <c r="N8" s="1">
-        <v>2.7364010799999998E-2</v>
+        <v>5.4728021599999996E-2</v>
       </c>
       <c r="O8" s="1">
-        <v>3.4891459999999999E-2</v>
+        <v>6.9782919999999998E-2</v>
       </c>
       <c r="P8" s="1">
-        <v>5.4488610000000014E-2</v>
+        <v>0.10897722000000003</v>
       </c>
       <c r="Q8" s="1">
-        <v>0.1011534825</v>
+        <v>0.20230696500000001</v>
       </c>
       <c r="R8" s="1">
-        <v>0.10494624</v>
+        <v>0.20989247999999999</v>
       </c>
       <c r="S8" s="1">
-        <v>0.10527018119999998</v>
+        <v>0.21054036239999996</v>
       </c>
       <c r="T8" s="1">
-        <v>5.6700750000000001E-2</v>
+        <v>0.1134015</v>
       </c>
       <c r="U8" s="1">
-        <v>0.12382719299999996</v>
+        <v>0.24765438599999992</v>
       </c>
       <c r="V8" s="1">
-        <v>7.0618270799999994E-2</v>
+        <v>0.14123654159999999</v>
       </c>
       <c r="W8" s="1">
-        <v>5.4251284499999983E-2</v>
+        <v>0.10850256899999997</v>
       </c>
       <c r="X8" s="1">
-        <v>7.6937760000000008E-2</v>
+        <v>0.15387552000000002</v>
       </c>
       <c r="Y8" s="1">
-        <v>4.6516028000000001E-2</v>
+        <v>9.3032056000000002E-2</v>
       </c>
       <c r="Z8" s="1">
-        <v>0.21480304440000003</v>
+        <v>0.42960608880000006</v>
       </c>
       <c r="AA8" s="1">
-        <v>0.24868704</v>
+        <v>0.49737408</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.2">
@@ -74330,76 +74394,76 @@
         <v>3</v>
       </c>
       <c r="D9" s="1">
-        <v>-0.60633750000000008</v>
+        <v>-1.2126750000000002</v>
       </c>
       <c r="E9" s="1">
-        <v>-0.67567697999999998</v>
+        <v>-1.35135396</v>
       </c>
       <c r="F9" s="1">
-        <v>-0.72922190000000009</v>
+        <v>-1.4584438000000002</v>
       </c>
       <c r="G9" s="1">
-        <v>-0.78662184999999996</v>
+        <v>-1.5732436999999999</v>
       </c>
       <c r="H9" s="1">
-        <v>-0.8928283520000001</v>
+        <v>-1.7856567040000002</v>
       </c>
       <c r="I9" s="1">
-        <v>-0.90870460800000008</v>
+        <v>-1.8174092160000002</v>
       </c>
       <c r="J9" s="1">
-        <v>-0.95877480990000008</v>
+        <v>-1.9175496198000002</v>
       </c>
       <c r="K9" s="1">
-        <v>-1.0131594759999998</v>
+        <v>-2.0263189519999996</v>
       </c>
       <c r="L9" s="1">
-        <v>-0.98455685999999965</v>
+        <v>-1.9691137199999993</v>
       </c>
       <c r="M9" s="1">
-        <v>-1.3771505711699996</v>
+        <v>-2.7543011423399992</v>
       </c>
       <c r="N9" s="1">
-        <v>-1.3487235640800004</v>
+        <v>-2.6974471281600008</v>
       </c>
       <c r="O9" s="1">
-        <v>-1.2578630024800002</v>
+        <v>-2.5157260049600003</v>
       </c>
       <c r="P9" s="1">
-        <v>-1.2298955011200001</v>
+        <v>-2.4597910022400002</v>
       </c>
       <c r="Q9" s="1">
-        <v>-1.19886065145</v>
+        <v>-2.3977213029</v>
       </c>
       <c r="R9" s="1">
-        <v>-1.1192540673600002</v>
+        <v>-2.2385081347200004</v>
       </c>
       <c r="S9" s="1">
-        <v>-0.9892437999999999</v>
+        <v>-1.9784875999999998</v>
       </c>
       <c r="T9" s="1">
-        <v>-0.89743519404000005</v>
+        <v>-1.7948703880800001</v>
       </c>
       <c r="U9" s="1">
-        <v>-0.82645934592000003</v>
+        <v>-1.6529186918400001</v>
       </c>
       <c r="V9" s="1">
-        <v>-0.54118146700000003</v>
+        <v>-1.0823629340000001</v>
       </c>
       <c r="W9" s="1">
-        <v>-0.57632095025999974</v>
+        <v>-1.1526419005199995</v>
       </c>
       <c r="X9" s="1">
-        <v>-0.60913448399999992</v>
+        <v>-1.2182689679999998</v>
       </c>
       <c r="Y9" s="1">
-        <v>-0.6149266257499999</v>
+        <v>-1.2298532514999998</v>
       </c>
       <c r="Z9" s="1">
-        <v>-0.54586612079999997</v>
+        <v>-1.0917322415999999</v>
       </c>
       <c r="AA9" s="1">
-        <v>-0.56786889600000001</v>
+        <v>-1.135737792</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.2">
@@ -74413,76 +74477,76 @@
         <v>3</v>
       </c>
       <c r="D10" s="1">
-        <v>0.59581842929999995</v>
+        <v>1.1916368585999999</v>
       </c>
       <c r="E10" s="1">
-        <v>0.64367530439999987</v>
+        <v>1.2873506087999997</v>
       </c>
       <c r="F10" s="1">
-        <v>0.70806364799999988</v>
+        <v>1.4161272959999998</v>
       </c>
       <c r="G10" s="1">
-        <v>0.73133953645000005</v>
+        <v>1.4626790729000001</v>
       </c>
       <c r="H10" s="1">
-        <v>0.77844219324999975</v>
+        <v>1.5568843864999995</v>
       </c>
       <c r="I10" s="1">
-        <v>0.90258307750000011</v>
+        <v>1.8051661550000002</v>
       </c>
       <c r="J10" s="1">
-        <v>0.80201735999999979</v>
+        <v>1.6040347199999996</v>
       </c>
       <c r="K10" s="1">
-        <v>0.90507035040000017</v>
+        <v>1.8101407008000003</v>
       </c>
       <c r="L10" s="1">
-        <v>0.89975462766000014</v>
+        <v>1.7995092553200003</v>
       </c>
       <c r="M10" s="1">
-        <v>1.02627276132</v>
+        <v>2.05254552264</v>
       </c>
       <c r="N10" s="1">
-        <v>1.066343802</v>
+        <v>2.132687604</v>
       </c>
       <c r="O10" s="1">
-        <v>0.9482917917</v>
+        <v>1.8965835834</v>
       </c>
       <c r="P10" s="1">
-        <v>0.9441319680000001</v>
+        <v>1.8882639360000002</v>
       </c>
       <c r="Q10" s="1">
-        <v>0.94916302571999989</v>
+        <v>1.8983260514399998</v>
       </c>
       <c r="R10" s="1">
-        <v>0.92474252640000021</v>
+        <v>1.8494850528000004</v>
       </c>
       <c r="S10" s="1">
-        <v>0.77730566688000013</v>
+        <v>1.5546113337600003</v>
       </c>
       <c r="T10" s="1">
-        <v>0.73876673623999978</v>
+        <v>1.4775334724799996</v>
       </c>
       <c r="U10" s="1">
-        <v>0.65346837503999988</v>
+        <v>1.3069367500799998</v>
       </c>
       <c r="V10" s="1">
-        <v>0.56479774049999987</v>
+        <v>1.1295954809999997</v>
       </c>
       <c r="W10" s="1">
-        <v>0.57913319200000002</v>
+        <v>1.158266384</v>
       </c>
       <c r="X10" s="1">
-        <v>0.60199057359999997</v>
+        <v>1.2039811471999999</v>
       </c>
       <c r="Y10" s="1">
-        <v>0.70982868180000014</v>
+        <v>1.4196573636000003</v>
       </c>
       <c r="Z10" s="1">
-        <v>0.51066392849999986</v>
+        <v>1.0213278569999997</v>
       </c>
       <c r="AA10" s="1">
-        <v>0.57022980000000012</v>
+        <v>1.1404596000000002</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.2">
@@ -74496,76 +74560,76 @@
         <v>1</v>
       </c>
       <c r="D11" s="1">
-        <v>0.26855835000000006</v>
+        <v>0.53711670000000011</v>
       </c>
       <c r="E11" s="1">
-        <v>0.27751684999999998</v>
+        <v>0.55503369999999996</v>
       </c>
       <c r="F11" s="1">
-        <v>0.24850005</v>
+        <v>0.4970001</v>
       </c>
       <c r="G11" s="1">
-        <v>0.23554299999999992</v>
+        <v>0.47108599999999984</v>
       </c>
       <c r="H11" s="1">
-        <v>0.19297919999999999</v>
+        <v>0.38595839999999998</v>
       </c>
       <c r="I11" s="1">
-        <v>0.16378760000000001</v>
+        <v>0.32757520000000001</v>
       </c>
       <c r="J11" s="1">
-        <v>0.20029895</v>
+        <v>0.40059790000000001</v>
       </c>
       <c r="K11" s="1">
-        <v>3.4785200000000002E-2</v>
+        <v>6.9570400000000004E-2</v>
       </c>
       <c r="L11" s="1">
-        <v>3.0589999999999999E-2</v>
+        <v>6.1179999999999998E-2</v>
       </c>
       <c r="M11" s="1">
-        <v>4.4595849999999986E-2</v>
+        <v>8.9191699999999971E-2</v>
       </c>
       <c r="N11" s="1">
-        <v>2.6263700000000001E-2</v>
+        <v>5.2527400000000002E-2</v>
       </c>
       <c r="O11" s="1">
-        <v>3.2818699999999992E-2</v>
+        <v>6.5637399999999985E-2</v>
       </c>
       <c r="P11" s="1">
-        <v>5.2287050000000015E-2</v>
+        <v>0.10457410000000003</v>
       </c>
       <c r="Q11" s="1">
-        <v>9.6336649999999996E-2</v>
+        <v>0.19267329999999999</v>
       </c>
       <c r="R11" s="1">
-        <v>0.10278239999999998</v>
+        <v>0.20556479999999996</v>
       </c>
       <c r="S11" s="1">
-        <v>0.10107809999999998</v>
+        <v>0.20215619999999995</v>
       </c>
       <c r="T11" s="1">
-        <v>5.6700750000000001E-2</v>
+        <v>0.1134015</v>
       </c>
       <c r="U11" s="1">
-        <v>0.11549909999999997</v>
+        <v>0.23099819999999993</v>
       </c>
       <c r="V11" s="1">
-        <v>6.7778699999999997E-2</v>
+        <v>0.13555739999999999</v>
       </c>
       <c r="W11" s="1">
-        <v>4.7654849999999985E-2</v>
+        <v>9.5309699999999969E-2</v>
       </c>
       <c r="X11" s="1">
-        <v>7.2367199999999993E-2</v>
+        <v>0.14473439999999999</v>
       </c>
       <c r="Y11" s="1">
-        <v>4.4726950000000001E-2</v>
+        <v>8.9453900000000003E-2</v>
       </c>
       <c r="Z11" s="1">
-        <v>0.20414455000000001</v>
+        <v>0.40828910000000002</v>
       </c>
       <c r="AA11" s="1">
-        <v>0.24609655</v>
+        <v>0.49219309999999999</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.2">
@@ -74579,76 +74643,76 @@
         <v>1</v>
       </c>
       <c r="D12" s="1">
-        <v>-0.63059100000000012</v>
+        <v>-1.2611820000000002</v>
       </c>
       <c r="E12" s="1">
-        <v>-0.67567697999999998</v>
+        <v>-1.35135396</v>
       </c>
       <c r="F12" s="1">
-        <v>-0.69276080500000004</v>
+        <v>-1.3855216100000001</v>
       </c>
       <c r="G12" s="1">
-        <v>-0.78662184999999996</v>
+        <v>-1.5732436999999999</v>
       </c>
       <c r="H12" s="1">
-        <v>-0.88390006848000002</v>
+        <v>-1.76780013696</v>
       </c>
       <c r="I12" s="1">
-        <v>-0.94505279231999995</v>
+        <v>-1.8901055846399999</v>
       </c>
       <c r="J12" s="1">
-        <v>-0.93001156560300013</v>
+        <v>-1.8600231312060003</v>
       </c>
       <c r="K12" s="1">
-        <v>-1.0030278812399998</v>
+        <v>-2.0060557624799995</v>
       </c>
       <c r="L12" s="1">
-        <v>-1.0042479971999998</v>
+        <v>-2.0084959943999996</v>
       </c>
       <c r="M12" s="1">
-        <v>-1.3220645483231999</v>
+        <v>-2.6441290966463997</v>
       </c>
       <c r="N12" s="1">
-        <v>-1.3622107997208006</v>
+        <v>-2.7244215994416012</v>
       </c>
       <c r="O12" s="1">
-        <v>-1.2955988925544002</v>
+        <v>-2.5911977851088004</v>
       </c>
       <c r="P12" s="1">
-        <v>-1.1929986360864</v>
+        <v>-2.3859972721728</v>
       </c>
       <c r="Q12" s="1">
-        <v>-1.1389176188774999</v>
+        <v>-2.2778352377549997</v>
       </c>
       <c r="R12" s="1">
-        <v>-1.1080615266864002</v>
+        <v>-2.2161230533728005</v>
       </c>
       <c r="S12" s="1">
-        <v>-0.9892437999999999</v>
+        <v>-1.9784875999999998</v>
       </c>
       <c r="T12" s="1">
-        <v>-0.93333260180160005</v>
+        <v>-1.8666652036032001</v>
       </c>
       <c r="U12" s="1">
-        <v>-0.80993015900159993</v>
+        <v>-1.6198603180031999</v>
       </c>
       <c r="V12" s="1">
-        <v>-0.51953420831999997</v>
+        <v>-1.0390684166399999</v>
       </c>
       <c r="W12" s="1">
-        <v>-0.58208415976259986</v>
+        <v>-1.1641683195251997</v>
       </c>
       <c r="X12" s="1">
-        <v>-0.63959120819999993</v>
+        <v>-1.2791824163999999</v>
       </c>
       <c r="Y12" s="1">
-        <v>-0.6149266257499999</v>
+        <v>-1.2298532514999998</v>
       </c>
       <c r="Z12" s="1">
-        <v>-0.52949013717600002</v>
+        <v>-1.058980274352</v>
       </c>
       <c r="AA12" s="1">
-        <v>-0.55651151807999999</v>
+        <v>-1.11302303616</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.2">
@@ -74662,76 +74726,76 @@
         <v>1</v>
       </c>
       <c r="D13" s="1">
-        <v>0.566027507835</v>
+        <v>1.13205501567</v>
       </c>
       <c r="E13" s="1">
-        <v>0.62436504526799996</v>
+        <v>1.2487300905359999</v>
       </c>
       <c r="F13" s="1">
-        <v>0.71514428447999978</v>
+        <v>1.4302885689599996</v>
       </c>
       <c r="G13" s="1">
-        <v>0.71671274572100008</v>
+        <v>1.4334254914420002</v>
       </c>
       <c r="H13" s="1">
-        <v>0.7706577713174998</v>
+        <v>1.5413155426349996</v>
       </c>
       <c r="I13" s="1">
-        <v>0.91160890827500007</v>
+        <v>1.8232178165500001</v>
       </c>
       <c r="J13" s="1">
-        <v>0.80201735999999979</v>
+        <v>1.6040347199999996</v>
       </c>
       <c r="K13" s="1">
-        <v>0.91412105390399989</v>
+        <v>1.8282421078079998</v>
       </c>
       <c r="L13" s="1">
-        <v>0.89975462766000014</v>
+        <v>1.7995092553200003</v>
       </c>
       <c r="M13" s="1">
-        <v>1.0570609441596002</v>
+        <v>2.1141218883192003</v>
       </c>
       <c r="N13" s="1">
-        <v>1.0130266119</v>
+        <v>2.0260532238</v>
       </c>
       <c r="O13" s="1">
-        <v>0.900877202115</v>
+        <v>1.80175440423</v>
       </c>
       <c r="P13" s="1">
-        <v>0.97245592704000006</v>
+        <v>1.9449118540800001</v>
       </c>
       <c r="Q13" s="1">
-        <v>0.93967139546279999</v>
+        <v>1.8793427909256</v>
       </c>
       <c r="R13" s="1">
-        <v>0.90624767587200028</v>
+        <v>1.8124953517440006</v>
       </c>
       <c r="S13" s="1">
-        <v>0.73844038353600017</v>
+        <v>1.4768807670720003</v>
       </c>
       <c r="T13" s="1">
-        <v>0.77570507305199976</v>
+        <v>1.5514101461039995</v>
       </c>
       <c r="U13" s="1">
-        <v>0.6796071100415999</v>
+        <v>1.3592142200831998</v>
       </c>
       <c r="V13" s="1">
-        <v>0.57044571790499998</v>
+        <v>1.14089143581</v>
       </c>
       <c r="W13" s="1">
-        <v>0.59650718776000011</v>
+        <v>1.1930143755200002</v>
       </c>
       <c r="X13" s="1">
-        <v>0.5959706678640001</v>
+        <v>1.1919413357280002</v>
       </c>
       <c r="Y13" s="1">
-        <v>0.73822182907200018</v>
+        <v>1.4764436581440004</v>
       </c>
       <c r="Z13" s="1">
-        <v>0.51066392849999986</v>
+        <v>1.0213278569999997</v>
       </c>
       <c r="AA13" s="1">
-        <v>0.58163439600000022</v>
+        <v>1.1632687920000004</v>
       </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.2">
@@ -74745,76 +74809,76 @@
         <v>2</v>
       </c>
       <c r="D14" s="1">
-        <v>0.27930068400000002</v>
+        <v>0.55860136800000004</v>
       </c>
       <c r="E14" s="1">
-        <v>0.28029201850000002</v>
+        <v>0.56058403700000004</v>
       </c>
       <c r="F14" s="1">
-        <v>0.24850005</v>
+        <v>0.4970001</v>
       </c>
       <c r="G14" s="1">
-        <v>0.24025385999999987</v>
+        <v>0.48050771999999975</v>
       </c>
       <c r="H14" s="1">
-        <v>0.19490899199999998</v>
+        <v>0.38981798399999995</v>
       </c>
       <c r="I14" s="1">
-        <v>0.158873972</v>
+        <v>0.317747944</v>
       </c>
       <c r="J14" s="1">
-        <v>0.20831090799999999</v>
+        <v>0.41662181599999998</v>
       </c>
       <c r="K14" s="1">
-        <v>3.4437348E-2</v>
+        <v>6.8874695999999999E-2</v>
       </c>
       <c r="L14" s="1">
-        <v>3.1507700000000007E-2</v>
+        <v>6.3015400000000013E-2</v>
       </c>
       <c r="M14" s="1">
-        <v>4.4149891499999989E-2</v>
+        <v>8.8299782999999979E-2</v>
       </c>
       <c r="N14" s="1">
-        <v>2.7051610999999996E-2</v>
+        <v>5.4103221999999992E-2</v>
       </c>
       <c r="O14" s="1">
-        <v>3.1177764999999996E-2</v>
+        <v>6.2355529999999992E-2</v>
       </c>
       <c r="P14" s="1">
-        <v>5.2287050000000015E-2</v>
+        <v>0.10457410000000003</v>
       </c>
       <c r="Q14" s="1">
-        <v>9.9226749500000003E-2</v>
+        <v>0.19845349900000001</v>
       </c>
       <c r="R14" s="1">
-        <v>0.10072675199999999</v>
+        <v>0.20145350399999998</v>
       </c>
       <c r="S14" s="1">
-        <v>0.10309966199999995</v>
+        <v>0.20619932399999991</v>
       </c>
       <c r="T14" s="1">
-        <v>5.443271999999999E-2</v>
+        <v>0.10886543999999998</v>
       </c>
       <c r="U14" s="1">
-        <v>0.11087913599999996</v>
+        <v>0.22175827199999992</v>
       </c>
       <c r="V14" s="1">
-        <v>6.5067552000000001E-2</v>
+        <v>0.130135104</v>
       </c>
       <c r="W14" s="1">
-        <v>5.0037592499999985E-2</v>
+        <v>0.10007518499999997</v>
       </c>
       <c r="X14" s="1">
-        <v>7.0196184000000009E-2</v>
+        <v>0.14039236800000002</v>
       </c>
       <c r="Y14" s="1">
-        <v>4.6068758499999994E-2</v>
+        <v>9.2137516999999988E-2</v>
       </c>
       <c r="Z14" s="1">
-        <v>0.2061859955</v>
+        <v>0.41237199099999999</v>
       </c>
       <c r="AA14" s="1">
-        <v>0.24117461900000001</v>
+        <v>0.48234923800000001</v>
       </c>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.2">
@@ -74828,76 +74892,76 @@
         <v>2</v>
       </c>
       <c r="D15" s="1">
-        <v>-0.63689691000000015</v>
+        <v>-1.2737938200000003</v>
       </c>
       <c r="E15" s="1">
-        <v>-0.66216344039999997</v>
+        <v>-1.3243268807999999</v>
       </c>
       <c r="F15" s="1">
-        <v>-0.66505037280000001</v>
+        <v>-1.3301007456</v>
       </c>
       <c r="G15" s="1">
-        <v>-0.75515697599999987</v>
+        <v>-1.5103139519999997</v>
       </c>
       <c r="H15" s="1">
-        <v>-0.91925607121920017</v>
+        <v>-1.8385121424384003</v>
       </c>
       <c r="I15" s="1">
-        <v>-0.92615173647359994</v>
+        <v>-1.8523034729471999</v>
       </c>
       <c r="J15" s="1">
-        <v>-0.91141133429094001</v>
+        <v>-1.82282266858188</v>
       </c>
       <c r="K15" s="1">
-        <v>-0.96290676599039959</v>
+        <v>-1.9258135319807992</v>
       </c>
       <c r="L15" s="1">
-        <v>-1.0142904771719998</v>
+        <v>-2.0285809543439997</v>
       </c>
       <c r="M15" s="1">
-        <v>-1.3088439028399679</v>
+        <v>-2.6176878056799358</v>
       </c>
       <c r="N15" s="1">
-        <v>-1.4166992317096325</v>
+        <v>-2.833398463419265</v>
       </c>
       <c r="O15" s="1">
-        <v>-1.2696869147033123</v>
+        <v>-2.5393738294066246</v>
       </c>
       <c r="P15" s="1">
-        <v>-1.181068649725536</v>
+        <v>-2.3621372994510721</v>
       </c>
       <c r="Q15" s="1">
-        <v>-1.0933609141223997</v>
+        <v>-2.1867218282447993</v>
       </c>
       <c r="R15" s="1">
-        <v>-1.0859002961526723</v>
+        <v>-2.1718005923053445</v>
       </c>
       <c r="S15" s="1">
-        <v>-0.93978160999999982</v>
+        <v>-1.8795632199999996</v>
       </c>
       <c r="T15" s="1">
-        <v>-0.93333260180160005</v>
+        <v>-1.8666652036032001</v>
       </c>
       <c r="U15" s="1">
-        <v>-0.80183085741158389</v>
+        <v>-1.6036617148231678</v>
       </c>
       <c r="V15" s="1">
-        <v>-0.51953420831999997</v>
+        <v>-1.0390684166399999</v>
       </c>
       <c r="W15" s="1">
-        <v>-0.5937258429578518</v>
+        <v>-1.1874516859157036</v>
       </c>
       <c r="X15" s="1">
-        <v>-0.64598712028199989</v>
+        <v>-1.2919742405639998</v>
       </c>
       <c r="Y15" s="1">
-        <v>-0.62107589200749991</v>
+        <v>-1.2421517840149998</v>
       </c>
       <c r="Z15" s="1">
-        <v>-0.50831053168896001</v>
+        <v>-1.01662106337792</v>
       </c>
       <c r="AA15" s="1">
-        <v>-0.57877197880319997</v>
+        <v>-1.1575439576063999</v>
       </c>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.2">
@@ -74911,76 +74975,76 @@
         <v>2</v>
       </c>
       <c r="D16" s="1">
-        <v>0.53772613244324996</v>
+        <v>1.0754522648864999</v>
       </c>
       <c r="E16" s="1">
-        <v>0.59939044345727999</v>
+        <v>1.19878088691456</v>
       </c>
       <c r="F16" s="1">
-        <v>0.75090149870399991</v>
+        <v>1.5018029974079998</v>
       </c>
       <c r="G16" s="1">
-        <v>0.68804423589216002</v>
+        <v>1.37608847178432</v>
       </c>
       <c r="H16" s="1">
-        <v>0.80919065988337469</v>
+        <v>1.6183813197667494</v>
       </c>
       <c r="I16" s="1">
-        <v>0.87514455194400009</v>
+        <v>1.7502891038880002</v>
       </c>
       <c r="J16" s="1">
-        <v>0.81003753359999986</v>
+        <v>1.6200750671999997</v>
       </c>
       <c r="K16" s="1">
-        <v>0.91412105390399989</v>
+        <v>1.8282421078079998</v>
       </c>
       <c r="L16" s="1">
-        <v>0.8547668962770002</v>
+        <v>1.7095337925540004</v>
       </c>
       <c r="M16" s="1">
-        <v>1.0782021630427923</v>
+        <v>2.1564043260855845</v>
       </c>
       <c r="N16" s="1">
-        <v>0.99276607966199992</v>
+        <v>1.9855321593239998</v>
       </c>
       <c r="O16" s="1">
-        <v>0.93691229019959987</v>
+        <v>1.8738245803991997</v>
       </c>
       <c r="P16" s="1">
-        <v>0.93355768995839994</v>
+        <v>1.8671153799167999</v>
       </c>
       <c r="Q16" s="1">
-        <v>0.9678615373266839</v>
+        <v>1.9357230746533678</v>
       </c>
       <c r="R16" s="1">
-        <v>0.92437262938944031</v>
+        <v>1.8487452587788806</v>
       </c>
       <c r="S16" s="1">
-        <v>0.74582478737136015</v>
+        <v>1.4916495747427203</v>
       </c>
       <c r="T16" s="1">
-        <v>0.79121917451303969</v>
+        <v>1.5824383490260794</v>
       </c>
       <c r="U16" s="1">
-        <v>0.66601496784076786</v>
+        <v>1.3320299356815357</v>
       </c>
       <c r="V16" s="1">
-        <v>0.57615017508404986</v>
+        <v>1.1523003501680997</v>
       </c>
       <c r="W16" s="1">
-        <v>0.59650718776000011</v>
+        <v>1.1930143755200002</v>
       </c>
       <c r="X16" s="1">
-        <v>0.61980949457856005</v>
+        <v>1.2396189891571201</v>
       </c>
       <c r="Y16" s="1">
-        <v>0.75298626565344029</v>
+        <v>1.5059725313068806</v>
       </c>
       <c r="Z16" s="1">
-        <v>0.51577056778499997</v>
+        <v>1.0315411355699999</v>
       </c>
       <c r="AA16" s="1">
-        <v>0.55836902016000023</v>
+        <v>1.1167380403200005</v>
       </c>
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.2">
@@ -74994,76 +75058,76 @@
         <v>3</v>
       </c>
       <c r="D17" s="1">
-        <v>0.26533564980000002</v>
+        <v>0.53067129960000003</v>
       </c>
       <c r="E17" s="1">
-        <v>0.29150369924000002</v>
+        <v>0.58300739848000005</v>
       </c>
       <c r="F17" s="1">
-        <v>0.24601504949999997</v>
+        <v>0.49203009899999994</v>
       </c>
       <c r="G17" s="1">
-        <v>0.25226655299999989</v>
+        <v>0.50453310599999979</v>
       </c>
       <c r="H17" s="1">
-        <v>0.19685808191999998</v>
+        <v>0.39371616383999997</v>
       </c>
       <c r="I17" s="1">
-        <v>0.15728523228000002</v>
+        <v>0.31457046456000004</v>
       </c>
       <c r="J17" s="1">
-        <v>0.20206158075999997</v>
+        <v>0.40412316151999994</v>
       </c>
       <c r="K17" s="1">
-        <v>3.478172148E-2</v>
+        <v>6.9563442959999999E-2</v>
       </c>
       <c r="L17" s="1">
-        <v>3.1507700000000007E-2</v>
+        <v>6.3015400000000013E-2</v>
       </c>
       <c r="M17" s="1">
-        <v>4.2825394754999989E-2</v>
+        <v>8.5650789509999978E-2</v>
       </c>
       <c r="N17" s="1">
-        <v>2.6781094890000003E-2</v>
+        <v>5.3562189780000005E-2</v>
       </c>
       <c r="O17" s="1">
-        <v>3.0865987349999995E-2</v>
+        <v>6.173197469999999E-2</v>
       </c>
       <c r="P17" s="1">
-        <v>5.2287050000000015E-2</v>
+        <v>0.10457410000000003</v>
       </c>
       <c r="Q17" s="1">
-        <v>0.10021901699499999</v>
+        <v>0.20043803398999999</v>
       </c>
       <c r="R17" s="1">
-        <v>0.10576308959999998</v>
+        <v>0.21152617919999997</v>
       </c>
       <c r="S17" s="1">
-        <v>9.7944678899999943E-2</v>
+        <v>0.19588935779999989</v>
       </c>
       <c r="T17" s="1">
-        <v>5.2799738399999997E-2</v>
+        <v>0.10559947679999999</v>
       </c>
       <c r="U17" s="1">
-        <v>0.10977034463999998</v>
+        <v>0.21954068927999995</v>
       </c>
       <c r="V17" s="1">
-        <v>6.6368903039999982E-2</v>
+        <v>0.13273780607999996</v>
       </c>
       <c r="W17" s="1">
-        <v>5.0037592499999985E-2</v>
+        <v>0.10007518499999997</v>
       </c>
       <c r="X17" s="1">
-        <v>6.8792260320000007E-2</v>
+        <v>0.13758452064000001</v>
       </c>
       <c r="Y17" s="1">
-        <v>4.6068758499999994E-2</v>
+        <v>9.2137516999999988E-2</v>
       </c>
       <c r="Z17" s="1">
-        <v>0.19793855568000002</v>
+        <v>0.39587711136000003</v>
       </c>
       <c r="AA17" s="1">
-        <v>0.23635112661999996</v>
+        <v>0.47270225323999993</v>
       </c>
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.2">
@@ -75077,76 +75141,76 @@
         <v>3</v>
       </c>
       <c r="D18" s="1">
-        <v>-0.63052794090000019</v>
+        <v>-1.2610558818000004</v>
       </c>
       <c r="E18" s="1">
-        <v>-0.68864997801600003</v>
+        <v>-1.3772999560320001</v>
       </c>
       <c r="F18" s="1">
-        <v>-0.63179785416000001</v>
+        <v>-1.26359570832</v>
       </c>
       <c r="G18" s="1">
-        <v>-0.76270854575999991</v>
+        <v>-1.5254170915199998</v>
       </c>
       <c r="H18" s="1">
-        <v>-0.94683375335577602</v>
+        <v>-1.893667506711552</v>
       </c>
       <c r="I18" s="1">
-        <v>-0.93541325383833573</v>
+        <v>-1.8708265076766715</v>
       </c>
       <c r="J18" s="1">
-        <v>-0.8749548809193024</v>
+        <v>-1.7499097618386048</v>
       </c>
       <c r="K18" s="1">
-        <v>-0.98216490131020751</v>
+        <v>-1.964329802620415</v>
       </c>
       <c r="L18" s="1">
-        <v>-1.0244333819437199</v>
+        <v>-2.0488667638874398</v>
       </c>
       <c r="M18" s="1">
-        <v>-1.2564901467263692</v>
+        <v>-2.5129802934527383</v>
       </c>
       <c r="N18" s="1">
-        <v>-1.4450332163438251</v>
+        <v>-2.8900664326876502</v>
       </c>
       <c r="O18" s="1">
-        <v>-1.2569900455562792</v>
+        <v>-2.5139800911125585</v>
       </c>
       <c r="P18" s="1">
-        <v>-1.2165007092173021</v>
+        <v>-2.4330014184346043</v>
       </c>
       <c r="Q18" s="1">
-        <v>-1.1261617415460716</v>
+        <v>-2.2523234830921433</v>
       </c>
       <c r="R18" s="1">
-        <v>-1.1401953109603058</v>
+        <v>-2.2803906219206116</v>
       </c>
       <c r="S18" s="1">
-        <v>-0.97737287439999976</v>
+        <v>-1.9547457487999995</v>
       </c>
       <c r="T18" s="1">
-        <v>-0.90533262374755208</v>
+        <v>-1.8106652474951042</v>
       </c>
       <c r="U18" s="1">
-        <v>-0.82588578313393146</v>
+        <v>-1.6517715662678629</v>
       </c>
       <c r="V18" s="1">
-        <v>-0.493557497904</v>
+        <v>-0.987114995808</v>
       </c>
       <c r="W18" s="1">
-        <v>-0.58185132609869483</v>
+        <v>-1.1637026521973897</v>
       </c>
       <c r="X18" s="1">
-        <v>-0.6395272490791799</v>
+        <v>-1.2790544981583598</v>
       </c>
       <c r="Y18" s="1">
-        <v>-0.60244361524727497</v>
+        <v>-1.2048872304945499</v>
       </c>
       <c r="Z18" s="1">
-        <v>-0.49814432105518075</v>
+        <v>-0.9962886421103615</v>
       </c>
       <c r="AA18" s="1">
-        <v>-0.57877197880319997</v>
+        <v>-1.1575439576063999</v>
       </c>
     </row>
     <row r="19" spans="1:27" x14ac:dyDescent="0.2">
@@ -75160,76 +75224,76 @@
         <v>3</v>
       </c>
       <c r="D19" s="1">
-        <v>0.51083982582108745</v>
+        <v>1.0216796516421749</v>
       </c>
       <c r="E19" s="1">
-        <v>0.61137825232642551</v>
+        <v>1.222756504652851</v>
       </c>
       <c r="F19" s="1">
-        <v>0.78093755865215986</v>
+        <v>1.5618751173043197</v>
       </c>
       <c r="G19" s="1">
-        <v>0.72244644768676802</v>
+        <v>1.444892895373536</v>
       </c>
       <c r="H19" s="1">
-        <v>0.84155828627870954</v>
+        <v>1.6831165725574191</v>
       </c>
       <c r="I19" s="1">
-        <v>0.8488902153856801</v>
+        <v>1.6977804307713602</v>
       </c>
       <c r="J19" s="1">
-        <v>0.85053941027999991</v>
+        <v>1.7010788205599998</v>
       </c>
       <c r="K19" s="1">
-        <v>0.95982710659920001</v>
+        <v>1.9196542131984</v>
       </c>
       <c r="L19" s="1">
-        <v>0.82912388938869019</v>
+        <v>1.6582477787773804</v>
       </c>
       <c r="M19" s="1">
-        <v>1.0782021630427923</v>
+        <v>2.1564043260855845</v>
       </c>
       <c r="N19" s="1">
-        <v>1.00269374045862</v>
+        <v>2.0053874809172401</v>
       </c>
       <c r="O19" s="1">
-        <v>0.91817404439560801</v>
+        <v>1.836348088791216</v>
       </c>
       <c r="P19" s="1">
-        <v>0.98023557445632004</v>
+        <v>1.9604711489126401</v>
       </c>
       <c r="Q19" s="1">
-        <v>0.93882569120688353</v>
+        <v>1.8776513824137671</v>
       </c>
       <c r="R19" s="1">
-        <v>0.8781539979199684</v>
+        <v>1.7563079958399368</v>
       </c>
       <c r="S19" s="1">
-        <v>0.73836653949764652</v>
+        <v>1.476733078995293</v>
       </c>
       <c r="T19" s="1">
-        <v>0.79121917451303969</v>
+        <v>1.5824383490260794</v>
       </c>
       <c r="U19" s="1">
-        <v>0.67933526719758319</v>
+        <v>1.3586705343951664</v>
       </c>
       <c r="V19" s="1">
-        <v>0.59919618208741188</v>
+        <v>1.1983923641748238</v>
       </c>
       <c r="W19" s="1">
-        <v>0.61440240339280017</v>
+        <v>1.2288048067856003</v>
       </c>
       <c r="X19" s="1">
-        <v>0.61980949457856005</v>
+        <v>1.2396189891571201</v>
       </c>
       <c r="Y19" s="1">
-        <v>0.73792654034037142</v>
+        <v>1.4758530806807428</v>
       </c>
       <c r="Z19" s="1">
-        <v>0.49513974507359987</v>
+        <v>0.99027949014719974</v>
       </c>
       <c r="AA19" s="1">
-        <v>0.54161794955520015</v>
+        <v>1.0832358991104003</v>
       </c>
     </row>
     <row r="20" spans="1:27" x14ac:dyDescent="0.2">
@@ -75243,76 +75307,76 @@
         <v>1</v>
       </c>
       <c r="D20" s="1">
-        <v>0.29541418500000011</v>
+        <v>0.59082837000000021</v>
       </c>
       <c r="E20" s="1">
-        <v>0.30526853500000006</v>
+        <v>0.61053707000000013</v>
       </c>
       <c r="F20" s="1">
-        <v>0.27335005500000004</v>
+        <v>0.54670011000000007</v>
       </c>
       <c r="G20" s="1">
-        <v>0.25909729999999997</v>
+        <v>0.51819459999999995</v>
       </c>
       <c r="H20" s="1">
-        <v>0.21227711999999999</v>
+        <v>0.42455423999999997</v>
       </c>
       <c r="I20" s="1">
-        <v>0.18016636000000003</v>
+        <v>0.36033272000000005</v>
       </c>
       <c r="J20" s="1">
-        <v>0.220328845</v>
+        <v>0.44065768999999999</v>
       </c>
       <c r="K20" s="1">
-        <v>3.8263720000000008E-2</v>
+        <v>7.6527440000000016E-2</v>
       </c>
       <c r="L20" s="1">
-        <v>3.3648999999999998E-2</v>
+        <v>6.7297999999999997E-2</v>
       </c>
       <c r="M20" s="1">
-        <v>4.9055434999999988E-2</v>
+        <v>9.8110869999999975E-2</v>
       </c>
       <c r="N20" s="1">
-        <v>2.889007E-2</v>
+        <v>5.7780140000000001E-2</v>
       </c>
       <c r="O20" s="1">
-        <v>3.6100569999999992E-2</v>
+        <v>7.2201139999999983E-2</v>
       </c>
       <c r="P20" s="1">
-        <v>5.7515755000000016E-2</v>
+        <v>0.11503151000000003</v>
       </c>
       <c r="Q20" s="1">
-        <v>0.10597031500000001</v>
+        <v>0.21194063000000002</v>
       </c>
       <c r="R20" s="1">
-        <v>0.11306064</v>
+        <v>0.22612128000000001</v>
       </c>
       <c r="S20" s="1">
-        <v>0.11118590999999997</v>
+        <v>0.22237181999999994</v>
       </c>
       <c r="T20" s="1">
-        <v>6.2370824999999998E-2</v>
+        <v>0.12474165</v>
       </c>
       <c r="U20" s="1">
-        <v>0.12704900999999996</v>
+        <v>0.25409801999999992</v>
       </c>
       <c r="V20" s="1">
-        <v>7.4556570000000003E-2</v>
+        <v>0.14911314000000001</v>
       </c>
       <c r="W20" s="1">
-        <v>5.2420334999999985E-2</v>
+        <v>0.10484066999999997</v>
       </c>
       <c r="X20" s="1">
-        <v>7.9603920000000022E-2</v>
+        <v>0.15920784000000004</v>
       </c>
       <c r="Y20" s="1">
-        <v>4.9199645E-2</v>
+        <v>9.839929E-2</v>
       </c>
       <c r="Z20" s="1">
-        <v>0.22455900500000001</v>
+        <v>0.44911801000000001</v>
       </c>
       <c r="AA20" s="1">
-        <v>0.27070620499999998</v>
+        <v>0.54141240999999996</v>
       </c>
     </row>
     <row r="21" spans="1:27" x14ac:dyDescent="0.2">
@@ -75326,76 +75390,76 @@
         <v>1</v>
       </c>
       <c r="D21" s="1">
-        <v>-0.61161210267300015</v>
+        <v>-1.2232242053460003</v>
       </c>
       <c r="E21" s="1">
-        <v>-0.72308247691680005</v>
+        <v>-1.4461649538336001</v>
       </c>
       <c r="F21" s="1">
-        <v>-0.61284391853519993</v>
+        <v>-1.2256878370703999</v>
       </c>
       <c r="G21" s="1">
-        <v>-0.77796271667519989</v>
+        <v>-1.5559254333503998</v>
       </c>
       <c r="H21" s="1">
-        <v>-0.98470710349000723</v>
+        <v>-1.9694142069800145</v>
       </c>
       <c r="I21" s="1">
-        <v>-0.93541325383833573</v>
+        <v>-1.8708265076766715</v>
       </c>
       <c r="J21" s="1">
-        <v>-0.88370442972849561</v>
+        <v>-1.7674088594569912</v>
       </c>
       <c r="K21" s="1">
-        <v>-0.97234325229710539</v>
+        <v>-1.9446865045942108</v>
       </c>
       <c r="L21" s="1">
-        <v>-1.0346777157631568</v>
+        <v>-2.0693554315263136</v>
       </c>
       <c r="M21" s="1">
-        <v>-1.2564901467263692</v>
+        <v>-2.5129802934527383</v>
       </c>
       <c r="N21" s="1">
-        <v>-1.4305828841803867</v>
+        <v>-2.8611657683607734</v>
       </c>
       <c r="O21" s="1">
-        <v>-1.3072696473785306</v>
+        <v>-2.6145392947570611</v>
       </c>
       <c r="P21" s="1">
-        <v>-1.2165007092173021</v>
+        <v>-2.4330014184346043</v>
       </c>
       <c r="Q21" s="1">
-        <v>-1.1599465937924536</v>
+        <v>-2.3198931875849071</v>
       </c>
       <c r="R21" s="1">
-        <v>-1.1059894516314965</v>
+        <v>-2.2119789032629931</v>
       </c>
       <c r="S21" s="1">
-        <v>-0.95782541691199974</v>
+        <v>-1.9156508338239995</v>
       </c>
       <c r="T21" s="1">
-        <v>-0.86006599256017446</v>
+        <v>-1.7201319851203489</v>
       </c>
       <c r="U21" s="1">
-        <v>-0.82588578313393146</v>
+        <v>-1.6517715662678629</v>
       </c>
       <c r="V21" s="1">
-        <v>-0.50342864786207997</v>
+        <v>-1.0068572957241599</v>
       </c>
       <c r="W21" s="1">
-        <v>-0.5993068658816556</v>
+        <v>-1.1986137317633112</v>
       </c>
       <c r="X21" s="1">
-        <v>-0.66510833904234712</v>
+        <v>-1.3302166780846942</v>
       </c>
       <c r="Y21" s="1">
-        <v>-0.59039474294232952</v>
+        <v>-1.180789485884659</v>
       </c>
       <c r="Z21" s="1">
-        <v>-0.49814432105518075</v>
+        <v>-0.9962886421103615</v>
       </c>
       <c r="AA21" s="1">
-        <v>-0.59613513816729591</v>
+        <v>-1.1922702763345918</v>
       </c>
     </row>
     <row r="22" spans="1:27" x14ac:dyDescent="0.2">
@@ -75409,76 +75473,76 @@
         <v>1</v>
       </c>
       <c r="D22" s="1">
-        <v>0.48529783453003306</v>
+        <v>0.97059566906006611</v>
       </c>
       <c r="E22" s="1">
-        <v>0.62360581737295395</v>
+        <v>1.2472116347459079</v>
       </c>
       <c r="F22" s="1">
-        <v>0.80436568541172471</v>
+        <v>1.6087313708234494</v>
       </c>
       <c r="G22" s="1">
-        <v>0.70799751873303252</v>
+        <v>1.415995037466065</v>
       </c>
       <c r="H22" s="1">
-        <v>0.85838945200428385</v>
+        <v>1.7167789040085677</v>
       </c>
       <c r="I22" s="1">
-        <v>0.84040131323182321</v>
+        <v>1.6808026264636464</v>
       </c>
       <c r="J22" s="1">
-        <v>0.82502322797159988</v>
+        <v>1.6500464559431998</v>
       </c>
       <c r="K22" s="1">
-        <v>0.98862191979717584</v>
+        <v>1.9772438395943517</v>
       </c>
       <c r="L22" s="1">
-        <v>0.87058008385812469</v>
+        <v>1.7411601677162494</v>
       </c>
       <c r="M22" s="1">
-        <v>1.1105482279340761</v>
+        <v>2.2210964558681523</v>
       </c>
       <c r="N22" s="1">
-        <v>0.98263986564944739</v>
+        <v>1.9652797312988948</v>
       </c>
       <c r="O22" s="1">
-        <v>0.93653752528352019</v>
+        <v>1.8730750505670404</v>
       </c>
       <c r="P22" s="1">
-        <v>1.0194449974345727</v>
+        <v>2.0388899948691455</v>
       </c>
       <c r="Q22" s="1">
-        <v>0.9669904619430898</v>
+        <v>1.9339809238861796</v>
       </c>
       <c r="R22" s="1">
-        <v>0.85180937798236922</v>
+        <v>1.7036187559647384</v>
       </c>
       <c r="S22" s="1">
-        <v>0.73098287410267004</v>
+        <v>1.4619657482053401</v>
       </c>
       <c r="T22" s="1">
-        <v>0.80704355800330041</v>
+        <v>1.6140871160066008</v>
       </c>
       <c r="U22" s="1">
-        <v>0.65895520918165584</v>
+        <v>1.3179104183633117</v>
       </c>
       <c r="V22" s="1">
-        <v>0.61717206755003429</v>
+        <v>1.2343441351000686</v>
       </c>
       <c r="W22" s="1">
-        <v>0.63897849952851205</v>
+        <v>1.2779569990570241</v>
       </c>
       <c r="X22" s="1">
-        <v>0.61361139963277445</v>
+        <v>1.2272227992655489</v>
       </c>
       <c r="Y22" s="1">
-        <v>0.73054727493696769</v>
+        <v>1.4610945498739354</v>
       </c>
       <c r="Z22" s="1">
-        <v>0.50504253997507187</v>
+        <v>1.0100850799501437</v>
       </c>
       <c r="AA22" s="1">
-        <v>0.5470341290507521</v>
+        <v>1.0940682581015042</v>
       </c>
     </row>
     <row r="23" spans="1:27" x14ac:dyDescent="0.2">
@@ -75492,76 +75556,76 @@
         <v>2</v>
       </c>
       <c r="D23" s="1">
-        <v>0.31018489425000006</v>
+        <v>0.62036978850000013</v>
       </c>
       <c r="E23" s="1">
-        <v>0.32053196174999998</v>
+        <v>0.64106392349999997</v>
       </c>
       <c r="F23" s="1">
-        <v>0.26241605280000002</v>
+        <v>0.52483210560000004</v>
       </c>
       <c r="G23" s="1">
-        <v>0.25132438099999999</v>
+        <v>0.50264876199999997</v>
       </c>
       <c r="H23" s="1">
-        <v>0.2101543488</v>
+        <v>0.4203086976</v>
       </c>
       <c r="I23" s="1">
-        <v>0.17656303280000002</v>
+        <v>0.35312606560000004</v>
       </c>
       <c r="J23" s="1">
-        <v>0.21812555654999999</v>
+        <v>0.43625111309999998</v>
       </c>
       <c r="K23" s="1">
-        <v>3.8646357200000002E-2</v>
+        <v>7.7292714400000004E-2</v>
       </c>
       <c r="L23" s="1">
-        <v>3.2976020000000002E-2</v>
+        <v>6.5952040000000003E-2</v>
       </c>
       <c r="M23" s="1">
-        <v>4.9545989349999993E-2</v>
+        <v>9.9091978699999986E-2</v>
       </c>
       <c r="N23" s="1">
-        <v>3.0045672800000006E-2</v>
+        <v>6.0091345600000012E-2</v>
       </c>
       <c r="O23" s="1">
-        <v>3.7544592799999998E-2</v>
+        <v>7.5089185599999997E-2</v>
       </c>
       <c r="P23" s="1">
-        <v>5.6365439900000015E-2</v>
+        <v>0.11273087980000003</v>
       </c>
       <c r="Q23" s="1">
-        <v>0.11020912760000001</v>
+        <v>0.22041825520000002</v>
       </c>
       <c r="R23" s="1">
-        <v>0.11871367199999998</v>
+        <v>0.23742734399999996</v>
       </c>
       <c r="S23" s="1">
-        <v>0.10562661449999999</v>
+        <v>0.21125322899999999</v>
       </c>
       <c r="T23" s="1">
-        <v>6.4241949749999999E-2</v>
+        <v>0.1284838995</v>
       </c>
       <c r="U23" s="1">
-        <v>0.13213097039999996</v>
+        <v>0.26426194079999993</v>
       </c>
       <c r="V23" s="1">
-        <v>7.3065438600000004E-2</v>
+        <v>0.14613087720000001</v>
       </c>
       <c r="W23" s="1">
-        <v>5.1896131649999989E-2</v>
+        <v>0.10379226329999998</v>
       </c>
       <c r="X23" s="1">
-        <v>7.9603920000000022E-2</v>
+        <v>0.15920784000000004</v>
       </c>
       <c r="Y23" s="1">
-        <v>5.0675634349999998E-2</v>
+        <v>0.1013512687</v>
       </c>
       <c r="Z23" s="1">
-        <v>0.23578695525000004</v>
+        <v>0.47157391050000008</v>
       </c>
       <c r="AA23" s="1">
-        <v>0.27612032910000001</v>
+        <v>0.55224065820000001</v>
       </c>
     </row>
     <row r="24" spans="1:27" x14ac:dyDescent="0.2">
@@ -75575,76 +75639,76 @@
         <v>2</v>
       </c>
       <c r="D24" s="1">
-        <v>-0.61772822369973024</v>
+        <v>-1.2354564473994605</v>
       </c>
       <c r="E24" s="1">
-        <v>-0.74477495122430404</v>
+        <v>-1.4895499024486081</v>
       </c>
       <c r="F24" s="1">
-        <v>-0.60058704016449593</v>
+        <v>-1.2011740803289919</v>
       </c>
       <c r="G24" s="1">
-        <v>-0.76240346234169576</v>
+        <v>-1.5248069246833915</v>
       </c>
       <c r="H24" s="1">
-        <v>-0.99455417452490735</v>
+        <v>-1.9891083490498147</v>
       </c>
       <c r="I24" s="1">
-        <v>-0.90735085622318556</v>
+        <v>-1.8147017124463711</v>
       </c>
       <c r="J24" s="1">
-        <v>-0.86603034113392585</v>
+        <v>-1.7320606822678517</v>
       </c>
       <c r="K24" s="1">
-        <v>-0.99179011734304745</v>
+        <v>-1.9835802346860949</v>
       </c>
       <c r="L24" s="1">
-        <v>-1.0760648243936832</v>
+        <v>-2.1521296487873665</v>
       </c>
       <c r="M24" s="1">
-        <v>-1.2941848511281602</v>
+        <v>-2.5883697022563203</v>
       </c>
       <c r="N24" s="1">
-        <v>-1.3733595688131714</v>
+        <v>-2.7467191376263429</v>
       </c>
       <c r="O24" s="1">
-        <v>-1.3464877367998864</v>
+        <v>-2.6929754735997729</v>
       </c>
       <c r="P24" s="1">
-        <v>-1.1800056879407834</v>
+        <v>-2.3600113758815668</v>
       </c>
       <c r="Q24" s="1">
-        <v>-1.1367476619166046</v>
+        <v>-2.2734953238332092</v>
       </c>
       <c r="R24" s="1">
-        <v>-1.1059894516314965</v>
+        <v>-2.2119789032629931</v>
       </c>
       <c r="S24" s="1">
-        <v>-0.91951240023551972</v>
+        <v>-1.8390248004710394</v>
       </c>
       <c r="T24" s="1">
-        <v>-0.86866665248577613</v>
+        <v>-1.7373333049715523</v>
       </c>
       <c r="U24" s="1">
-        <v>-0.78459149397723493</v>
+        <v>-1.5691829879544699</v>
       </c>
       <c r="V24" s="1">
-        <v>-0.48329150194759685</v>
+        <v>-0.96658300389519369</v>
       </c>
       <c r="W24" s="1">
-        <v>-0.5993068658816556</v>
+        <v>-1.1986137317633112</v>
       </c>
       <c r="X24" s="1">
-        <v>-0.69171267260404101</v>
+        <v>-1.383425345208082</v>
       </c>
       <c r="Y24" s="1">
-        <v>-0.57268290065405958</v>
+        <v>-1.1453658013081192</v>
       </c>
       <c r="Z24" s="1">
-        <v>-0.50810720747628446</v>
+        <v>-1.0162144149525689</v>
       </c>
       <c r="AA24" s="1">
-        <v>-0.59017378678562293</v>
+        <v>-1.1803475735712459</v>
       </c>
     </row>
     <row r="25" spans="1:27" x14ac:dyDescent="0.2">
@@ -75658,76 +75722,76 @@
         <v>2</v>
       </c>
       <c r="D25" s="1">
-        <v>0.48044485618473276</v>
+        <v>0.96088971236946552</v>
       </c>
       <c r="E25" s="1">
-        <v>0.62360581737295395</v>
+        <v>1.2472116347459079</v>
       </c>
       <c r="F25" s="1">
-        <v>0.76414740114113844</v>
+        <v>1.5282948022822769</v>
       </c>
       <c r="G25" s="1">
-        <v>0.7221574691076933</v>
+        <v>1.4443149382153866</v>
       </c>
       <c r="H25" s="1">
-        <v>0.87555724104436961</v>
+        <v>1.7511144820887392</v>
       </c>
       <c r="I25" s="1">
-        <v>0.86561335262877781</v>
+        <v>1.7312267052575556</v>
       </c>
       <c r="J25" s="1">
-        <v>0.83327346025131577</v>
+        <v>1.6665469205026315</v>
       </c>
       <c r="K25" s="1">
-        <v>0.98862191979717584</v>
+        <v>1.9772438395943517</v>
       </c>
       <c r="L25" s="1">
-        <v>0.8270510796652184</v>
+        <v>1.6541021593304368</v>
       </c>
       <c r="M25" s="1">
-        <v>1.154970157051439</v>
+        <v>2.309940314102878</v>
       </c>
       <c r="N25" s="1">
-        <v>1.0121190616189311</v>
+        <v>2.0242381232378621</v>
       </c>
       <c r="O25" s="1">
-        <v>0.9459029005363554</v>
+        <v>1.8918058010727108</v>
       </c>
       <c r="P25" s="1">
-        <v>1.0194449974345727</v>
+        <v>2.0388899948691455</v>
       </c>
       <c r="Q25" s="1">
-        <v>0.95732055732365906</v>
+        <v>1.9146411146473181</v>
       </c>
       <c r="R25" s="1">
-        <v>0.80921890908325067</v>
+        <v>1.6184378181665013</v>
       </c>
       <c r="S25" s="1">
-        <v>0.69443373039753642</v>
+        <v>1.3888674607950728</v>
       </c>
       <c r="T25" s="1">
-        <v>0.78283225126320144</v>
+        <v>1.5656645025264029</v>
       </c>
       <c r="U25" s="1">
-        <v>0.64577610499802274</v>
+        <v>1.2915522099960455</v>
       </c>
       <c r="V25" s="1">
-        <v>0.61717206755003429</v>
+        <v>1.2343441351000686</v>
       </c>
       <c r="W25" s="1">
-        <v>0.65814785451436753</v>
+        <v>1.3162957090287351</v>
       </c>
       <c r="X25" s="1">
-        <v>0.58293082965113574</v>
+        <v>1.1658616593022715</v>
       </c>
       <c r="Y25" s="1">
-        <v>0.76707463868381598</v>
+        <v>1.534149277367632</v>
       </c>
       <c r="Z25" s="1">
-        <v>0.49494168917557041</v>
+        <v>0.98988337835114082</v>
       </c>
       <c r="AA25" s="1">
-        <v>0.56344515292227471</v>
+        <v>1.1268903058445494</v>
       </c>
     </row>
     <row r="26" spans="1:27" x14ac:dyDescent="0.2">
@@ -75741,76 +75805,76 @@
         <v>3</v>
       </c>
       <c r="D26" s="1">
-        <v>0.31949044107750008</v>
+        <v>0.63898088215500015</v>
       </c>
       <c r="E26" s="1">
-        <v>0.32373728136750002</v>
+        <v>0.64747456273500004</v>
       </c>
       <c r="F26" s="1">
-        <v>0.25979189227200006</v>
+        <v>0.51958378454400012</v>
       </c>
       <c r="G26" s="1">
-        <v>0.26389060004999998</v>
+        <v>0.52778120009999996</v>
       </c>
       <c r="H26" s="1">
-        <v>0.21225589228800001</v>
+        <v>0.42451178457600003</v>
       </c>
       <c r="I26" s="1">
-        <v>0.17656303280000002</v>
+        <v>0.35312606560000004</v>
       </c>
       <c r="J26" s="1">
-        <v>0.20721927872249996</v>
+        <v>0.41443855744499991</v>
       </c>
       <c r="K26" s="1">
-        <v>3.6714039340000004E-2</v>
+        <v>7.3428078680000008E-2</v>
       </c>
       <c r="L26" s="1">
-        <v>3.1327219000000003E-2</v>
+        <v>6.2654438000000007E-2</v>
       </c>
       <c r="M26" s="1">
-        <v>4.8059609669499993E-2</v>
+        <v>9.6119219338999987E-2</v>
       </c>
       <c r="N26" s="1">
-        <v>2.9745216072000001E-2</v>
+        <v>5.9490432144000002E-2</v>
       </c>
       <c r="O26" s="1">
-        <v>3.8295484655999995E-2</v>
+        <v>7.659096931199999E-2</v>
       </c>
       <c r="P26" s="1">
-        <v>5.5238131102000008E-2</v>
+        <v>0.11047626220400002</v>
       </c>
       <c r="Q26" s="1">
-        <v>0.11571958398000001</v>
+        <v>0.23143916796000003</v>
       </c>
       <c r="R26" s="1">
-        <v>0.12464935559999998</v>
+        <v>0.24929871119999997</v>
       </c>
       <c r="S26" s="1">
-        <v>0.11090794522499998</v>
+        <v>0.22181589044999997</v>
       </c>
       <c r="T26" s="1">
-        <v>6.4884369247500004E-2</v>
+        <v>0.12976873849500001</v>
       </c>
       <c r="U26" s="1">
-        <v>0.13213097039999996</v>
+        <v>0.26426194079999993</v>
       </c>
       <c r="V26" s="1">
-        <v>7.3065438600000004E-2</v>
+        <v>0.14613087720000001</v>
       </c>
       <c r="W26" s="1">
-        <v>4.982028638399999E-2</v>
+        <v>9.964057276799998E-2</v>
       </c>
       <c r="X26" s="1">
-        <v>7.7215802400000005E-2</v>
+        <v>0.15443160480000001</v>
       </c>
       <c r="Y26" s="1">
-        <v>5.1182390693500002E-2</v>
+        <v>0.102364781387</v>
       </c>
       <c r="Z26" s="1">
-        <v>0.22871334659250003</v>
+        <v>0.45742669318500007</v>
       </c>
       <c r="AA26" s="1">
-        <v>0.28440393897299998</v>
+        <v>0.56880787794599996</v>
       </c>
     </row>
     <row r="27" spans="1:27" x14ac:dyDescent="0.2">
@@ -75824,76 +75888,76 @@
         <v>3</v>
       </c>
       <c r="D27" s="1">
-        <v>-0.64861463488471682</v>
+        <v>-1.2972292697694336</v>
       </c>
       <c r="E27" s="1">
-        <v>-0.73732720171206112</v>
+        <v>-1.4746544034241222</v>
       </c>
       <c r="F27" s="1">
-        <v>-0.59458116976285091</v>
+        <v>-1.1891623395257018</v>
       </c>
       <c r="G27" s="1">
-        <v>-0.73953135847144491</v>
+        <v>-1.4790627169428898</v>
       </c>
       <c r="H27" s="1">
-        <v>-0.98460863277965838</v>
+        <v>-1.9692172655593168</v>
       </c>
       <c r="I27" s="1">
-        <v>-0.93457138190988132</v>
+        <v>-1.8691427638197626</v>
       </c>
       <c r="J27" s="1">
-        <v>-0.82272882407722947</v>
+        <v>-1.6454576481544589</v>
       </c>
       <c r="K27" s="1">
-        <v>-0.98187221616961706</v>
+        <v>-1.9637444323392341</v>
       </c>
       <c r="L27" s="1">
-        <v>-1.0437828796618727</v>
+        <v>-2.0875657593237453</v>
       </c>
       <c r="M27" s="1">
-        <v>-1.333010396662005</v>
+        <v>-2.6660207933240101</v>
       </c>
       <c r="N27" s="1">
-        <v>-1.3733595688131714</v>
+        <v>-2.7467191376263429</v>
       </c>
       <c r="O27" s="1">
-        <v>-1.3464877367998864</v>
+        <v>-2.6929754735997729</v>
       </c>
       <c r="P27" s="1">
-        <v>-1.1564055741819677</v>
+        <v>-2.3128111483639353</v>
       </c>
       <c r="Q27" s="1">
-        <v>-1.1367476619166046</v>
+        <v>-2.2734953238332092</v>
       </c>
       <c r="R27" s="1">
-        <v>-1.1281092406641267</v>
+        <v>-2.2562184813282533</v>
       </c>
       <c r="S27" s="1">
-        <v>-0.93790264824023006</v>
+        <v>-1.8758052964804601</v>
       </c>
       <c r="T27" s="1">
-        <v>-0.89472665206034951</v>
+        <v>-1.789453304120699</v>
       </c>
       <c r="U27" s="1">
-        <v>-0.78459149397723493</v>
+        <v>-1.5691829879544699</v>
       </c>
       <c r="V27" s="1">
-        <v>-0.49295733198654884</v>
+        <v>-0.98591466397309768</v>
       </c>
       <c r="W27" s="1">
-        <v>-0.6232791405169219</v>
+        <v>-1.2465582810338438</v>
       </c>
       <c r="X27" s="1">
-        <v>-0.67096129242591984</v>
+        <v>-1.3419225848518397</v>
       </c>
       <c r="Y27" s="1">
-        <v>-0.57840972966060011</v>
+        <v>-1.1568194593212002</v>
       </c>
       <c r="Z27" s="1">
-        <v>-0.48270184710247027</v>
+        <v>-0.96540369420494054</v>
       </c>
       <c r="AA27" s="1">
-        <v>-0.60197726252133543</v>
+        <v>-1.2039545250426709</v>
       </c>
     </row>
     <row r="28" spans="1:27" x14ac:dyDescent="0.2">
@@ -75907,76 +75971,76 @@
         <v>3</v>
       </c>
       <c r="D28" s="1">
-        <v>0.46603151049919084</v>
+        <v>0.93206302099838167</v>
       </c>
       <c r="E28" s="1">
-        <v>0.6048976428517655</v>
+        <v>1.209795285703531</v>
       </c>
       <c r="F28" s="1">
-        <v>0.76414740114113844</v>
+        <v>1.5282948022822769</v>
       </c>
       <c r="G28" s="1">
-        <v>0.74382219318092402</v>
+        <v>1.487644386361848</v>
       </c>
       <c r="H28" s="1">
-        <v>0.91933510309658806</v>
+        <v>1.8386702061931761</v>
       </c>
       <c r="I28" s="1">
-        <v>0.85695721910249001</v>
+        <v>1.71391443820498</v>
       </c>
       <c r="J28" s="1">
-        <v>0.87493713326388156</v>
+        <v>1.7498742665277631</v>
       </c>
       <c r="K28" s="1">
-        <v>0.9688494814012325</v>
+        <v>1.937698962802465</v>
       </c>
       <c r="L28" s="1">
-        <v>0.81878056886856621</v>
+        <v>1.6375611377371324</v>
       </c>
       <c r="M28" s="1">
-        <v>1.2127186649040111</v>
+        <v>2.4254373298080223</v>
       </c>
       <c r="N28" s="1">
-        <v>1.0526038240836884</v>
+        <v>2.1052076481673767</v>
       </c>
       <c r="O28" s="1">
-        <v>0.91752581352026485</v>
+        <v>1.8350516270405297</v>
       </c>
       <c r="P28" s="1">
-        <v>1.0194449974345727</v>
+        <v>2.0388899948691455</v>
       </c>
       <c r="Q28" s="1">
-        <v>0.99561337961660512</v>
+        <v>1.9912267592332102</v>
       </c>
       <c r="R28" s="1">
-        <v>0.80921890908325067</v>
+        <v>1.6184378181665013</v>
       </c>
       <c r="S28" s="1">
-        <v>0.68054505578958557</v>
+        <v>1.3610901115791711</v>
       </c>
       <c r="T28" s="1">
-        <v>0.75934728372530536</v>
+        <v>1.5186945674506107</v>
       </c>
       <c r="U28" s="1">
-        <v>0.67806491024792392</v>
+        <v>1.3561298204958478</v>
       </c>
       <c r="V28" s="1">
-        <v>0.61717206755003429</v>
+        <v>1.2343441351000686</v>
       </c>
       <c r="W28" s="1">
-        <v>0.65156637596922384</v>
+        <v>1.3031327519384477</v>
       </c>
       <c r="X28" s="1">
-        <v>0.60624806283718102</v>
+        <v>1.212496125674362</v>
       </c>
       <c r="Y28" s="1">
-        <v>0.74406239952330155</v>
+        <v>1.4881247990466031</v>
       </c>
       <c r="Z28" s="1">
-        <v>0.50978993985083743</v>
+        <v>1.0195798797016749</v>
       </c>
       <c r="AA28" s="1">
-        <v>0.54654179833460648</v>
+        <v>1.093083596669213</v>
       </c>
     </row>
     <row r="29" spans="1:27" x14ac:dyDescent="0.2">
@@ -75990,76 +76054,76 @@
         <v>1</v>
       </c>
       <c r="D29" s="1">
-        <v>0.28064347575000004</v>
+        <v>0.56128695150000008</v>
       </c>
       <c r="E29" s="1">
-        <v>0.29000510825000003</v>
+        <v>0.58001021650000006</v>
       </c>
       <c r="F29" s="1">
-        <v>0.25968255225000003</v>
+        <v>0.51936510450000006</v>
       </c>
       <c r="G29" s="1">
-        <v>0.24614243499999997</v>
+        <v>0.49228486999999993</v>
       </c>
       <c r="H29" s="1">
-        <v>0.20166326400000001</v>
+        <v>0.40332652800000002</v>
       </c>
       <c r="I29" s="1">
-        <v>0.17115804200000001</v>
+        <v>0.34231608400000002</v>
       </c>
       <c r="J29" s="1">
-        <v>0.20931240275000002</v>
+        <v>0.41862480550000003</v>
       </c>
       <c r="K29" s="1">
-        <v>3.6350534000000004E-2</v>
+        <v>7.2701068000000008E-2</v>
       </c>
       <c r="L29" s="1">
-        <v>3.1966549999999996E-2</v>
+        <v>6.3933099999999993E-2</v>
       </c>
       <c r="M29" s="1">
-        <v>4.6602663249999988E-2</v>
+        <v>9.3205326499999977E-2</v>
       </c>
       <c r="N29" s="1">
-        <v>2.7445566500000001E-2</v>
+        <v>5.4891133000000002E-2</v>
       </c>
       <c r="O29" s="1">
-        <v>3.4295541499999985E-2</v>
+        <v>6.8591082999999969E-2</v>
       </c>
       <c r="P29" s="1">
-        <v>5.4639967250000011E-2</v>
+        <v>0.10927993450000002</v>
       </c>
       <c r="Q29" s="1">
-        <v>0.10067179925</v>
+        <v>0.2013435985</v>
       </c>
       <c r="R29" s="1">
-        <v>0.107407608</v>
+        <v>0.214815216</v>
       </c>
       <c r="S29" s="1">
-        <v>0.10562661449999997</v>
+        <v>0.21125322899999993</v>
       </c>
       <c r="T29" s="1">
-        <v>5.9252283749999989E-2</v>
+        <v>0.11850456749999998</v>
       </c>
       <c r="U29" s="1">
-        <v>0.12069655949999998</v>
+        <v>0.24139311899999996</v>
       </c>
       <c r="V29" s="1">
-        <v>7.0828741499999986E-2</v>
+        <v>0.14165748299999997</v>
       </c>
       <c r="W29" s="1">
-        <v>4.9799318249999988E-2</v>
+        <v>9.9598636499999976E-2</v>
       </c>
       <c r="X29" s="1">
-        <v>7.5623724000000003E-2</v>
+        <v>0.15124744800000001</v>
       </c>
       <c r="Y29" s="1">
-        <v>4.6739662749999994E-2</v>
+        <v>9.3479325499999988E-2</v>
       </c>
       <c r="Z29" s="1">
-        <v>0.21333105475000003</v>
+        <v>0.42666210950000005</v>
       </c>
       <c r="AA29" s="1">
-        <v>0.25717089474999999</v>
+        <v>0.51434178949999998</v>
       </c>
     </row>
     <row r="30" spans="1:27" x14ac:dyDescent="0.2">
@@ -76073,76 +76137,76 @@
         <v>1</v>
       </c>
       <c r="D30" s="1">
-        <v>-0.64212848853586957</v>
+        <v>-1.2842569770717391</v>
       </c>
       <c r="E30" s="1">
-        <v>-0.73732720171206112</v>
+        <v>-1.4746544034241222</v>
       </c>
       <c r="F30" s="1">
-        <v>-0.57674373466996554</v>
+        <v>-1.1534874693399311</v>
       </c>
       <c r="G30" s="1">
-        <v>-0.76911261281030274</v>
+        <v>-1.5382252256206055</v>
       </c>
       <c r="H30" s="1">
-        <v>-1.023992978090845</v>
+        <v>-2.04798595618169</v>
       </c>
       <c r="I30" s="1">
-        <v>-0.97195423718627649</v>
+        <v>-1.943908474372553</v>
       </c>
       <c r="J30" s="1">
-        <v>-0.86386526528109076</v>
+        <v>-1.7277305305621815</v>
       </c>
       <c r="K30" s="1">
-        <v>-1.0211471048164018</v>
+        <v>-2.0422942096328036</v>
       </c>
       <c r="L30" s="1">
-        <v>-1.075096366051729</v>
+        <v>-2.150192732103458</v>
       </c>
       <c r="M30" s="1">
-        <v>-1.3596706045952451</v>
+        <v>-2.7193412091904903</v>
       </c>
       <c r="N30" s="1">
-        <v>-1.3870931645013029</v>
+        <v>-2.7741863290026059</v>
       </c>
       <c r="O30" s="1">
-        <v>-1.3599526141678853</v>
+        <v>-2.7199052283357705</v>
       </c>
       <c r="P30" s="1">
-        <v>-1.1101493512146889</v>
+        <v>-2.2202987024293779</v>
       </c>
       <c r="Q30" s="1">
-        <v>-1.0912777554399404</v>
+        <v>-2.1825555108798809</v>
       </c>
       <c r="R30" s="1">
-        <v>-1.1506714254774091</v>
+        <v>-2.3013428509548182</v>
       </c>
       <c r="S30" s="1">
-        <v>-0.94728167472263247</v>
+        <v>-1.8945633494452649</v>
       </c>
       <c r="T30" s="1">
-        <v>-0.90367391858095303</v>
+        <v>-1.8073478371619061</v>
       </c>
       <c r="U30" s="1">
-        <v>-0.80812923879655185</v>
+        <v>-1.6162584775931037</v>
       </c>
       <c r="V30" s="1">
-        <v>-0.46830946538722129</v>
+        <v>-0.93661893077444258</v>
       </c>
       <c r="W30" s="1">
-        <v>-0.62951193192209109</v>
+        <v>-1.2590238638441822</v>
       </c>
       <c r="X30" s="1">
-        <v>-0.64412284072888304</v>
+        <v>-1.2882456814577661</v>
       </c>
       <c r="Y30" s="1">
-        <v>-0.59576202155041813</v>
+        <v>-1.1915240431008363</v>
       </c>
       <c r="Z30" s="1">
-        <v>-0.49235588404451969</v>
+        <v>-0.98471176808903937</v>
       </c>
       <c r="AA30" s="1">
-        <v>-0.63207612564740223</v>
+        <v>-1.2641522512948045</v>
       </c>
     </row>
     <row r="31" spans="1:27" x14ac:dyDescent="0.2">
@@ -76156,76 +76220,76 @@
         <v>1</v>
       </c>
       <c r="D31" s="1">
-        <v>0.48467277091915839</v>
+        <v>0.96934554183831678</v>
       </c>
       <c r="E31" s="1">
-        <v>0.61094661928028304</v>
+        <v>1.2218932385605661</v>
       </c>
       <c r="F31" s="1">
-        <v>0.79471329718678396</v>
+        <v>1.5894265943735679</v>
       </c>
       <c r="G31" s="1">
-        <v>0.75869863704454243</v>
+        <v>1.5173972740890849</v>
       </c>
       <c r="H31" s="1">
-        <v>0.94691515618948563</v>
+        <v>1.8938303123789713</v>
       </c>
       <c r="I31" s="1">
-        <v>0.83981807472044034</v>
+        <v>1.6796361494408807</v>
       </c>
       <c r="J31" s="1">
-        <v>0.83119027660068734</v>
+        <v>1.6623805532013747</v>
       </c>
       <c r="K31" s="1">
-        <v>0.9688494814012325</v>
+        <v>1.937698962802465</v>
       </c>
       <c r="L31" s="1">
-        <v>0.83515618024593774</v>
+        <v>1.6703123604918755</v>
       </c>
       <c r="M31" s="1">
-        <v>1.2733545981492116</v>
+        <v>2.5467091962984232</v>
       </c>
       <c r="N31" s="1">
-        <v>1.0315517476020146</v>
+        <v>2.0631034952040292</v>
       </c>
       <c r="O31" s="1">
-        <v>0.91752581352026485</v>
+        <v>1.8350516270405297</v>
       </c>
       <c r="P31" s="1">
-        <v>1.0602227973319556</v>
+        <v>2.1204455946639111</v>
       </c>
       <c r="Q31" s="1">
-        <v>0.94583271063577479</v>
+        <v>1.8916654212715496</v>
       </c>
       <c r="R31" s="1">
-        <v>0.80921890908325067</v>
+        <v>1.6184378181665013</v>
       </c>
       <c r="S31" s="1">
-        <v>0.71457230857906484</v>
+        <v>1.4291446171581297</v>
       </c>
       <c r="T31" s="1">
-        <v>0.75175381088805238</v>
+        <v>1.5035076217761048</v>
       </c>
       <c r="U31" s="1">
-        <v>0.66450361204296537</v>
+        <v>1.3290072240859307</v>
       </c>
       <c r="V31" s="1">
-        <v>0.62951550890103503</v>
+        <v>1.2590310178020701</v>
       </c>
       <c r="W31" s="1">
-        <v>0.6711133672483004</v>
+        <v>1.3422267344966008</v>
       </c>
       <c r="X31" s="1">
-        <v>0.61837302409392481</v>
+        <v>1.2367460481878496</v>
       </c>
       <c r="Y31" s="1">
-        <v>0.72174052753760243</v>
+        <v>1.4434810550752049</v>
       </c>
       <c r="Z31" s="1">
-        <v>0.51488783924934589</v>
+        <v>1.0297756784986918</v>
       </c>
       <c r="AA31" s="1">
-        <v>0.55200721631795246</v>
+        <v>1.1040144326359049</v>
       </c>
     </row>
     <row r="32" spans="1:27" x14ac:dyDescent="0.2">
@@ -76239,76 +76303,76 @@
         <v>2</v>
       </c>
       <c r="D32" s="1">
-        <v>0.27783704099250006</v>
+        <v>0.55567408198500012</v>
       </c>
       <c r="E32" s="1">
-        <v>0.30450536366250003</v>
+        <v>0.60901072732500006</v>
       </c>
       <c r="F32" s="1">
-        <v>0.25968255225000003</v>
+        <v>0.51936510450000006</v>
       </c>
       <c r="G32" s="1">
-        <v>0.23383531324999995</v>
+        <v>0.46767062649999991</v>
       </c>
       <c r="H32" s="1">
-        <v>0.19964663136000002</v>
+        <v>0.39929326272000004</v>
       </c>
       <c r="I32" s="1">
-        <v>0.16260013990000002</v>
+        <v>0.32520027980000005</v>
       </c>
       <c r="J32" s="1">
-        <v>0.20093990664</v>
+        <v>0.40187981328</v>
       </c>
       <c r="K32" s="1">
-        <v>3.7441050020000012E-2</v>
+        <v>7.4882100040000024E-2</v>
       </c>
       <c r="L32" s="1">
-        <v>3.1966549999999996E-2</v>
+        <v>6.3933099999999993E-2</v>
       </c>
       <c r="M32" s="1">
-        <v>4.5670609984999985E-2</v>
+        <v>9.1341219969999971E-2</v>
       </c>
       <c r="N32" s="1">
-        <v>2.7171110835000001E-2</v>
+        <v>5.4342221670000003E-2</v>
       </c>
       <c r="O32" s="1">
-        <v>3.463849691499999E-2</v>
+        <v>6.927699382999998E-2</v>
       </c>
       <c r="P32" s="1">
-        <v>5.4093567577500015E-2</v>
+        <v>0.10818713515500003</v>
       </c>
       <c r="Q32" s="1">
-        <v>9.9665081257499982E-2</v>
+        <v>0.19933016251499996</v>
       </c>
       <c r="R32" s="1">
-        <v>0.10848168407999999</v>
+        <v>0.21696336815999998</v>
       </c>
       <c r="S32" s="1">
-        <v>0.10140154991999999</v>
+        <v>0.20280309983999997</v>
       </c>
       <c r="T32" s="1">
-        <v>5.9252283749999989E-2</v>
+        <v>0.11850456749999998</v>
       </c>
       <c r="U32" s="1">
-        <v>0.12673138747499996</v>
+        <v>0.25346277494999991</v>
       </c>
       <c r="V32" s="1">
-        <v>6.7995591840000008E-2</v>
+        <v>0.13599118368000002</v>
       </c>
       <c r="W32" s="1">
-        <v>5.0795304614999981E-2</v>
+        <v>0.10159060922999996</v>
       </c>
       <c r="X32" s="1">
-        <v>7.2598775040000008E-2</v>
+        <v>0.14519755008000002</v>
       </c>
       <c r="Y32" s="1">
-        <v>4.4870076239999994E-2</v>
+        <v>8.9740152479999988E-2</v>
       </c>
       <c r="Z32" s="1">
-        <v>0.21119774420250001</v>
+        <v>0.42239548840500002</v>
       </c>
       <c r="AA32" s="1">
-        <v>0.25717089474999999</v>
+        <v>0.51434178949999998</v>
       </c>
     </row>
     <row r="33" spans="1:27" x14ac:dyDescent="0.2">
@@ -76322,76 +76386,76 @@
         <v>2</v>
       </c>
       <c r="D33" s="1">
-        <v>-0.62928591876515205</v>
+        <v>-1.2585718375303041</v>
       </c>
       <c r="E33" s="1">
-        <v>-0.72258065767781987</v>
+        <v>-1.4451613153556397</v>
       </c>
       <c r="F33" s="1">
-        <v>-0.56520885997656611</v>
+        <v>-1.1304177199531322</v>
       </c>
       <c r="G33" s="1">
-        <v>-0.74603923442599351</v>
+        <v>-1.492078468851987</v>
       </c>
       <c r="H33" s="1">
-        <v>-1.0751926269953871</v>
+        <v>-2.1503852539907742</v>
       </c>
       <c r="I33" s="1">
-        <v>-0.94279561007068824</v>
+        <v>-1.8855912201413765</v>
       </c>
       <c r="J33" s="1">
-        <v>-0.88114257058671264</v>
+        <v>-1.7622851411734253</v>
       </c>
       <c r="K33" s="1">
-        <v>-1.0109356337682378</v>
+        <v>-2.0218712675364756</v>
       </c>
       <c r="L33" s="1">
-        <v>-1.0428434750701769</v>
+        <v>-2.0856869501403539</v>
       </c>
       <c r="M33" s="1">
-        <v>-1.3188804864573878</v>
+        <v>-2.6377609729147755</v>
       </c>
       <c r="N33" s="1">
-        <v>-1.3177385062762377</v>
+        <v>-2.6354770125524754</v>
       </c>
       <c r="O33" s="1">
-        <v>-1.4279502448762798</v>
+        <v>-2.8559004897525595</v>
       </c>
       <c r="P33" s="1">
-        <v>-1.1434538317511298</v>
+        <v>-2.2869076635022596</v>
       </c>
       <c r="Q33" s="1">
-        <v>-1.1131033105487391</v>
+        <v>-2.2262066210974782</v>
       </c>
       <c r="R33" s="1">
-        <v>-1.1966982824965056</v>
+        <v>-2.3933965649930111</v>
       </c>
       <c r="S33" s="1">
-        <v>-0.9851729417115378</v>
+        <v>-1.9703458834230756</v>
       </c>
       <c r="T33" s="1">
-        <v>-0.89463717939514353</v>
+        <v>-1.7892743587902871</v>
       </c>
       <c r="U33" s="1">
-        <v>-0.80004794640858656</v>
+        <v>-1.6000958928171731</v>
       </c>
       <c r="V33" s="1">
-        <v>-0.47299256004109347</v>
+        <v>-0.94598512008218694</v>
       </c>
       <c r="W33" s="1">
-        <v>-0.62951193192209109</v>
+        <v>-1.2590238638441822</v>
       </c>
       <c r="X33" s="1">
-        <v>-0.6570052975434606</v>
+        <v>-1.3140105950869212</v>
       </c>
       <c r="Y33" s="1">
-        <v>-0.62555012262793908</v>
+        <v>-1.2511002452558782</v>
       </c>
       <c r="Z33" s="1">
-        <v>-0.51697367824674567</v>
+        <v>-1.0339473564934913</v>
       </c>
       <c r="AA33" s="1">
-        <v>-0.60679308062150628</v>
+        <v>-1.2135861612430126</v>
       </c>
     </row>
     <row r="34" spans="1:27" x14ac:dyDescent="0.2">
@@ -76405,76 +76469,76 @@
         <v>2</v>
       </c>
       <c r="D34" s="1">
-        <v>0.46043913237320055</v>
+        <v>0.92087826474640111</v>
       </c>
       <c r="E34" s="1">
-        <v>0.62927501785869155</v>
+        <v>1.2585500357173831</v>
       </c>
       <c r="F34" s="1">
-        <v>0.75497763232744475</v>
+        <v>1.5099552646548895</v>
       </c>
       <c r="G34" s="1">
-        <v>0.72835069156276089</v>
+        <v>1.4567013831255218</v>
       </c>
       <c r="H34" s="1">
-        <v>0.89956939838001149</v>
+        <v>1.799138796760023</v>
       </c>
       <c r="I34" s="1">
-        <v>0.86501261696205345</v>
+        <v>1.7300252339241069</v>
       </c>
       <c r="J34" s="1">
-        <v>0.79794266553665982</v>
+        <v>1.5958853310733196</v>
       </c>
       <c r="K34" s="1">
-        <v>0.92040700733117087</v>
+        <v>1.8408140146623417</v>
       </c>
       <c r="L34" s="1">
-        <v>0.86856242745577517</v>
+        <v>1.7371248549115503</v>
       </c>
       <c r="M34" s="1">
-        <v>1.209686868241751</v>
+        <v>2.419373736483502</v>
       </c>
       <c r="N34" s="1">
-        <v>0.97997416022191375</v>
+        <v>1.9599483204438275</v>
       </c>
       <c r="O34" s="1">
-        <v>0.96340210419627803</v>
+        <v>1.9268042083925561</v>
       </c>
       <c r="P34" s="1">
-        <v>1.0814272532785947</v>
+        <v>2.1628545065571894</v>
       </c>
       <c r="Q34" s="1">
-        <v>0.96474936484849039</v>
+        <v>1.9294987296969808</v>
       </c>
       <c r="R34" s="1">
-        <v>0.82540328726491585</v>
+        <v>1.6508065745298317</v>
       </c>
       <c r="S34" s="1">
-        <v>0.71457230857906484</v>
+        <v>1.4291446171581297</v>
       </c>
       <c r="T34" s="1">
-        <v>0.75927134899693283</v>
+        <v>1.5185426979938657</v>
       </c>
       <c r="U34" s="1">
-        <v>0.64456850368167651</v>
+        <v>1.289137007363353</v>
       </c>
       <c r="V34" s="1">
-        <v>0.64840097416806608</v>
+        <v>1.2968019483361322</v>
       </c>
       <c r="W34" s="1">
-        <v>0.6845356345932665</v>
+        <v>1.369071269186533</v>
       </c>
       <c r="X34" s="1">
-        <v>0.58745437288922853</v>
+        <v>1.1749087457784571</v>
       </c>
       <c r="Y34" s="1">
-        <v>0.71452312226222647</v>
+        <v>1.4290462445244529</v>
       </c>
       <c r="Z34" s="1">
-        <v>0.48914344728687864</v>
+        <v>0.97828689457375728</v>
       </c>
       <c r="AA34" s="1">
-        <v>0.568567432807491</v>
+        <v>1.137134865614982</v>
       </c>
     </row>
     <row r="35" spans="1:27" x14ac:dyDescent="0.2">
@@ -76488,76 +76552,76 @@
         <v>3</v>
       </c>
       <c r="D35" s="1">
-        <v>0.27783704099250006</v>
+        <v>0.55567408198500012</v>
       </c>
       <c r="E35" s="1">
-        <v>0.31668557820900006</v>
+        <v>0.63337115641800013</v>
       </c>
       <c r="F35" s="1">
-        <v>0.25968255225000003</v>
+        <v>0.51936510450000006</v>
       </c>
       <c r="G35" s="1">
-        <v>0.22915860698499996</v>
+        <v>0.45831721396999991</v>
       </c>
       <c r="H35" s="1">
-        <v>0.18966429979200003</v>
+        <v>0.37932859958400006</v>
       </c>
       <c r="I35" s="1">
-        <v>0.15934813710200002</v>
+        <v>0.31869627420400004</v>
       </c>
       <c r="J35" s="1">
-        <v>0.19089291130799999</v>
+        <v>0.38178582261599997</v>
       </c>
       <c r="K35" s="1">
-        <v>3.6692229019600016E-2</v>
+        <v>7.3384458039200032E-2</v>
       </c>
       <c r="L35" s="1">
-        <v>3.1966549999999996E-2</v>
+        <v>6.3933099999999993E-2</v>
       </c>
       <c r="M35" s="1">
-        <v>4.612731608484999E-2</v>
+        <v>9.2254632169699979E-2</v>
       </c>
       <c r="N35" s="1">
-        <v>2.8529666376750001E-2</v>
+        <v>5.7059332753500003E-2</v>
       </c>
       <c r="O35" s="1">
-        <v>3.4292111945849989E-2</v>
+        <v>6.8584223891699977E-2</v>
       </c>
       <c r="P35" s="1">
-        <v>5.6798245956375018E-2</v>
+        <v>0.11359649191275004</v>
       </c>
       <c r="Q35" s="1">
-        <v>0.10165838288264999</v>
+        <v>0.20331676576529997</v>
       </c>
       <c r="R35" s="1">
-        <v>0.11065131776159998</v>
+        <v>0.22130263552319995</v>
       </c>
       <c r="S35" s="1">
-        <v>9.8359503422399991E-2</v>
+        <v>0.19671900684479998</v>
       </c>
       <c r="T35" s="1">
-        <v>6.1029852262499996E-2</v>
+        <v>0.12205970452499999</v>
       </c>
       <c r="U35" s="1">
-        <v>0.12292944585074997</v>
+        <v>0.24585889170149994</v>
       </c>
       <c r="V35" s="1">
-        <v>7.07154155136E-2</v>
+        <v>0.1414308310272</v>
       </c>
       <c r="W35" s="1">
-        <v>4.9271445476549984E-2</v>
+        <v>9.8542890953099968E-2</v>
       </c>
       <c r="X35" s="1">
-        <v>6.8968836288000004E-2</v>
+        <v>0.13793767257600001</v>
       </c>
       <c r="Y35" s="1">
-        <v>4.44213754776E-2</v>
+        <v>8.8842750955200001E-2</v>
       </c>
       <c r="Z35" s="1">
-        <v>0.21542169908655001</v>
+        <v>0.43084339817310002</v>
       </c>
       <c r="AA35" s="1">
-        <v>0.25459918580250002</v>
+        <v>0.50919837160500003</v>
       </c>
     </row>
     <row r="36" spans="1:27" x14ac:dyDescent="0.2">
@@ -76571,76 +76635,76 @@
         <v>3</v>
       </c>
       <c r="D36" s="1">
-        <v>-0.66075021470340967</v>
+        <v>-1.3215004294068193</v>
       </c>
       <c r="E36" s="1">
-        <v>-0.75870969056171089</v>
+        <v>-1.5174193811234218</v>
       </c>
       <c r="F36" s="1">
-        <v>-0.5821651257758631</v>
+        <v>-1.1643302515517262</v>
       </c>
       <c r="G36" s="1">
-        <v>-0.7609600191145135</v>
+        <v>-1.521920038229027</v>
       </c>
       <c r="H36" s="1">
-        <v>-1.0966964795352949</v>
+        <v>-2.1933929590705898</v>
       </c>
       <c r="I36" s="1">
-        <v>-0.98993539057422275</v>
+        <v>-1.9798707811484455</v>
       </c>
       <c r="J36" s="1">
-        <v>-0.85470829346911115</v>
+        <v>-1.7094165869382223</v>
       </c>
       <c r="K36" s="1">
-        <v>-1.0311543464436026</v>
+        <v>-2.0623086928872052</v>
       </c>
       <c r="L36" s="1">
-        <v>-1.0324150403194754</v>
+        <v>-2.0648300806389508</v>
       </c>
       <c r="M36" s="1">
-        <v>-1.2793140718636664</v>
+        <v>-2.5586281437273328</v>
       </c>
       <c r="N36" s="1">
-        <v>-1.2518515809624262</v>
+        <v>-2.5037031619248524</v>
       </c>
       <c r="O36" s="1">
-        <v>-1.399391239978754</v>
+        <v>-2.7987824799575081</v>
       </c>
       <c r="P36" s="1">
-        <v>-1.0862811401635732</v>
+        <v>-2.1725622803271465</v>
       </c>
       <c r="Q36" s="1">
-        <v>-1.1019722774432519</v>
+        <v>-2.2039445548865038</v>
       </c>
       <c r="R36" s="1">
-        <v>-1.2565331966213309</v>
+        <v>-2.5130663932426618</v>
       </c>
       <c r="S36" s="1">
-        <v>-1.0147281299628841</v>
+        <v>-2.0294562599257682</v>
       </c>
       <c r="T36" s="1">
-        <v>-0.84990532042538613</v>
+        <v>-1.6998106408507723</v>
       </c>
       <c r="U36" s="1">
-        <v>-0.84005034372901566</v>
+        <v>-1.6801006874580313</v>
       </c>
       <c r="V36" s="1">
-        <v>-0.47772248564150444</v>
+        <v>-0.95544497128300887</v>
       </c>
       <c r="W36" s="1">
-        <v>-0.64210217056053276</v>
+        <v>-1.2842043411210655</v>
       </c>
       <c r="X36" s="1">
-        <v>-0.6372951386171567</v>
+        <v>-1.2745902772343134</v>
       </c>
       <c r="Y36" s="1">
-        <v>-0.60052811772282144</v>
+        <v>-1.2010562354456429</v>
       </c>
       <c r="Z36" s="1">
-        <v>-0.53765262537661551</v>
+        <v>-1.075305250753231</v>
       </c>
       <c r="AA36" s="1">
-        <v>-0.59465721900907609</v>
+        <v>-1.1893144380181522</v>
       </c>
     </row>
     <row r="37" spans="1:27" x14ac:dyDescent="0.2">
@@ -76654,1013 +76718,77 @@
         <v>3</v>
       </c>
       <c r="D37" s="1">
-        <v>0.46043913237320055</v>
+        <v>0.92087826474640111</v>
       </c>
       <c r="E37" s="1">
-        <v>0.61668951750151779</v>
+        <v>1.2333790350030356</v>
       </c>
       <c r="F37" s="1">
-        <v>0.75497763232744475</v>
+        <v>1.5099552646548895</v>
       </c>
       <c r="G37" s="1">
-        <v>0.69193315698462277</v>
+        <v>1.3838663139692455</v>
       </c>
       <c r="H37" s="1">
-        <v>0.92655648033141191</v>
+        <v>1.8531129606628238</v>
       </c>
       <c r="I37" s="1">
-        <v>0.90826324781015622</v>
+        <v>1.8165264956203124</v>
       </c>
       <c r="J37" s="1">
-        <v>0.82986037215812625</v>
+        <v>1.6597207443162525</v>
       </c>
       <c r="K37" s="1">
-        <v>0.93881514747779404</v>
+        <v>1.8776302949555881</v>
       </c>
       <c r="L37" s="1">
-        <v>0.86856242745577517</v>
+        <v>1.7371248549115503</v>
       </c>
       <c r="M37" s="1">
-        <v>1.2338806056065859</v>
+        <v>2.4677612112131717</v>
       </c>
       <c r="N37" s="1">
-        <v>1.0191731266307904</v>
+        <v>2.0383462532615808</v>
       </c>
       <c r="O37" s="1">
-        <v>0.99230416732216631</v>
+        <v>1.9846083346443326</v>
       </c>
       <c r="P37" s="1">
-        <v>1.0273558906146651</v>
+        <v>2.0547117812293303</v>
       </c>
       <c r="Q37" s="1">
-        <v>0.91651189660606591</v>
+        <v>1.8330237932121318</v>
       </c>
       <c r="R37" s="1">
-        <v>0.84191135301021414</v>
+        <v>1.6838227060204283</v>
       </c>
       <c r="S37" s="1">
-        <v>0.70028086240748366</v>
+        <v>1.4005617248149673</v>
       </c>
       <c r="T37" s="1">
-        <v>0.77445677597687146</v>
+        <v>1.5489135519537429</v>
       </c>
       <c r="U37" s="1">
-        <v>0.62523144857122626</v>
+        <v>1.2504628971424525</v>
       </c>
       <c r="V37" s="1">
-        <v>0.67433701313478855</v>
+        <v>1.3486740262695771</v>
       </c>
       <c r="W37" s="1">
-        <v>0.67084492190140099</v>
+        <v>1.341689843802802</v>
       </c>
       <c r="X37" s="1">
-        <v>0.58157982916033624</v>
+        <v>1.1631596583206725</v>
       </c>
       <c r="Y37" s="1">
-        <v>0.71452312226222647</v>
+        <v>1.4290462445244529</v>
       </c>
       <c r="Z37" s="1">
-        <v>0.46957770939540344</v>
+        <v>0.93915541879080688</v>
       </c>
       <c r="AA37" s="1">
-        <v>0.568567432807491</v>
-      </c>
-    </row>
-    <row r="38" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="D38" s="1"/>
-      <c r="E38" s="1"/>
-      <c r="F38" s="1"/>
-      <c r="G38" s="1"/>
-      <c r="H38" s="1"/>
-      <c r="I38" s="1"/>
-      <c r="J38" s="1"/>
-      <c r="K38" s="1"/>
-      <c r="L38" s="1"/>
-      <c r="M38" s="1"/>
-      <c r="N38" s="1"/>
-      <c r="O38" s="1"/>
-      <c r="P38" s="1"/>
-      <c r="Q38" s="1"/>
-      <c r="R38" s="1"/>
-      <c r="S38" s="1"/>
-      <c r="T38" s="1"/>
-      <c r="U38" s="1"/>
-      <c r="V38" s="1"/>
-      <c r="W38" s="1"/>
-      <c r="X38" s="1"/>
-      <c r="Y38" s="1"/>
-      <c r="Z38" s="1"/>
-      <c r="AA38" s="1"/>
-    </row>
-    <row r="39" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="D39" s="1"/>
-      <c r="E39" s="1"/>
-      <c r="F39" s="1"/>
-      <c r="G39" s="1"/>
-      <c r="H39" s="1"/>
-      <c r="I39" s="1"/>
-      <c r="J39" s="1"/>
-      <c r="K39" s="1"/>
-      <c r="L39" s="1"/>
-      <c r="M39" s="1"/>
-      <c r="N39" s="1"/>
-      <c r="O39" s="1"/>
-      <c r="P39" s="1"/>
-      <c r="Q39" s="1"/>
-      <c r="R39" s="1"/>
-      <c r="S39" s="1"/>
-      <c r="T39" s="1"/>
-      <c r="U39" s="1"/>
-      <c r="V39" s="1"/>
-      <c r="W39" s="1"/>
-      <c r="X39" s="1"/>
-      <c r="Y39" s="1"/>
-      <c r="Z39" s="1"/>
-      <c r="AA39" s="1"/>
-    </row>
-    <row r="40" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="D40" s="1"/>
-      <c r="E40" s="1"/>
-      <c r="F40" s="1"/>
-      <c r="G40" s="1"/>
-      <c r="H40" s="1"/>
-      <c r="I40" s="1"/>
-      <c r="J40" s="1"/>
-      <c r="K40" s="1"/>
-      <c r="L40" s="1"/>
-      <c r="M40" s="1"/>
-      <c r="N40" s="1"/>
-      <c r="O40" s="1"/>
-      <c r="P40" s="1"/>
-      <c r="Q40" s="1"/>
-      <c r="R40" s="1"/>
-      <c r="S40" s="1"/>
-      <c r="T40" s="1"/>
-      <c r="U40" s="1"/>
-      <c r="V40" s="1"/>
-      <c r="W40" s="1"/>
-      <c r="X40" s="1"/>
-      <c r="Y40" s="1"/>
-      <c r="Z40" s="1"/>
-      <c r="AA40" s="1"/>
-    </row>
-    <row r="41" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="D41" s="1"/>
-      <c r="E41" s="1"/>
-      <c r="F41" s="1"/>
-      <c r="G41" s="1"/>
-      <c r="H41" s="1"/>
-      <c r="I41" s="1"/>
-      <c r="J41" s="1"/>
-      <c r="K41" s="1"/>
-      <c r="L41" s="1"/>
-      <c r="M41" s="1"/>
-      <c r="N41" s="1"/>
-      <c r="O41" s="1"/>
-      <c r="P41" s="1"/>
-      <c r="Q41" s="1"/>
-      <c r="R41" s="1"/>
-      <c r="S41" s="1"/>
-      <c r="T41" s="1"/>
-      <c r="U41" s="1"/>
-      <c r="V41" s="1"/>
-      <c r="W41" s="1"/>
-      <c r="X41" s="1"/>
-      <c r="Y41" s="1"/>
-      <c r="Z41" s="1"/>
-      <c r="AA41" s="1"/>
-    </row>
-    <row r="42" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="D42" s="1"/>
-      <c r="E42" s="1"/>
-      <c r="F42" s="1"/>
-      <c r="G42" s="1"/>
-      <c r="H42" s="1"/>
-      <c r="I42" s="1"/>
-      <c r="J42" s="1"/>
-      <c r="K42" s="1"/>
-      <c r="L42" s="1"/>
-      <c r="M42" s="1"/>
-      <c r="N42" s="1"/>
-      <c r="O42" s="1"/>
-      <c r="P42" s="1"/>
-      <c r="Q42" s="1"/>
-      <c r="R42" s="1"/>
-      <c r="S42" s="1"/>
-      <c r="T42" s="1"/>
-      <c r="U42" s="1"/>
-      <c r="V42" s="1"/>
-      <c r="W42" s="1"/>
-      <c r="X42" s="1"/>
-      <c r="Y42" s="1"/>
-      <c r="Z42" s="1"/>
-      <c r="AA42" s="1"/>
-    </row>
-    <row r="43" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="D43" s="1"/>
-      <c r="E43" s="1"/>
-      <c r="F43" s="1"/>
-      <c r="G43" s="1"/>
-      <c r="H43" s="1"/>
-      <c r="I43" s="1"/>
-      <c r="J43" s="1"/>
-      <c r="K43" s="1"/>
-      <c r="L43" s="1"/>
-      <c r="M43" s="1"/>
-      <c r="N43" s="1"/>
-      <c r="O43" s="1"/>
-      <c r="P43" s="1"/>
-      <c r="Q43" s="1"/>
-      <c r="R43" s="1"/>
-      <c r="S43" s="1"/>
-      <c r="T43" s="1"/>
-      <c r="U43" s="1"/>
-      <c r="V43" s="1"/>
-      <c r="W43" s="1"/>
-      <c r="X43" s="1"/>
-      <c r="Y43" s="1"/>
-      <c r="Z43" s="1"/>
-      <c r="AA43" s="1"/>
-    </row>
-    <row r="44" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="D44" s="1"/>
-      <c r="E44" s="1"/>
-      <c r="F44" s="1"/>
-      <c r="G44" s="1"/>
-      <c r="H44" s="1"/>
-      <c r="I44" s="1"/>
-      <c r="J44" s="1"/>
-      <c r="K44" s="1"/>
-      <c r="L44" s="1"/>
-      <c r="M44" s="1"/>
-      <c r="N44" s="1"/>
-      <c r="O44" s="1"/>
-      <c r="P44" s="1"/>
-      <c r="Q44" s="1"/>
-      <c r="R44" s="1"/>
-      <c r="S44" s="1"/>
-      <c r="T44" s="1"/>
-      <c r="U44" s="1"/>
-      <c r="V44" s="1"/>
-      <c r="W44" s="1"/>
-      <c r="X44" s="1"/>
-      <c r="Y44" s="1"/>
-      <c r="Z44" s="1"/>
-      <c r="AA44" s="1"/>
-    </row>
-    <row r="45" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="D45" s="1"/>
-      <c r="E45" s="1"/>
-      <c r="F45" s="1"/>
-      <c r="G45" s="1"/>
-      <c r="H45" s="1"/>
-      <c r="I45" s="1"/>
-      <c r="J45" s="1"/>
-      <c r="K45" s="1"/>
-      <c r="L45" s="1"/>
-      <c r="M45" s="1"/>
-      <c r="N45" s="1"/>
-      <c r="O45" s="1"/>
-      <c r="P45" s="1"/>
-      <c r="Q45" s="1"/>
-      <c r="R45" s="1"/>
-      <c r="S45" s="1"/>
-      <c r="T45" s="1"/>
-      <c r="U45" s="1"/>
-      <c r="V45" s="1"/>
-      <c r="W45" s="1"/>
-      <c r="X45" s="1"/>
-      <c r="Y45" s="1"/>
-      <c r="Z45" s="1"/>
-      <c r="AA45" s="1"/>
-    </row>
-    <row r="46" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="D46" s="1"/>
-      <c r="E46" s="1"/>
-      <c r="F46" s="1"/>
-      <c r="G46" s="1"/>
-      <c r="H46" s="1"/>
-      <c r="I46" s="1"/>
-      <c r="J46" s="1"/>
-      <c r="K46" s="1"/>
-      <c r="L46" s="1"/>
-      <c r="M46" s="1"/>
-      <c r="N46" s="1"/>
-      <c r="O46" s="1"/>
-      <c r="P46" s="1"/>
-      <c r="Q46" s="1"/>
-      <c r="R46" s="1"/>
-      <c r="S46" s="1"/>
-      <c r="T46" s="1"/>
-      <c r="U46" s="1"/>
-      <c r="V46" s="1"/>
-      <c r="W46" s="1"/>
-      <c r="X46" s="1"/>
-      <c r="Y46" s="1"/>
-      <c r="Z46" s="1"/>
-      <c r="AA46" s="1"/>
-    </row>
-    <row r="47" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="D47" s="1"/>
-      <c r="E47" s="1"/>
-      <c r="F47" s="1"/>
-      <c r="G47" s="1"/>
-      <c r="H47" s="1"/>
-      <c r="I47" s="1"/>
-      <c r="J47" s="1"/>
-      <c r="K47" s="1"/>
-      <c r="L47" s="1"/>
-      <c r="M47" s="1"/>
-      <c r="N47" s="1"/>
-      <c r="O47" s="1"/>
-      <c r="P47" s="1"/>
-      <c r="Q47" s="1"/>
-      <c r="R47" s="1"/>
-      <c r="S47" s="1"/>
-      <c r="T47" s="1"/>
-      <c r="U47" s="1"/>
-      <c r="V47" s="1"/>
-      <c r="W47" s="1"/>
-      <c r="X47" s="1"/>
-      <c r="Y47" s="1"/>
-      <c r="Z47" s="1"/>
-      <c r="AA47" s="1"/>
-    </row>
-    <row r="48" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="D48" s="1"/>
-      <c r="E48" s="1"/>
-      <c r="F48" s="1"/>
-      <c r="G48" s="1"/>
-      <c r="H48" s="1"/>
-      <c r="I48" s="1"/>
-      <c r="J48" s="1"/>
-      <c r="K48" s="1"/>
-      <c r="L48" s="1"/>
-      <c r="M48" s="1"/>
-      <c r="N48" s="1"/>
-      <c r="O48" s="1"/>
-      <c r="P48" s="1"/>
-      <c r="Q48" s="1"/>
-      <c r="R48" s="1"/>
-      <c r="S48" s="1"/>
-      <c r="T48" s="1"/>
-      <c r="U48" s="1"/>
-      <c r="V48" s="1"/>
-      <c r="W48" s="1"/>
-      <c r="X48" s="1"/>
-      <c r="Y48" s="1"/>
-      <c r="Z48" s="1"/>
-      <c r="AA48" s="1"/>
-    </row>
-    <row r="49" spans="4:27" x14ac:dyDescent="0.2">
-      <c r="D49" s="1"/>
-      <c r="E49" s="1"/>
-      <c r="F49" s="1"/>
-      <c r="G49" s="1"/>
-      <c r="H49" s="1"/>
-      <c r="I49" s="1"/>
-      <c r="J49" s="1"/>
-      <c r="K49" s="1"/>
-      <c r="L49" s="1"/>
-      <c r="M49" s="1"/>
-      <c r="N49" s="1"/>
-      <c r="O49" s="1"/>
-      <c r="P49" s="1"/>
-      <c r="Q49" s="1"/>
-      <c r="R49" s="1"/>
-      <c r="S49" s="1"/>
-      <c r="T49" s="1"/>
-      <c r="U49" s="1"/>
-      <c r="V49" s="1"/>
-      <c r="W49" s="1"/>
-      <c r="X49" s="1"/>
-      <c r="Y49" s="1"/>
-      <c r="Z49" s="1"/>
-      <c r="AA49" s="1"/>
-    </row>
-    <row r="50" spans="4:27" x14ac:dyDescent="0.2">
-      <c r="D50" s="1"/>
-      <c r="E50" s="1"/>
-      <c r="F50" s="1"/>
-      <c r="G50" s="1"/>
-      <c r="H50" s="1"/>
-      <c r="I50" s="1"/>
-      <c r="J50" s="1"/>
-      <c r="K50" s="1"/>
-      <c r="L50" s="1"/>
-      <c r="M50" s="1"/>
-      <c r="N50" s="1"/>
-      <c r="O50" s="1"/>
-      <c r="P50" s="1"/>
-      <c r="Q50" s="1"/>
-      <c r="R50" s="1"/>
-      <c r="S50" s="1"/>
-      <c r="T50" s="1"/>
-      <c r="U50" s="1"/>
-      <c r="V50" s="1"/>
-      <c r="W50" s="1"/>
-      <c r="X50" s="1"/>
-      <c r="Y50" s="1"/>
-      <c r="Z50" s="1"/>
-      <c r="AA50" s="1"/>
-    </row>
-    <row r="51" spans="4:27" x14ac:dyDescent="0.2">
-      <c r="D51" s="1"/>
-      <c r="E51" s="1"/>
-      <c r="F51" s="1"/>
-      <c r="G51" s="1"/>
-      <c r="H51" s="1"/>
-      <c r="I51" s="1"/>
-      <c r="J51" s="1"/>
-      <c r="K51" s="1"/>
-      <c r="L51" s="1"/>
-      <c r="M51" s="1"/>
-      <c r="N51" s="1"/>
-      <c r="O51" s="1"/>
-      <c r="P51" s="1"/>
-      <c r="Q51" s="1"/>
-      <c r="R51" s="1"/>
-      <c r="S51" s="1"/>
-      <c r="T51" s="1"/>
-      <c r="U51" s="1"/>
-      <c r="V51" s="1"/>
-      <c r="W51" s="1"/>
-      <c r="X51" s="1"/>
-      <c r="Y51" s="1"/>
-      <c r="Z51" s="1"/>
-      <c r="AA51" s="1"/>
-    </row>
-    <row r="52" spans="4:27" x14ac:dyDescent="0.2">
-      <c r="D52" s="1"/>
-      <c r="E52" s="1"/>
-      <c r="F52" s="1"/>
-      <c r="G52" s="1"/>
-      <c r="H52" s="1"/>
-      <c r="I52" s="1"/>
-      <c r="J52" s="1"/>
-      <c r="K52" s="1"/>
-      <c r="L52" s="1"/>
-      <c r="M52" s="1"/>
-      <c r="N52" s="1"/>
-      <c r="O52" s="1"/>
-      <c r="P52" s="1"/>
-      <c r="Q52" s="1"/>
-      <c r="R52" s="1"/>
-      <c r="S52" s="1"/>
-      <c r="T52" s="1"/>
-      <c r="U52" s="1"/>
-      <c r="V52" s="1"/>
-      <c r="W52" s="1"/>
-      <c r="X52" s="1"/>
-      <c r="Y52" s="1"/>
-      <c r="Z52" s="1"/>
-      <c r="AA52" s="1"/>
-    </row>
-    <row r="53" spans="4:27" x14ac:dyDescent="0.2">
-      <c r="D53" s="1"/>
-      <c r="E53" s="1"/>
-      <c r="F53" s="1"/>
-      <c r="G53" s="1"/>
-      <c r="H53" s="1"/>
-      <c r="I53" s="1"/>
-      <c r="J53" s="1"/>
-      <c r="K53" s="1"/>
-      <c r="L53" s="1"/>
-      <c r="M53" s="1"/>
-      <c r="N53" s="1"/>
-      <c r="O53" s="1"/>
-      <c r="P53" s="1"/>
-      <c r="Q53" s="1"/>
-      <c r="R53" s="1"/>
-      <c r="S53" s="1"/>
-      <c r="T53" s="1"/>
-      <c r="U53" s="1"/>
-      <c r="V53" s="1"/>
-      <c r="W53" s="1"/>
-      <c r="X53" s="1"/>
-      <c r="Y53" s="1"/>
-      <c r="Z53" s="1"/>
-      <c r="AA53" s="1"/>
-    </row>
-    <row r="54" spans="4:27" x14ac:dyDescent="0.2">
-      <c r="D54" s="1"/>
-      <c r="E54" s="1"/>
-      <c r="F54" s="1"/>
-      <c r="G54" s="1"/>
-      <c r="H54" s="1"/>
-      <c r="I54" s="1"/>
-      <c r="J54" s="1"/>
-      <c r="K54" s="1"/>
-      <c r="L54" s="1"/>
-      <c r="M54" s="1"/>
-      <c r="N54" s="1"/>
-      <c r="O54" s="1"/>
-      <c r="P54" s="1"/>
-      <c r="Q54" s="1"/>
-      <c r="R54" s="1"/>
-      <c r="S54" s="1"/>
-      <c r="T54" s="1"/>
-      <c r="U54" s="1"/>
-      <c r="V54" s="1"/>
-      <c r="W54" s="1"/>
-      <c r="X54" s="1"/>
-      <c r="Y54" s="1"/>
-      <c r="Z54" s="1"/>
-      <c r="AA54" s="1"/>
-    </row>
-    <row r="55" spans="4:27" x14ac:dyDescent="0.2">
-      <c r="D55" s="1"/>
-      <c r="E55" s="1"/>
-      <c r="F55" s="1"/>
-      <c r="G55" s="1"/>
-      <c r="H55" s="1"/>
-      <c r="I55" s="1"/>
-      <c r="J55" s="1"/>
-      <c r="K55" s="1"/>
-      <c r="L55" s="1"/>
-      <c r="M55" s="1"/>
-      <c r="N55" s="1"/>
-      <c r="O55" s="1"/>
-      <c r="P55" s="1"/>
-      <c r="Q55" s="1"/>
-      <c r="R55" s="1"/>
-      <c r="S55" s="1"/>
-      <c r="T55" s="1"/>
-      <c r="U55" s="1"/>
-      <c r="V55" s="1"/>
-      <c r="W55" s="1"/>
-      <c r="X55" s="1"/>
-      <c r="Y55" s="1"/>
-      <c r="Z55" s="1"/>
-      <c r="AA55" s="1"/>
-    </row>
-    <row r="56" spans="4:27" x14ac:dyDescent="0.2">
-      <c r="D56" s="1"/>
-      <c r="E56" s="1"/>
-      <c r="F56" s="1"/>
-      <c r="G56" s="1"/>
-      <c r="H56" s="1"/>
-      <c r="I56" s="1"/>
-      <c r="J56" s="1"/>
-      <c r="K56" s="1"/>
-      <c r="L56" s="1"/>
-      <c r="M56" s="1"/>
-      <c r="N56" s="1"/>
-      <c r="O56" s="1"/>
-      <c r="P56" s="1"/>
-      <c r="Q56" s="1"/>
-      <c r="R56" s="1"/>
-      <c r="S56" s="1"/>
-      <c r="T56" s="1"/>
-      <c r="U56" s="1"/>
-      <c r="V56" s="1"/>
-      <c r="W56" s="1"/>
-      <c r="X56" s="1"/>
-      <c r="Y56" s="1"/>
-      <c r="Z56" s="1"/>
-      <c r="AA56" s="1"/>
-    </row>
-    <row r="57" spans="4:27" x14ac:dyDescent="0.2">
-      <c r="D57" s="1"/>
-      <c r="E57" s="1"/>
-      <c r="F57" s="1"/>
-      <c r="G57" s="1"/>
-      <c r="H57" s="1"/>
-      <c r="I57" s="1"/>
-      <c r="J57" s="1"/>
-      <c r="K57" s="1"/>
-      <c r="L57" s="1"/>
-      <c r="M57" s="1"/>
-      <c r="N57" s="1"/>
-      <c r="O57" s="1"/>
-      <c r="P57" s="1"/>
-      <c r="Q57" s="1"/>
-      <c r="R57" s="1"/>
-      <c r="S57" s="1"/>
-      <c r="T57" s="1"/>
-      <c r="U57" s="1"/>
-      <c r="V57" s="1"/>
-      <c r="W57" s="1"/>
-      <c r="X57" s="1"/>
-      <c r="Y57" s="1"/>
-      <c r="Z57" s="1"/>
-      <c r="AA57" s="1"/>
-    </row>
-    <row r="58" spans="4:27" x14ac:dyDescent="0.2">
-      <c r="D58" s="1"/>
-      <c r="E58" s="1"/>
-      <c r="F58" s="1"/>
-      <c r="G58" s="1"/>
-      <c r="H58" s="1"/>
-      <c r="I58" s="1"/>
-      <c r="J58" s="1"/>
-      <c r="K58" s="1"/>
-      <c r="L58" s="1"/>
-      <c r="M58" s="1"/>
-      <c r="N58" s="1"/>
-      <c r="O58" s="1"/>
-      <c r="P58" s="1"/>
-      <c r="Q58" s="1"/>
-      <c r="R58" s="1"/>
-      <c r="S58" s="1"/>
-      <c r="T58" s="1"/>
-      <c r="U58" s="1"/>
-      <c r="V58" s="1"/>
-      <c r="W58" s="1"/>
-      <c r="X58" s="1"/>
-      <c r="Y58" s="1"/>
-      <c r="Z58" s="1"/>
-      <c r="AA58" s="1"/>
-    </row>
-    <row r="59" spans="4:27" x14ac:dyDescent="0.2">
-      <c r="D59" s="1"/>
-      <c r="E59" s="1"/>
-      <c r="F59" s="1"/>
-      <c r="G59" s="1"/>
-      <c r="H59" s="1"/>
-      <c r="I59" s="1"/>
-      <c r="J59" s="1"/>
-      <c r="K59" s="1"/>
-      <c r="L59" s="1"/>
-      <c r="M59" s="1"/>
-      <c r="N59" s="1"/>
-      <c r="O59" s="1"/>
-      <c r="P59" s="1"/>
-      <c r="Q59" s="1"/>
-      <c r="R59" s="1"/>
-      <c r="S59" s="1"/>
-      <c r="T59" s="1"/>
-      <c r="U59" s="1"/>
-      <c r="V59" s="1"/>
-      <c r="W59" s="1"/>
-      <c r="X59" s="1"/>
-      <c r="Y59" s="1"/>
-      <c r="Z59" s="1"/>
-      <c r="AA59" s="1"/>
-    </row>
-    <row r="60" spans="4:27" x14ac:dyDescent="0.2">
-      <c r="D60" s="1"/>
-      <c r="E60" s="1"/>
-      <c r="F60" s="1"/>
-      <c r="G60" s="1"/>
-      <c r="H60" s="1"/>
-      <c r="I60" s="1"/>
-      <c r="J60" s="1"/>
-      <c r="K60" s="1"/>
-      <c r="L60" s="1"/>
-      <c r="M60" s="1"/>
-      <c r="N60" s="1"/>
-      <c r="O60" s="1"/>
-      <c r="P60" s="1"/>
-      <c r="Q60" s="1"/>
-      <c r="R60" s="1"/>
-      <c r="S60" s="1"/>
-      <c r="T60" s="1"/>
-      <c r="U60" s="1"/>
-      <c r="V60" s="1"/>
-      <c r="W60" s="1"/>
-      <c r="X60" s="1"/>
-      <c r="Y60" s="1"/>
-      <c r="Z60" s="1"/>
-      <c r="AA60" s="1"/>
-    </row>
-    <row r="61" spans="4:27" x14ac:dyDescent="0.2">
-      <c r="D61" s="1"/>
-      <c r="E61" s="1"/>
-      <c r="F61" s="1"/>
-      <c r="G61" s="1"/>
-      <c r="H61" s="1"/>
-      <c r="I61" s="1"/>
-      <c r="J61" s="1"/>
-      <c r="K61" s="1"/>
-      <c r="L61" s="1"/>
-      <c r="M61" s="1"/>
-      <c r="N61" s="1"/>
-      <c r="O61" s="1"/>
-      <c r="P61" s="1"/>
-      <c r="Q61" s="1"/>
-      <c r="R61" s="1"/>
-      <c r="S61" s="1"/>
-      <c r="T61" s="1"/>
-      <c r="U61" s="1"/>
-      <c r="V61" s="1"/>
-      <c r="W61" s="1"/>
-      <c r="X61" s="1"/>
-      <c r="Y61" s="1"/>
-      <c r="Z61" s="1"/>
-      <c r="AA61" s="1"/>
-    </row>
-    <row r="62" spans="4:27" x14ac:dyDescent="0.2">
-      <c r="D62" s="1"/>
-      <c r="E62" s="1"/>
-      <c r="F62" s="1"/>
-      <c r="G62" s="1"/>
-      <c r="H62" s="1"/>
-      <c r="I62" s="1"/>
-      <c r="J62" s="1"/>
-      <c r="K62" s="1"/>
-      <c r="L62" s="1"/>
-      <c r="M62" s="1"/>
-      <c r="N62" s="1"/>
-      <c r="O62" s="1"/>
-      <c r="P62" s="1"/>
-      <c r="Q62" s="1"/>
-      <c r="R62" s="1"/>
-      <c r="S62" s="1"/>
-      <c r="T62" s="1"/>
-      <c r="U62" s="1"/>
-      <c r="V62" s="1"/>
-      <c r="W62" s="1"/>
-      <c r="X62" s="1"/>
-      <c r="Y62" s="1"/>
-      <c r="Z62" s="1"/>
-      <c r="AA62" s="1"/>
-    </row>
-    <row r="63" spans="4:27" x14ac:dyDescent="0.2">
-      <c r="D63" s="1"/>
-      <c r="E63" s="1"/>
-      <c r="F63" s="1"/>
-      <c r="G63" s="1"/>
-      <c r="H63" s="1"/>
-      <c r="I63" s="1"/>
-      <c r="J63" s="1"/>
-      <c r="K63" s="1"/>
-      <c r="L63" s="1"/>
-      <c r="M63" s="1"/>
-      <c r="N63" s="1"/>
-      <c r="O63" s="1"/>
-      <c r="P63" s="1"/>
-      <c r="Q63" s="1"/>
-      <c r="R63" s="1"/>
-      <c r="S63" s="1"/>
-      <c r="T63" s="1"/>
-      <c r="U63" s="1"/>
-      <c r="V63" s="1"/>
-      <c r="W63" s="1"/>
-      <c r="X63" s="1"/>
-      <c r="Y63" s="1"/>
-      <c r="Z63" s="1"/>
-      <c r="AA63" s="1"/>
-    </row>
-    <row r="64" spans="4:27" x14ac:dyDescent="0.2">
-      <c r="D64" s="1"/>
-      <c r="E64" s="1"/>
-      <c r="F64" s="1"/>
-      <c r="G64" s="1"/>
-      <c r="H64" s="1"/>
-      <c r="I64" s="1"/>
-      <c r="J64" s="1"/>
-      <c r="K64" s="1"/>
-      <c r="L64" s="1"/>
-      <c r="M64" s="1"/>
-      <c r="N64" s="1"/>
-      <c r="O64" s="1"/>
-      <c r="P64" s="1"/>
-      <c r="Q64" s="1"/>
-      <c r="R64" s="1"/>
-      <c r="S64" s="1"/>
-      <c r="T64" s="1"/>
-      <c r="U64" s="1"/>
-      <c r="V64" s="1"/>
-      <c r="W64" s="1"/>
-      <c r="X64" s="1"/>
-      <c r="Y64" s="1"/>
-      <c r="Z64" s="1"/>
-      <c r="AA64" s="1"/>
-    </row>
-    <row r="65" spans="4:27" x14ac:dyDescent="0.2">
-      <c r="D65" s="1"/>
-      <c r="E65" s="1"/>
-      <c r="F65" s="1"/>
-      <c r="G65" s="1"/>
-      <c r="H65" s="1"/>
-      <c r="I65" s="1"/>
-      <c r="J65" s="1"/>
-      <c r="K65" s="1"/>
-      <c r="L65" s="1"/>
-      <c r="M65" s="1"/>
-      <c r="N65" s="1"/>
-      <c r="O65" s="1"/>
-      <c r="P65" s="1"/>
-      <c r="Q65" s="1"/>
-      <c r="R65" s="1"/>
-      <c r="S65" s="1"/>
-      <c r="T65" s="1"/>
-      <c r="U65" s="1"/>
-      <c r="V65" s="1"/>
-      <c r="W65" s="1"/>
-      <c r="X65" s="1"/>
-      <c r="Y65" s="1"/>
-      <c r="Z65" s="1"/>
-      <c r="AA65" s="1"/>
-    </row>
-    <row r="66" spans="4:27" x14ac:dyDescent="0.2">
-      <c r="D66" s="1"/>
-      <c r="E66" s="1"/>
-      <c r="F66" s="1"/>
-      <c r="G66" s="1"/>
-      <c r="H66" s="1"/>
-      <c r="I66" s="1"/>
-      <c r="J66" s="1"/>
-      <c r="K66" s="1"/>
-      <c r="L66" s="1"/>
-      <c r="M66" s="1"/>
-      <c r="N66" s="1"/>
-      <c r="O66" s="1"/>
-      <c r="P66" s="1"/>
-      <c r="Q66" s="1"/>
-      <c r="R66" s="1"/>
-      <c r="S66" s="1"/>
-      <c r="T66" s="1"/>
-      <c r="U66" s="1"/>
-      <c r="V66" s="1"/>
-      <c r="W66" s="1"/>
-      <c r="X66" s="1"/>
-      <c r="Y66" s="1"/>
-      <c r="Z66" s="1"/>
-      <c r="AA66" s="1"/>
-    </row>
-    <row r="67" spans="4:27" x14ac:dyDescent="0.2">
-      <c r="D67" s="1"/>
-      <c r="E67" s="1"/>
-      <c r="F67" s="1"/>
-      <c r="G67" s="1"/>
-      <c r="H67" s="1"/>
-      <c r="I67" s="1"/>
-      <c r="J67" s="1"/>
-      <c r="K67" s="1"/>
-      <c r="L67" s="1"/>
-      <c r="M67" s="1"/>
-      <c r="N67" s="1"/>
-      <c r="O67" s="1"/>
-      <c r="P67" s="1"/>
-      <c r="Q67" s="1"/>
-      <c r="R67" s="1"/>
-      <c r="S67" s="1"/>
-      <c r="T67" s="1"/>
-      <c r="U67" s="1"/>
-      <c r="V67" s="1"/>
-      <c r="W67" s="1"/>
-      <c r="X67" s="1"/>
-      <c r="Y67" s="1"/>
-      <c r="Z67" s="1"/>
-      <c r="AA67" s="1"/>
-    </row>
-    <row r="68" spans="4:27" x14ac:dyDescent="0.2">
-      <c r="D68" s="1"/>
-      <c r="E68" s="1"/>
-      <c r="F68" s="1"/>
-      <c r="G68" s="1"/>
-      <c r="H68" s="1"/>
-      <c r="I68" s="1"/>
-      <c r="J68" s="1"/>
-      <c r="K68" s="1"/>
-      <c r="L68" s="1"/>
-      <c r="M68" s="1"/>
-      <c r="N68" s="1"/>
-      <c r="O68" s="1"/>
-      <c r="P68" s="1"/>
-      <c r="Q68" s="1"/>
-      <c r="R68" s="1"/>
-      <c r="S68" s="1"/>
-      <c r="T68" s="1"/>
-      <c r="U68" s="1"/>
-      <c r="V68" s="1"/>
-      <c r="W68" s="1"/>
-      <c r="X68" s="1"/>
-      <c r="Y68" s="1"/>
-      <c r="Z68" s="1"/>
-      <c r="AA68" s="1"/>
-    </row>
-    <row r="69" spans="4:27" x14ac:dyDescent="0.2">
-      <c r="D69" s="1"/>
-      <c r="E69" s="1"/>
-      <c r="F69" s="1"/>
-      <c r="G69" s="1"/>
-      <c r="H69" s="1"/>
-      <c r="I69" s="1"/>
-      <c r="J69" s="1"/>
-      <c r="K69" s="1"/>
-      <c r="L69" s="1"/>
-      <c r="M69" s="1"/>
-      <c r="N69" s="1"/>
-      <c r="O69" s="1"/>
-      <c r="P69" s="1"/>
-      <c r="Q69" s="1"/>
-      <c r="R69" s="1"/>
-      <c r="S69" s="1"/>
-      <c r="T69" s="1"/>
-      <c r="U69" s="1"/>
-      <c r="V69" s="1"/>
-      <c r="W69" s="1"/>
-      <c r="X69" s="1"/>
-      <c r="Y69" s="1"/>
-      <c r="Z69" s="1"/>
-      <c r="AA69" s="1"/>
-    </row>
-    <row r="70" spans="4:27" x14ac:dyDescent="0.2">
-      <c r="D70" s="1"/>
-      <c r="E70" s="1"/>
-      <c r="F70" s="1"/>
-      <c r="G70" s="1"/>
-      <c r="H70" s="1"/>
-      <c r="I70" s="1"/>
-      <c r="J70" s="1"/>
-      <c r="K70" s="1"/>
-      <c r="L70" s="1"/>
-      <c r="M70" s="1"/>
-      <c r="N70" s="1"/>
-      <c r="O70" s="1"/>
-      <c r="P70" s="1"/>
-      <c r="Q70" s="1"/>
-      <c r="R70" s="1"/>
-      <c r="S70" s="1"/>
-      <c r="T70" s="1"/>
-      <c r="U70" s="1"/>
-      <c r="V70" s="1"/>
-      <c r="W70" s="1"/>
-      <c r="X70" s="1"/>
-      <c r="Y70" s="1"/>
-      <c r="Z70" s="1"/>
-      <c r="AA70" s="1"/>
-    </row>
-    <row r="71" spans="4:27" x14ac:dyDescent="0.2">
-      <c r="D71" s="1"/>
-      <c r="E71" s="1"/>
-      <c r="F71" s="1"/>
-      <c r="G71" s="1"/>
-      <c r="H71" s="1"/>
-      <c r="I71" s="1"/>
-      <c r="J71" s="1"/>
-      <c r="K71" s="1"/>
-      <c r="L71" s="1"/>
-      <c r="M71" s="1"/>
-      <c r="N71" s="1"/>
-      <c r="O71" s="1"/>
-      <c r="P71" s="1"/>
-      <c r="Q71" s="1"/>
-      <c r="R71" s="1"/>
-      <c r="S71" s="1"/>
-      <c r="T71" s="1"/>
-      <c r="U71" s="1"/>
-      <c r="V71" s="1"/>
-      <c r="W71" s="1"/>
-      <c r="X71" s="1"/>
-      <c r="Y71" s="1"/>
-      <c r="Z71" s="1"/>
-      <c r="AA71" s="1"/>
-    </row>
-    <row r="72" spans="4:27" x14ac:dyDescent="0.2">
-      <c r="D72" s="1"/>
-      <c r="E72" s="1"/>
-      <c r="F72" s="1"/>
-      <c r="G72" s="1"/>
-      <c r="H72" s="1"/>
-      <c r="I72" s="1"/>
-      <c r="J72" s="1"/>
-      <c r="K72" s="1"/>
-      <c r="L72" s="1"/>
-      <c r="M72" s="1"/>
-      <c r="N72" s="1"/>
-      <c r="O72" s="1"/>
-      <c r="P72" s="1"/>
-      <c r="Q72" s="1"/>
-      <c r="R72" s="1"/>
-      <c r="S72" s="1"/>
-      <c r="T72" s="1"/>
-      <c r="U72" s="1"/>
-      <c r="V72" s="1"/>
-      <c r="W72" s="1"/>
-      <c r="X72" s="1"/>
-      <c r="Y72" s="1"/>
-      <c r="Z72" s="1"/>
-      <c r="AA72" s="1"/>
-    </row>
-    <row r="73" spans="4:27" x14ac:dyDescent="0.2">
-      <c r="D73" s="1"/>
-      <c r="E73" s="1"/>
-      <c r="F73" s="1"/>
-      <c r="G73" s="1"/>
-      <c r="H73" s="1"/>
-      <c r="I73" s="1"/>
-      <c r="J73" s="1"/>
-      <c r="K73" s="1"/>
-      <c r="L73" s="1"/>
-      <c r="M73" s="1"/>
-      <c r="N73" s="1"/>
-      <c r="O73" s="1"/>
-      <c r="P73" s="1"/>
-      <c r="Q73" s="1"/>
-      <c r="R73" s="1"/>
-      <c r="S73" s="1"/>
-      <c r="T73" s="1"/>
-      <c r="U73" s="1"/>
-      <c r="V73" s="1"/>
-      <c r="W73" s="1"/>
-      <c r="X73" s="1"/>
-      <c r="Y73" s="1"/>
-      <c r="Z73" s="1"/>
-      <c r="AA73" s="1"/>
+        <v>1.137134865614982</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
